--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="234">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,12 +232,6 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -418,9 +412,6 @@
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -725,21 +716,6 @@
   </si>
   <si>
     <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P238"/>
+  <dimension ref="A1:P232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1194,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1244,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1258,7 +1234,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1294,7 +1270,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1308,7 +1284,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1344,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1358,7 +1334,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1394,7 +1370,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1408,7 +1384,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1444,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1494,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1544,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1558,7 +1534,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1594,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1608,7 +1584,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1644,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1658,7 +1634,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1694,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1708,7 +1684,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1744,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1758,7 +1734,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1794,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1808,7 +1784,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1844,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1858,7 +1834,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1894,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1908,7 +1884,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1944,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1958,7 +1934,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1994,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2008,7 +1984,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2044,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2058,7 +2034,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2094,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2108,7 +2084,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2144,7 +2120,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2158,7 +2134,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2194,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2208,7 +2184,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2244,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2258,7 +2234,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2294,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2308,7 +2284,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2344,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2358,7 +2334,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2394,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2408,7 +2384,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2444,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2494,7 +2470,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2544,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2558,7 +2534,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2594,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2608,7 +2584,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2644,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2658,7 +2634,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2694,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2708,7 +2684,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2744,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2758,7 +2734,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2794,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2808,7 +2784,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2844,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2894,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2908,7 +2884,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2944,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2958,7 +2934,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2994,7 +2970,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3008,7 +2984,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3044,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3058,7 +3034,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3094,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3108,7 +3084,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3144,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3158,7 +3134,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3194,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3244,7 +3220,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3258,7 +3234,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3294,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3308,7 +3284,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3344,7 +3320,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3358,7 +3334,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3394,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3408,7 +3384,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3444,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3458,7 +3434,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3494,7 +3470,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3508,7 +3484,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3544,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3558,7 +3534,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3594,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3608,7 +3584,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3644,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3658,7 +3634,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3708,7 +3684,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3744,7 +3720,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3758,7 +3734,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3794,7 +3770,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3808,7 +3784,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3844,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3858,7 +3834,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3894,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3908,7 +3884,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3944,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3958,7 +3934,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3994,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4008,7 +3984,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4044,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4058,7 +4034,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4094,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4108,7 +4084,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4144,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4158,7 +4134,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4194,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4208,7 +4184,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4244,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4258,7 +4234,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4294,7 +4270,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4308,7 +4284,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4344,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4358,7 +4334,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4394,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4408,7 +4384,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4444,7 +4420,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4458,7 +4434,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4494,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4508,7 +4484,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4558,7 +4534,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4608,7 +4584,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4644,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4658,7 +4634,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4694,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4708,7 +4684,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4744,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4758,7 +4734,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4794,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4808,7 +4784,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4844,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4858,7 +4834,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4894,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4908,7 +4884,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4944,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4958,7 +4934,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5008,7 +4984,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5058,7 +5034,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5094,7 +5070,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5108,7 +5084,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5144,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5158,7 +5134,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5194,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5208,7 +5184,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5244,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5258,7 +5234,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5294,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5308,7 +5284,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5344,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5358,7 +5334,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5394,7 +5370,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5408,7 +5384,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5444,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5458,7 +5434,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5508,7 +5484,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5544,7 +5520,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5558,7 +5534,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5594,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5608,7 +5584,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5644,7 +5620,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5658,7 +5634,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5694,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5708,7 +5684,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5744,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5758,7 +5734,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5794,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5808,7 +5784,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5844,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5858,7 +5834,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5894,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5908,7 +5884,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5944,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5958,7 +5934,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5994,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6008,7 +5984,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6044,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6058,7 +6034,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6094,7 +6070,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6108,7 +6084,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6144,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6158,7 +6134,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6194,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6208,7 +6184,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6244,7 +6220,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6258,7 +6234,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6294,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6308,7 +6284,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6344,7 +6320,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6358,7 +6334,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6394,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6408,7 +6384,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6444,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6458,7 +6434,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6494,7 +6470,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6508,7 +6484,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6558,7 +6534,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6608,7 +6584,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6658,7 +6634,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6708,7 +6684,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6758,7 +6734,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6794,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6808,7 +6784,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6844,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6858,7 +6834,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6894,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6908,7 +6884,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6944,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6958,7 +6934,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6994,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7008,7 +6984,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7058,7 +7034,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7108,7 +7084,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7158,7 +7134,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7208,7 +7184,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7244,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7258,7 +7234,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7294,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7308,7 +7284,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7344,7 +7320,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7358,7 +7334,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7394,7 +7370,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7408,7 +7384,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7444,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7458,7 +7434,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7494,7 +7470,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7508,7 +7484,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7544,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7558,7 +7534,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7594,7 +7570,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7608,7 +7584,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7644,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7658,7 +7634,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7694,7 +7670,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7708,7 +7684,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7744,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7758,7 +7734,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7794,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7808,7 +7784,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7844,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7858,7 +7834,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7894,7 +7870,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7908,7 +7884,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7944,7 +7920,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7958,7 +7934,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7994,7 +7970,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8008,7 +7984,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8044,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8058,7 +8034,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8094,7 +8070,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8108,7 +8084,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8144,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8158,7 +8134,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8194,7 +8170,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8208,7 +8184,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8244,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8258,7 +8234,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8294,7 +8270,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8308,7 +8284,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8344,7 +8320,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8358,7 +8334,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8394,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8408,7 +8384,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8444,7 +8420,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8458,7 +8434,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8494,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8508,7 +8484,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8544,7 +8520,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8558,7 +8534,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8594,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8608,7 +8584,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8644,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8658,7 +8634,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8694,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8708,7 +8684,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8744,7 +8720,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8758,7 +8734,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8794,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8808,7 +8784,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8844,7 +8820,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8858,7 +8834,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8894,7 +8870,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8908,7 +8884,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8944,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8958,7 +8934,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8994,7 +8970,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9008,7 +8984,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9044,7 +9020,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9058,7 +9034,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9094,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9108,7 +9084,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9144,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9158,7 +9134,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9194,7 +9170,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9208,7 +9184,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9244,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9258,7 +9234,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9294,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9308,7 +9284,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9344,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9358,7 +9334,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9394,7 +9370,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9408,7 +9384,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9444,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9458,7 +9434,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9494,7 +9470,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9508,7 +9484,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9544,7 +9520,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9558,7 +9534,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9594,7 +9570,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9608,7 +9584,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9644,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9658,7 +9634,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9694,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9708,7 +9684,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9744,7 +9720,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9758,7 +9734,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9794,7 +9770,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9808,7 +9784,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9844,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9894,7 +9870,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9908,7 +9884,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9944,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9958,7 +9934,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9994,7 +9970,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10008,7 +9984,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10044,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10058,7 +10034,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10094,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10108,7 +10084,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10144,7 +10120,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10158,7 +10134,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10194,7 +10170,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10208,7 +10184,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10244,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10258,7 +10234,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10294,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10308,7 +10284,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10344,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10358,7 +10334,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10394,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10408,7 +10384,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10444,7 +10420,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10458,7 +10434,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10494,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10508,7 +10484,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10544,7 +10520,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10558,7 +10534,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10594,7 +10570,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10608,7 +10584,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10644,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10658,7 +10634,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10694,7 +10670,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10708,7 +10684,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10744,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10758,7 +10734,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10794,7 +10770,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10808,7 +10784,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10844,7 +10820,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10858,7 +10834,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10894,7 +10870,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10908,7 +10884,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10944,7 +10920,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10958,7 +10934,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10994,7 +10970,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11008,7 +10984,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11044,7 +11020,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11058,7 +11034,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11094,7 +11070,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11108,7 +11084,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11144,7 +11120,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11158,7 +11134,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11194,7 +11170,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11208,7 +11184,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11244,7 +11220,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11258,7 +11234,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11294,7 +11270,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11308,7 +11284,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11344,7 +11320,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11358,7 +11334,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11394,7 +11370,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11408,7 +11384,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11444,7 +11420,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11458,7 +11434,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11494,7 +11470,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11508,7 +11484,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11544,7 +11520,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11558,7 +11534,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11594,7 +11570,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11608,7 +11584,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11644,7 +11620,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11658,7 +11634,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11694,7 +11670,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11708,7 +11684,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11744,7 +11720,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11758,7 +11734,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11794,7 +11770,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11808,7 +11784,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11844,7 +11820,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11858,7 +11834,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11908,7 +11884,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11944,7 +11920,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11994,7 +11970,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12008,7 +11984,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12044,7 +12020,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12058,7 +12034,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12094,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12108,7 +12084,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12144,7 +12120,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12158,7 +12134,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12194,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12244,7 +12220,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12258,7 +12234,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12294,7 +12270,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12308,7 +12284,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12344,7 +12320,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12358,7 +12334,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12394,7 +12370,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12444,7 +12420,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12494,7 +12470,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12508,7 +12484,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12544,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12558,7 +12534,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12594,7 +12570,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12608,7 +12584,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12644,7 +12620,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12658,7 +12634,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12694,307 +12670,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16">
-      <c r="A233" s="1">
-        <v>0</v>
-      </c>
-      <c r="B233" t="s">
-        <v>72</v>
-      </c>
-      <c r="C233">
-        <v>8.559077962935032</v>
-      </c>
-      <c r="D233" t="s">
-        <v>134</v>
-      </c>
-      <c r="E233">
-        <v>8.676734571863783</v>
-      </c>
-      <c r="F233">
-        <v>1</v>
-      </c>
-      <c r="G233">
-        <v>0.06874092203706496</v>
-      </c>
-      <c r="H233">
-        <v>0.06794326542813621</v>
-      </c>
-      <c r="I233">
-        <v>0.1176566089287512</v>
-      </c>
-      <c r="J233">
-        <v>0.7627610148812412</v>
-      </c>
-      <c r="K233">
-        <v>39.45</v>
-      </c>
-      <c r="L233">
-        <v>38.65</v>
-      </c>
-      <c r="M233">
-        <v>38.85</v>
-      </c>
-      <c r="N233">
-        <v>38.31</v>
-      </c>
-      <c r="O233">
-        <v>1</v>
-      </c>
-      <c r="P233" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16">
-      <c r="A234" s="1">
-        <v>0</v>
-      </c>
-      <c r="B234" t="s">
-        <v>72</v>
-      </c>
-      <c r="C234">
-        <v>8.558492192617088</v>
-      </c>
-      <c r="D234" t="s">
-        <v>134</v>
-      </c>
-      <c r="E234">
-        <v>8.676157710600105</v>
-      </c>
-      <c r="F234">
-        <v>1</v>
-      </c>
-      <c r="G234">
-        <v>0.0687415078073829</v>
-      </c>
-      <c r="H234">
-        <v>0.0679438422893999</v>
-      </c>
-      <c r="I234">
-        <v>0.1176655179830171</v>
-      </c>
-      <c r="J234">
-        <v>0.7627758633050167</v>
-      </c>
-      <c r="K234">
-        <v>39.45</v>
-      </c>
-      <c r="L234">
-        <v>38.65</v>
-      </c>
-      <c r="M234">
-        <v>38.85</v>
-      </c>
-      <c r="N234">
-        <v>38.31</v>
-      </c>
-      <c r="O234">
-        <v>1</v>
-      </c>
-      <c r="P234" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" s="1">
-        <v>0</v>
-      </c>
-      <c r="B235" t="s">
-        <v>72</v>
-      </c>
-      <c r="C235">
-        <v>8.623866945080792</v>
-      </c>
-      <c r="D235" t="s">
-        <v>134</v>
-      </c>
-      <c r="E235">
-        <v>8.740538170250673</v>
-      </c>
-      <c r="F235">
-        <v>1</v>
-      </c>
-      <c r="G235">
-        <v>0.06867613305491921</v>
-      </c>
-      <c r="H235">
-        <v>0.06787946182974933</v>
-      </c>
-      <c r="I235">
-        <v>0.1166712251698812</v>
-      </c>
-      <c r="J235">
-        <v>0.7611187086164564</v>
-      </c>
-      <c r="K235">
-        <v>39.45</v>
-      </c>
-      <c r="L235">
-        <v>38.65</v>
-      </c>
-      <c r="M235">
-        <v>38.85</v>
-      </c>
-      <c r="N235">
-        <v>38.31</v>
-      </c>
-      <c r="O235">
-        <v>1</v>
-      </c>
-      <c r="P235" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16">
-      <c r="A236" s="1">
-        <v>0</v>
-      </c>
-      <c r="B236" t="s">
-        <v>72</v>
-      </c>
-      <c r="C236">
-        <v>8.650130704284244</v>
-      </c>
-      <c r="D236" t="s">
-        <v>134</v>
-      </c>
-      <c r="E236">
-        <v>8.766402480644945</v>
-      </c>
-      <c r="F236">
-        <v>1</v>
-      </c>
-      <c r="G236">
-        <v>0.06864986929571575</v>
-      </c>
-      <c r="H236">
-        <v>0.06785359751935506</v>
-      </c>
-      <c r="I236">
-        <v>0.1162717763607013</v>
-      </c>
-      <c r="J236">
-        <v>0.7604529606011597</v>
-      </c>
-      <c r="K236">
-        <v>39.45</v>
-      </c>
-      <c r="L236">
-        <v>38.65</v>
-      </c>
-      <c r="M236">
-        <v>38.85</v>
-      </c>
-      <c r="N236">
-        <v>38.31</v>
-      </c>
-      <c r="O236">
-        <v>1</v>
-      </c>
-      <c r="P236" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16">
-      <c r="A237" s="1">
-        <v>0</v>
-      </c>
-      <c r="B237" t="s">
-        <v>72</v>
-      </c>
-      <c r="C237">
-        <v>8.633707542884785</v>
-      </c>
-      <c r="D237" t="s">
-        <v>134</v>
-      </c>
-      <c r="E237">
-        <v>8.750229101167911</v>
-      </c>
-      <c r="F237">
-        <v>1</v>
-      </c>
-      <c r="G237">
-        <v>0.06866629245711522</v>
-      </c>
-      <c r="H237">
-        <v>0.06786977089883209</v>
-      </c>
-      <c r="I237">
-        <v>0.1165215582831252</v>
-      </c>
-      <c r="J237">
-        <v>0.7608692638052018</v>
-      </c>
-      <c r="K237">
-        <v>39.45</v>
-      </c>
-      <c r="L237">
-        <v>38.65</v>
-      </c>
-      <c r="M237">
-        <v>38.85</v>
-      </c>
-      <c r="N237">
-        <v>38.31</v>
-      </c>
-      <c r="O237">
-        <v>1</v>
-      </c>
-      <c r="P237" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16">
-      <c r="A238" s="1">
-        <v>0</v>
-      </c>
-      <c r="B238" t="s">
-        <v>73</v>
-      </c>
-      <c r="C238">
-        <v>11.09936735679353</v>
-      </c>
-      <c r="D238" t="s">
-        <v>65</v>
-      </c>
-      <c r="E238">
-        <v>6.600011940326141</v>
-      </c>
-      <c r="F238">
-        <v>-1</v>
-      </c>
-      <c r="G238">
-        <v>0.08306063264320648</v>
-      </c>
-      <c r="H238">
-        <v>0.07523998805967387</v>
-      </c>
-      <c r="I238">
-        <v>4.499355416467388</v>
-      </c>
-      <c r="J238">
-        <v>0.851612606939798</v>
-      </c>
-      <c r="K238">
-        <v>42.25</v>
-      </c>
-      <c r="L238">
-        <v>47.08</v>
-      </c>
-      <c r="M238">
-        <v>40.3</v>
-      </c>
-      <c r="N238">
-        <v>40.92</v>
-      </c>
-      <c r="O238">
-        <v>1</v>
-      </c>
-      <c r="P238" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="234">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,6 +232,9 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -401,9 +404,6 @@
   </si>
   <si>
     <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -1073,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P232"/>
+  <dimension ref="A1:P233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1234,7 +1234,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1284,7 +1284,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1334,7 +1334,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1384,7 +1384,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1534,7 +1534,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1584,7 +1584,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1634,7 +1634,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1684,7 +1684,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1734,7 +1734,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1784,7 +1784,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1834,7 +1834,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1884,7 +1884,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1934,7 +1934,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1984,7 +1984,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2034,7 +2034,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2084,7 +2084,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2134,7 +2134,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2184,7 +2184,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2234,7 +2234,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2284,7 +2284,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2334,7 +2334,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2384,7 +2384,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2534,7 +2534,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2584,7 +2584,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2634,7 +2634,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2684,7 +2684,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2734,7 +2734,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2784,7 +2784,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2884,7 +2884,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2934,7 +2934,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2984,7 +2984,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3034,7 +3034,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3084,7 +3084,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3134,7 +3134,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3234,7 +3234,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3284,7 +3284,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3334,7 +3334,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3384,7 +3384,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3434,7 +3434,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3484,7 +3484,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3534,7 +3534,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3584,7 +3584,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3634,7 +3634,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3684,7 +3684,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3734,7 +3734,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3784,7 +3784,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3834,7 +3834,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3884,7 +3884,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3934,7 +3934,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3984,7 +3984,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4034,7 +4034,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4084,7 +4084,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4134,7 +4134,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4184,7 +4184,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4234,7 +4234,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4284,7 +4284,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4334,7 +4334,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4384,7 +4384,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4434,7 +4434,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4484,7 +4484,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4534,7 +4534,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4584,7 +4584,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4634,7 +4634,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4684,7 +4684,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4734,7 +4734,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4784,7 +4784,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4834,7 +4834,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4884,7 +4884,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4934,7 +4934,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -4984,7 +4984,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5034,7 +5034,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5084,7 +5084,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5134,7 +5134,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5184,7 +5184,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5234,7 +5234,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5284,7 +5284,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5334,7 +5334,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5384,7 +5384,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5434,7 +5434,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5484,7 +5484,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5534,7 +5534,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5584,7 +5584,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5634,7 +5634,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5684,7 +5684,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5734,7 +5734,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5784,7 +5784,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5834,7 +5834,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5884,7 +5884,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5934,7 +5934,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5984,7 +5984,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6034,7 +6034,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6084,7 +6084,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6134,7 +6134,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6184,7 +6184,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6234,7 +6234,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6284,7 +6284,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6334,7 +6334,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6384,7 +6384,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6434,7 +6434,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6484,7 +6484,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6534,7 +6534,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6584,7 +6584,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6634,7 +6634,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6684,7 +6684,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6734,7 +6734,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6784,7 +6784,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6834,7 +6834,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6884,7 +6884,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6934,7 +6934,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6984,7 +6984,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7034,7 +7034,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7084,7 +7084,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7134,7 +7134,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7184,7 +7184,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7234,7 +7234,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7284,7 +7284,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7334,7 +7334,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7384,7 +7384,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7434,7 +7434,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7484,7 +7484,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7534,7 +7534,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7584,7 +7584,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7634,7 +7634,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7670,7 +7670,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7684,7 +7684,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7720,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7734,7 +7734,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7784,7 +7784,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7834,7 +7834,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7884,7 +7884,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7934,7 +7934,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7984,7 +7984,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8034,7 +8034,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8084,7 +8084,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8134,7 +8134,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8184,7 +8184,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8234,7 +8234,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8284,7 +8284,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8334,7 +8334,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8384,7 +8384,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8434,7 +8434,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8484,7 +8484,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8534,7 +8534,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8584,7 +8584,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8634,7 +8634,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8684,7 +8684,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8734,7 +8734,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8784,7 +8784,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8834,7 +8834,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8884,7 +8884,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8934,7 +8934,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8984,7 +8984,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9034,7 +9034,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9084,7 +9084,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9134,7 +9134,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9184,7 +9184,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9234,7 +9234,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9284,7 +9284,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9334,7 +9334,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9384,7 +9384,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9434,7 +9434,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9484,7 +9484,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9534,7 +9534,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9584,7 +9584,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9634,7 +9634,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9684,7 +9684,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9734,7 +9734,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9784,7 +9784,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9884,7 +9884,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9934,7 +9934,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9984,7 +9984,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10034,7 +10034,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10070,7 +10070,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10084,7 +10084,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10120,7 +10120,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10134,7 +10134,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10170,7 +10170,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10184,7 +10184,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10220,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10234,7 +10234,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10270,7 +10270,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10284,7 +10284,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10320,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10334,7 +10334,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10370,7 +10370,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10384,7 +10384,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10420,7 +10420,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10434,7 +10434,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10470,7 +10470,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10484,7 +10484,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10520,7 +10520,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10534,7 +10534,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10584,7 +10584,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10634,7 +10634,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10684,7 +10684,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10734,7 +10734,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10784,7 +10784,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10834,7 +10834,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10884,7 +10884,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10934,7 +10934,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10984,7 +10984,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11034,7 +11034,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11084,7 +11084,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11134,7 +11134,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11184,7 +11184,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11234,7 +11234,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11284,7 +11284,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11334,7 +11334,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11384,7 +11384,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11434,7 +11434,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11484,7 +11484,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11534,7 +11534,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11584,7 +11584,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11634,7 +11634,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11684,7 +11684,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11734,7 +11734,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11784,7 +11784,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11834,7 +11834,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11884,7 +11884,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11984,7 +11984,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12034,7 +12034,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12084,7 +12084,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12134,7 +12134,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12234,7 +12234,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12270,7 +12270,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12284,7 +12284,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12320,7 +12320,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12334,7 +12334,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12370,7 +12370,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12520,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12570,7 +12570,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12671,6 +12671,56 @@
       </c>
       <c r="P232" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16">
+      <c r="A233" s="1">
+        <v>0</v>
+      </c>
+      <c r="B233" t="s">
+        <v>72</v>
+      </c>
+      <c r="C233">
+        <v>0.8256419503565553</v>
+      </c>
+      <c r="D233" t="s">
+        <v>131</v>
+      </c>
+      <c r="E233">
+        <v>-0.5448785482702903</v>
+      </c>
+      <c r="F233">
+        <v>-1</v>
+      </c>
+      <c r="G233">
+        <v>0.07761435804964345</v>
+      </c>
+      <c r="H233">
+        <v>0.07714487854827029</v>
+      </c>
+      <c r="I233">
+        <v>1.370520498626846</v>
+      </c>
+      <c r="J233">
+        <v>1.001156663615214</v>
+      </c>
+      <c r="K233">
+        <v>38.35</v>
+      </c>
+      <c r="L233">
+        <v>39.22</v>
+      </c>
+      <c r="M233">
+        <v>38.8</v>
+      </c>
+      <c r="N233">
+        <v>38.3</v>
+      </c>
+      <c r="O233">
+        <v>1</v>
+      </c>
+      <c r="P233" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="241">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,6 +232,12 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
   </si>
   <si>
@@ -412,6 +418,9 @@
     <t>2021-07-14</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -716,6 +725,18 @@
   </si>
   <si>
     <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-03-11</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
   </si>
 </sst>
 </file>
@@ -1073,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P233"/>
+  <dimension ref="A1:P238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1170,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1220,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1234,7 +1255,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1270,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1284,7 +1305,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1320,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1334,7 +1355,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1370,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1384,7 +1405,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1420,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1470,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1520,7 +1541,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1534,7 +1555,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1570,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1584,7 +1605,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1620,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1634,7 +1655,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1670,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1684,7 +1705,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1720,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1734,7 +1755,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1770,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1784,7 +1805,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1820,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1834,7 +1855,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1870,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1884,7 +1905,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1920,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1934,7 +1955,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1970,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1984,7 +2005,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2020,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2034,7 +2055,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2070,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2084,7 +2105,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2120,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2134,7 +2155,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2170,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2184,7 +2205,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2220,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2234,7 +2255,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2270,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2284,7 +2305,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2320,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2334,7 +2355,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2370,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2384,7 +2405,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2420,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2470,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2520,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2534,7 +2555,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2570,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2584,7 +2605,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2620,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2634,7 +2655,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2670,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2684,7 +2705,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2720,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2734,7 +2755,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2770,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2784,7 +2805,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2820,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2870,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2884,7 +2905,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2920,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2934,7 +2955,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2970,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2984,7 +3005,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3020,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3034,7 +3055,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3070,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3084,7 +3105,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3120,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3134,7 +3155,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3170,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3220,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3234,7 +3255,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3270,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3284,7 +3305,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3320,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3334,7 +3355,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3370,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3384,7 +3405,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3420,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3434,7 +3455,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3470,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3484,7 +3505,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3520,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3534,7 +3555,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3570,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3584,7 +3605,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3620,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3634,7 +3655,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3684,7 +3705,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3720,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3734,7 +3755,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3770,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3784,7 +3805,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3820,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3834,7 +3855,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3870,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3884,7 +3905,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3920,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3934,7 +3955,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3970,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3984,7 +4005,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4020,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4034,7 +4055,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4070,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4084,7 +4105,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4120,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4134,7 +4155,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4170,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4184,7 +4205,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4220,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4234,7 +4255,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4270,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4284,7 +4305,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4320,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4334,7 +4355,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4370,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4384,7 +4405,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4420,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4434,7 +4455,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4470,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4484,7 +4505,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4534,7 +4555,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4584,7 +4605,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4620,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4634,7 +4655,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4670,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4684,7 +4705,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4720,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4734,7 +4755,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4770,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4784,7 +4805,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4820,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4834,7 +4855,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4870,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4884,7 +4905,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4920,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4934,7 +4955,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -4984,7 +5005,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5034,7 +5055,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5070,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5084,7 +5105,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5120,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5134,7 +5155,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5170,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5184,7 +5205,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5220,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5234,7 +5255,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5270,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5284,7 +5305,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5320,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5334,7 +5355,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5370,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5384,7 +5405,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5420,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5434,7 +5455,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5484,7 +5505,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5520,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5534,7 +5555,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5570,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5584,7 +5605,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5620,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5634,7 +5655,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5670,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5684,7 +5705,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5720,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5734,7 +5755,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5770,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5784,7 +5805,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5820,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5834,7 +5855,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5870,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5884,7 +5905,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5920,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5934,7 +5955,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5970,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5984,7 +6005,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6020,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6034,7 +6055,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6070,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6084,7 +6105,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6120,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6134,7 +6155,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6170,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6184,7 +6205,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6220,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6234,7 +6255,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6270,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6284,7 +6305,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6320,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6334,7 +6355,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6370,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6384,7 +6405,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6420,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6434,7 +6455,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6470,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6484,7 +6505,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6534,7 +6555,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6584,7 +6605,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6634,7 +6655,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6684,7 +6705,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6734,7 +6755,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6770,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6784,7 +6805,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6820,7 +6841,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6834,7 +6855,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6870,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6884,7 +6905,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6920,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6934,7 +6955,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6970,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6984,7 +7005,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7034,7 +7055,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7084,7 +7105,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7134,7 +7155,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7184,7 +7205,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7220,7 +7241,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7234,7 +7255,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7270,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7284,7 +7305,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7320,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7334,7 +7355,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7370,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7384,7 +7405,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7420,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7434,7 +7455,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7470,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7484,7 +7505,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7520,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7534,7 +7555,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7570,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7584,7 +7605,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7620,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7634,7 +7655,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7670,7 +7691,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7684,7 +7705,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7720,7 +7741,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7734,7 +7755,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7770,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7784,7 +7805,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7820,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7834,7 +7855,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7870,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7884,7 +7905,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7920,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7934,7 +7955,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7970,7 +7991,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7984,7 +8005,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8020,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8034,7 +8055,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8070,7 +8091,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8084,7 +8105,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8120,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8134,7 +8155,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8170,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8184,7 +8205,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8220,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8234,7 +8255,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8270,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8284,7 +8305,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8320,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8334,7 +8355,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8370,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8384,7 +8405,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8420,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8434,7 +8455,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8470,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8484,7 +8505,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8520,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8534,7 +8555,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8570,7 +8591,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8584,7 +8605,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8620,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8634,7 +8655,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8670,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8684,7 +8705,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8720,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8734,7 +8755,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8770,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8784,7 +8805,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8820,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8834,7 +8855,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8870,7 +8891,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8884,7 +8905,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8920,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8934,7 +8955,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8970,7 +8991,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8984,7 +9005,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9020,7 +9041,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9034,7 +9055,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9070,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9084,7 +9105,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9120,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9134,7 +9155,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9170,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9184,7 +9205,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9220,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9234,7 +9255,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9270,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9284,7 +9305,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9320,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9334,7 +9355,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9370,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9384,7 +9405,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9420,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9434,7 +9455,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9470,7 +9491,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9484,7 +9505,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9520,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9534,7 +9555,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9570,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9584,7 +9605,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9620,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9634,7 +9655,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9670,7 +9691,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9684,7 +9705,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9720,7 +9741,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9734,7 +9755,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9770,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9784,7 +9805,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9820,7 +9841,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9870,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9884,7 +9905,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9920,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9934,7 +9955,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9970,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9984,7 +10005,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10020,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10034,7 +10055,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10070,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10084,7 +10105,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10120,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10134,7 +10155,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10170,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10184,7 +10205,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10220,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10234,7 +10255,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10270,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10284,7 +10305,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10320,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10334,7 +10355,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10370,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10384,7 +10405,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10420,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10434,7 +10455,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10470,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10484,7 +10505,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10520,7 +10541,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10534,7 +10555,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10570,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10584,7 +10605,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10620,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10634,7 +10655,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10670,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10684,7 +10705,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10720,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10734,7 +10755,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10770,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10784,7 +10805,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10820,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10834,7 +10855,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10870,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10884,7 +10905,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10920,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10934,7 +10955,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10970,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10984,7 +11005,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11020,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11034,7 +11055,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11070,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11084,7 +11105,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11120,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11134,7 +11155,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11170,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11184,7 +11205,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11220,7 +11241,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11234,7 +11255,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11270,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11284,7 +11305,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11320,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11334,7 +11355,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11370,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11384,7 +11405,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11420,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11434,7 +11455,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11470,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11484,7 +11505,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11520,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11534,7 +11555,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11570,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11584,7 +11605,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11620,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11634,7 +11655,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11670,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11684,7 +11705,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11720,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11734,7 +11755,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11770,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11784,7 +11805,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11820,7 +11841,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11834,7 +11855,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11884,7 +11905,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11920,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11970,7 +11991,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11984,7 +12005,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12020,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12034,7 +12055,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12070,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12084,7 +12105,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12120,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12134,7 +12155,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12170,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12220,7 +12241,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12234,7 +12255,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12270,7 +12291,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12284,7 +12305,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12320,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12334,7 +12355,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12370,7 +12391,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12420,7 +12441,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12470,7 +12491,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12484,7 +12505,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12520,7 +12541,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12534,7 +12555,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12570,7 +12591,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12584,7 +12605,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12620,7 +12641,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12634,7 +12655,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12670,7 +12691,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12681,45 +12702,295 @@
         <v>72</v>
       </c>
       <c r="C233">
+        <v>7.713700927072214</v>
+      </c>
+      <c r="D233" t="s">
+        <v>134</v>
+      </c>
+      <c r="E233">
+        <v>7.382946855346571</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233">
+        <v>0.06644629907292779</v>
+      </c>
+      <c r="H233">
+        <v>0.06321705314465342</v>
+      </c>
+      <c r="I233">
+        <v>-0.330754071725643</v>
+      </c>
+      <c r="J233">
+        <v>0.7627610148812412</v>
+      </c>
+      <c r="K233">
+        <v>38.5</v>
+      </c>
+      <c r="L233">
+        <v>37.08</v>
+      </c>
+      <c r="M233">
+        <v>36.6</v>
+      </c>
+      <c r="N233">
+        <v>35.3</v>
+      </c>
+      <c r="O233">
+        <v>1</v>
+      </c>
+      <c r="P233" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16">
+      <c r="A234" s="1">
+        <v>0</v>
+      </c>
+      <c r="B234" t="s">
+        <v>72</v>
+      </c>
+      <c r="C234">
+        <v>7.713129262756855</v>
+      </c>
+      <c r="D234" t="s">
+        <v>134</v>
+      </c>
+      <c r="E234">
+        <v>7.382403403036385</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
+      </c>
+      <c r="G234">
+        <v>0.06644687073724315</v>
+      </c>
+      <c r="H234">
+        <v>0.0632175965969636</v>
+      </c>
+      <c r="I234">
+        <v>-0.3307258597204701</v>
+      </c>
+      <c r="J234">
+        <v>0.7627758633050167</v>
+      </c>
+      <c r="K234">
+        <v>38.5</v>
+      </c>
+      <c r="L234">
+        <v>37.08</v>
+      </c>
+      <c r="M234">
+        <v>36.6</v>
+      </c>
+      <c r="N234">
+        <v>35.3</v>
+      </c>
+      <c r="O234">
+        <v>1</v>
+      </c>
+      <c r="P234" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" s="1">
+        <v>0</v>
+      </c>
+      <c r="B235" t="s">
+        <v>72</v>
+      </c>
+      <c r="C235">
+        <v>7.776929718266427</v>
+      </c>
+      <c r="D235" t="s">
+        <v>134</v>
+      </c>
+      <c r="E235">
+        <v>7.443055264637692</v>
+      </c>
+      <c r="F235">
+        <v>1</v>
+      </c>
+      <c r="G235">
+        <v>0.06638307028173357</v>
+      </c>
+      <c r="H235">
+        <v>0.06315694473536231</v>
+      </c>
+      <c r="I235">
+        <v>-0.3338744536287344</v>
+      </c>
+      <c r="J235">
+        <v>0.7611187086164564</v>
+      </c>
+      <c r="K235">
+        <v>38.5</v>
+      </c>
+      <c r="L235">
+        <v>37.08</v>
+      </c>
+      <c r="M235">
+        <v>36.6</v>
+      </c>
+      <c r="N235">
+        <v>35.3</v>
+      </c>
+      <c r="O235">
+        <v>1</v>
+      </c>
+      <c r="P235" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16">
+      <c r="A236" s="1">
+        <v>0</v>
+      </c>
+      <c r="B236" t="s">
+        <v>72</v>
+      </c>
+      <c r="C236">
+        <v>7.80256101685535</v>
+      </c>
+      <c r="D236" t="s">
+        <v>134</v>
+      </c>
+      <c r="E236">
+        <v>7.46742164199755</v>
+      </c>
+      <c r="F236">
+        <v>1</v>
+      </c>
+      <c r="G236">
+        <v>0.06635743898314465</v>
+      </c>
+      <c r="H236">
+        <v>0.06313257835800246</v>
+      </c>
+      <c r="I236">
+        <v>-0.3351393748577998</v>
+      </c>
+      <c r="J236">
+        <v>0.7604529606011597</v>
+      </c>
+      <c r="K236">
+        <v>38.5</v>
+      </c>
+      <c r="L236">
+        <v>37.08</v>
+      </c>
+      <c r="M236">
+        <v>36.6</v>
+      </c>
+      <c r="N236">
+        <v>35.3</v>
+      </c>
+      <c r="O236">
+        <v>1</v>
+      </c>
+      <c r="P236" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16">
+      <c r="A237" s="1">
+        <v>0</v>
+      </c>
+      <c r="B237" t="s">
+        <v>73</v>
+      </c>
+      <c r="C237">
+        <v>7.558054555158837</v>
+      </c>
+      <c r="D237" t="s">
+        <v>134</v>
+      </c>
+      <c r="E237">
+        <v>7.452184944729609</v>
+      </c>
+      <c r="F237">
+        <v>1</v>
+      </c>
+      <c r="G237">
+        <v>0.06348194544484118</v>
+      </c>
+      <c r="H237">
+        <v>0.06314781505527038</v>
+      </c>
+      <c r="I237">
+        <v>-0.1058696104292274</v>
+      </c>
+      <c r="J237">
+        <v>0.7608692638052018</v>
+      </c>
+      <c r="K237">
+        <v>36.75</v>
+      </c>
+      <c r="L237">
+        <v>35.52</v>
+      </c>
+      <c r="M237">
+        <v>36.6</v>
+      </c>
+      <c r="N237">
+        <v>35.3</v>
+      </c>
+      <c r="O237">
+        <v>1</v>
+      </c>
+      <c r="P237" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16">
+      <c r="A238" s="1">
+        <v>0</v>
+      </c>
+      <c r="B238" t="s">
+        <v>74</v>
+      </c>
+      <c r="C238">
         <v>0.8256419503565553</v>
       </c>
-      <c r="D233" t="s">
-        <v>131</v>
-      </c>
-      <c r="E233">
+      <c r="D238" t="s">
+        <v>133</v>
+      </c>
+      <c r="E238">
         <v>-0.5448785482702903</v>
       </c>
-      <c r="F233">
-        <v>-1</v>
-      </c>
-      <c r="G233">
+      <c r="F238">
+        <v>-1</v>
+      </c>
+      <c r="G238">
         <v>0.07761435804964345</v>
       </c>
-      <c r="H233">
+      <c r="H238">
         <v>0.07714487854827029</v>
       </c>
-      <c r="I233">
+      <c r="I238">
         <v>1.370520498626846</v>
       </c>
-      <c r="J233">
+      <c r="J238">
         <v>1.001156663615214</v>
       </c>
-      <c r="K233">
+      <c r="K238">
         <v>38.35</v>
       </c>
-      <c r="L233">
+      <c r="L238">
         <v>39.22</v>
       </c>
-      <c r="M233">
+      <c r="M238">
         <v>38.8</v>
       </c>
-      <c r="N233">
+      <c r="N238">
         <v>38.3</v>
       </c>
-      <c r="O233">
-        <v>1</v>
-      </c>
-      <c r="P233" t="s">
+      <c r="O238">
+        <v>1</v>
+      </c>
+      <c r="P238" t="s">
         <v>68</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="242">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,12 +232,12 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
   </si>
   <si>
@@ -418,7 +418,10 @@
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-07-15</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -1094,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P238"/>
+  <dimension ref="A1:P243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1191,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1241,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1291,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1341,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1391,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1441,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1491,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1541,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1591,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1641,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1691,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1741,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1791,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1841,7 +1844,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1891,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1941,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1991,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2041,7 +2044,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2091,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2141,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2191,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2241,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2291,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2341,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2391,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2441,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2491,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2541,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2591,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2641,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2691,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2741,7 +2744,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2791,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2841,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2891,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2941,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2991,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3041,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3091,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3141,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3191,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3241,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3291,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3341,7 +3344,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3391,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3441,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3491,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3541,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3591,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3641,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3741,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3791,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3841,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3891,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3941,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3991,7 +3994,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4041,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4091,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4141,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4191,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4241,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4291,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4341,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4391,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4441,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4491,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4641,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4691,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4741,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4791,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4841,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4891,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4941,7 +4944,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5091,7 +5094,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5141,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5191,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5241,7 +5244,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5291,7 +5294,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5341,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5391,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5441,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5541,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5591,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5641,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5691,7 +5694,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5741,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5791,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5841,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5891,7 +5894,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5941,7 +5944,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5991,7 +5994,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6041,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6091,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6141,7 +6144,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6191,7 +6194,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6241,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6291,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6341,7 +6344,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6391,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6441,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6491,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6791,7 +6794,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6841,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6891,7 +6894,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6941,7 +6944,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6991,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7241,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7291,7 +7294,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7341,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7391,7 +7394,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7441,7 +7444,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7491,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7541,7 +7544,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7591,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7791,7 +7794,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7841,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7891,7 +7894,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7941,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7991,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8041,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8091,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8141,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8191,7 +8194,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8241,7 +8244,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8291,7 +8294,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8341,7 +8344,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8391,7 +8394,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8441,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8491,7 +8494,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8541,7 +8544,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8591,7 +8594,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8641,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8691,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8741,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8791,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8841,7 +8844,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8891,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8941,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8991,7 +8994,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9041,7 +9044,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9091,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9141,7 +9144,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9191,7 +9194,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9241,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9291,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9341,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9391,7 +9394,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9441,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9491,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9541,7 +9544,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9591,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9641,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9691,7 +9694,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9741,7 +9744,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9791,7 +9794,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9841,7 +9844,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9891,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9941,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9991,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10041,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10591,7 +10594,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10641,7 +10644,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10691,7 +10694,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10741,7 +10744,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10791,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10841,7 +10844,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10891,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10941,7 +10944,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10991,7 +10994,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11041,7 +11044,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11091,7 +11094,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11141,7 +11144,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11191,7 +11194,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11241,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11291,7 +11294,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11341,7 +11344,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11391,7 +11394,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11441,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11491,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11541,7 +11544,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11591,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11641,7 +11644,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11691,7 +11694,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11741,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11791,7 +11794,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11841,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11941,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11991,7 +11994,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12041,7 +12044,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12091,7 +12094,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12141,7 +12144,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12191,7 +12194,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12241,7 +12244,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12441,7 +12444,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12491,7 +12494,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12641,7 +12644,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12691,7 +12694,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12702,90 +12705,90 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>7.713700927072214</v>
+        <v>7.488532703114391</v>
       </c>
       <c r="D233" t="s">
         <v>134</v>
       </c>
       <c r="E233">
-        <v>7.382946855346571</v>
+        <v>7.063428297161892</v>
       </c>
       <c r="F233">
         <v>1</v>
       </c>
       <c r="G233">
-        <v>0.06644629907292779</v>
+        <v>0.06355146729688561</v>
       </c>
       <c r="H233">
-        <v>0.06321705314465342</v>
+        <v>0.06373657170283811</v>
       </c>
       <c r="I233">
-        <v>-0.330754071725643</v>
+        <v>-0.4251044059524993</v>
       </c>
       <c r="J233">
         <v>0.7627610148812412</v>
       </c>
       <c r="K233">
-        <v>38.5</v>
+        <v>36.75</v>
       </c>
       <c r="L233">
-        <v>37.08</v>
+        <v>35.52</v>
       </c>
       <c r="M233">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="N233">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B234" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C234">
-        <v>7.713129262756855</v>
+        <v>7.382946855346571</v>
       </c>
       <c r="D234" t="s">
         <v>134</v>
       </c>
       <c r="E234">
-        <v>7.382403403036385</v>
+        <v>7.063428297161892</v>
       </c>
       <c r="F234">
         <v>1</v>
       </c>
       <c r="G234">
-        <v>0.06644687073724315</v>
+        <v>0.06321705314465342</v>
       </c>
       <c r="H234">
-        <v>0.0632175965969636</v>
+        <v>0.06373657170283811</v>
       </c>
       <c r="I234">
-        <v>-0.3307258597204701</v>
+        <v>-0.3195185581846793</v>
       </c>
       <c r="J234">
-        <v>0.7627758633050167</v>
+        <v>0.7627610148812412</v>
       </c>
       <c r="K234">
-        <v>38.5</v>
+        <v>36.6</v>
       </c>
       <c r="L234">
-        <v>37.08</v>
+        <v>35.3</v>
       </c>
       <c r="M234">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="N234">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="O234">
         <v>1</v>
@@ -12802,40 +12805,40 @@
         <v>72</v>
       </c>
       <c r="C235">
-        <v>7.776929718266427</v>
+        <v>7.48798702354064</v>
       </c>
       <c r="D235" t="s">
         <v>134</v>
       </c>
       <c r="E235">
-        <v>7.443055264637692</v>
+        <v>7.062876678218629</v>
       </c>
       <c r="F235">
         <v>1</v>
       </c>
       <c r="G235">
-        <v>0.06638307028173357</v>
+        <v>0.06355201297645936</v>
       </c>
       <c r="H235">
-        <v>0.06315694473536231</v>
+        <v>0.06373712332178137</v>
       </c>
       <c r="I235">
-        <v>-0.3338744536287344</v>
+        <v>-0.4251103453220111</v>
       </c>
       <c r="J235">
-        <v>0.7611187086164564</v>
+        <v>0.7627758633050167</v>
       </c>
       <c r="K235">
-        <v>38.5</v>
+        <v>36.75</v>
       </c>
       <c r="L235">
-        <v>37.08</v>
+        <v>35.52</v>
       </c>
       <c r="M235">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="N235">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="O235">
         <v>1</v>
@@ -12846,52 +12849,52 @@
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C236">
-        <v>7.80256101685535</v>
+        <v>7.382403403036385</v>
       </c>
       <c r="D236" t="s">
         <v>134</v>
       </c>
       <c r="E236">
-        <v>7.46742164199755</v>
+        <v>7.062876678218629</v>
       </c>
       <c r="F236">
         <v>1</v>
       </c>
       <c r="G236">
-        <v>0.06635743898314465</v>
+        <v>0.0632175965969636</v>
       </c>
       <c r="H236">
-        <v>0.06313257835800246</v>
+        <v>0.06373712332178137</v>
       </c>
       <c r="I236">
-        <v>-0.3351393748577998</v>
+        <v>-0.3195267248177558</v>
       </c>
       <c r="J236">
-        <v>0.7604529606011597</v>
+        <v>0.7627758633050167</v>
       </c>
       <c r="K236">
-        <v>38.5</v>
+        <v>36.6</v>
       </c>
       <c r="L236">
-        <v>37.08</v>
+        <v>35.3</v>
       </c>
       <c r="M236">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="N236">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12899,31 +12902,31 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C237">
-        <v>7.558054555158837</v>
+        <v>7.548887458345231</v>
       </c>
       <c r="D237" t="s">
         <v>134</v>
       </c>
       <c r="E237">
-        <v>7.452184944729609</v>
+        <v>7.124439974898646</v>
       </c>
       <c r="F237">
         <v>1</v>
       </c>
       <c r="G237">
-        <v>0.06348194544484118</v>
+        <v>0.06349111254165478</v>
       </c>
       <c r="H237">
-        <v>0.06314781505527038</v>
+        <v>0.06367556002510134</v>
       </c>
       <c r="I237">
-        <v>-0.1058696104292274</v>
+        <v>-0.4244474834465848</v>
       </c>
       <c r="J237">
-        <v>0.7608692638052018</v>
+        <v>0.7611187086164564</v>
       </c>
       <c r="K237">
         <v>36.75</v>
@@ -12932,65 +12935,315 @@
         <v>35.52</v>
       </c>
       <c r="M237">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="N237">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="O237">
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>59</v>
+        <v>240</v>
       </c>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="1">
+        <v>1</v>
+      </c>
+      <c r="B238" t="s">
+        <v>73</v>
+      </c>
+      <c r="C238">
+        <v>7.443055264637692</v>
+      </c>
+      <c r="D238" t="s">
+        <v>134</v>
+      </c>
+      <c r="E238">
+        <v>7.124439974898646</v>
+      </c>
+      <c r="F238">
+        <v>1</v>
+      </c>
+      <c r="G238">
+        <v>0.06315694473536231</v>
+      </c>
+      <c r="H238">
+        <v>0.06367556002510134</v>
+      </c>
+      <c r="I238">
+        <v>-0.3186152897390464</v>
+      </c>
+      <c r="J238">
+        <v>0.7611187086164564</v>
+      </c>
+      <c r="K238">
+        <v>36.6</v>
+      </c>
+      <c r="L238">
+        <v>35.3</v>
+      </c>
+      <c r="M238">
+        <v>37.15</v>
+      </c>
+      <c r="N238">
+        <v>35.4</v>
+      </c>
+      <c r="O238">
+        <v>1</v>
+      </c>
+      <c r="P238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16">
+      <c r="A239" s="1">
         <v>0</v>
       </c>
-      <c r="B238" t="s">
+      <c r="B239" t="s">
+        <v>72</v>
+      </c>
+      <c r="C239">
+        <v>7.573353697907383</v>
+      </c>
+      <c r="D239" t="s">
+        <v>134</v>
+      </c>
+      <c r="E239">
+        <v>7.149172513666915</v>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239">
+        <v>0.06346664630209263</v>
+      </c>
+      <c r="H239">
+        <v>0.06365082748633309</v>
+      </c>
+      <c r="I239">
+        <v>-0.4241811842404672</v>
+      </c>
+      <c r="J239">
+        <v>0.7604529606011597</v>
+      </c>
+      <c r="K239">
+        <v>36.75</v>
+      </c>
+      <c r="L239">
+        <v>35.52</v>
+      </c>
+      <c r="M239">
+        <v>37.15</v>
+      </c>
+      <c r="N239">
+        <v>35.4</v>
+      </c>
+      <c r="O239">
+        <v>1</v>
+      </c>
+      <c r="P239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16">
+      <c r="A240" s="1">
+        <v>1</v>
+      </c>
+      <c r="B240" t="s">
+        <v>73</v>
+      </c>
+      <c r="C240">
+        <v>7.46742164199755</v>
+      </c>
+      <c r="D240" t="s">
+        <v>134</v>
+      </c>
+      <c r="E240">
+        <v>7.149172513666915</v>
+      </c>
+      <c r="F240">
+        <v>1</v>
+      </c>
+      <c r="G240">
+        <v>0.06313257835800246</v>
+      </c>
+      <c r="H240">
+        <v>0.06365082748633309</v>
+      </c>
+      <c r="I240">
+        <v>-0.3182491283306348</v>
+      </c>
+      <c r="J240">
+        <v>0.7604529606011597</v>
+      </c>
+      <c r="K240">
+        <v>36.6</v>
+      </c>
+      <c r="L240">
+        <v>35.3</v>
+      </c>
+      <c r="M240">
+        <v>37.15</v>
+      </c>
+      <c r="N240">
+        <v>35.4</v>
+      </c>
+      <c r="O240">
+        <v>1</v>
+      </c>
+      <c r="P240" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16">
+      <c r="A241" s="1">
+        <v>0</v>
+      </c>
+      <c r="B241" t="s">
+        <v>72</v>
+      </c>
+      <c r="C241">
+        <v>7.558054555158837</v>
+      </c>
+      <c r="D241" t="s">
+        <v>134</v>
+      </c>
+      <c r="E241">
+        <v>7.133706849636752</v>
+      </c>
+      <c r="F241">
+        <v>1</v>
+      </c>
+      <c r="G241">
+        <v>0.06348194544484118</v>
+      </c>
+      <c r="H241">
+        <v>0.06366629315036325</v>
+      </c>
+      <c r="I241">
+        <v>-0.4243477055220843</v>
+      </c>
+      <c r="J241">
+        <v>0.7608692638052018</v>
+      </c>
+      <c r="K241">
+        <v>36.75</v>
+      </c>
+      <c r="L241">
+        <v>35.52</v>
+      </c>
+      <c r="M241">
+        <v>37.15</v>
+      </c>
+      <c r="N241">
+        <v>35.4</v>
+      </c>
+      <c r="O241">
+        <v>1</v>
+      </c>
+      <c r="P241" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16">
+      <c r="A242" s="1">
+        <v>1</v>
+      </c>
+      <c r="B242" t="s">
+        <v>73</v>
+      </c>
+      <c r="C242">
+        <v>7.452184944729609</v>
+      </c>
+      <c r="D242" t="s">
+        <v>134</v>
+      </c>
+      <c r="E242">
+        <v>7.133706849636752</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242">
+        <v>0.06314781505527038</v>
+      </c>
+      <c r="H242">
+        <v>0.06366629315036325</v>
+      </c>
+      <c r="I242">
+        <v>-0.318478095092857</v>
+      </c>
+      <c r="J242">
+        <v>0.7608692638052018</v>
+      </c>
+      <c r="K242">
+        <v>36.6</v>
+      </c>
+      <c r="L242">
+        <v>35.3</v>
+      </c>
+      <c r="M242">
+        <v>37.15</v>
+      </c>
+      <c r="N242">
+        <v>35.4</v>
+      </c>
+      <c r="O242">
+        <v>1</v>
+      </c>
+      <c r="P242" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16">
+      <c r="A243" s="1">
+        <v>0</v>
+      </c>
+      <c r="B243" t="s">
         <v>74</v>
       </c>
-      <c r="C238">
+      <c r="C243">
         <v>0.8256419503565553</v>
       </c>
-      <c r="D238" t="s">
-        <v>133</v>
-      </c>
-      <c r="E238">
-        <v>-0.5448785482702903</v>
-      </c>
-      <c r="F238">
-        <v>-1</v>
-      </c>
-      <c r="G238">
+      <c r="D243" t="s">
+        <v>135</v>
+      </c>
+      <c r="E243">
+        <v>-0.7660930450662633</v>
+      </c>
+      <c r="F243">
+        <v>-1</v>
+      </c>
+      <c r="G243">
         <v>0.07761435804964345</v>
       </c>
-      <c r="H238">
-        <v>0.07714487854827029</v>
-      </c>
-      <c r="I238">
-        <v>1.370520498626846</v>
-      </c>
-      <c r="J238">
+      <c r="H243">
+        <v>0.07902609304506626</v>
+      </c>
+      <c r="I243">
+        <v>1.591734995422819</v>
+      </c>
+      <c r="J243">
         <v>1.001156663615214</v>
       </c>
-      <c r="K238">
+      <c r="K243">
         <v>38.35</v>
       </c>
-      <c r="L238">
+      <c r="L243">
         <v>39.22</v>
       </c>
-      <c r="M238">
-        <v>38.8</v>
-      </c>
-      <c r="N238">
-        <v>38.3</v>
-      </c>
-      <c r="O238">
-        <v>1</v>
-      </c>
-      <c r="P238" t="s">
+      <c r="M243">
+        <v>39.85</v>
+      </c>
+      <c r="N243">
+        <v>39.13</v>
+      </c>
+      <c r="O243">
+        <v>1</v>
+      </c>
+      <c r="P243" t="s">
         <v>68</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="246">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,514 +232,526 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
   </si>
   <si>
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-03-11</t>
+  </si>
+  <si>
+    <t>2021-03-12</t>
+  </si>
+  <si>
+    <t>2021-03-15</t>
+  </si>
+  <si>
+    <t>2021-03-16</t>
+  </si>
+  <si>
+    <t>2021-06-23</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
   </si>
   <si>
     <t>2021-07-15</t>
   </si>
   <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
+    <t>2021-07-16</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P243"/>
+  <dimension ref="A1:P248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1194,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1244,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1258,7 +1270,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1294,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1308,7 +1320,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1344,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1358,7 +1370,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1394,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1408,7 +1420,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1444,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1494,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1544,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1558,7 +1570,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1594,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1608,7 +1620,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1644,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1658,7 +1670,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1694,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1708,7 +1720,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1744,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1758,7 +1770,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1794,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1808,7 +1820,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1844,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1858,7 +1870,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1894,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1908,7 +1920,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1944,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1958,7 +1970,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1994,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2008,7 +2020,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2044,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2058,7 +2070,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2094,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2108,7 +2120,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2144,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2158,7 +2170,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2194,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2208,7 +2220,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2244,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2258,7 +2270,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2294,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2308,7 +2320,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2344,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2358,7 +2370,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2394,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2408,7 +2420,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2444,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2494,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2544,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2558,7 +2570,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2594,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2608,7 +2620,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2644,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2658,7 +2670,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2694,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2708,7 +2720,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2744,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2758,7 +2770,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2794,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2808,7 +2820,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2844,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2894,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2908,7 +2920,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2944,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2958,7 +2970,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2994,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3008,7 +3020,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3044,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3058,7 +3070,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3094,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3108,7 +3120,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3144,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3158,7 +3170,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3194,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3244,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3258,7 +3270,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3294,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3308,7 +3320,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3344,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3358,7 +3370,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3394,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3408,7 +3420,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3444,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3458,7 +3470,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3494,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3508,7 +3520,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3544,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3558,7 +3570,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3594,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3608,7 +3620,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3644,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3658,7 +3670,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3708,7 +3720,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3744,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3758,7 +3770,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3794,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3808,7 +3820,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3844,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3858,7 +3870,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3894,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3908,7 +3920,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3944,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3958,7 +3970,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3994,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4008,7 +4020,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4044,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4058,7 +4070,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4094,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4108,7 +4120,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4144,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4158,7 +4170,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4194,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4208,7 +4220,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4244,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4258,7 +4270,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4294,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4308,7 +4320,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4344,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4358,7 +4370,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4394,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4408,7 +4420,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4444,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4458,7 +4470,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4494,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4508,7 +4520,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4558,7 +4570,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4608,7 +4620,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4644,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4658,7 +4670,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4694,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4708,7 +4720,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4744,7 +4756,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4758,7 +4770,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4794,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4808,7 +4820,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4844,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4858,7 +4870,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4894,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4908,7 +4920,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4944,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4958,7 +4970,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5008,7 +5020,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5058,7 +5070,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5094,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5108,7 +5120,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5144,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5158,7 +5170,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5194,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5208,7 +5220,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5244,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5258,7 +5270,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5294,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5308,7 +5320,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5344,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5358,7 +5370,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5394,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5408,7 +5420,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5444,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5458,7 +5470,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5508,7 +5520,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5544,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5558,7 +5570,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5594,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5608,7 +5620,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5644,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5658,7 +5670,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5694,7 +5706,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5708,7 +5720,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5744,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5758,7 +5770,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5794,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5808,7 +5820,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5844,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5858,7 +5870,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5894,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5908,7 +5920,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5944,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5958,7 +5970,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5994,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6008,7 +6020,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6044,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6058,7 +6070,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6094,7 +6106,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6108,7 +6120,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6144,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6158,7 +6170,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6194,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6208,7 +6220,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6244,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6258,7 +6270,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6294,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6308,7 +6320,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6344,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6358,7 +6370,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6394,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6408,7 +6420,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6444,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6458,7 +6470,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6494,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6508,7 +6520,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6558,7 +6570,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6608,7 +6620,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6658,7 +6670,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6708,7 +6720,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6758,7 +6770,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6794,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6808,7 +6820,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6844,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6858,7 +6870,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6894,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6908,7 +6920,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6944,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6958,7 +6970,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6994,7 +7006,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7008,7 +7020,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7058,7 +7070,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7108,7 +7120,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7158,7 +7170,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7208,7 +7220,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7244,7 +7256,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7258,7 +7270,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7294,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7308,7 +7320,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7344,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7358,7 +7370,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7394,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7408,7 +7420,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7444,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7458,7 +7470,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7494,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7508,7 +7520,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7544,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7558,7 +7570,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7594,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7608,7 +7620,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7644,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7658,7 +7670,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7694,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7708,7 +7720,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7744,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7758,7 +7770,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7794,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7808,7 +7820,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7844,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7858,7 +7870,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7894,7 +7906,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7908,7 +7920,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7944,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7958,7 +7970,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7994,7 +8006,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8008,7 +8020,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8044,7 +8056,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8058,7 +8070,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8094,7 +8106,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8108,7 +8120,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8144,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8158,7 +8170,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8194,7 +8206,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8208,7 +8220,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8244,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8258,7 +8270,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8294,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8308,7 +8320,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8344,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8358,7 +8370,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8394,7 +8406,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8408,7 +8420,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8444,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8458,7 +8470,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8494,7 +8506,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8508,7 +8520,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8544,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8558,7 +8570,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8594,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8608,7 +8620,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8644,7 +8656,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8658,7 +8670,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8694,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8708,7 +8720,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8744,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8758,7 +8770,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8794,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8808,7 +8820,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8844,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8858,7 +8870,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8894,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8908,7 +8920,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8944,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8958,7 +8970,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8994,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9008,7 +9020,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9044,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9058,7 +9070,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9094,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9108,7 +9120,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9144,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9158,7 +9170,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9194,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9208,7 +9220,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9244,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9258,7 +9270,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9294,7 +9306,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9308,7 +9320,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9344,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9358,7 +9370,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9394,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9408,7 +9420,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9444,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9458,7 +9470,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9494,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9508,7 +9520,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9544,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9558,7 +9570,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9594,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9608,7 +9620,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9644,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9658,7 +9670,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9694,7 +9706,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9708,7 +9720,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9744,7 +9756,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9758,7 +9770,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9794,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9808,7 +9820,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9844,7 +9856,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9894,7 +9906,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9908,7 +9920,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9944,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9958,7 +9970,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9994,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10008,7 +10020,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10044,7 +10056,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10058,7 +10070,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10094,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10108,7 +10120,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10144,7 +10156,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10158,7 +10170,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10194,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10208,7 +10220,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10244,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10258,7 +10270,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10294,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10308,7 +10320,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10344,7 +10356,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10358,7 +10370,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10394,7 +10406,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10408,7 +10420,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10444,7 +10456,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10458,7 +10470,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10494,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10508,7 +10520,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10544,7 +10556,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10558,7 +10570,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10594,7 +10606,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10608,7 +10620,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10644,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10658,7 +10670,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10694,7 +10706,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10708,7 +10720,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10744,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10758,7 +10770,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10794,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10808,7 +10820,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10844,7 +10856,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10858,7 +10870,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10894,7 +10906,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10908,7 +10920,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10944,7 +10956,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10958,7 +10970,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10994,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11008,7 +11020,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11044,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11058,7 +11070,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11094,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11108,7 +11120,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11144,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11158,7 +11170,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11194,7 +11206,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11208,7 +11220,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11244,7 +11256,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11258,7 +11270,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11294,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11308,7 +11320,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11344,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11358,7 +11370,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11394,7 +11406,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11408,7 +11420,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11444,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11458,7 +11470,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11494,7 +11506,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11508,7 +11520,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11544,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11558,7 +11570,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11594,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11608,7 +11620,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11644,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11658,7 +11670,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11694,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11708,7 +11720,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11744,7 +11756,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11758,7 +11770,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11794,7 +11806,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11808,7 +11820,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11844,7 +11856,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11858,7 +11870,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11908,7 +11920,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11944,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11994,7 +12006,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12008,7 +12020,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12044,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12058,7 +12070,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12094,7 +12106,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12108,7 +12120,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12144,7 +12156,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12158,7 +12170,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12194,7 +12206,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12244,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12258,7 +12270,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12294,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12308,7 +12320,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12344,7 +12356,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12358,7 +12370,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12394,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12444,7 +12456,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12494,7 +12506,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12544,7 +12556,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12594,7 +12606,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12644,7 +12656,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12694,7 +12706,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12705,90 +12717,90 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>7.488532703114391</v>
+        <v>7.063428297161892</v>
       </c>
       <c r="D233" t="s">
         <v>134</v>
       </c>
       <c r="E233">
-        <v>7.063428297161892</v>
+        <v>7.364037374987873</v>
       </c>
       <c r="F233">
         <v>1</v>
       </c>
       <c r="G233">
-        <v>0.06355146729688561</v>
+        <v>0.06373657170283811</v>
       </c>
       <c r="H233">
-        <v>0.06373657170283811</v>
+        <v>0.07143596262501213</v>
       </c>
       <c r="I233">
-        <v>-0.4251044059524993</v>
+        <v>0.3006090778259818</v>
       </c>
       <c r="J233">
         <v>0.7627610148812412</v>
       </c>
       <c r="K233">
-        <v>36.75</v>
+        <v>37.15</v>
       </c>
       <c r="L233">
-        <v>35.52</v>
+        <v>35.4</v>
       </c>
       <c r="M233">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N233">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C234">
-        <v>7.382946855346571</v>
+        <v>7.062876678218629</v>
       </c>
       <c r="D234" t="s">
         <v>134</v>
       </c>
       <c r="E234">
-        <v>7.063428297161892</v>
+        <v>7.363413741189298</v>
       </c>
       <c r="F234">
         <v>1</v>
       </c>
       <c r="G234">
-        <v>0.06321705314465342</v>
+        <v>0.06373712332178137</v>
       </c>
       <c r="H234">
-        <v>0.06373657170283811</v>
+        <v>0.07143658625881071</v>
       </c>
       <c r="I234">
-        <v>-0.3195185581846793</v>
+        <v>0.300537062970669</v>
       </c>
       <c r="J234">
-        <v>0.7627610148812412</v>
+        <v>0.7627758633050167</v>
       </c>
       <c r="K234">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="L234">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="M234">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N234">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O234">
         <v>1</v>
@@ -12805,40 +12817,40 @@
         <v>72</v>
       </c>
       <c r="C235">
-        <v>7.48798702354064</v>
+        <v>7.124439974898646</v>
       </c>
       <c r="D235" t="s">
         <v>134</v>
       </c>
       <c r="E235">
-        <v>7.062876678218629</v>
+        <v>7.433014238108832</v>
       </c>
       <c r="F235">
         <v>1</v>
       </c>
       <c r="G235">
-        <v>0.06355201297645936</v>
+        <v>0.06367556002510134</v>
       </c>
       <c r="H235">
-        <v>0.06373712332178137</v>
+        <v>0.07136698576189116</v>
       </c>
       <c r="I235">
-        <v>-0.4251103453220111</v>
+        <v>0.3085742632101862</v>
       </c>
       <c r="J235">
-        <v>0.7627758633050167</v>
+        <v>0.7611187086164564</v>
       </c>
       <c r="K235">
-        <v>36.75</v>
+        <v>37.15</v>
       </c>
       <c r="L235">
-        <v>35.52</v>
+        <v>35.4</v>
       </c>
       <c r="M235">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N235">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O235">
         <v>1</v>
@@ -12849,52 +12861,52 @@
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C236">
-        <v>7.382403403036385</v>
+        <v>7.149172513666915</v>
       </c>
       <c r="D236" t="s">
         <v>134</v>
       </c>
       <c r="E236">
-        <v>7.062876678218629</v>
+        <v>7.460975654751291</v>
       </c>
       <c r="F236">
         <v>1</v>
       </c>
       <c r="G236">
-        <v>0.0632175965969636</v>
+        <v>0.06365082748633309</v>
       </c>
       <c r="H236">
-        <v>0.06373712332178137</v>
+        <v>0.07133902434524871</v>
       </c>
       <c r="I236">
-        <v>-0.3195267248177558</v>
+        <v>0.3118031410843756</v>
       </c>
       <c r="J236">
-        <v>0.7627758633050167</v>
+        <v>0.7604529606011597</v>
       </c>
       <c r="K236">
-        <v>36.6</v>
+        <v>37.15</v>
       </c>
       <c r="L236">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="M236">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N236">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12905,96 +12917,96 @@
         <v>72</v>
       </c>
       <c r="C237">
-        <v>7.548887458345231</v>
+        <v>7.133706849636752</v>
       </c>
       <c r="D237" t="s">
         <v>134</v>
       </c>
       <c r="E237">
-        <v>7.124439974898646</v>
+        <v>7.443490920181521</v>
       </c>
       <c r="F237">
         <v>1</v>
       </c>
       <c r="G237">
-        <v>0.06349111254165478</v>
+        <v>0.06366629315036325</v>
       </c>
       <c r="H237">
-        <v>0.06367556002510134</v>
+        <v>0.07135650907981848</v>
       </c>
       <c r="I237">
-        <v>-0.4244474834465848</v>
+        <v>0.3097840705447688</v>
       </c>
       <c r="J237">
-        <v>0.7611187086164564</v>
+        <v>0.7608692638052018</v>
       </c>
       <c r="K237">
-        <v>36.75</v>
+        <v>37.15</v>
       </c>
       <c r="L237">
-        <v>35.52</v>
+        <v>35.4</v>
       </c>
       <c r="M237">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N237">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O237">
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
     </row>
     <row r="238" spans="1:16">
       <c r="A238" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B238" t="s">
         <v>73</v>
       </c>
       <c r="C238">
-        <v>7.443055264637692</v>
+        <v>2.000557447825351</v>
       </c>
       <c r="D238" t="s">
         <v>134</v>
       </c>
       <c r="E238">
-        <v>7.124439974898646</v>
+        <v>1.953079443852872</v>
       </c>
       <c r="F238">
         <v>1</v>
       </c>
       <c r="G238">
-        <v>0.06315694473536231</v>
+        <v>0.07635944255217464</v>
       </c>
       <c r="H238">
-        <v>0.06367556002510134</v>
+        <v>0.07684692055614713</v>
       </c>
       <c r="I238">
-        <v>-0.3186152897390464</v>
+        <v>-0.04747800397247914</v>
       </c>
       <c r="J238">
-        <v>0.7611187086164564</v>
+        <v>0.8915933465749316</v>
       </c>
       <c r="K238">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="L238">
-        <v>35.3</v>
+        <v>39.18</v>
       </c>
       <c r="M238">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N238">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O238">
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13002,99 +13014,99 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C239">
-        <v>7.573353697907383</v>
+        <v>1.484572639564057</v>
       </c>
       <c r="D239" t="s">
         <v>134</v>
       </c>
       <c r="E239">
-        <v>7.149172513666915</v>
+        <v>1.433382514668835</v>
       </c>
       <c r="F239">
         <v>1</v>
       </c>
       <c r="G239">
-        <v>0.06346664630209263</v>
+        <v>0.07687542736043594</v>
       </c>
       <c r="H239">
-        <v>0.06365082748633309</v>
+        <v>0.07736661748533116</v>
       </c>
       <c r="I239">
-        <v>-0.4241811842404672</v>
+        <v>-0.05119012489522135</v>
       </c>
       <c r="J239">
-        <v>0.7604529606011597</v>
+        <v>0.9039670829840752</v>
       </c>
       <c r="K239">
-        <v>36.75</v>
+        <v>41.7</v>
       </c>
       <c r="L239">
-        <v>35.52</v>
+        <v>39.18</v>
       </c>
       <c r="M239">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N239">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>241</v>
+        <v>66</v>
       </c>
     </row>
     <row r="240" spans="1:16">
       <c r="A240" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B240" t="s">
         <v>73</v>
       </c>
       <c r="C240">
-        <v>7.46742164199755</v>
+        <v>0.9408600133438938</v>
       </c>
       <c r="D240" t="s">
         <v>134</v>
       </c>
       <c r="E240">
-        <v>7.149172513666915</v>
+        <v>0.8857582868211864</v>
       </c>
       <c r="F240">
         <v>1</v>
       </c>
       <c r="G240">
-        <v>0.06313257835800246</v>
+        <v>0.0774191399866561</v>
       </c>
       <c r="H240">
-        <v>0.06365082748633309</v>
+        <v>0.07791424171317882</v>
       </c>
       <c r="I240">
-        <v>-0.3182491283306348</v>
+        <v>-0.05510172652270739</v>
       </c>
       <c r="J240">
-        <v>0.7604529606011597</v>
+        <v>0.9170057550756859</v>
       </c>
       <c r="K240">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="L240">
-        <v>35.3</v>
+        <v>39.18</v>
       </c>
       <c r="M240">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N240">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>241</v>
+        <v>69</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13102,99 +13114,99 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C241">
-        <v>7.558054555158837</v>
+        <v>0.3763210661608767</v>
       </c>
       <c r="D241" t="s">
         <v>134</v>
       </c>
       <c r="E241">
-        <v>7.133706849636752</v>
+        <v>0.3171579083634697</v>
       </c>
       <c r="F241">
         <v>1</v>
       </c>
       <c r="G241">
-        <v>0.06348194544484118</v>
+        <v>0.07798367893383912</v>
       </c>
       <c r="H241">
-        <v>0.06366629315036325</v>
+        <v>0.07848284209163653</v>
       </c>
       <c r="I241">
-        <v>-0.4243477055220843</v>
+        <v>-0.059163157797407</v>
       </c>
       <c r="J241">
-        <v>0.7608692638052018</v>
+        <v>0.9305438593246792</v>
       </c>
       <c r="K241">
-        <v>36.75</v>
+        <v>41.7</v>
       </c>
       <c r="L241">
-        <v>35.52</v>
+        <v>39.18</v>
       </c>
       <c r="M241">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N241">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>59</v>
+        <v>242</v>
       </c>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B242" t="s">
         <v>73</v>
       </c>
       <c r="C242">
-        <v>7.452184944729609</v>
+        <v>-0.07232488166065565</v>
       </c>
       <c r="D242" t="s">
         <v>134</v>
       </c>
       <c r="E242">
-        <v>7.133706849636752</v>
+        <v>-0.1347157081474251</v>
       </c>
       <c r="F242">
         <v>1</v>
       </c>
       <c r="G242">
-        <v>0.06314781505527038</v>
+        <v>0.07843232488166066</v>
       </c>
       <c r="H242">
-        <v>0.06366629315036325</v>
+        <v>0.07893471570814742</v>
       </c>
       <c r="I242">
-        <v>-0.318478095092857</v>
+        <v>-0.06239082648676941</v>
       </c>
       <c r="J242">
-        <v>0.7608692638052018</v>
+        <v>0.941302754955891</v>
       </c>
       <c r="K242">
-        <v>36.6</v>
+        <v>41.7</v>
       </c>
       <c r="L242">
-        <v>35.3</v>
+        <v>39.18</v>
       </c>
       <c r="M242">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="N242">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13202,49 +13214,299 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C243">
-        <v>0.8256419503565553</v>
+        <v>-0.5989358924832047</v>
       </c>
       <c r="D243" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E243">
-        <v>-0.7660930450662633</v>
+        <v>-0.6651152873931565</v>
       </c>
       <c r="F243">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G243">
-        <v>0.07761435804964345</v>
+        <v>0.07895893589248319</v>
       </c>
       <c r="H243">
-        <v>0.07902609304506626</v>
+        <v>0.07946511528739317</v>
       </c>
       <c r="I243">
-        <v>1.591734995422819</v>
+        <v>-0.06617939490995184</v>
       </c>
       <c r="J243">
-        <v>1.001156663615214</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K243">
-        <v>38.35</v>
+        <v>41.7</v>
       </c>
       <c r="L243">
-        <v>39.22</v>
+        <v>39.18</v>
       </c>
       <c r="M243">
-        <v>39.85</v>
+        <v>42</v>
       </c>
       <c r="N243">
-        <v>39.13</v>
+        <v>39.4</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>68</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16">
+      <c r="A244" s="1">
+        <v>0</v>
+      </c>
+      <c r="B244" t="s">
+        <v>73</v>
+      </c>
+      <c r="C244">
+        <v>-2.784807767532328</v>
+      </c>
+      <c r="D244" t="s">
+        <v>134</v>
+      </c>
+      <c r="E244">
+        <v>-2.866712859385082</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>0.08114480776753233</v>
+      </c>
+      <c r="H244">
+        <v>0.08166671285938509</v>
+      </c>
+      <c r="I244">
+        <v>-0.08190509185275374</v>
+      </c>
+      <c r="J244">
+        <v>1.006350306175835</v>
+      </c>
+      <c r="K244">
+        <v>41.7</v>
+      </c>
+      <c r="L244">
+        <v>39.18</v>
+      </c>
+      <c r="M244">
+        <v>42</v>
+      </c>
+      <c r="N244">
+        <v>39.4</v>
+      </c>
+      <c r="O244">
+        <v>1</v>
+      </c>
+      <c r="P244" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16">
+      <c r="A245" s="1">
+        <v>0</v>
+      </c>
+      <c r="B245" t="s">
+        <v>73</v>
+      </c>
+      <c r="C245">
+        <v>-3.090001992666821</v>
+      </c>
+      <c r="D245" t="s">
+        <v>134</v>
+      </c>
+      <c r="E245">
+        <v>-3.174102726427016</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245">
+        <v>0.08145000199266682</v>
+      </c>
+      <c r="H245">
+        <v>0.08197410272642702</v>
+      </c>
+      <c r="I245">
+        <v>-0.08410073376019511</v>
+      </c>
+      <c r="J245">
+        <v>1.013669112533977</v>
+      </c>
+      <c r="K245">
+        <v>41.7</v>
+      </c>
+      <c r="L245">
+        <v>39.18</v>
+      </c>
+      <c r="M245">
+        <v>42</v>
+      </c>
+      <c r="N245">
+        <v>39.4</v>
+      </c>
+      <c r="O245">
+        <v>1</v>
+      </c>
+      <c r="P245" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16">
+      <c r="A246" s="1">
+        <v>0</v>
+      </c>
+      <c r="B246" t="s">
+        <v>73</v>
+      </c>
+      <c r="C246">
+        <v>-3.490469695643036</v>
+      </c>
+      <c r="D246" t="s">
+        <v>134</v>
+      </c>
+      <c r="E246">
+        <v>-3.577451492014568</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246">
+        <v>0.08185046969564302</v>
+      </c>
+      <c r="H246">
+        <v>0.08237745149201456</v>
+      </c>
+      <c r="I246">
+        <v>-0.08698179637153203</v>
+      </c>
+      <c r="J246">
+        <v>1.023272654571775</v>
+      </c>
+      <c r="K246">
+        <v>41.7</v>
+      </c>
+      <c r="L246">
+        <v>39.18</v>
+      </c>
+      <c r="M246">
+        <v>42</v>
+      </c>
+      <c r="N246">
+        <v>39.4</v>
+      </c>
+      <c r="O246">
+        <v>1</v>
+      </c>
+      <c r="P246" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16">
+      <c r="A247" s="1">
+        <v>0</v>
+      </c>
+      <c r="B247" t="s">
+        <v>73</v>
+      </c>
+      <c r="C247">
+        <v>-4.034032449447146</v>
+      </c>
+      <c r="D247" t="s">
+        <v>134</v>
+      </c>
+      <c r="E247">
+        <v>-4.124924769227341</v>
+      </c>
+      <c r="F247">
+        <v>1</v>
+      </c>
+      <c r="G247">
+        <v>0.08239403244944714</v>
+      </c>
+      <c r="H247">
+        <v>0.08292492476922735</v>
+      </c>
+      <c r="I247">
+        <v>-0.09089231978019541</v>
+      </c>
+      <c r="J247">
+        <v>1.036307732600651</v>
+      </c>
+      <c r="K247">
+        <v>41.7</v>
+      </c>
+      <c r="L247">
+        <v>39.18</v>
+      </c>
+      <c r="M247">
+        <v>42</v>
+      </c>
+      <c r="N247">
+        <v>39.4</v>
+      </c>
+      <c r="O247">
+        <v>1</v>
+      </c>
+      <c r="P247" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16">
+      <c r="A248" s="1">
+        <v>0</v>
+      </c>
+      <c r="B248" t="s">
+        <v>73</v>
+      </c>
+      <c r="C248">
+        <v>-4.603061330483833</v>
+      </c>
+      <c r="D248" t="s">
+        <v>134</v>
+      </c>
+      <c r="E248">
+        <v>-4.698047383221123</v>
+      </c>
+      <c r="F248">
+        <v>1</v>
+      </c>
+      <c r="G248">
+        <v>0.08296306133048384</v>
+      </c>
+      <c r="H248">
+        <v>0.08349804738322113</v>
+      </c>
+      <c r="I248">
+        <v>-0.09498605273729055</v>
+      </c>
+      <c r="J248">
+        <v>1.049953509124312</v>
+      </c>
+      <c r="K248">
+        <v>41.7</v>
+      </c>
+      <c r="L248">
+        <v>39.18</v>
+      </c>
+      <c r="M248">
+        <v>42</v>
+      </c>
+      <c r="N248">
+        <v>39.4</v>
+      </c>
+      <c r="O248">
+        <v>1</v>
+      </c>
+      <c r="P248" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -235,6 +235,9 @@
     <t>2021-07-30</t>
   </si>
   <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
     <t>2021-08-03</t>
   </si>
   <si>
@@ -418,7 +421,7 @@
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-08-04</t>
+    <t>2021-08-05</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -737,9 +740,6 @@
   </si>
   <si>
     <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-06-23</t>
   </si>
   <si>
     <t>2021-06-28</t>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1256,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1270,7 +1270,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1306,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1320,7 +1320,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1370,7 +1370,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1420,7 +1420,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1456,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1506,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1570,7 +1570,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1620,7 +1620,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1656,7 +1656,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1670,7 +1670,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1706,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1720,7 +1720,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1770,7 +1770,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1820,7 +1820,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1856,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1870,7 +1870,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1920,7 +1920,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1956,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1970,7 +1970,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2006,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2020,7 +2020,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2070,7 +2070,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2106,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2120,7 +2120,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2156,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2170,7 +2170,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2206,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2220,7 +2220,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2256,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2270,7 +2270,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2320,7 +2320,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2356,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2370,7 +2370,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2420,7 +2420,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2456,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2506,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2556,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2570,7 +2570,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2620,7 +2620,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2670,7 +2670,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2706,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2720,7 +2720,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2756,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2770,7 +2770,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2806,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2820,7 +2820,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2856,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2920,7 +2920,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2956,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2970,7 +2970,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3020,7 +3020,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3070,7 +3070,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3120,7 +3120,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3156,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3170,7 +3170,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3256,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3270,7 +3270,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3306,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3320,7 +3320,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3356,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3370,7 +3370,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3406,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3420,7 +3420,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3456,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3470,7 +3470,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3506,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3520,7 +3520,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3570,7 +3570,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3606,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3620,7 +3620,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3670,7 +3670,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3720,7 +3720,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3756,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3770,7 +3770,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3806,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3820,7 +3820,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3856,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3870,7 +3870,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3906,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3920,7 +3920,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3956,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3970,7 +3970,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4006,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4020,7 +4020,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4056,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4070,7 +4070,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4120,7 +4120,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4156,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4170,7 +4170,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4206,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4220,7 +4220,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4256,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4270,7 +4270,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4306,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4320,7 +4320,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4356,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4370,7 +4370,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4406,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4420,7 +4420,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4456,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4470,7 +4470,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4506,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4520,7 +4520,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4570,7 +4570,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4620,7 +4620,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4670,7 +4670,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4706,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4720,7 +4720,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4756,7 +4756,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4770,7 +4770,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4820,7 +4820,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4856,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4870,7 +4870,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4906,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4920,7 +4920,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4970,7 +4970,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5020,7 +5020,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5070,7 +5070,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5106,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5120,7 +5120,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5170,7 +5170,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5206,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5220,7 +5220,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5256,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5270,7 +5270,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5306,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5320,7 +5320,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5356,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5370,7 +5370,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5406,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5420,7 +5420,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5456,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5470,7 +5470,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5520,7 +5520,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5556,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5570,7 +5570,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5606,7 +5606,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5620,7 +5620,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5656,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5670,7 +5670,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5706,7 +5706,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5720,7 +5720,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5770,7 +5770,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5806,7 +5806,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5820,7 +5820,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5870,7 +5870,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5906,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5920,7 +5920,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5956,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5970,7 +5970,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6006,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6020,7 +6020,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6070,7 +6070,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6106,7 +6106,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6120,7 +6120,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6156,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6170,7 +6170,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6206,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6220,7 +6220,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6256,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6270,7 +6270,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6306,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6320,7 +6320,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6356,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6370,7 +6370,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6406,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6420,7 +6420,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6456,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6470,7 +6470,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6506,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6520,7 +6520,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6570,7 +6570,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6620,7 +6620,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6670,7 +6670,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6720,7 +6720,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6770,7 +6770,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6806,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6820,7 +6820,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6856,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6870,7 +6870,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6906,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6920,7 +6920,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6956,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6970,7 +6970,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7006,7 +7006,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7020,7 +7020,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7070,7 +7070,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7120,7 +7120,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7170,7 +7170,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7220,7 +7220,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7256,7 +7256,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7270,7 +7270,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7306,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7320,7 +7320,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7356,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7370,7 +7370,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7406,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7420,7 +7420,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7456,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7470,7 +7470,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7506,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7520,7 +7520,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7556,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7570,7 +7570,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7606,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7620,7 +7620,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7656,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7670,7 +7670,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7706,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7720,7 +7720,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7756,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7770,7 +7770,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7806,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7820,7 +7820,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7856,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7870,7 +7870,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7906,7 +7906,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7920,7 +7920,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7956,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7970,7 +7970,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8006,7 +8006,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8020,7 +8020,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8056,7 +8056,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8070,7 +8070,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8106,7 +8106,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8120,7 +8120,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8156,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8170,7 +8170,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8206,7 +8206,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8220,7 +8220,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8256,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8270,7 +8270,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8306,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8320,7 +8320,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8356,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8370,7 +8370,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8406,7 +8406,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8420,7 +8420,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8456,7 +8456,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8470,7 +8470,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8506,7 +8506,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8520,7 +8520,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8556,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8570,7 +8570,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8606,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8620,7 +8620,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8656,7 +8656,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8670,7 +8670,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8706,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8720,7 +8720,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8756,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8770,7 +8770,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8806,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8820,7 +8820,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8856,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8870,7 +8870,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8906,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8920,7 +8920,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8956,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8970,7 +8970,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9006,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9020,7 +9020,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9056,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9070,7 +9070,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9106,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9120,7 +9120,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9156,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9170,7 +9170,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9220,7 +9220,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9256,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9270,7 +9270,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9306,7 +9306,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9320,7 +9320,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9356,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9370,7 +9370,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9406,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9420,7 +9420,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9470,7 +9470,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9506,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9520,7 +9520,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9570,7 +9570,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9606,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9620,7 +9620,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9656,7 +9656,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9670,7 +9670,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9706,7 +9706,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9720,7 +9720,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9756,7 +9756,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9770,7 +9770,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9806,7 +9806,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9820,7 +9820,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9856,7 +9856,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9906,7 +9906,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9920,7 +9920,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9956,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9970,7 +9970,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10006,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10020,7 +10020,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10056,7 +10056,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10070,7 +10070,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10106,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10120,7 +10120,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10156,7 +10156,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10170,7 +10170,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10206,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10220,7 +10220,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10256,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10270,7 +10270,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10306,7 +10306,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10320,7 +10320,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10356,7 +10356,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10370,7 +10370,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10406,7 +10406,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10420,7 +10420,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10456,7 +10456,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10470,7 +10470,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10520,7 +10520,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10556,7 +10556,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10570,7 +10570,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10606,7 +10606,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10620,7 +10620,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10656,7 +10656,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10670,7 +10670,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10706,7 +10706,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10720,7 +10720,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10756,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10770,7 +10770,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10806,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10820,7 +10820,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10856,7 +10856,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10870,7 +10870,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10906,7 +10906,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10920,7 +10920,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10956,7 +10956,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10970,7 +10970,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11006,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11020,7 +11020,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11056,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11070,7 +11070,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11106,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11120,7 +11120,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11156,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11170,7 +11170,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11206,7 +11206,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11220,7 +11220,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11256,7 +11256,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11270,7 +11270,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11306,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11320,7 +11320,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11356,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11370,7 +11370,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11406,7 +11406,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11420,7 +11420,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11456,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11470,7 +11470,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11520,7 +11520,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11556,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11570,7 +11570,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11606,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11620,7 +11620,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11656,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11670,7 +11670,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11706,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11720,7 +11720,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11756,7 +11756,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11770,7 +11770,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11806,7 +11806,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11820,7 +11820,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11856,7 +11856,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11870,7 +11870,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11920,7 +11920,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11956,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12006,7 +12006,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12020,7 +12020,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12056,7 +12056,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12070,7 +12070,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12106,7 +12106,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12120,7 +12120,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12156,7 +12156,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12170,7 +12170,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12206,7 +12206,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12256,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12270,7 +12270,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12306,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12320,7 +12320,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12356,7 +12356,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12370,7 +12370,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12406,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12456,7 +12456,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12506,7 +12506,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12520,7 +12520,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12556,7 +12556,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12570,7 +12570,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12606,7 +12606,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12620,7 +12620,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12656,7 +12656,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12670,7 +12670,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12706,7 +12706,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12720,10 +12720,10 @@
         <v>7.063428297161892</v>
       </c>
       <c r="D233" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E233">
-        <v>7.364037374987873</v>
+        <v>8.064037374987876</v>
       </c>
       <c r="F233">
         <v>1</v>
@@ -12732,10 +12732,10 @@
         <v>0.06373657170283811</v>
       </c>
       <c r="H233">
-        <v>0.07143596262501213</v>
+        <v>0.07213596262501212</v>
       </c>
       <c r="I233">
-        <v>0.3006090778259818</v>
+        <v>1.000609077825985</v>
       </c>
       <c r="J233">
         <v>0.7627610148812412</v>
@@ -12750,13 +12750,13 @@
         <v>42</v>
       </c>
       <c r="N233">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12770,10 +12770,10 @@
         <v>7.062876678218629</v>
       </c>
       <c r="D234" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E234">
-        <v>7.363413741189298</v>
+        <v>8.063413741189301</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -12782,10 +12782,10 @@
         <v>0.06373712332178137</v>
       </c>
       <c r="H234">
-        <v>0.07143658625881071</v>
+        <v>0.0721365862588107</v>
       </c>
       <c r="I234">
-        <v>0.300537062970669</v>
+        <v>1.000537062970672</v>
       </c>
       <c r="J234">
         <v>0.7627758633050167</v>
@@ -12800,13 +12800,13 @@
         <v>42</v>
       </c>
       <c r="N234">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O234">
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12820,10 +12820,10 @@
         <v>7.124439974898646</v>
       </c>
       <c r="D235" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E235">
-        <v>7.433014238108832</v>
+        <v>8.133014238108835</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -12832,10 +12832,10 @@
         <v>0.06367556002510134</v>
       </c>
       <c r="H235">
-        <v>0.07136698576189116</v>
+        <v>0.07206698576189118</v>
       </c>
       <c r="I235">
-        <v>0.3085742632101862</v>
+        <v>1.008574263210189</v>
       </c>
       <c r="J235">
         <v>0.7611187086164564</v>
@@ -12850,13 +12850,13 @@
         <v>42</v>
       </c>
       <c r="N235">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O235">
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12870,10 +12870,10 @@
         <v>7.149172513666915</v>
       </c>
       <c r="D236" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E236">
-        <v>7.460975654751291</v>
+        <v>8.160975654751294</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -12882,10 +12882,10 @@
         <v>0.06365082748633309</v>
       </c>
       <c r="H236">
-        <v>0.07133902434524871</v>
+        <v>0.07203902434524871</v>
       </c>
       <c r="I236">
-        <v>0.3118031410843756</v>
+        <v>1.011803141084378</v>
       </c>
       <c r="J236">
         <v>0.7604529606011597</v>
@@ -12900,13 +12900,13 @@
         <v>42</v>
       </c>
       <c r="N236">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12920,10 +12920,10 @@
         <v>7.133706849636752</v>
       </c>
       <c r="D237" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E237">
-        <v>7.443490920181521</v>
+        <v>8.143490920181524</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -12932,10 +12932,10 @@
         <v>0.06366629315036325</v>
       </c>
       <c r="H237">
-        <v>0.07135650907981848</v>
+        <v>0.07205650907981849</v>
       </c>
       <c r="I237">
-        <v>0.3097840705447688</v>
+        <v>1.009784070544772</v>
       </c>
       <c r="J237">
         <v>0.7608692638052018</v>
@@ -12950,7 +12950,7 @@
         <v>42</v>
       </c>
       <c r="N237">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O237">
         <v>1</v>
@@ -12967,46 +12967,46 @@
         <v>73</v>
       </c>
       <c r="C238">
-        <v>2.000557447825351</v>
+        <v>1.433382514668835</v>
       </c>
       <c r="D238" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E238">
-        <v>1.953079443852872</v>
+        <v>2.133382514668838</v>
       </c>
       <c r="F238">
         <v>1</v>
       </c>
       <c r="G238">
-        <v>0.07635944255217464</v>
+        <v>0.07736661748533116</v>
       </c>
       <c r="H238">
-        <v>0.07684692055614713</v>
+        <v>0.07806661748533117</v>
       </c>
       <c r="I238">
-        <v>-0.04747800397247914</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J238">
-        <v>0.8915933465749316</v>
+        <v>0.9039670829840752</v>
       </c>
       <c r="K238">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L238">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M238">
         <v>42</v>
       </c>
       <c r="N238">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O238">
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>241</v>
+        <v>66</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13017,46 +13017,46 @@
         <v>73</v>
       </c>
       <c r="C239">
-        <v>1.484572639564057</v>
+        <v>0.8857582868211864</v>
       </c>
       <c r="D239" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E239">
-        <v>1.433382514668835</v>
+        <v>1.585758286821189</v>
       </c>
       <c r="F239">
         <v>1</v>
       </c>
       <c r="G239">
-        <v>0.07687542736043594</v>
+        <v>0.07791424171317882</v>
       </c>
       <c r="H239">
-        <v>0.07736661748533116</v>
+        <v>0.07861424171317881</v>
       </c>
       <c r="I239">
-        <v>-0.05119012489522135</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J239">
-        <v>0.9039670829840752</v>
+        <v>0.9170057550756859</v>
       </c>
       <c r="K239">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L239">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M239">
         <v>42</v>
       </c>
       <c r="N239">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13067,46 +13067,46 @@
         <v>73</v>
       </c>
       <c r="C240">
-        <v>0.9408600133438938</v>
+        <v>0.3171579083634697</v>
       </c>
       <c r="D240" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E240">
-        <v>0.8857582868211864</v>
+        <v>1.017157908363473</v>
       </c>
       <c r="F240">
         <v>1</v>
       </c>
       <c r="G240">
-        <v>0.0774191399866561</v>
+        <v>0.07848284209163653</v>
       </c>
       <c r="H240">
-        <v>0.07791424171317882</v>
+        <v>0.07918284209163653</v>
       </c>
       <c r="I240">
-        <v>-0.05510172652270739</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J240">
-        <v>0.9170057550756859</v>
+        <v>0.9305438593246792</v>
       </c>
       <c r="K240">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L240">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M240">
         <v>42</v>
       </c>
       <c r="N240">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>69</v>
+        <v>242</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13117,46 +13117,46 @@
         <v>73</v>
       </c>
       <c r="C241">
-        <v>0.3763210661608767</v>
+        <v>-0.1347157081474251</v>
       </c>
       <c r="D241" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E241">
-        <v>0.3171579083634697</v>
+        <v>0.5652842918525778</v>
       </c>
       <c r="F241">
         <v>1</v>
       </c>
       <c r="G241">
-        <v>0.07798367893383912</v>
+        <v>0.07893471570814742</v>
       </c>
       <c r="H241">
-        <v>0.07848284209163653</v>
+        <v>0.07963471570814742</v>
       </c>
       <c r="I241">
-        <v>-0.059163157797407</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J241">
-        <v>0.9305438593246792</v>
+        <v>0.941302754955891</v>
       </c>
       <c r="K241">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L241">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M241">
         <v>42</v>
       </c>
       <c r="N241">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>242</v>
+        <v>67</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13167,46 +13167,46 @@
         <v>73</v>
       </c>
       <c r="C242">
-        <v>-0.07232488166065565</v>
+        <v>-0.6651152873931565</v>
       </c>
       <c r="D242" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E242">
-        <v>-0.1347157081474251</v>
+        <v>0.03488471260684634</v>
       </c>
       <c r="F242">
         <v>1</v>
       </c>
       <c r="G242">
-        <v>0.07843232488166066</v>
+        <v>0.07946511528739317</v>
       </c>
       <c r="H242">
-        <v>0.07893471570814742</v>
+        <v>0.08016511528739315</v>
       </c>
       <c r="I242">
-        <v>-0.06239082648676941</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J242">
-        <v>0.941302754955891</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K242">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L242">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M242">
         <v>42</v>
       </c>
       <c r="N242">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13217,46 +13217,46 @@
         <v>73</v>
       </c>
       <c r="C243">
-        <v>-0.5989358924832047</v>
+        <v>-2.754182538335044</v>
       </c>
       <c r="D243" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E243">
-        <v>-0.6651152873931565</v>
+        <v>-2.054182538335041</v>
       </c>
       <c r="F243">
         <v>1</v>
       </c>
       <c r="G243">
-        <v>0.07895893589248319</v>
+        <v>0.08155418253833505</v>
       </c>
       <c r="H243">
-        <v>0.07946511528739317</v>
+        <v>0.08225418253833505</v>
       </c>
       <c r="I243">
-        <v>-0.06617939490995184</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J243">
-        <v>0.9539313163665036</v>
+        <v>1.003671012817501</v>
       </c>
       <c r="K243">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L243">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M243">
         <v>42</v>
       </c>
       <c r="N243">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13264,16 +13264,16 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C244">
         <v>-2.784807767532328</v>
       </c>
       <c r="D244" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E244">
-        <v>-2.866712859385082</v>
+        <v>-2.166712859385079</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -13282,10 +13282,10 @@
         <v>0.08114480776753233</v>
       </c>
       <c r="H244">
-        <v>0.08166671285938509</v>
+        <v>0.08236671285938507</v>
       </c>
       <c r="I244">
-        <v>-0.08190509185275374</v>
+        <v>0.6180949081472491</v>
       </c>
       <c r="J244">
         <v>1.006350306175835</v>
@@ -13300,7 +13300,7 @@
         <v>42</v>
       </c>
       <c r="N244">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O244">
         <v>1</v>
@@ -13317,46 +13317,46 @@
         <v>73</v>
       </c>
       <c r="C245">
-        <v>-3.090001992666821</v>
+        <v>-3.174102726427016</v>
       </c>
       <c r="D245" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E245">
-        <v>-3.174102726427016</v>
+        <v>-2.474102726427013</v>
       </c>
       <c r="F245">
         <v>1</v>
       </c>
       <c r="G245">
-        <v>0.08145000199266682</v>
+        <v>0.08197410272642702</v>
       </c>
       <c r="H245">
-        <v>0.08197410272642702</v>
+        <v>0.08267410272642702</v>
       </c>
       <c r="I245">
-        <v>-0.08410073376019511</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J245">
         <v>1.013669112533977</v>
       </c>
       <c r="K245">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L245">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M245">
         <v>42</v>
       </c>
       <c r="N245">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13364,16 +13364,16 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C246">
         <v>-3.490469695643036</v>
       </c>
       <c r="D246" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E246">
-        <v>-3.577451492014568</v>
+        <v>-2.877451492014565</v>
       </c>
       <c r="F246">
         <v>1</v>
@@ -13382,10 +13382,10 @@
         <v>0.08185046969564302</v>
       </c>
       <c r="H246">
-        <v>0.08237745149201456</v>
+        <v>0.08307745149201458</v>
       </c>
       <c r="I246">
-        <v>-0.08698179637153203</v>
+        <v>0.6130182036284708</v>
       </c>
       <c r="J246">
         <v>1.023272654571775</v>
@@ -13400,13 +13400,13 @@
         <v>42</v>
       </c>
       <c r="N246">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13417,40 +13417,40 @@
         <v>73</v>
       </c>
       <c r="C247">
-        <v>-4.034032449447146</v>
+        <v>-4.124924769227341</v>
       </c>
       <c r="D247" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E247">
-        <v>-4.124924769227341</v>
+        <v>-3.424924769227339</v>
       </c>
       <c r="F247">
         <v>1</v>
       </c>
       <c r="G247">
-        <v>0.08239403244944714</v>
+        <v>0.08292492476922735</v>
       </c>
       <c r="H247">
-        <v>0.08292492476922735</v>
+        <v>0.08362492476922734</v>
       </c>
       <c r="I247">
-        <v>-0.09089231978019541</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J247">
         <v>1.036307732600651</v>
       </c>
       <c r="K247">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L247">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M247">
         <v>42</v>
       </c>
       <c r="N247">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O247">
         <v>1</v>
@@ -13467,40 +13467,40 @@
         <v>73</v>
       </c>
       <c r="C248">
-        <v>-4.603061330483833</v>
+        <v>-4.698047383221123</v>
       </c>
       <c r="D248" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E248">
-        <v>-4.698047383221123</v>
+        <v>-3.99804738322112</v>
       </c>
       <c r="F248">
         <v>1</v>
       </c>
       <c r="G248">
-        <v>0.08296306133048384</v>
+        <v>0.08349804738322113</v>
       </c>
       <c r="H248">
-        <v>0.08349804738322113</v>
+        <v>0.08419804738322112</v>
       </c>
       <c r="I248">
-        <v>-0.09498605273729055</v>
+        <v>0.7000000000000028</v>
       </c>
       <c r="J248">
         <v>1.049953509124312</v>
       </c>
       <c r="K248">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="L248">
-        <v>39.18</v>
+        <v>39.4</v>
       </c>
       <c r="M248">
         <v>42</v>
       </c>
       <c r="N248">
-        <v>39.4</v>
+        <v>40.1</v>
       </c>
       <c r="O248">
         <v>1</v>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="237">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,15 +232,12 @@
     <t>2021-07-02</t>
   </si>
   <si>
-    <t>2021-07-30</t>
+    <t>2021-07-09</t>
   </si>
   <si>
     <t>2021-08-04</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -412,16 +409,16 @@
     <t>2021-07-07</t>
   </si>
   <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-08-05</t>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -728,30 +725,6 @@
   </si>
   <si>
     <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P248"/>
+  <dimension ref="A1:P236"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1206,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1256,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1270,7 +1243,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1306,7 +1279,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1320,7 +1293,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1356,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1370,7 +1343,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1406,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1420,7 +1393,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1456,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1506,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1556,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1570,7 +1543,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1606,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1620,7 +1593,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1656,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1670,7 +1643,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1706,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1720,7 +1693,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1756,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1770,7 +1743,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1806,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1820,7 +1793,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1856,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1870,7 +1843,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1906,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1920,7 +1893,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1956,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1970,7 +1943,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2006,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2020,7 +1993,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2056,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2070,7 +2043,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2106,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2120,7 +2093,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2156,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2170,7 +2143,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2206,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2220,7 +2193,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2256,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2270,7 +2243,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2306,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2320,7 +2293,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2356,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2370,7 +2343,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2406,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2420,7 +2393,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2456,7 +2429,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2506,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2556,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2570,7 +2543,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2606,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2620,7 +2593,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2656,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2670,7 +2643,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2706,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2720,7 +2693,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2756,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2770,7 +2743,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2806,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2820,7 +2793,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2856,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2906,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2920,7 +2893,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2956,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2970,7 +2943,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3006,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3020,7 +2993,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3056,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3070,7 +3043,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3106,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3120,7 +3093,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3156,7 +3129,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3170,7 +3143,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3206,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3256,7 +3229,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3270,7 +3243,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3306,7 +3279,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3320,7 +3293,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3356,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3370,7 +3343,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3406,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3420,7 +3393,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3456,7 +3429,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3470,7 +3443,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3506,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3520,7 +3493,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3556,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3570,7 +3543,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3606,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3620,7 +3593,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3656,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3670,7 +3643,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3720,7 +3693,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3756,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3770,7 +3743,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3806,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3820,7 +3793,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3856,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3870,7 +3843,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3906,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3920,7 +3893,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3956,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3970,7 +3943,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4006,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4020,7 +3993,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4056,7 +4029,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4070,7 +4043,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4106,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4120,7 +4093,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4156,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4170,7 +4143,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4206,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4220,7 +4193,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4256,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4270,7 +4243,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4306,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4320,7 +4293,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4356,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4370,7 +4343,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4406,7 +4379,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4420,7 +4393,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4456,7 +4429,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4470,7 +4443,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4506,7 +4479,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4520,7 +4493,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4570,7 +4543,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4620,7 +4593,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4656,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4670,7 +4643,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4706,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4720,7 +4693,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4756,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4770,7 +4743,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4806,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4820,7 +4793,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4856,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4870,7 +4843,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4906,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4920,7 +4893,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4956,7 +4929,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4970,7 +4943,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5020,7 +4993,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5070,7 +5043,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5106,7 +5079,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5120,7 +5093,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5156,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5170,7 +5143,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5206,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5220,7 +5193,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5256,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5270,7 +5243,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5306,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5320,7 +5293,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5356,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5370,7 +5343,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5406,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5420,7 +5393,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5456,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5470,7 +5443,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5520,7 +5493,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5556,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5570,7 +5543,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5606,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5620,7 +5593,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5656,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5670,7 +5643,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5706,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5720,7 +5693,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5756,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5770,7 +5743,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5806,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5820,7 +5793,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5856,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5870,7 +5843,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5906,7 +5879,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5920,7 +5893,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5956,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5970,7 +5943,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6006,7 +5979,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6020,7 +5993,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6056,7 +6029,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6070,7 +6043,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6106,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6120,7 +6093,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6156,7 +6129,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6170,7 +6143,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6206,7 +6179,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6220,7 +6193,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6256,7 +6229,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6270,7 +6243,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6306,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6320,7 +6293,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6356,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6370,7 +6343,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6406,7 +6379,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6420,7 +6393,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6456,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6470,7 +6443,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6506,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6520,7 +6493,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6570,7 +6543,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6620,7 +6593,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6670,7 +6643,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6720,7 +6693,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6770,7 +6743,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6806,7 +6779,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6820,7 +6793,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6856,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6870,7 +6843,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6906,7 +6879,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6920,7 +6893,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6956,7 +6929,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6970,7 +6943,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7006,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7020,7 +6993,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7070,7 +7043,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7120,7 +7093,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7170,7 +7143,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7220,7 +7193,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7256,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7270,7 +7243,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7306,7 +7279,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7320,7 +7293,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7356,7 +7329,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7370,7 +7343,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7406,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7420,7 +7393,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7456,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7470,7 +7443,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7506,7 +7479,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7520,7 +7493,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7556,7 +7529,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7570,7 +7543,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7606,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7620,7 +7593,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7656,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7670,7 +7643,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7706,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7720,7 +7693,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7756,7 +7729,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7770,7 +7743,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7806,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7820,7 +7793,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7856,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7870,7 +7843,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7906,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7920,7 +7893,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7956,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7970,7 +7943,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8006,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8020,7 +7993,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8056,7 +8029,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8070,7 +8043,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8106,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8120,7 +8093,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8156,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8170,7 +8143,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8206,7 +8179,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8220,7 +8193,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8256,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8270,7 +8243,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8306,7 +8279,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8320,7 +8293,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8356,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8370,7 +8343,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8406,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8420,7 +8393,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8456,7 +8429,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8470,7 +8443,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8506,7 +8479,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8520,7 +8493,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8556,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8570,7 +8543,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8606,7 +8579,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8620,7 +8593,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8656,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8670,7 +8643,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8706,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8720,7 +8693,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8756,7 +8729,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8770,7 +8743,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8806,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8820,7 +8793,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8856,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8870,7 +8843,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8906,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8920,7 +8893,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8956,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8970,7 +8943,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9006,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9020,7 +8993,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9056,7 +9029,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9070,7 +9043,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9106,7 +9079,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9120,7 +9093,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9156,7 +9129,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9170,7 +9143,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9206,7 +9179,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9220,7 +9193,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9256,7 +9229,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9270,7 +9243,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9306,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9320,7 +9293,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9356,7 +9329,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9370,7 +9343,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9406,7 +9379,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9420,7 +9393,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9456,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9470,7 +9443,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9506,7 +9479,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9520,7 +9493,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9556,7 +9529,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9570,7 +9543,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9606,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9620,7 +9593,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9656,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9670,7 +9643,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9706,7 +9679,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9720,7 +9693,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9756,7 +9729,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9770,7 +9743,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9806,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9820,7 +9793,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9856,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9906,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9920,7 +9893,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9956,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9970,7 +9943,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10006,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10020,7 +9993,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10056,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10070,7 +10043,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10106,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10120,7 +10093,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10156,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10170,7 +10143,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10206,7 +10179,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10220,7 +10193,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10256,7 +10229,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10270,7 +10243,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10306,7 +10279,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10320,7 +10293,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10356,7 +10329,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10370,7 +10343,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10406,7 +10379,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10420,7 +10393,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10456,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10470,7 +10443,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10506,7 +10479,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10520,7 +10493,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10556,7 +10529,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10570,7 +10543,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10606,7 +10579,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10620,7 +10593,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10656,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10670,7 +10643,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10706,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10720,7 +10693,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10756,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10770,7 +10743,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10806,7 +10779,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10820,7 +10793,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10856,7 +10829,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10870,7 +10843,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10906,7 +10879,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10920,7 +10893,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10956,7 +10929,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10970,7 +10943,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11006,7 +10979,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11020,7 +10993,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11056,7 +11029,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11070,7 +11043,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11106,7 +11079,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11120,7 +11093,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11156,7 +11129,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11170,7 +11143,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11206,7 +11179,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11220,7 +11193,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11256,7 +11229,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11270,7 +11243,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11306,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11320,7 +11293,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11356,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11370,7 +11343,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11406,7 +11379,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11420,7 +11393,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11456,7 +11429,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11470,7 +11443,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11506,7 +11479,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11520,7 +11493,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11556,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11570,7 +11543,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11606,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11620,7 +11593,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11656,7 +11629,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11670,7 +11643,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11706,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11720,7 +11693,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11756,7 +11729,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11770,7 +11743,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11806,7 +11779,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11820,7 +11793,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11856,7 +11829,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11870,7 +11843,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11920,7 +11893,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11956,7 +11929,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12006,7 +11979,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12020,7 +11993,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12056,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12070,7 +12043,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12106,7 +12079,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12120,7 +12093,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12156,7 +12129,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12170,7 +12143,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12206,7 +12179,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12256,7 +12229,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12270,7 +12243,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12306,7 +12279,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12320,7 +12293,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12356,7 +12329,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12370,7 +12343,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12406,7 +12379,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12456,7 +12429,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12506,7 +12479,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12520,7 +12493,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12556,7 +12529,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12570,7 +12543,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12606,7 +12579,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12620,7 +12593,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12656,7 +12629,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12670,7 +12643,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12706,7 +12679,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12717,46 +12690,46 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>7.063428297161892</v>
+        <v>0.8256419503565553</v>
       </c>
       <c r="D233" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E233">
-        <v>8.064037374987876</v>
+        <v>-1.464531549185729</v>
       </c>
       <c r="F233">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.06373657170283811</v>
+        <v>0.07761435804964345</v>
       </c>
       <c r="H233">
-        <v>0.07213596262501212</v>
+        <v>0.07562453154918572</v>
       </c>
       <c r="I233">
-        <v>1.000609077825985</v>
+        <v>2.290173499542284</v>
       </c>
       <c r="J233">
-        <v>0.7627610148812412</v>
+        <v>1.001156663615214</v>
       </c>
       <c r="K233">
-        <v>37.15</v>
+        <v>38.35</v>
       </c>
       <c r="L233">
-        <v>35.4</v>
+        <v>39.22</v>
       </c>
       <c r="M233">
-        <v>42</v>
+        <v>38.5</v>
       </c>
       <c r="N233">
-        <v>40.1</v>
+        <v>37.08</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>238</v>
+        <v>68</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12764,49 +12737,49 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C234">
-        <v>7.062876678218629</v>
+        <v>-2.866712859385082</v>
       </c>
       <c r="D234" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E234">
-        <v>8.063413741189301</v>
+        <v>-2.054333226796082</v>
       </c>
       <c r="F234">
         <v>1</v>
       </c>
       <c r="G234">
-        <v>0.06373712332178137</v>
+        <v>0.08166671285938509</v>
       </c>
       <c r="H234">
-        <v>0.0721365862588107</v>
+        <v>0.08489433322679608</v>
       </c>
       <c r="I234">
-        <v>1.000537062970672</v>
+        <v>0.8123796325889998</v>
       </c>
       <c r="J234">
-        <v>0.7627758633050167</v>
+        <v>1.006350306175835</v>
       </c>
       <c r="K234">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="L234">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="M234">
-        <v>42</v>
+        <v>43.2</v>
       </c>
       <c r="N234">
-        <v>40.1</v>
+        <v>41.42</v>
       </c>
       <c r="O234">
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>239</v>
+        <v>70</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12814,49 +12787,49 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C235">
-        <v>7.124439974898646</v>
+        <v>-3.174102726427016</v>
       </c>
       <c r="D235" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E235">
-        <v>8.133014238108835</v>
+        <v>-2.370505661467789</v>
       </c>
       <c r="F235">
         <v>1</v>
       </c>
       <c r="G235">
-        <v>0.06367556002510134</v>
+        <v>0.08197410272642702</v>
       </c>
       <c r="H235">
-        <v>0.07206698576189118</v>
+        <v>0.08521050566146779</v>
       </c>
       <c r="I235">
-        <v>1.008574263210189</v>
+        <v>0.8035970649592272</v>
       </c>
       <c r="J235">
-        <v>0.7611187086164564</v>
+        <v>1.013669112533977</v>
       </c>
       <c r="K235">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="L235">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="M235">
-        <v>42</v>
+        <v>43.2</v>
       </c>
       <c r="N235">
-        <v>40.1</v>
+        <v>41.42</v>
       </c>
       <c r="O235">
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>240</v>
+        <v>131</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12864,649 +12837,49 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C236">
-        <v>7.149172513666915</v>
+        <v>-3.577451492014568</v>
       </c>
       <c r="D236" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E236">
-        <v>8.160975654751294</v>
+        <v>-2.785378677500702</v>
       </c>
       <c r="F236">
         <v>1</v>
       </c>
       <c r="G236">
-        <v>0.06365082748633309</v>
+        <v>0.08237745149201456</v>
       </c>
       <c r="H236">
-        <v>0.07203902434524871</v>
+        <v>0.08562537867750071</v>
       </c>
       <c r="I236">
-        <v>1.011803141084378</v>
+        <v>0.7920728145138654</v>
       </c>
       <c r="J236">
-        <v>0.7604529606011597</v>
+        <v>1.023272654571775</v>
       </c>
       <c r="K236">
-        <v>37.15</v>
+        <v>42</v>
       </c>
       <c r="L236">
-        <v>35.4</v>
+        <v>39.4</v>
       </c>
       <c r="M236">
-        <v>42</v>
+        <v>43.2</v>
       </c>
       <c r="N236">
-        <v>40.1</v>
+        <v>41.42</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16">
-      <c r="A237" s="1">
-        <v>0</v>
-      </c>
-      <c r="B237" t="s">
-        <v>72</v>
-      </c>
-      <c r="C237">
-        <v>7.133706849636752</v>
-      </c>
-      <c r="D237" t="s">
-        <v>135</v>
-      </c>
-      <c r="E237">
-        <v>8.143490920181524</v>
-      </c>
-      <c r="F237">
-        <v>1</v>
-      </c>
-      <c r="G237">
-        <v>0.06366629315036325</v>
-      </c>
-      <c r="H237">
-        <v>0.07205650907981849</v>
-      </c>
-      <c r="I237">
-        <v>1.009784070544772</v>
-      </c>
-      <c r="J237">
-        <v>0.7608692638052018</v>
-      </c>
-      <c r="K237">
-        <v>37.15</v>
-      </c>
-      <c r="L237">
-        <v>35.4</v>
-      </c>
-      <c r="M237">
-        <v>42</v>
-      </c>
-      <c r="N237">
-        <v>40.1</v>
-      </c>
-      <c r="O237">
-        <v>1</v>
-      </c>
-      <c r="P237" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16">
-      <c r="A238" s="1">
-        <v>0</v>
-      </c>
-      <c r="B238" t="s">
-        <v>73</v>
-      </c>
-      <c r="C238">
-        <v>1.433382514668835</v>
-      </c>
-      <c r="D238" t="s">
-        <v>135</v>
-      </c>
-      <c r="E238">
-        <v>2.133382514668838</v>
-      </c>
-      <c r="F238">
-        <v>1</v>
-      </c>
-      <c r="G238">
-        <v>0.07736661748533116</v>
-      </c>
-      <c r="H238">
-        <v>0.07806661748533117</v>
-      </c>
-      <c r="I238">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J238">
-        <v>0.9039670829840752</v>
-      </c>
-      <c r="K238">
-        <v>42</v>
-      </c>
-      <c r="L238">
-        <v>39.4</v>
-      </c>
-      <c r="M238">
-        <v>42</v>
-      </c>
-      <c r="N238">
-        <v>40.1</v>
-      </c>
-      <c r="O238">
-        <v>1</v>
-      </c>
-      <c r="P238" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16">
-      <c r="A239" s="1">
-        <v>0</v>
-      </c>
-      <c r="B239" t="s">
-        <v>73</v>
-      </c>
-      <c r="C239">
-        <v>0.8857582868211864</v>
-      </c>
-      <c r="D239" t="s">
-        <v>135</v>
-      </c>
-      <c r="E239">
-        <v>1.585758286821189</v>
-      </c>
-      <c r="F239">
-        <v>1</v>
-      </c>
-      <c r="G239">
-        <v>0.07791424171317882</v>
-      </c>
-      <c r="H239">
-        <v>0.07861424171317881</v>
-      </c>
-      <c r="I239">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J239">
-        <v>0.9170057550756859</v>
-      </c>
-      <c r="K239">
-        <v>42</v>
-      </c>
-      <c r="L239">
-        <v>39.4</v>
-      </c>
-      <c r="M239">
-        <v>42</v>
-      </c>
-      <c r="N239">
-        <v>40.1</v>
-      </c>
-      <c r="O239">
-        <v>1</v>
-      </c>
-      <c r="P239" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16">
-      <c r="A240" s="1">
-        <v>0</v>
-      </c>
-      <c r="B240" t="s">
-        <v>73</v>
-      </c>
-      <c r="C240">
-        <v>0.3171579083634697</v>
-      </c>
-      <c r="D240" t="s">
-        <v>135</v>
-      </c>
-      <c r="E240">
-        <v>1.017157908363473</v>
-      </c>
-      <c r="F240">
-        <v>1</v>
-      </c>
-      <c r="G240">
-        <v>0.07848284209163653</v>
-      </c>
-      <c r="H240">
-        <v>0.07918284209163653</v>
-      </c>
-      <c r="I240">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J240">
-        <v>0.9305438593246792</v>
-      </c>
-      <c r="K240">
-        <v>42</v>
-      </c>
-      <c r="L240">
-        <v>39.4</v>
-      </c>
-      <c r="M240">
-        <v>42</v>
-      </c>
-      <c r="N240">
-        <v>40.1</v>
-      </c>
-      <c r="O240">
-        <v>1</v>
-      </c>
-      <c r="P240" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16">
-      <c r="A241" s="1">
-        <v>0</v>
-      </c>
-      <c r="B241" t="s">
-        <v>73</v>
-      </c>
-      <c r="C241">
-        <v>-0.1347157081474251</v>
-      </c>
-      <c r="D241" t="s">
-        <v>135</v>
-      </c>
-      <c r="E241">
-        <v>0.5652842918525778</v>
-      </c>
-      <c r="F241">
-        <v>1</v>
-      </c>
-      <c r="G241">
-        <v>0.07893471570814742</v>
-      </c>
-      <c r="H241">
-        <v>0.07963471570814742</v>
-      </c>
-      <c r="I241">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J241">
-        <v>0.941302754955891</v>
-      </c>
-      <c r="K241">
-        <v>42</v>
-      </c>
-      <c r="L241">
-        <v>39.4</v>
-      </c>
-      <c r="M241">
-        <v>42</v>
-      </c>
-      <c r="N241">
-        <v>40.1</v>
-      </c>
-      <c r="O241">
-        <v>1</v>
-      </c>
-      <c r="P241" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16">
-      <c r="A242" s="1">
-        <v>0</v>
-      </c>
-      <c r="B242" t="s">
-        <v>73</v>
-      </c>
-      <c r="C242">
-        <v>-0.6651152873931565</v>
-      </c>
-      <c r="D242" t="s">
-        <v>135</v>
-      </c>
-      <c r="E242">
-        <v>0.03488471260684634</v>
-      </c>
-      <c r="F242">
-        <v>1</v>
-      </c>
-      <c r="G242">
-        <v>0.07946511528739317</v>
-      </c>
-      <c r="H242">
-        <v>0.08016511528739315</v>
-      </c>
-      <c r="I242">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J242">
-        <v>0.9539313163665036</v>
-      </c>
-      <c r="K242">
-        <v>42</v>
-      </c>
-      <c r="L242">
-        <v>39.4</v>
-      </c>
-      <c r="M242">
-        <v>42</v>
-      </c>
-      <c r="N242">
-        <v>40.1</v>
-      </c>
-      <c r="O242">
-        <v>1</v>
-      </c>
-      <c r="P242" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16">
-      <c r="A243" s="1">
-        <v>0</v>
-      </c>
-      <c r="B243" t="s">
-        <v>73</v>
-      </c>
-      <c r="C243">
-        <v>-2.754182538335044</v>
-      </c>
-      <c r="D243" t="s">
-        <v>135</v>
-      </c>
-      <c r="E243">
-        <v>-2.054182538335041</v>
-      </c>
-      <c r="F243">
-        <v>1</v>
-      </c>
-      <c r="G243">
-        <v>0.08155418253833505</v>
-      </c>
-      <c r="H243">
-        <v>0.08225418253833505</v>
-      </c>
-      <c r="I243">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J243">
-        <v>1.003671012817501</v>
-      </c>
-      <c r="K243">
-        <v>42</v>
-      </c>
-      <c r="L243">
-        <v>39.4</v>
-      </c>
-      <c r="M243">
-        <v>42</v>
-      </c>
-      <c r="N243">
-        <v>40.1</v>
-      </c>
-      <c r="O243">
-        <v>1</v>
-      </c>
-      <c r="P243" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16">
-      <c r="A244" s="1">
-        <v>0</v>
-      </c>
-      <c r="B244" t="s">
-        <v>74</v>
-      </c>
-      <c r="C244">
-        <v>-2.784807767532328</v>
-      </c>
-      <c r="D244" t="s">
-        <v>135</v>
-      </c>
-      <c r="E244">
-        <v>-2.166712859385079</v>
-      </c>
-      <c r="F244">
-        <v>1</v>
-      </c>
-      <c r="G244">
-        <v>0.08114480776753233</v>
-      </c>
-      <c r="H244">
-        <v>0.08236671285938507</v>
-      </c>
-      <c r="I244">
-        <v>0.6180949081472491</v>
-      </c>
-      <c r="J244">
-        <v>1.006350306175835</v>
-      </c>
-      <c r="K244">
-        <v>41.7</v>
-      </c>
-      <c r="L244">
-        <v>39.18</v>
-      </c>
-      <c r="M244">
-        <v>42</v>
-      </c>
-      <c r="N244">
-        <v>40.1</v>
-      </c>
-      <c r="O244">
-        <v>1</v>
-      </c>
-      <c r="P244" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16">
-      <c r="A245" s="1">
-        <v>0</v>
-      </c>
-      <c r="B245" t="s">
-        <v>73</v>
-      </c>
-      <c r="C245">
-        <v>-3.174102726427016</v>
-      </c>
-      <c r="D245" t="s">
-        <v>135</v>
-      </c>
-      <c r="E245">
-        <v>-2.474102726427013</v>
-      </c>
-      <c r="F245">
-        <v>1</v>
-      </c>
-      <c r="G245">
-        <v>0.08197410272642702</v>
-      </c>
-      <c r="H245">
-        <v>0.08267410272642702</v>
-      </c>
-      <c r="I245">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J245">
-        <v>1.013669112533977</v>
-      </c>
-      <c r="K245">
-        <v>42</v>
-      </c>
-      <c r="L245">
-        <v>39.4</v>
-      </c>
-      <c r="M245">
-        <v>42</v>
-      </c>
-      <c r="N245">
-        <v>40.1</v>
-      </c>
-      <c r="O245">
-        <v>1</v>
-      </c>
-      <c r="P245" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16">
-      <c r="A246" s="1">
-        <v>0</v>
-      </c>
-      <c r="B246" t="s">
-        <v>74</v>
-      </c>
-      <c r="C246">
-        <v>-3.490469695643036</v>
-      </c>
-      <c r="D246" t="s">
-        <v>135</v>
-      </c>
-      <c r="E246">
-        <v>-2.877451492014565</v>
-      </c>
-      <c r="F246">
-        <v>1</v>
-      </c>
-      <c r="G246">
-        <v>0.08185046969564302</v>
-      </c>
-      <c r="H246">
-        <v>0.08307745149201458</v>
-      </c>
-      <c r="I246">
-        <v>0.6130182036284708</v>
-      </c>
-      <c r="J246">
-        <v>1.023272654571775</v>
-      </c>
-      <c r="K246">
-        <v>41.7</v>
-      </c>
-      <c r="L246">
-        <v>39.18</v>
-      </c>
-      <c r="M246">
-        <v>42</v>
-      </c>
-      <c r="N246">
-        <v>40.1</v>
-      </c>
-      <c r="O246">
-        <v>1</v>
-      </c>
-      <c r="P246" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16">
-      <c r="A247" s="1">
-        <v>0</v>
-      </c>
-      <c r="B247" t="s">
-        <v>73</v>
-      </c>
-      <c r="C247">
-        <v>-4.124924769227341</v>
-      </c>
-      <c r="D247" t="s">
-        <v>135</v>
-      </c>
-      <c r="E247">
-        <v>-3.424924769227339</v>
-      </c>
-      <c r="F247">
-        <v>1</v>
-      </c>
-      <c r="G247">
-        <v>0.08292492476922735</v>
-      </c>
-      <c r="H247">
-        <v>0.08362492476922734</v>
-      </c>
-      <c r="I247">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J247">
-        <v>1.036307732600651</v>
-      </c>
-      <c r="K247">
-        <v>42</v>
-      </c>
-      <c r="L247">
-        <v>39.4</v>
-      </c>
-      <c r="M247">
-        <v>42</v>
-      </c>
-      <c r="N247">
-        <v>40.1</v>
-      </c>
-      <c r="O247">
-        <v>1</v>
-      </c>
-      <c r="P247" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16">
-      <c r="A248" s="1">
-        <v>0</v>
-      </c>
-      <c r="B248" t="s">
-        <v>73</v>
-      </c>
-      <c r="C248">
-        <v>-4.698047383221123</v>
-      </c>
-      <c r="D248" t="s">
-        <v>135</v>
-      </c>
-      <c r="E248">
-        <v>-3.99804738322112</v>
-      </c>
-      <c r="F248">
-        <v>1</v>
-      </c>
-      <c r="G248">
-        <v>0.08349804738322113</v>
-      </c>
-      <c r="H248">
-        <v>0.08419804738322112</v>
-      </c>
-      <c r="I248">
-        <v>0.7000000000000028</v>
-      </c>
-      <c r="J248">
-        <v>1.049953509124312</v>
-      </c>
-      <c r="K248">
-        <v>42</v>
-      </c>
-      <c r="L248">
-        <v>39.4</v>
-      </c>
-      <c r="M248">
-        <v>42</v>
-      </c>
-      <c r="N248">
-        <v>40.1</v>
-      </c>
-      <c r="O248">
-        <v>1</v>
-      </c>
-      <c r="P248" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="235">
   <si>
     <t>trade_time</t>
   </si>
@@ -235,9 +235,6 @@
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -416,9 +413,6 @@
   </si>
   <si>
     <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-08-09</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -1082,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P236"/>
+  <dimension ref="A1:P233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1179,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1229,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1243,7 +1237,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1279,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1293,7 +1287,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1329,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1343,7 +1337,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1379,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1393,7 +1387,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1429,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1479,7 +1473,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1529,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1543,7 +1537,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1579,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1593,7 +1587,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1629,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1643,7 +1637,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1679,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1693,7 +1687,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1729,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1743,7 +1737,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1779,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1793,7 +1787,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1829,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1843,7 +1837,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1879,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1893,7 +1887,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1929,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1943,7 +1937,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1979,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1993,7 +1987,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2029,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2043,7 +2037,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2079,7 +2073,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2093,7 +2087,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2129,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2143,7 +2137,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2179,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2193,7 +2187,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2229,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2243,7 +2237,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2279,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2293,7 +2287,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2329,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2343,7 +2337,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2379,7 +2373,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2393,7 +2387,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2429,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2479,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2529,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2543,7 +2537,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2579,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2593,7 +2587,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2629,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2643,7 +2637,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2679,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2693,7 +2687,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2729,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2743,7 +2737,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2779,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2793,7 +2787,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2829,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2879,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2893,7 +2887,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2929,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2943,7 +2937,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2979,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2993,7 +2987,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3029,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3043,7 +3037,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3079,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3093,7 +3087,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3129,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3143,7 +3137,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3179,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3229,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3243,7 +3237,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3279,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3293,7 +3287,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3329,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3343,7 +3337,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3379,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3393,7 +3387,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3429,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3443,7 +3437,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3479,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3493,7 +3487,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3529,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3543,7 +3537,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3579,7 +3573,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3593,7 +3587,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3629,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3643,7 +3637,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3693,7 +3687,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3729,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3743,7 +3737,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3779,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3793,7 +3787,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3829,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3843,7 +3837,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3879,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3893,7 +3887,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3929,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3943,7 +3937,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3979,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3993,7 +3987,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4029,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4043,7 +4037,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4079,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4093,7 +4087,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4129,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4143,7 +4137,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4179,7 +4173,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4193,7 +4187,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4229,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4243,7 +4237,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4279,7 +4273,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4293,7 +4287,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4329,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4343,7 +4337,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4379,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4393,7 +4387,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4429,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4443,7 +4437,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4479,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4493,7 +4487,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4543,7 +4537,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4593,7 +4587,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4629,7 +4623,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4643,7 +4637,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4679,7 +4673,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4693,7 +4687,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4729,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4743,7 +4737,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4779,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4793,7 +4787,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4829,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4843,7 +4837,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4879,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4893,7 +4887,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4929,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4943,7 +4937,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -4993,7 +4987,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5043,7 +5037,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5079,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5093,7 +5087,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5129,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5143,7 +5137,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5179,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5193,7 +5187,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5229,7 +5223,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5243,7 +5237,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5279,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5293,7 +5287,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5329,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5343,7 +5337,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5379,7 +5373,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5393,7 +5387,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5429,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5443,7 +5437,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5493,7 +5487,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5529,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5543,7 +5537,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5579,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5593,7 +5587,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5629,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5643,7 +5637,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5679,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5693,7 +5687,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5729,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5743,7 +5737,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5779,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5793,7 +5787,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5829,7 +5823,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5843,7 +5837,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5879,7 +5873,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5893,7 +5887,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5929,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5943,7 +5937,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5979,7 +5973,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5993,7 +5987,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6029,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6043,7 +6037,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6079,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6093,7 +6087,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6129,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6143,7 +6137,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6179,7 +6173,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6193,7 +6187,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6229,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6243,7 +6237,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6279,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6293,7 +6287,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6329,7 +6323,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6343,7 +6337,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6379,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6393,7 +6387,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6429,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6443,7 +6437,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6479,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6493,7 +6487,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6543,7 +6537,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6593,7 +6587,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6643,7 +6637,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6693,7 +6687,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6743,7 +6737,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6779,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6793,7 +6787,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6829,7 +6823,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6843,7 +6837,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6879,7 +6873,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6893,7 +6887,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6929,7 +6923,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6943,7 +6937,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6979,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6993,7 +6987,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7043,7 +7037,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7093,7 +7087,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7143,7 +7137,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7193,7 +7187,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7229,7 +7223,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7243,7 +7237,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7279,7 +7273,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7293,7 +7287,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7329,7 +7323,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7343,7 +7337,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7379,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7393,7 +7387,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7429,7 +7423,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7443,7 +7437,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7479,7 +7473,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7493,7 +7487,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7529,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7543,7 +7537,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7579,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7593,7 +7587,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7629,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7643,7 +7637,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7679,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7693,7 +7687,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7729,7 +7723,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7743,7 +7737,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7779,7 +7773,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7793,7 +7787,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7829,7 +7823,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7843,7 +7837,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7879,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7893,7 +7887,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7929,7 +7923,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7943,7 +7937,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7979,7 +7973,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7993,7 +7987,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8029,7 +8023,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8043,7 +8037,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8079,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8093,7 +8087,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8129,7 +8123,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8143,7 +8137,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8179,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8193,7 +8187,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8229,7 +8223,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8243,7 +8237,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8279,7 +8273,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8293,7 +8287,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8329,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8343,7 +8337,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8379,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8393,7 +8387,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8429,7 +8423,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8443,7 +8437,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8479,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8493,7 +8487,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8529,7 +8523,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8543,7 +8537,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8579,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8593,7 +8587,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8629,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8643,7 +8637,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8679,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8693,7 +8687,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8729,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8743,7 +8737,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8779,7 +8773,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8793,7 +8787,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8829,7 +8823,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8843,7 +8837,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8879,7 +8873,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8893,7 +8887,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8929,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8943,7 +8937,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8979,7 +8973,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8993,7 +8987,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9029,7 +9023,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9043,7 +9037,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9079,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9093,7 +9087,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9129,7 +9123,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9143,7 +9137,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9179,7 +9173,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9193,7 +9187,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9229,7 +9223,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9243,7 +9237,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9279,7 +9273,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9293,7 +9287,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9329,7 +9323,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9343,7 +9337,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9379,7 +9373,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9393,7 +9387,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9429,7 +9423,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9443,7 +9437,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9479,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9493,7 +9487,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9529,7 +9523,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9543,7 +9537,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9579,7 +9573,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9593,7 +9587,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9629,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9643,7 +9637,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9679,7 +9673,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9693,7 +9687,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9729,7 +9723,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9743,7 +9737,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9779,7 +9773,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9793,7 +9787,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9829,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9879,7 +9873,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9893,7 +9887,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9929,7 +9923,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9943,7 +9937,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9979,7 +9973,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9993,7 +9987,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10029,7 +10023,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10043,7 +10037,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10079,7 +10073,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10093,7 +10087,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10129,7 +10123,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10143,7 +10137,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10179,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10193,7 +10187,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10229,7 +10223,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10243,7 +10237,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10279,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10293,7 +10287,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10329,7 +10323,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10343,7 +10337,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10379,7 +10373,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10393,7 +10387,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10429,7 +10423,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10443,7 +10437,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10479,7 +10473,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10493,7 +10487,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10529,7 +10523,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10543,7 +10537,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10579,7 +10573,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10593,7 +10587,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10629,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10643,7 +10637,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10679,7 +10673,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10693,7 +10687,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10729,7 +10723,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10743,7 +10737,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10779,7 +10773,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10793,7 +10787,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10829,7 +10823,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10843,7 +10837,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10879,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10893,7 +10887,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10929,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10943,7 +10937,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10979,7 +10973,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10993,7 +10987,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11029,7 +11023,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11043,7 +11037,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11079,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11093,7 +11087,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11129,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11143,7 +11137,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11179,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11193,7 +11187,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11229,7 +11223,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11243,7 +11237,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11279,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11293,7 +11287,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11329,7 +11323,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11343,7 +11337,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11379,7 +11373,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11393,7 +11387,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11429,7 +11423,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11443,7 +11437,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11479,7 +11473,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11493,7 +11487,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11529,7 +11523,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11543,7 +11537,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11579,7 +11573,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11593,7 +11587,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11629,7 +11623,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11643,7 +11637,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11679,7 +11673,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11693,7 +11687,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11729,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11743,7 +11737,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11779,7 +11773,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11793,7 +11787,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11829,7 +11823,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11843,7 +11837,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11893,7 +11887,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11929,7 +11923,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11979,7 +11973,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11993,7 +11987,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12029,7 +12023,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12043,7 +12037,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12079,7 +12073,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12093,7 +12087,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12129,7 +12123,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12143,7 +12137,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12179,7 +12173,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12229,7 +12223,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12279,7 +12273,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12329,7 +12323,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12379,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12429,7 +12423,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12479,7 +12473,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12493,7 +12487,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12529,7 +12523,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12543,7 +12537,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12579,7 +12573,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12593,7 +12587,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12629,7 +12623,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12643,7 +12637,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12679,7 +12673,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12693,7 +12687,7 @@
         <v>0.8256419503565553</v>
       </c>
       <c r="D233" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E233">
         <v>-1.464531549185729</v>
@@ -12730,156 +12724,6 @@
       </c>
       <c r="P233" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16">
-      <c r="A234" s="1">
-        <v>0</v>
-      </c>
-      <c r="B234" t="s">
-        <v>73</v>
-      </c>
-      <c r="C234">
-        <v>-2.866712859385082</v>
-      </c>
-      <c r="D234" t="s">
-        <v>134</v>
-      </c>
-      <c r="E234">
-        <v>-2.054333226796082</v>
-      </c>
-      <c r="F234">
-        <v>1</v>
-      </c>
-      <c r="G234">
-        <v>0.08166671285938509</v>
-      </c>
-      <c r="H234">
-        <v>0.08489433322679608</v>
-      </c>
-      <c r="I234">
-        <v>0.8123796325889998</v>
-      </c>
-      <c r="J234">
-        <v>1.006350306175835</v>
-      </c>
-      <c r="K234">
-        <v>42</v>
-      </c>
-      <c r="L234">
-        <v>39.4</v>
-      </c>
-      <c r="M234">
-        <v>43.2</v>
-      </c>
-      <c r="N234">
-        <v>41.42</v>
-      </c>
-      <c r="O234">
-        <v>1</v>
-      </c>
-      <c r="P234" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" s="1">
-        <v>0</v>
-      </c>
-      <c r="B235" t="s">
-        <v>73</v>
-      </c>
-      <c r="C235">
-        <v>-3.174102726427016</v>
-      </c>
-      <c r="D235" t="s">
-        <v>134</v>
-      </c>
-      <c r="E235">
-        <v>-2.370505661467789</v>
-      </c>
-      <c r="F235">
-        <v>1</v>
-      </c>
-      <c r="G235">
-        <v>0.08197410272642702</v>
-      </c>
-      <c r="H235">
-        <v>0.08521050566146779</v>
-      </c>
-      <c r="I235">
-        <v>0.8035970649592272</v>
-      </c>
-      <c r="J235">
-        <v>1.013669112533977</v>
-      </c>
-      <c r="K235">
-        <v>42</v>
-      </c>
-      <c r="L235">
-        <v>39.4</v>
-      </c>
-      <c r="M235">
-        <v>43.2</v>
-      </c>
-      <c r="N235">
-        <v>41.42</v>
-      </c>
-      <c r="O235">
-        <v>1</v>
-      </c>
-      <c r="P235" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16">
-      <c r="A236" s="1">
-        <v>0</v>
-      </c>
-      <c r="B236" t="s">
-        <v>73</v>
-      </c>
-      <c r="C236">
-        <v>-3.577451492014568</v>
-      </c>
-      <c r="D236" t="s">
-        <v>134</v>
-      </c>
-      <c r="E236">
-        <v>-2.785378677500702</v>
-      </c>
-      <c r="F236">
-        <v>1</v>
-      </c>
-      <c r="G236">
-        <v>0.08237745149201456</v>
-      </c>
-      <c r="H236">
-        <v>0.08562537867750071</v>
-      </c>
-      <c r="I236">
-        <v>0.7920728145138654</v>
-      </c>
-      <c r="J236">
-        <v>1.023272654571775</v>
-      </c>
-      <c r="K236">
-        <v>42</v>
-      </c>
-      <c r="L236">
-        <v>39.4</v>
-      </c>
-      <c r="M236">
-        <v>43.2</v>
-      </c>
-      <c r="N236">
-        <v>41.42</v>
-      </c>
-      <c r="O236">
-        <v>1</v>
-      </c>
-      <c r="P236" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -12684,28 +12684,28 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>0.8256419503565553</v>
+        <v>1.074295946695607</v>
       </c>
       <c r="D233" t="s">
         <v>132</v>
       </c>
       <c r="E233">
-        <v>-1.464531549185729</v>
+        <v>-1.214904981804928</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07761435804964345</v>
+        <v>0.0773657040533044</v>
       </c>
       <c r="H233">
-        <v>0.07562453154918572</v>
+        <v>0.07537490498180492</v>
       </c>
       <c r="I233">
-        <v>2.290173499542284</v>
+        <v>2.289200928500534</v>
       </c>
       <c r="J233">
-        <v>1.001156663615214</v>
+        <v>0.9946728566702578</v>
       </c>
       <c r="K233">
         <v>38.35</v>
@@ -12723,7 +12723,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="238">
   <si>
     <t>trade_time</t>
   </si>
@@ -235,6 +235,9 @@
     <t>2021-07-09</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -415,6 +418,9 @@
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -719,6 +725,9 @@
   </si>
   <si>
     <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P233"/>
+  <dimension ref="A1:P234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1173,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1223,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1237,7 +1246,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1273,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1287,7 +1296,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1323,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1337,7 +1346,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1373,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1387,7 +1396,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1423,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1473,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1523,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1537,7 +1546,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1573,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1587,7 +1596,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1623,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1637,7 +1646,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1673,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1687,7 +1696,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1723,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1737,7 +1746,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1773,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1787,7 +1796,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1823,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1837,7 +1846,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1873,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1887,7 +1896,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1923,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1937,7 +1946,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1973,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1987,7 +1996,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2023,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2037,7 +2046,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2073,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2087,7 +2096,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2123,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2137,7 +2146,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2173,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2187,7 +2196,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2223,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2237,7 +2246,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2273,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2287,7 +2296,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2323,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2337,7 +2346,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2373,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2387,7 +2396,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2423,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2473,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2523,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2537,7 +2546,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2573,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2587,7 +2596,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2623,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2637,7 +2646,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2673,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2687,7 +2696,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2723,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2737,7 +2746,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2773,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2787,7 +2796,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2823,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2873,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2887,7 +2896,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2923,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2937,7 +2946,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2973,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -2987,7 +2996,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3023,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3037,7 +3046,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3073,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3087,7 +3096,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3123,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3137,7 +3146,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3173,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3223,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3237,7 +3246,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3273,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3287,7 +3296,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3323,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3337,7 +3346,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3373,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3387,7 +3396,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3423,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3437,7 +3446,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3473,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3487,7 +3496,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3523,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3537,7 +3546,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3573,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3587,7 +3596,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3623,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3637,7 +3646,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3687,7 +3696,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3723,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3737,7 +3746,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3773,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3787,7 +3796,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3823,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3837,7 +3846,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3873,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3887,7 +3896,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3923,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3937,7 +3946,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3973,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -3987,7 +3996,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4023,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4037,7 +4046,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4073,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4087,7 +4096,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4123,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4137,7 +4146,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4173,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4187,7 +4196,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4223,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4237,7 +4246,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4273,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4287,7 +4296,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4323,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4337,7 +4346,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4373,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4387,7 +4396,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4423,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4437,7 +4446,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4473,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4487,7 +4496,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4537,7 +4546,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4587,7 +4596,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4623,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4637,7 +4646,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4673,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4687,7 +4696,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4723,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4737,7 +4746,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4773,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4787,7 +4796,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4823,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4837,7 +4846,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4873,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4887,7 +4896,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4923,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4937,7 +4946,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -4987,7 +4996,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5037,7 +5046,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5073,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5087,7 +5096,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5123,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5137,7 +5146,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5173,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5187,7 +5196,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5223,7 +5232,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5237,7 +5246,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5273,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5287,7 +5296,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5323,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5337,7 +5346,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5373,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5387,7 +5396,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5423,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5437,7 +5446,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5487,7 +5496,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5523,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5537,7 +5546,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5573,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5587,7 +5596,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5623,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5637,7 +5646,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5673,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5687,7 +5696,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5723,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5737,7 +5746,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5773,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5787,7 +5796,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5823,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5837,7 +5846,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5873,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5887,7 +5896,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5923,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5937,7 +5946,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5973,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -5987,7 +5996,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6023,7 +6032,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6037,7 +6046,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6073,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6087,7 +6096,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6123,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6137,7 +6146,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6173,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6187,7 +6196,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6223,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6237,7 +6246,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6273,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6287,7 +6296,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6323,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6337,7 +6346,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6373,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6387,7 +6396,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6423,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6437,7 +6446,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6473,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6487,7 +6496,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6537,7 +6546,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6587,7 +6596,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6637,7 +6646,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6687,7 +6696,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6737,7 +6746,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6773,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6787,7 +6796,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6823,7 +6832,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6837,7 +6846,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6873,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6887,7 +6896,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6923,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6937,7 +6946,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6973,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6987,7 +6996,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7037,7 +7046,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7087,7 +7096,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7137,7 +7146,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7187,7 +7196,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7223,7 +7232,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7237,7 +7246,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7273,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7287,7 +7296,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7323,7 +7332,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7337,7 +7346,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7373,7 +7382,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7387,7 +7396,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7423,7 +7432,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7437,7 +7446,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7473,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7487,7 +7496,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7523,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7537,7 +7546,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7573,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7587,7 +7596,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7623,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7637,7 +7646,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7673,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7687,7 +7696,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7723,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7737,7 +7746,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7773,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7787,7 +7796,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7823,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7837,7 +7846,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7873,7 +7882,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7887,7 +7896,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7923,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7937,7 +7946,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7973,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -7987,7 +7996,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8023,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8037,7 +8046,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8073,7 +8082,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8087,7 +8096,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8123,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8137,7 +8146,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8173,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8187,7 +8196,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8223,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8237,7 +8246,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8273,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8287,7 +8296,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8323,7 +8332,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8337,7 +8346,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8373,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8387,7 +8396,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8423,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8437,7 +8446,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8473,7 +8482,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8487,7 +8496,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8523,7 +8532,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8537,7 +8546,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8573,7 +8582,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8587,7 +8596,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8623,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8637,7 +8646,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8673,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8687,7 +8696,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8723,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8737,7 +8746,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8773,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8787,7 +8796,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8823,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8837,7 +8846,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8873,7 +8882,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8887,7 +8896,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8923,7 +8932,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8937,7 +8946,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8973,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -8987,7 +8996,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9023,7 +9032,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9037,7 +9046,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9073,7 +9082,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9087,7 +9096,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9123,7 +9132,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9137,7 +9146,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9173,7 +9182,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9187,7 +9196,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9223,7 +9232,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9237,7 +9246,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9273,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9287,7 +9296,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9323,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9337,7 +9346,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9373,7 +9382,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9387,7 +9396,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9423,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9437,7 +9446,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9473,7 +9482,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9487,7 +9496,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9523,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9537,7 +9546,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9573,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9587,7 +9596,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9623,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9637,7 +9646,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9673,7 +9682,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9687,7 +9696,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9723,7 +9732,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9737,7 +9746,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9773,7 +9782,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9787,7 +9796,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9823,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9873,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9887,7 +9896,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9923,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9937,7 +9946,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9973,7 +9982,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9987,7 +9996,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10023,7 +10032,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10037,7 +10046,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10073,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10087,7 +10096,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10123,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10137,7 +10146,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10173,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10187,7 +10196,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10223,7 +10232,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10237,7 +10246,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10273,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10287,7 +10296,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10323,7 +10332,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10337,7 +10346,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10373,7 +10382,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10387,7 +10396,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10423,7 +10432,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10437,7 +10446,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10473,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10487,7 +10496,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10523,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10537,7 +10546,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10573,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10587,7 +10596,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10623,7 +10632,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10637,7 +10646,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10673,7 +10682,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10687,7 +10696,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10723,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10737,7 +10746,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10773,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10787,7 +10796,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10823,7 +10832,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10837,7 +10846,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10873,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10887,7 +10896,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10923,7 +10932,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10937,7 +10946,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10973,7 +10982,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10987,7 +10996,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11023,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11037,7 +11046,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11073,7 +11082,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11087,7 +11096,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11123,7 +11132,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11137,7 +11146,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11173,7 +11182,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11187,7 +11196,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11223,7 +11232,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11237,7 +11246,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11273,7 +11282,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11287,7 +11296,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11323,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11337,7 +11346,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11373,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11387,7 +11396,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11423,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11437,7 +11446,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11473,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11487,7 +11496,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11523,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11537,7 +11546,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11573,7 +11582,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11587,7 +11596,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11623,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11637,7 +11646,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11673,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11687,7 +11696,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11723,7 +11732,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11737,7 +11746,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11773,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11787,7 +11796,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11823,7 +11832,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11837,7 +11846,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11887,7 +11896,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11923,7 +11932,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11973,7 +11982,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -11987,7 +11996,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12023,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12037,7 +12046,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12073,7 +12082,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12087,7 +12096,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12123,7 +12132,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12137,7 +12146,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12173,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12223,7 +12232,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12273,7 +12282,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12323,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12373,7 +12382,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12423,7 +12432,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12473,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12487,7 +12496,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12523,7 +12532,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12537,7 +12546,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12573,7 +12582,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12587,7 +12596,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12623,7 +12632,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12637,7 +12646,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12673,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12687,7 +12696,7 @@
         <v>1.074295946695607</v>
       </c>
       <c r="D233" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E233">
         <v>-1.214904981804928</v>
@@ -12723,7 +12732,57 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16">
+      <c r="A234" s="1">
+        <v>0</v>
+      </c>
+      <c r="B234" t="s">
+        <v>73</v>
+      </c>
+      <c r="C234">
+        <v>-5.523389518570603</v>
+      </c>
+      <c r="D234" t="s">
+        <v>134</v>
+      </c>
+      <c r="E234">
+        <v>-7.749202268793276</v>
+      </c>
+      <c r="F234">
+        <v>-1</v>
+      </c>
+      <c r="G234">
+        <v>0.07674338951857061</v>
+      </c>
+      <c r="H234">
+        <v>0.08610920226879328</v>
+      </c>
+      <c r="I234">
+        <v>2.225812750222673</v>
+      </c>
+      <c r="J234">
+        <v>1.12540053402382</v>
+      </c>
+      <c r="K234">
+        <v>36.55</v>
+      </c>
+      <c r="L234">
+        <v>35.61</v>
+      </c>
+      <c r="M234">
+        <v>41.7</v>
+      </c>
+      <c r="N234">
+        <v>39.18</v>
+      </c>
+      <c r="O234">
+        <v>1</v>
+      </c>
+      <c r="P234" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="238">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,181 +232,181 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -1085,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P234"/>
+  <dimension ref="A1:P235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1246,7 +1246,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1296,7 +1296,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1346,7 +1346,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1396,7 +1396,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1546,7 +1546,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1596,7 +1596,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1646,7 +1646,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1696,7 +1696,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1746,7 +1746,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1796,7 +1796,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1846,7 +1846,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1896,7 +1896,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1946,7 +1946,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -1996,7 +1996,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2046,7 +2046,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2096,7 +2096,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2146,7 +2146,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2196,7 +2196,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2246,7 +2246,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2296,7 +2296,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2346,7 +2346,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2396,7 +2396,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2546,7 +2546,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2596,7 +2596,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2646,7 +2646,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2696,7 +2696,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2746,7 +2746,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2796,7 +2796,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2896,7 +2896,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2946,7 +2946,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -2996,7 +2996,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3046,7 +3046,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3096,7 +3096,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3146,7 +3146,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3246,7 +3246,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3296,7 +3296,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3346,7 +3346,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3396,7 +3396,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3446,7 +3446,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3496,7 +3496,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3546,7 +3546,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3596,7 +3596,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3646,7 +3646,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3696,7 +3696,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3746,7 +3746,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3796,7 +3796,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3846,7 +3846,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3896,7 +3896,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3946,7 +3946,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -3996,7 +3996,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4046,7 +4046,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4096,7 +4096,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4146,7 +4146,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4196,7 +4196,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4246,7 +4246,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4296,7 +4296,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4346,7 +4346,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4396,7 +4396,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4446,7 +4446,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4496,7 +4496,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4546,7 +4546,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4596,7 +4596,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4646,7 +4646,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4696,7 +4696,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4746,7 +4746,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4796,7 +4796,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4846,7 +4846,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4896,7 +4896,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4946,7 +4946,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -4996,7 +4996,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5046,7 +5046,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5096,7 +5096,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5146,7 +5146,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5196,7 +5196,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5246,7 +5246,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5296,7 +5296,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5346,7 +5346,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5396,7 +5396,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5446,7 +5446,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5496,7 +5496,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5546,7 +5546,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5596,7 +5596,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5646,7 +5646,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5696,7 +5696,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5746,7 +5746,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5796,7 +5796,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5846,7 +5846,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5896,7 +5896,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5946,7 +5946,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -5996,7 +5996,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6046,7 +6046,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6096,7 +6096,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6146,7 +6146,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6196,7 +6196,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6246,7 +6246,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6296,7 +6296,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6346,7 +6346,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6396,7 +6396,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6446,7 +6446,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6496,7 +6496,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6546,7 +6546,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6596,7 +6596,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6646,7 +6646,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6696,7 +6696,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6746,7 +6746,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6796,7 +6796,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6846,7 +6846,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6896,7 +6896,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6946,7 +6946,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -6996,7 +6996,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7046,7 +7046,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7096,7 +7096,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7146,7 +7146,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7196,7 +7196,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7246,7 +7246,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7296,7 +7296,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7346,7 +7346,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7396,7 +7396,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7446,7 +7446,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7496,7 +7496,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7546,7 +7546,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7596,7 +7596,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7632,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7646,7 +7646,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7682,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7696,7 +7696,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7732,7 +7732,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7746,7 +7746,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7796,7 +7796,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7846,7 +7846,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7896,7 +7896,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7946,7 +7946,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -7996,7 +7996,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8046,7 +8046,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8096,7 +8096,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8146,7 +8146,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8196,7 +8196,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8246,7 +8246,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8296,7 +8296,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8346,7 +8346,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8396,7 +8396,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8446,7 +8446,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8496,7 +8496,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8546,7 +8546,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8596,7 +8596,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8646,7 +8646,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8696,7 +8696,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8746,7 +8746,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8796,7 +8796,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8846,7 +8846,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8896,7 +8896,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8946,7 +8946,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -8996,7 +8996,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9046,7 +9046,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9096,7 +9096,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9146,7 +9146,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9196,7 +9196,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9246,7 +9246,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9296,7 +9296,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9346,7 +9346,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9396,7 +9396,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9446,7 +9446,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9496,7 +9496,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9546,7 +9546,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9596,7 +9596,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9646,7 +9646,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9696,7 +9696,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9746,7 +9746,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9796,7 +9796,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9896,7 +9896,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9946,7 +9946,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -9996,7 +9996,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10046,7 +10046,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10082,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10096,7 +10096,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10132,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10146,7 +10146,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10182,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10196,7 +10196,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10232,7 +10232,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10246,7 +10246,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10282,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10296,7 +10296,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10332,7 +10332,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10346,7 +10346,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10382,7 +10382,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10396,7 +10396,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10432,7 +10432,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10446,7 +10446,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10482,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10496,7 +10496,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10532,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10546,7 +10546,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10596,7 +10596,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10646,7 +10646,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10696,7 +10696,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10746,7 +10746,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10796,7 +10796,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10846,7 +10846,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10896,7 +10896,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10946,7 +10946,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -10996,7 +10996,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11046,7 +11046,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11096,7 +11096,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11146,7 +11146,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11196,7 +11196,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11246,7 +11246,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11296,7 +11296,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11346,7 +11346,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11396,7 +11396,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11446,7 +11446,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11496,7 +11496,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11546,7 +11546,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11596,7 +11596,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11646,7 +11646,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11696,7 +11696,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11746,7 +11746,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11796,7 +11796,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11846,7 +11846,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11896,7 +11896,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11996,7 +11996,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12046,7 +12046,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12096,7 +12096,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12146,7 +12146,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12246,7 +12246,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12282,7 +12282,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12296,7 +12296,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12332,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12346,7 +12346,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12382,7 +12382,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12532,7 +12532,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12582,7 +12582,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12690,10 +12690,10 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C233">
-        <v>1.074295946695607</v>
+        <v>0.9864268040275093</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
@@ -12705,22 +12705,22 @@
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.0773657040533044</v>
+        <v>0.0780735731959725</v>
       </c>
       <c r="H233">
         <v>0.07537490498180492</v>
       </c>
       <c r="I233">
-        <v>2.289200928500534</v>
+        <v>2.201331785832437</v>
       </c>
       <c r="J233">
         <v>0.9946728566702578</v>
       </c>
       <c r="K233">
-        <v>38.35</v>
+        <v>38.75</v>
       </c>
       <c r="L233">
-        <v>39.22</v>
+        <v>39.53</v>
       </c>
       <c r="M233">
         <v>38.5</v>
@@ -12732,7 +12732,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12740,31 +12740,31 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C234">
-        <v>-5.523389518570603</v>
+        <v>-5.123690195894106</v>
       </c>
       <c r="D234" t="s">
         <v>134</v>
       </c>
       <c r="E234">
-        <v>-7.749202268793276</v>
+        <v>-7.293184163304637</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07674338951857061</v>
+        <v>0.07634369019589411</v>
       </c>
       <c r="H234">
-        <v>0.08610920226879328</v>
+        <v>0.08565318416330464</v>
       </c>
       <c r="I234">
-        <v>2.225812750222673</v>
+        <v>2.169493967410531</v>
       </c>
       <c r="J234">
-        <v>1.12540053402382</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K234">
         <v>36.55</v>
@@ -12782,6 +12782,56 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" s="1">
+        <v>0</v>
+      </c>
+      <c r="B235" t="s">
+        <v>72</v>
+      </c>
+      <c r="C235">
+        <v>-5.523389518570603</v>
+      </c>
+      <c r="D235" t="s">
+        <v>134</v>
+      </c>
+      <c r="E235">
+        <v>-7.749202268793276</v>
+      </c>
+      <c r="F235">
+        <v>-1</v>
+      </c>
+      <c r="G235">
+        <v>0.07674338951857061</v>
+      </c>
+      <c r="H235">
+        <v>0.08610920226879328</v>
+      </c>
+      <c r="I235">
+        <v>2.225812750222673</v>
+      </c>
+      <c r="J235">
+        <v>1.12540053402382</v>
+      </c>
+      <c r="K235">
+        <v>36.55</v>
+      </c>
+      <c r="L235">
+        <v>35.61</v>
+      </c>
+      <c r="M235">
+        <v>41.7</v>
+      </c>
+      <c r="N235">
+        <v>39.18</v>
+      </c>
+      <c r="O235">
+        <v>1</v>
+      </c>
+      <c r="P235" t="s">
         <v>237</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="238">
   <si>
     <t>trade_time</t>
   </si>
@@ -415,316 +415,316 @@
     <t>2021-07-14</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
     <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
   </si>
   <si>
     <t>2021-07-27</t>
@@ -1085,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P235"/>
+  <dimension ref="A1:P234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1232,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1332,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1482,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1532,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1582,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1732,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1782,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1832,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1932,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1982,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2032,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2132,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2182,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2282,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2332,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2382,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2432,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2482,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2532,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2632,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2732,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2782,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2932,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2982,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3032,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3082,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3132,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3282,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3382,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3432,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3532,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3582,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3632,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3732,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3782,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3832,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3932,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3982,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4032,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4082,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4132,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4182,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4232,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4282,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4332,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4382,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4432,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4482,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4632,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4682,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4732,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4782,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4832,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4882,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4932,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5082,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5132,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5182,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5232,7 +5232,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5282,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5332,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5382,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5532,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5582,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5682,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5732,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5832,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5882,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5932,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5982,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6032,7 +6032,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6082,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6132,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6232,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6282,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6332,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6382,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6432,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6482,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6782,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6832,7 +6832,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6882,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6932,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6982,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7232,7 +7232,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7282,7 +7282,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7332,7 +7332,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7382,7 +7382,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7432,7 +7432,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7482,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7532,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7582,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7782,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7832,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7882,7 +7882,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7932,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7982,7 +7982,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8032,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8082,7 +8082,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8132,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8182,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8232,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8282,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8332,7 +8332,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8382,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8482,7 +8482,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8532,7 +8532,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8582,7 +8582,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8632,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8682,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8732,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8782,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8882,7 +8882,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8932,7 +8932,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8982,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9032,7 +9032,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9082,7 +9082,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9132,7 +9132,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9182,7 +9182,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9232,7 +9232,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9282,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9382,7 +9382,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9432,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9482,7 +9482,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9532,7 +9532,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9582,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9632,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9682,7 +9682,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9732,7 +9732,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9782,7 +9782,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9832,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9882,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9932,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9982,7 +9982,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10032,7 +10032,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10582,7 +10582,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10632,7 +10632,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10682,7 +10682,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10732,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10782,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10832,7 +10832,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10882,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10932,7 +10932,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10982,7 +10982,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11032,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11082,7 +11082,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11132,7 +11132,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11182,7 +11182,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11232,7 +11232,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11282,7 +11282,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11332,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11382,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11432,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11532,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11582,7 +11582,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11632,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11682,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11732,7 +11732,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11782,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11832,7 +11832,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11932,7 +11932,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -11982,7 +11982,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12082,7 +12082,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12132,7 +12132,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12182,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12232,7 +12232,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12432,7 +12432,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12482,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12632,7 +12632,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12682,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12690,49 +12690,49 @@
         <v>0</v>
       </c>
       <c r="B233" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C233">
-        <v>0.9864268040275093</v>
+        <v>-5.123690195894106</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
       </c>
       <c r="E233">
-        <v>-1.214904981804928</v>
+        <v>-7.293184163304637</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.0780735731959725</v>
+        <v>0.07634369019589411</v>
       </c>
       <c r="H233">
-        <v>0.07537490498180492</v>
+        <v>0.08565318416330464</v>
       </c>
       <c r="I233">
-        <v>2.201331785832437</v>
+        <v>2.169493967410531</v>
       </c>
       <c r="J233">
-        <v>0.9946728566702578</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K233">
-        <v>38.75</v>
+        <v>36.55</v>
       </c>
       <c r="L233">
-        <v>39.53</v>
+        <v>35.61</v>
       </c>
       <c r="M233">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="N233">
-        <v>37.08</v>
+        <v>39.18</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12743,28 +12743,28 @@
         <v>72</v>
       </c>
       <c r="C234">
-        <v>-5.123690195894106</v>
+        <v>-5.523389518570603</v>
       </c>
       <c r="D234" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E234">
-        <v>-7.293184163304637</v>
+        <v>-7.749202268793276</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07634369019589411</v>
+        <v>0.07674338951857061</v>
       </c>
       <c r="H234">
-        <v>0.08565318416330464</v>
+        <v>0.08610920226879328</v>
       </c>
       <c r="I234">
-        <v>2.169493967410531</v>
+        <v>2.225812750222673</v>
       </c>
       <c r="J234">
-        <v>1.114464848040879</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K234">
         <v>36.55</v>
@@ -12782,56 +12782,6 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16">
-      <c r="A235" s="1">
-        <v>0</v>
-      </c>
-      <c r="B235" t="s">
-        <v>72</v>
-      </c>
-      <c r="C235">
-        <v>-5.523389518570603</v>
-      </c>
-      <c r="D235" t="s">
-        <v>134</v>
-      </c>
-      <c r="E235">
-        <v>-7.749202268793276</v>
-      </c>
-      <c r="F235">
-        <v>-1</v>
-      </c>
-      <c r="G235">
-        <v>0.07674338951857061</v>
-      </c>
-      <c r="H235">
-        <v>0.08610920226879328</v>
-      </c>
-      <c r="I235">
-        <v>2.225812750222673</v>
-      </c>
-      <c r="J235">
-        <v>1.12540053402382</v>
-      </c>
-      <c r="K235">
-        <v>36.55</v>
-      </c>
-      <c r="L235">
-        <v>35.61</v>
-      </c>
-      <c r="M235">
-        <v>41.7</v>
-      </c>
-      <c r="N235">
-        <v>39.18</v>
-      </c>
-      <c r="O235">
-        <v>1</v>
-      </c>
-      <c r="P235" t="s">
         <v>237</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="249">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,502 +232,535 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-14</t>
+  </si>
+  <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
     <t>2021-07-28</t>
   </si>
   <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-07-14</t>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
   </si>
   <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-08-05</t>
+  </si>
+  <si>
+    <t>2021-08-06</t>
+  </si>
+  <si>
+    <t>2021-08-09</t>
+  </si>
+  <si>
+    <t>2021-08-10</t>
+  </si>
+  <si>
+    <t>2021-08-11</t>
+  </si>
+  <si>
+    <t>2021-08-13</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P234"/>
+  <dimension ref="A1:P245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -12693,40 +12726,40 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>-5.123690195894106</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
       </c>
       <c r="E233">
-        <v>-7.293184163304637</v>
+        <v>-6.02337225374756</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07634369019589411</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H233">
-        <v>0.08565318416330464</v>
+        <v>0.08926337225374754</v>
       </c>
       <c r="I233">
-        <v>2.169493967410531</v>
+        <v>1.087232424020442</v>
       </c>
       <c r="J233">
         <v>1.114464848040879</v>
       </c>
       <c r="K233">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L233">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M233">
-        <v>41.7</v>
+        <v>42.75</v>
       </c>
       <c r="N233">
-        <v>39.18</v>
+        <v>41.62</v>
       </c>
       <c r="O233">
         <v>1</v>
@@ -12743,46 +12776,596 @@
         <v>72</v>
       </c>
       <c r="C234">
-        <v>-5.523389518570603</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D234" t="s">
         <v>133</v>
       </c>
       <c r="E234">
-        <v>-7.749202268793276</v>
+        <v>-6.963974342393676</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07674338951857061</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H234">
-        <v>0.08610920226879328</v>
+        <v>0.09020397434239368</v>
       </c>
       <c r="I234">
-        <v>2.225812750222673</v>
+        <v>1.098233618039693</v>
       </c>
       <c r="J234">
-        <v>1.12540053402382</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K234">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L234">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M234">
-        <v>41.7</v>
+        <v>42.75</v>
       </c>
       <c r="N234">
-        <v>39.18</v>
+        <v>41.62</v>
       </c>
       <c r="O234">
         <v>1</v>
       </c>
       <c r="P234" t="s">
         <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16">
+      <c r="A235" s="1">
+        <v>0</v>
+      </c>
+      <c r="B235" t="s">
+        <v>72</v>
+      </c>
+      <c r="C235">
+        <v>-6.356723940668068</v>
+      </c>
+      <c r="D235" t="s">
+        <v>133</v>
+      </c>
+      <c r="E235">
+        <v>-7.46076801097184</v>
+      </c>
+      <c r="F235">
+        <v>-1</v>
+      </c>
+      <c r="G235">
+        <v>0.09065672394066807</v>
+      </c>
+      <c r="H235">
+        <v>0.09070076801097185</v>
+      </c>
+      <c r="I235">
+        <v>1.104044070303772</v>
+      </c>
+      <c r="J235">
+        <v>1.148088140607528</v>
+      </c>
+      <c r="K235">
+        <v>42.25</v>
+      </c>
+      <c r="L235">
+        <v>42.15</v>
+      </c>
+      <c r="M235">
+        <v>42.75</v>
+      </c>
+      <c r="N235">
+        <v>41.62</v>
+      </c>
+      <c r="O235">
+        <v>1</v>
+      </c>
+      <c r="P235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16">
+      <c r="A236" s="1">
+        <v>0</v>
+      </c>
+      <c r="B236" t="s">
+        <v>72</v>
+      </c>
+      <c r="C236">
+        <v>-6.77136034625692</v>
+      </c>
+      <c r="D236" t="s">
+        <v>133</v>
+      </c>
+      <c r="E236">
+        <v>-7.880311356271797</v>
+      </c>
+      <c r="F236">
+        <v>-1</v>
+      </c>
+      <c r="G236">
+        <v>0.09107136034625692</v>
+      </c>
+      <c r="H236">
+        <v>0.0911203113562718</v>
+      </c>
+      <c r="I236">
+        <v>1.108951010014877</v>
+      </c>
+      <c r="J236">
+        <v>1.15790202002975</v>
+      </c>
+      <c r="K236">
+        <v>42.25</v>
+      </c>
+      <c r="L236">
+        <v>42.15</v>
+      </c>
+      <c r="M236">
+        <v>42.75</v>
+      </c>
+      <c r="N236">
+        <v>41.62</v>
+      </c>
+      <c r="O236">
+        <v>1</v>
+      </c>
+      <c r="P236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16">
+      <c r="A237" s="1">
+        <v>0</v>
+      </c>
+      <c r="B237" t="s">
+        <v>72</v>
+      </c>
+      <c r="C237">
+        <v>-7.112794598132552</v>
+      </c>
+      <c r="D237" t="s">
+        <v>133</v>
+      </c>
+      <c r="E237">
+        <v>-8.225786250181457</v>
+      </c>
+      <c r="F237">
+        <v>-1</v>
+      </c>
+      <c r="G237">
+        <v>0.09141279459813255</v>
+      </c>
+      <c r="H237">
+        <v>0.09146578625018145</v>
+      </c>
+      <c r="I237">
+        <v>1.112991652048905</v>
+      </c>
+      <c r="J237">
+        <v>1.165983304097812</v>
+      </c>
+      <c r="K237">
+        <v>42.25</v>
+      </c>
+      <c r="L237">
+        <v>42.15</v>
+      </c>
+      <c r="M237">
+        <v>42.75</v>
+      </c>
+      <c r="N237">
+        <v>41.62</v>
+      </c>
+      <c r="O237">
+        <v>1</v>
+      </c>
+      <c r="P237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16">
+      <c r="A238" s="1">
+        <v>0</v>
+      </c>
+      <c r="B238" t="s">
+        <v>72</v>
+      </c>
+      <c r="C238">
+        <v>-7.379527992135429</v>
+      </c>
+      <c r="D238" t="s">
+        <v>133</v>
+      </c>
+      <c r="E238">
+        <v>-8.495676252397395</v>
+      </c>
+      <c r="F238">
+        <v>-1</v>
+      </c>
+      <c r="G238">
+        <v>0.09167952799213544</v>
+      </c>
+      <c r="H238">
+        <v>0.09173567625239738</v>
+      </c>
+      <c r="I238">
+        <v>1.116148260261966</v>
+      </c>
+      <c r="J238">
+        <v>1.172296520523916</v>
+      </c>
+      <c r="K238">
+        <v>42.25</v>
+      </c>
+      <c r="L238">
+        <v>42.15</v>
+      </c>
+      <c r="M238">
+        <v>42.75</v>
+      </c>
+      <c r="N238">
+        <v>41.62</v>
+      </c>
+      <c r="O238">
+        <v>1</v>
+      </c>
+      <c r="P238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16">
+      <c r="A239" s="1">
+        <v>0</v>
+      </c>
+      <c r="B239" t="s">
+        <v>72</v>
+      </c>
+      <c r="C239">
+        <v>-7.702700683679339</v>
+      </c>
+      <c r="D239" t="s">
+        <v>133</v>
+      </c>
+      <c r="E239">
+        <v>-8.822673472835312</v>
+      </c>
+      <c r="F239">
+        <v>-1</v>
+      </c>
+      <c r="G239">
+        <v>0.09200270068367934</v>
+      </c>
+      <c r="H239">
+        <v>0.09206267347283531</v>
+      </c>
+      <c r="I239">
+        <v>1.119972789155973</v>
+      </c>
+      <c r="J239">
+        <v>1.179945578311937</v>
+      </c>
+      <c r="K239">
+        <v>42.25</v>
+      </c>
+      <c r="L239">
+        <v>42.15</v>
+      </c>
+      <c r="M239">
+        <v>42.75</v>
+      </c>
+      <c r="N239">
+        <v>41.62</v>
+      </c>
+      <c r="O239">
+        <v>1</v>
+      </c>
+      <c r="P239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16">
+      <c r="A240" s="1">
+        <v>0</v>
+      </c>
+      <c r="B240" t="s">
+        <v>72</v>
+      </c>
+      <c r="C240">
+        <v>-8.001107320444035</v>
+      </c>
+      <c r="D240" t="s">
+        <v>133</v>
+      </c>
+      <c r="E240">
+        <v>-9.124611549088343</v>
+      </c>
+      <c r="F240">
+        <v>-1</v>
+      </c>
+      <c r="G240">
+        <v>0.09230110732044404</v>
+      </c>
+      <c r="H240">
+        <v>0.09236461154908834</v>
+      </c>
+      <c r="I240">
+        <v>1.123504228644308</v>
+      </c>
+      <c r="J240">
+        <v>1.187008457288616</v>
+      </c>
+      <c r="K240">
+        <v>42.25</v>
+      </c>
+      <c r="L240">
+        <v>42.15</v>
+      </c>
+      <c r="M240">
+        <v>42.75</v>
+      </c>
+      <c r="N240">
+        <v>41.62</v>
+      </c>
+      <c r="O240">
+        <v>1</v>
+      </c>
+      <c r="P240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16">
+      <c r="A241" s="1">
+        <v>0</v>
+      </c>
+      <c r="B241" t="s">
+        <v>72</v>
+      </c>
+      <c r="C241">
+        <v>-8.280300561754309</v>
+      </c>
+      <c r="D241" t="s">
+        <v>133</v>
+      </c>
+      <c r="E241">
+        <v>-9.407108852425964</v>
+      </c>
+      <c r="F241">
+        <v>-1</v>
+      </c>
+      <c r="G241">
+        <v>0.09258030056175431</v>
+      </c>
+      <c r="H241">
+        <v>0.09264710885242596</v>
+      </c>
+      <c r="I241">
+        <v>1.126808290671654</v>
+      </c>
+      <c r="J241">
+        <v>1.193616581343297</v>
+      </c>
+      <c r="K241">
+        <v>42.25</v>
+      </c>
+      <c r="L241">
+        <v>42.15</v>
+      </c>
+      <c r="M241">
+        <v>42.75</v>
+      </c>
+      <c r="N241">
+        <v>41.62</v>
+      </c>
+      <c r="O241">
+        <v>1</v>
+      </c>
+      <c r="P241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16">
+      <c r="A242" s="1">
+        <v>0</v>
+      </c>
+      <c r="B242" t="s">
+        <v>72</v>
+      </c>
+      <c r="C242">
+        <v>-8.625026882373376</v>
+      </c>
+      <c r="D242" t="s">
+        <v>133</v>
+      </c>
+      <c r="E242">
+        <v>-9.755914774472473</v>
+      </c>
+      <c r="F242">
+        <v>-1</v>
+      </c>
+      <c r="G242">
+        <v>0.09292502688237338</v>
+      </c>
+      <c r="H242">
+        <v>0.09299591477447247</v>
+      </c>
+      <c r="I242">
+        <v>1.130887892099096</v>
+      </c>
+      <c r="J242">
+        <v>1.201775784198186</v>
+      </c>
+      <c r="K242">
+        <v>42.25</v>
+      </c>
+      <c r="L242">
+        <v>42.15</v>
+      </c>
+      <c r="M242">
+        <v>42.75</v>
+      </c>
+      <c r="N242">
+        <v>41.62</v>
+      </c>
+      <c r="O242">
+        <v>1</v>
+      </c>
+      <c r="P242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16">
+      <c r="A243" s="1">
+        <v>0</v>
+      </c>
+      <c r="B243" t="s">
+        <v>72</v>
+      </c>
+      <c r="C243">
+        <v>-8.846388689296894</v>
+      </c>
+      <c r="D243" t="s">
+        <v>133</v>
+      </c>
+      <c r="E243">
+        <v>-9.979896247750112</v>
+      </c>
+      <c r="F243">
+        <v>-1</v>
+      </c>
+      <c r="G243">
+        <v>0.09314638868929688</v>
+      </c>
+      <c r="H243">
+        <v>0.09321989624775012</v>
+      </c>
+      <c r="I243">
+        <v>1.133507558453218</v>
+      </c>
+      <c r="J243">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K243">
+        <v>42.25</v>
+      </c>
+      <c r="L243">
+        <v>42.15</v>
+      </c>
+      <c r="M243">
+        <v>42.75</v>
+      </c>
+      <c r="N243">
+        <v>41.62</v>
+      </c>
+      <c r="O243">
+        <v>1</v>
+      </c>
+      <c r="P243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16">
+      <c r="A244" s="1">
+        <v>0</v>
+      </c>
+      <c r="B244" t="s">
+        <v>72</v>
+      </c>
+      <c r="C244">
+        <v>-9.123967366600709</v>
+      </c>
+      <c r="D244" t="s">
+        <v>133</v>
+      </c>
+      <c r="E244">
+        <v>-10.26075987981492</v>
+      </c>
+      <c r="F244">
+        <v>-1</v>
+      </c>
+      <c r="G244">
+        <v>0.0934239673666007</v>
+      </c>
+      <c r="H244">
+        <v>0.09350075987981492</v>
+      </c>
+      <c r="I244">
+        <v>1.13679251321421</v>
+      </c>
+      <c r="J244">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K244">
+        <v>42.25</v>
+      </c>
+      <c r="L244">
+        <v>42.15</v>
+      </c>
+      <c r="M244">
+        <v>42.75</v>
+      </c>
+      <c r="N244">
+        <v>41.62</v>
+      </c>
+      <c r="O244">
+        <v>1</v>
+      </c>
+      <c r="P244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16">
+      <c r="A245" s="1">
+        <v>0</v>
+      </c>
+      <c r="B245" t="s">
+        <v>72</v>
+      </c>
+      <c r="C245">
+        <v>-9.62255528559681</v>
+      </c>
+      <c r="D245" t="s">
+        <v>133</v>
+      </c>
+      <c r="E245">
+        <v>-10.76524824755653</v>
+      </c>
+      <c r="F245">
+        <v>-1</v>
+      </c>
+      <c r="G245">
+        <v>0.09392255528559681</v>
+      </c>
+      <c r="H245">
+        <v>0.09400524824755653</v>
+      </c>
+      <c r="I245">
+        <v>1.142692961959725</v>
+      </c>
+      <c r="J245">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K245">
+        <v>42.25</v>
+      </c>
+      <c r="L245">
+        <v>42.15</v>
+      </c>
+      <c r="M245">
+        <v>42.75</v>
+      </c>
+      <c r="N245">
+        <v>41.62</v>
+      </c>
+      <c r="O245">
+        <v>1</v>
+      </c>
+      <c r="P245" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="252">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,6 +232,9 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2021-08-20</t>
   </si>
   <si>
@@ -406,16 +409,16 @@
     <t>2021-07-07</t>
   </si>
   <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -724,7 +727,10 @@
     <t>2021-02-05</t>
   </si>
   <si>
-    <t>2021-07-26</t>
+    <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2021-07-28</t>
@@ -761,6 +767,9 @@
   </si>
   <si>
     <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-16</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P245"/>
+  <dimension ref="A1:P249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1215,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1265,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1279,7 +1288,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1315,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1329,7 +1338,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1365,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1379,7 +1388,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1415,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1429,7 +1438,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1465,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1515,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1565,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1579,7 +1588,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1615,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1629,7 +1638,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1665,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1679,7 +1688,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1715,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1729,7 +1738,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1765,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1779,7 +1788,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1815,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1829,7 +1838,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1865,7 +1874,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1879,7 +1888,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1915,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1929,7 +1938,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1965,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1979,7 +1988,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2015,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2029,7 +2038,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2065,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2079,7 +2088,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2115,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2129,7 +2138,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2165,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2179,7 +2188,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2215,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2229,7 +2238,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2265,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2279,7 +2288,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2315,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2329,7 +2338,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2365,7 +2374,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2379,7 +2388,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2415,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2429,7 +2438,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2465,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2515,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2565,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2579,7 +2588,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2615,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2629,7 +2638,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2665,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2679,7 +2688,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2715,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2729,7 +2738,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2765,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2779,7 +2788,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2815,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2829,7 +2838,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2865,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2915,7 +2924,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2929,7 +2938,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2965,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -2979,7 +2988,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3015,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3029,7 +3038,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3065,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3079,7 +3088,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3115,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3129,7 +3138,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3165,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3179,7 +3188,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3215,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3265,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3279,7 +3288,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3315,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3329,7 +3338,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3365,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3379,7 +3388,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3415,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3429,7 +3438,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3465,7 +3474,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3479,7 +3488,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3515,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3529,7 +3538,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3565,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3579,7 +3588,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3615,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3629,7 +3638,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3665,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3679,7 +3688,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3729,7 +3738,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3765,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3779,7 +3788,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3815,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3829,7 +3838,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3865,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3879,7 +3888,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3915,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3929,7 +3938,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3965,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -3979,7 +3988,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4015,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4029,7 +4038,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4065,7 +4074,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4079,7 +4088,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4115,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4129,7 +4138,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4165,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4179,7 +4188,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4215,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4229,7 +4238,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4265,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4279,7 +4288,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4315,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4329,7 +4338,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4365,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4379,7 +4388,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4415,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4429,7 +4438,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4465,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4479,7 +4488,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4515,7 +4524,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4529,7 +4538,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4579,7 +4588,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4629,7 +4638,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4665,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4679,7 +4688,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4715,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4729,7 +4738,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4765,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4779,7 +4788,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4815,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4829,7 +4838,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4865,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4879,7 +4888,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4915,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4929,7 +4938,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4965,7 +4974,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -4979,7 +4988,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5029,7 +5038,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5079,7 +5088,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5115,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5129,7 +5138,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5165,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5179,7 +5188,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5215,7 +5224,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5229,7 +5238,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5265,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5279,7 +5288,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5315,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5329,7 +5338,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5365,7 +5374,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5379,7 +5388,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5415,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5429,7 +5438,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5465,7 +5474,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5479,7 +5488,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5529,7 +5538,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5565,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5579,7 +5588,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5615,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5629,7 +5638,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5665,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5679,7 +5688,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5715,7 +5724,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5729,7 +5738,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5765,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5779,7 +5788,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5815,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5829,7 +5838,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5865,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5879,7 +5888,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5915,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5929,7 +5938,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5965,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -5979,7 +5988,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6015,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6029,7 +6038,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6065,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6079,7 +6088,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6115,7 +6124,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6129,7 +6138,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6165,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6179,7 +6188,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6215,7 +6224,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6229,7 +6238,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6265,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6279,7 +6288,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6315,7 +6324,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6329,7 +6338,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6365,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6379,7 +6388,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6415,7 +6424,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6429,7 +6438,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6465,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6479,7 +6488,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6515,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6529,7 +6538,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6579,7 +6588,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6629,7 +6638,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6679,7 +6688,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6729,7 +6738,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6779,7 +6788,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6815,7 +6824,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6829,7 +6838,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6865,7 +6874,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6879,7 +6888,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6915,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6929,7 +6938,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6965,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6979,7 +6988,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7015,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7029,7 +7038,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7079,7 +7088,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7129,7 +7138,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7179,7 +7188,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7229,7 +7238,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7265,7 +7274,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7279,7 +7288,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7315,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7329,7 +7338,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7365,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7379,7 +7388,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7415,7 +7424,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7429,7 +7438,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7465,7 +7474,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7479,7 +7488,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7515,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7529,7 +7538,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7565,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7579,7 +7588,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7615,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7629,7 +7638,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7665,7 +7674,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7679,7 +7688,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7715,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7729,7 +7738,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7765,7 +7774,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7779,7 +7788,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7815,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7829,7 +7838,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7865,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7879,7 +7888,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7915,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7929,7 +7938,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7965,7 +7974,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -7979,7 +7988,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8015,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8029,7 +8038,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8065,7 +8074,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8079,7 +8088,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8115,7 +8124,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8129,7 +8138,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8165,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8179,7 +8188,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8215,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8229,7 +8238,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8265,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8279,7 +8288,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8315,7 +8324,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8329,7 +8338,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8365,7 +8374,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8379,7 +8388,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8415,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8429,7 +8438,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8465,7 +8474,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8479,7 +8488,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8515,7 +8524,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8529,7 +8538,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8565,7 +8574,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8579,7 +8588,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8615,7 +8624,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8629,7 +8638,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8665,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8679,7 +8688,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8715,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8729,7 +8738,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8765,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8779,7 +8788,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8815,7 +8824,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8829,7 +8838,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8865,7 +8874,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8879,7 +8888,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8915,7 +8924,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8929,7 +8938,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8965,7 +8974,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -8979,7 +8988,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9015,7 +9024,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9029,7 +9038,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9065,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9079,7 +9088,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9115,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9129,7 +9138,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9165,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9179,7 +9188,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9215,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9229,7 +9238,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9265,7 +9274,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9279,7 +9288,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9315,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9329,7 +9338,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9365,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9379,7 +9388,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9415,7 +9424,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9429,7 +9438,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9465,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9479,7 +9488,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9515,7 +9524,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9529,7 +9538,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9565,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9579,7 +9588,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9615,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9629,7 +9638,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9665,7 +9674,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9679,7 +9688,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9715,7 +9724,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9729,7 +9738,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9765,7 +9774,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9779,7 +9788,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9815,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9829,7 +9838,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9865,7 +9874,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9915,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9929,7 +9938,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9965,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9979,7 +9988,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10015,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10029,7 +10038,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10065,7 +10074,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10079,7 +10088,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10115,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10129,7 +10138,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10165,7 +10174,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10179,7 +10188,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10215,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10229,7 +10238,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10265,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10279,7 +10288,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10315,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10329,7 +10338,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10365,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10379,7 +10388,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10415,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10429,7 +10438,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10465,7 +10474,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10479,7 +10488,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10515,7 +10524,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10529,7 +10538,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10565,7 +10574,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10579,7 +10588,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10615,7 +10624,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10629,7 +10638,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10665,7 +10674,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10679,7 +10688,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10715,7 +10724,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10729,7 +10738,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10765,7 +10774,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10779,7 +10788,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10815,7 +10824,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10829,7 +10838,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10865,7 +10874,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10879,7 +10888,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10915,7 +10924,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10929,7 +10938,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10965,7 +10974,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10979,7 +10988,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11015,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11029,7 +11038,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11065,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11079,7 +11088,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11115,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11129,7 +11138,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11165,7 +11174,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11179,7 +11188,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11215,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11229,7 +11238,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11265,7 +11274,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11279,7 +11288,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11315,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11329,7 +11338,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11365,7 +11374,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11379,7 +11388,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11415,7 +11424,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11429,7 +11438,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11465,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11479,7 +11488,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11515,7 +11524,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11529,7 +11538,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11565,7 +11574,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11579,7 +11588,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11615,7 +11624,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11629,7 +11638,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11665,7 +11674,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11679,7 +11688,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11715,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11729,7 +11738,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11765,7 +11774,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11779,7 +11788,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11815,7 +11824,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11829,7 +11838,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11865,7 +11874,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11879,7 +11888,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11929,7 +11938,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11965,7 +11974,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12015,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12029,7 +12038,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12065,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12079,7 +12088,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12115,7 +12124,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12129,7 +12138,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12165,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12179,7 +12188,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12215,7 +12224,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12265,7 +12274,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12279,7 +12288,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12315,7 +12324,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12329,7 +12338,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12365,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12379,7 +12388,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12415,7 +12424,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12465,7 +12474,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12515,7 +12524,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12565,7 +12574,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12615,7 +12624,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12665,7 +12674,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12715,7 +12724,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12726,46 +12735,46 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>-4.936139829727118</v>
+        <v>1.750223976867943</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
       </c>
       <c r="E233">
-        <v>-6.02337225374756</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.08923613982972711</v>
+        <v>0.07668977602313205</v>
       </c>
       <c r="H233">
-        <v>0.08926337225374754</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I233">
-        <v>1.087232424020442</v>
+        <v>2.286557142202597</v>
       </c>
       <c r="J233">
-        <v>1.114464848040879</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K233">
-        <v>42.25</v>
+        <v>38.35</v>
       </c>
       <c r="L233">
-        <v>42.15</v>
+        <v>39.22</v>
       </c>
       <c r="M233">
-        <v>42.75</v>
+        <v>38.5</v>
       </c>
       <c r="N233">
-        <v>41.62</v>
+        <v>37.08</v>
       </c>
       <c r="O233">
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12776,40 +12785,40 @@
         <v>72</v>
       </c>
       <c r="C234">
-        <v>-5.865740724353984</v>
+        <v>1.316205734022681</v>
       </c>
       <c r="D234" t="s">
         <v>133</v>
       </c>
       <c r="E234">
-        <v>-6.963974342393676</v>
+        <v>-0.9720490023501114</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.09016574072435399</v>
+        <v>0.07712379426597732</v>
       </c>
       <c r="H234">
-        <v>0.09020397434239368</v>
+        <v>0.0751320490023501</v>
       </c>
       <c r="I234">
-        <v>1.098233618039693</v>
+        <v>2.288254736372792</v>
       </c>
       <c r="J234">
-        <v>1.136467236079384</v>
+        <v>0.988364909151951</v>
       </c>
       <c r="K234">
-        <v>42.25</v>
+        <v>38.35</v>
       </c>
       <c r="L234">
-        <v>42.15</v>
+        <v>39.22</v>
       </c>
       <c r="M234">
-        <v>42.75</v>
+        <v>38.5</v>
       </c>
       <c r="N234">
-        <v>41.62</v>
+        <v>37.08</v>
       </c>
       <c r="O234">
         <v>1</v>
@@ -12823,31 +12832,31 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C235">
-        <v>-6.356723940668068</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D235" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E235">
-        <v>-7.46076801097184</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.09065672394066807</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H235">
-        <v>0.09070076801097185</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I235">
-        <v>1.104044070303772</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J235">
-        <v>1.148088140607528</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K235">
         <v>42.25</v>
@@ -12856,16 +12865,16 @@
         <v>42.15</v>
       </c>
       <c r="M235">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N235">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O235">
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>238</v>
+        <v>133</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12873,31 +12882,31 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C236">
-        <v>-6.77136034625692</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D236" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E236">
-        <v>-7.880311356271797</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.09107136034625692</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H236">
-        <v>0.0911203113562718</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I236">
-        <v>1.108951010014877</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J236">
-        <v>1.15790202002975</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K236">
         <v>42.25</v>
@@ -12906,16 +12915,16 @@
         <v>42.15</v>
       </c>
       <c r="M236">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N236">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12923,31 +12932,31 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C237">
-        <v>-7.112794598132552</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D237" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E237">
-        <v>-8.225786250181457</v>
+        <v>-7.386210809765892</v>
       </c>
       <c r="F237">
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.09141279459813255</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H237">
-        <v>0.09146578625018145</v>
+        <v>0.08898621080976588</v>
       </c>
       <c r="I237">
-        <v>1.112991652048905</v>
+        <v>1.520470085411908</v>
       </c>
       <c r="J237">
-        <v>1.165983304097812</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K237">
         <v>42.25</v>
@@ -12956,16 +12965,16 @@
         <v>42.15</v>
       </c>
       <c r="M237">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N237">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O237">
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12973,31 +12982,31 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C238">
-        <v>-7.379527992135429</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D238" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E238">
-        <v>-8.495676252397395</v>
+        <v>-7.878937161759204</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.09167952799213544</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H238">
-        <v>0.09173567625239738</v>
+        <v>0.08947893716175921</v>
       </c>
       <c r="I238">
-        <v>1.116148260261966</v>
+        <v>1.522213221091135</v>
       </c>
       <c r="J238">
-        <v>1.172296520523916</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K238">
         <v>42.25</v>
@@ -13006,16 +13015,16 @@
         <v>42.15</v>
       </c>
       <c r="M238">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N238">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O238">
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13023,31 +13032,31 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C239">
-        <v>-7.702700683679339</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D239" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E239">
-        <v>-8.822673472835312</v>
+        <v>-8.295045649261382</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.09200270068367934</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H239">
-        <v>0.09206267347283531</v>
+        <v>0.08989504564926137</v>
       </c>
       <c r="I239">
-        <v>1.119972789155973</v>
+        <v>1.523685303004463</v>
       </c>
       <c r="J239">
-        <v>1.179945578311937</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K239">
         <v>42.25</v>
@@ -13056,16 +13065,16 @@
         <v>42.15</v>
       </c>
       <c r="M239">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N239">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13073,31 +13082,31 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C240">
-        <v>-8.001107320444035</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D240" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E240">
-        <v>-9.124611549088343</v>
+        <v>-8.637692093747219</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.09230110732044404</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H240">
-        <v>0.09236461154908834</v>
+        <v>0.09023769209374721</v>
       </c>
       <c r="I240">
-        <v>1.123504228644308</v>
+        <v>1.524897495614667</v>
       </c>
       <c r="J240">
-        <v>1.187008457288616</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K240">
         <v>42.25</v>
@@ -13106,16 +13115,16 @@
         <v>42.15</v>
       </c>
       <c r="M240">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N240">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13123,31 +13132,31 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C241">
-        <v>-8.280300561754309</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D241" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E241">
-        <v>-9.407108852425964</v>
+        <v>-8.905372470214019</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.09258030056175431</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H241">
-        <v>0.09264710885242596</v>
+        <v>0.09050537247021402</v>
       </c>
       <c r="I241">
-        <v>1.126808290671654</v>
+        <v>1.525844478078589</v>
       </c>
       <c r="J241">
-        <v>1.193616581343297</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K241">
         <v>42.25</v>
@@ -13156,16 +13165,16 @@
         <v>42.15</v>
       </c>
       <c r="M241">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N241">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13173,31 +13182,31 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C242">
-        <v>-8.625026882373376</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D242" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E242">
-        <v>-9.755914774472473</v>
+        <v>-9.229692520426134</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.09292502688237338</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H242">
-        <v>0.09299591477447247</v>
+        <v>0.09082969252042614</v>
       </c>
       <c r="I242">
-        <v>1.130887892099096</v>
+        <v>1.526991836746795</v>
       </c>
       <c r="J242">
-        <v>1.201775784198186</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13206,16 +13215,16 @@
         <v>42.15</v>
       </c>
       <c r="M242">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N242">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13223,31 +13232,31 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C243">
-        <v>-8.846388689296894</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D243" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E243">
-        <v>-9.979896247750112</v>
+        <v>-9.529158589037323</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.09314638868929688</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H243">
-        <v>0.09321989624775012</v>
+        <v>0.09112915858903732</v>
       </c>
       <c r="I243">
-        <v>1.133507558453218</v>
+        <v>1.528051268593288</v>
       </c>
       <c r="J243">
-        <v>1.207015116906435</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K243">
         <v>42.25</v>
@@ -13256,16 +13265,16 @@
         <v>42.15</v>
       </c>
       <c r="M243">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N243">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13273,31 +13282,31 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C244">
-        <v>-9.123967366600709</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D244" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E244">
-        <v>-10.26075987981492</v>
+        <v>-9.809343048955803</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.0934239673666007</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H244">
-        <v>0.09350075987981492</v>
+        <v>0.0914093430489558</v>
       </c>
       <c r="I244">
-        <v>1.13679251321421</v>
+        <v>1.529042487201494</v>
       </c>
       <c r="J244">
-        <v>1.213585026428419</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K244">
         <v>42.25</v>
@@ -13306,16 +13315,16 @@
         <v>42.15</v>
       </c>
       <c r="M244">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N244">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13323,31 +13332,31 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C245">
-        <v>-9.62255528559681</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D245" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E245">
-        <v>-10.76524824755653</v>
+        <v>-10.1552932500031</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.09392255528559681</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H245">
-        <v>0.09400524824755653</v>
+        <v>0.09175529325000309</v>
       </c>
       <c r="I245">
-        <v>1.142692961959725</v>
+        <v>1.530266367629729</v>
       </c>
       <c r="J245">
-        <v>1.225385923919451</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K245">
         <v>42.25</v>
@@ -13356,16 +13365,216 @@
         <v>42.15</v>
       </c>
       <c r="M245">
-        <v>42.75</v>
+        <v>42.4</v>
       </c>
       <c r="N245">
-        <v>41.62</v>
+        <v>40.8</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16">
+      <c r="A246" s="1">
+        <v>0</v>
+      </c>
+      <c r="B246" t="s">
+        <v>73</v>
+      </c>
+      <c r="C246">
+        <v>-8.846388689296894</v>
+      </c>
+      <c r="D246" t="s">
+        <v>134</v>
+      </c>
+      <c r="E246">
+        <v>-10.37744095683286</v>
+      </c>
+      <c r="F246">
+        <v>-1</v>
+      </c>
+      <c r="G246">
+        <v>0.09314638868929688</v>
+      </c>
+      <c r="H246">
+        <v>0.09197744095683286</v>
+      </c>
+      <c r="I246">
+        <v>1.531052267535969</v>
+      </c>
+      <c r="J246">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K246">
+        <v>42.25</v>
+      </c>
+      <c r="L246">
+        <v>42.15</v>
+      </c>
+      <c r="M246">
+        <v>42.4</v>
+      </c>
+      <c r="N246">
+        <v>40.8</v>
+      </c>
+      <c r="O246">
+        <v>1</v>
+      </c>
+      <c r="P246" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16">
+      <c r="A247" s="1">
+        <v>0</v>
+      </c>
+      <c r="B247" t="s">
+        <v>73</v>
+      </c>
+      <c r="C247">
+        <v>-9.123967366600709</v>
+      </c>
+      <c r="D247" t="s">
+        <v>134</v>
+      </c>
+      <c r="E247">
+        <v>-10.65600512056497</v>
+      </c>
+      <c r="F247">
+        <v>-1</v>
+      </c>
+      <c r="G247">
+        <v>0.0934239673666007</v>
+      </c>
+      <c r="H247">
+        <v>0.09225600512056496</v>
+      </c>
+      <c r="I247">
+        <v>1.532037753964261</v>
+      </c>
+      <c r="J247">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K247">
+        <v>42.25</v>
+      </c>
+      <c r="L247">
+        <v>42.15</v>
+      </c>
+      <c r="M247">
+        <v>42.4</v>
+      </c>
+      <c r="N247">
+        <v>40.8</v>
+      </c>
+      <c r="O247">
+        <v>1</v>
+      </c>
+      <c r="P247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16">
+      <c r="A248" s="1">
+        <v>0</v>
+      </c>
+      <c r="B248" t="s">
+        <v>73</v>
+      </c>
+      <c r="C248">
+        <v>-9.62255528559681</v>
+      </c>
+      <c r="D248" t="s">
+        <v>134</v>
+      </c>
+      <c r="E248">
+        <v>-11.15636317418473</v>
+      </c>
+      <c r="F248">
+        <v>-1</v>
+      </c>
+      <c r="G248">
+        <v>0.09392255528559681</v>
+      </c>
+      <c r="H248">
+        <v>0.09275636317418472</v>
+      </c>
+      <c r="I248">
+        <v>1.533807888587916</v>
+      </c>
+      <c r="J248">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K248">
+        <v>42.25</v>
+      </c>
+      <c r="L248">
+        <v>42.15</v>
+      </c>
+      <c r="M248">
+        <v>42.4</v>
+      </c>
+      <c r="N248">
+        <v>40.8</v>
+      </c>
+      <c r="O248">
+        <v>1</v>
+      </c>
+      <c r="P248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16">
+      <c r="A249" s="1">
+        <v>0</v>
+      </c>
+      <c r="B249" t="s">
+        <v>73</v>
+      </c>
+      <c r="C249">
+        <v>-9.818321109702786</v>
+      </c>
+      <c r="D249" t="s">
+        <v>134</v>
+      </c>
+      <c r="E249">
+        <v>-11.35282402488517</v>
+      </c>
+      <c r="F249">
+        <v>-1</v>
+      </c>
+      <c r="G249">
+        <v>0.09411832110970278</v>
+      </c>
+      <c r="H249">
+        <v>0.09295282402488517</v>
+      </c>
+      <c r="I249">
+        <v>1.534502915182379</v>
+      </c>
+      <c r="J249">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K249">
+        <v>42.25</v>
+      </c>
+      <c r="L249">
+        <v>42.15</v>
+      </c>
+      <c r="M249">
+        <v>42.4</v>
+      </c>
+      <c r="N249">
+        <v>40.8</v>
+      </c>
+      <c r="O249">
+        <v>1</v>
+      </c>
+      <c r="P249" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="255">
   <si>
     <t>trade_time</t>
   </si>
@@ -421,6 +421,9 @@
     <t>2021-08-24</t>
   </si>
   <si>
+    <t>2021-08-25</t>
+  </si>
+  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -730,6 +733,9 @@
     <t>2021-07-06</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -770,6 +776,9 @@
   </si>
   <si>
     <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P249"/>
+  <dimension ref="A1:P252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1224,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1274,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1324,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1374,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1424,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1474,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1524,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1574,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1624,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1674,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1724,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1774,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1824,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1874,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1924,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1974,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2024,7 +2033,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2074,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2124,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2174,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2224,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2274,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2324,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2374,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2424,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2474,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2524,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2574,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2624,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2674,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2724,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2774,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2824,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2874,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2924,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2974,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3024,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3074,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3124,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3174,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3224,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3274,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3324,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3374,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3424,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3474,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3524,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3574,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3624,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3674,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3774,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3824,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3874,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3924,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3974,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4024,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4074,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4124,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4174,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4224,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4274,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4324,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4374,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4424,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4474,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4524,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4674,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4724,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4774,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4824,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4874,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4924,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4974,7 +4983,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5124,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5174,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5224,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5274,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5324,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5374,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5424,7 +5433,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5474,7 +5483,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5574,7 +5583,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5624,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5674,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5724,7 +5733,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5774,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5824,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5874,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5924,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5974,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6024,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6074,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6124,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6174,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6224,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6274,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6324,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6374,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6424,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6474,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6524,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6824,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6874,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6924,7 +6933,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6974,7 +6983,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7024,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7274,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7324,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7374,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7424,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7474,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7524,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7574,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7624,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7824,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7874,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7924,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7974,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8024,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8074,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8124,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8174,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8224,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8274,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8324,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8374,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8424,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8474,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8524,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8574,7 +8583,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8624,7 +8633,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8674,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8724,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8774,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8824,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8874,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8924,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8974,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9024,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9074,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9124,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9174,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9224,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9274,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9324,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9374,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9424,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9474,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9524,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9574,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9624,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9674,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9724,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9774,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9824,7 +9833,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9874,7 +9883,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9924,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9974,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10024,7 +10033,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10074,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10624,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10674,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10724,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10774,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10824,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10874,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10924,7 +10933,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10974,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11024,7 +11033,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11074,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11124,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11174,7 +11183,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11224,7 +11233,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11274,7 +11283,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11324,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11374,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11424,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11474,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11524,7 +11533,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11574,7 +11583,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11624,7 +11633,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11674,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11724,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11774,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11824,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11874,7 +11883,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11974,7 +11983,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12024,7 +12033,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12074,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12124,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12174,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12224,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12274,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12474,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12524,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12674,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12724,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12735,28 +12744,28 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>1.750223976867943</v>
+        <v>2.217490520459279</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
       </c>
       <c r="E233">
-        <v>-0.5363331653346535</v>
+        <v>-0.06723898206826107</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07668977602313205</v>
+        <v>0.07622250947954072</v>
       </c>
       <c r="H233">
-        <v>0.07469633316533465</v>
+        <v>0.07422723898206826</v>
       </c>
       <c r="I233">
-        <v>2.286557142202597</v>
+        <v>2.28472950252754</v>
       </c>
       <c r="J233">
-        <v>0.977047614684017</v>
+        <v>0.9648633501835912</v>
       </c>
       <c r="K233">
         <v>38.35</v>
@@ -12774,7 +12783,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12785,28 +12794,28 @@
         <v>72</v>
       </c>
       <c r="C234">
-        <v>1.316205734022681</v>
+        <v>1.750223976867943</v>
       </c>
       <c r="D234" t="s">
         <v>133</v>
       </c>
       <c r="E234">
-        <v>-0.9720490023501114</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07712379426597732</v>
+        <v>0.07668977602313205</v>
       </c>
       <c r="H234">
-        <v>0.0751320490023501</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I234">
-        <v>2.288254736372792</v>
+        <v>2.286557142202597</v>
       </c>
       <c r="J234">
-        <v>0.988364909151951</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K234">
         <v>38.35</v>
@@ -12824,7 +12833,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12832,49 +12841,49 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C235">
-        <v>-4.936139829727118</v>
+        <v>1.316205734022681</v>
       </c>
       <c r="D235" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E235">
-        <v>-6.453309556933249</v>
+        <v>-0.9720490023501114</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.08923613982972711</v>
+        <v>0.07712379426597732</v>
       </c>
       <c r="H235">
-        <v>0.08805330955693325</v>
+        <v>0.0751320490023501</v>
       </c>
       <c r="I235">
-        <v>1.517169727206131</v>
+        <v>2.288254736372792</v>
       </c>
       <c r="J235">
-        <v>1.114464848040879</v>
+        <v>0.988364909151951</v>
       </c>
       <c r="K235">
-        <v>42.25</v>
+        <v>38.35</v>
       </c>
       <c r="L235">
-        <v>42.15</v>
+        <v>39.22</v>
       </c>
       <c r="M235">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N235">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O235">
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>133</v>
+        <v>238</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12885,28 +12894,28 @@
         <v>73</v>
       </c>
       <c r="C236">
-        <v>-5.398172562506375</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D236" t="s">
         <v>134</v>
       </c>
       <c r="E236">
-        <v>-6.916982642609952</v>
+        <v>-6.044764406415567</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.08969817256250637</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H236">
-        <v>0.08851698264260995</v>
+        <v>0.08764476440641557</v>
       </c>
       <c r="I236">
-        <v>1.518810080103577</v>
+        <v>1.515724402381188</v>
       </c>
       <c r="J236">
-        <v>1.12540053402382</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K236">
         <v>42.25</v>
@@ -12924,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12935,28 +12944,28 @@
         <v>73</v>
       </c>
       <c r="C237">
-        <v>-5.865740724353984</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D237" t="s">
         <v>134</v>
       </c>
       <c r="E237">
-        <v>-7.386210809765892</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F237">
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.09016574072435399</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H237">
-        <v>0.08898621080976588</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I237">
-        <v>1.520470085411908</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J237">
-        <v>1.136467236079384</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K237">
         <v>42.25</v>
@@ -12974,7 +12983,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>239</v>
+        <v>133</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12985,28 +12994,28 @@
         <v>73</v>
       </c>
       <c r="C238">
-        <v>-6.356723940668068</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D238" t="s">
         <v>134</v>
       </c>
       <c r="E238">
-        <v>-7.878937161759204</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.09065672394066807</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H238">
-        <v>0.08947893716175921</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I238">
-        <v>1.522213221091135</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J238">
-        <v>1.148088140607528</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K238">
         <v>42.25</v>
@@ -13035,28 +13044,28 @@
         <v>73</v>
       </c>
       <c r="C239">
-        <v>-6.77136034625692</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D239" t="s">
         <v>134</v>
       </c>
       <c r="E239">
-        <v>-8.295045649261382</v>
+        <v>-7.386210809765892</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.09107136034625692</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H239">
-        <v>0.08989504564926137</v>
+        <v>0.08898621080976588</v>
       </c>
       <c r="I239">
-        <v>1.523685303004463</v>
+        <v>1.520470085411908</v>
       </c>
       <c r="J239">
-        <v>1.15790202002975</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K239">
         <v>42.25</v>
@@ -13085,28 +13094,28 @@
         <v>73</v>
       </c>
       <c r="C240">
-        <v>-7.112794598132552</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D240" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E240">
-        <v>-8.637692093747219</v>
+        <v>-8.064128347698443</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.09141279459813255</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H240">
-        <v>0.09023769209374721</v>
+        <v>0.08906412834769845</v>
       </c>
       <c r="I240">
-        <v>1.524897495614667</v>
+        <v>1.707404407030374</v>
       </c>
       <c r="J240">
-        <v>1.165983304097812</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K240">
         <v>42.25</v>
@@ -13115,10 +13124,10 @@
         <v>42.15</v>
       </c>
       <c r="M240">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N240">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O240">
         <v>1</v>
@@ -13135,28 +13144,28 @@
         <v>73</v>
       </c>
       <c r="C241">
-        <v>-7.379527992135429</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D241" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E241">
-        <v>-8.905372470214019</v>
+        <v>-8.479255447258403</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.09167952799213544</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H241">
-        <v>0.09050537247021402</v>
+        <v>0.0894792554472584</v>
       </c>
       <c r="I241">
-        <v>1.525844478078589</v>
+        <v>1.707895101001483</v>
       </c>
       <c r="J241">
-        <v>1.172296520523916</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K241">
         <v>42.25</v>
@@ -13165,10 +13174,10 @@
         <v>42.15</v>
       </c>
       <c r="M241">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N241">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O241">
         <v>1</v>
@@ -13185,28 +13194,28 @@
         <v>73</v>
       </c>
       <c r="C242">
-        <v>-7.702700683679339</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D242" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E242">
-        <v>-9.229692520426134</v>
+        <v>-8.821093763337437</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.09200270068367934</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H242">
-        <v>0.09082969252042614</v>
+        <v>0.08982109376333744</v>
       </c>
       <c r="I242">
-        <v>1.526991836746795</v>
+        <v>1.708299165204885</v>
       </c>
       <c r="J242">
-        <v>1.179945578311937</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13215,10 +13224,10 @@
         <v>42.15</v>
       </c>
       <c r="M242">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N242">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O242">
         <v>1</v>
@@ -13235,28 +13244,28 @@
         <v>73</v>
       </c>
       <c r="C243">
-        <v>-8.001107320444035</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D243" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E243">
-        <v>-9.529158589037323</v>
+        <v>-9.088142818161622</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.09230110732044404</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H243">
-        <v>0.09112915858903732</v>
+        <v>0.09008814281816163</v>
       </c>
       <c r="I243">
-        <v>1.528051268593288</v>
+        <v>1.708614826026192</v>
       </c>
       <c r="J243">
-        <v>1.187008457288616</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K243">
         <v>42.25</v>
@@ -13265,10 +13274,10 @@
         <v>42.15</v>
       </c>
       <c r="M243">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N243">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O243">
         <v>1</v>
@@ -13285,28 +13294,28 @@
         <v>73</v>
       </c>
       <c r="C244">
-        <v>-8.280300561754309</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D244" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E244">
-        <v>-9.809343048955803</v>
+        <v>-9.411697962594936</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.09258030056175431</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H244">
-        <v>0.0914093430489558</v>
+        <v>0.09041169796259493</v>
       </c>
       <c r="I244">
-        <v>1.529042487201494</v>
+        <v>1.708997278915596</v>
       </c>
       <c r="J244">
-        <v>1.193616581343297</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K244">
         <v>42.25</v>
@@ -13315,10 +13324,10 @@
         <v>42.15</v>
       </c>
       <c r="M244">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N244">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O244">
         <v>1</v>
@@ -13335,28 +13344,28 @@
         <v>73</v>
       </c>
       <c r="C245">
-        <v>-8.625026882373376</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D245" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E245">
-        <v>-10.1552932500031</v>
+        <v>-9.71045774330846</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.09292502688237338</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H245">
-        <v>0.09175529325000309</v>
+        <v>0.09071045774330846</v>
       </c>
       <c r="I245">
-        <v>1.530266367629729</v>
+        <v>1.709350422864425</v>
       </c>
       <c r="J245">
-        <v>1.201775784198186</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K245">
         <v>42.25</v>
@@ -13365,10 +13374,10 @@
         <v>42.15</v>
       </c>
       <c r="M245">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N245">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O245">
         <v>1</v>
@@ -13385,28 +13394,28 @@
         <v>73</v>
       </c>
       <c r="C246">
-        <v>-8.846388689296894</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D246" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E246">
-        <v>-10.37744095683286</v>
+        <v>-9.98998139082147</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.09314638868929688</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H246">
-        <v>0.09197744095683286</v>
+        <v>0.09098998139082147</v>
       </c>
       <c r="I246">
-        <v>1.531052267535969</v>
+        <v>1.70968082906716</v>
       </c>
       <c r="J246">
-        <v>1.207015116906435</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13415,10 +13424,10 @@
         <v>42.15</v>
       </c>
       <c r="M246">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N246">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O246">
         <v>1</v>
@@ -13435,28 +13444,28 @@
         <v>73</v>
       </c>
       <c r="C247">
-        <v>-9.123967366600709</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D247" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E247">
-        <v>-10.65600512056497</v>
+        <v>-10.33511567158328</v>
       </c>
       <c r="F247">
         <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.0934239673666007</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H247">
-        <v>0.09225600512056496</v>
+        <v>0.09133511567158328</v>
       </c>
       <c r="I247">
-        <v>1.532037753964261</v>
+        <v>1.710088789209905</v>
       </c>
       <c r="J247">
-        <v>1.213585026428419</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K247">
         <v>42.25</v>
@@ -13465,10 +13474,10 @@
         <v>42.15</v>
       </c>
       <c r="M247">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N247">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O247">
         <v>1</v>
@@ -13485,28 +13494,28 @@
         <v>73</v>
       </c>
       <c r="C248">
-        <v>-9.62255528559681</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D248" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E248">
-        <v>-11.15636317418473</v>
+        <v>-10.55673944514221</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09392255528559681</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H248">
-        <v>0.09275636317418472</v>
+        <v>0.09155673944514221</v>
       </c>
       <c r="I248">
-        <v>1.533807888587916</v>
+        <v>1.710350755845319</v>
       </c>
       <c r="J248">
-        <v>1.225385923919451</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13515,10 +13524,10 @@
         <v>42.15</v>
       </c>
       <c r="M248">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N248">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O248">
         <v>1</v>
@@ -13535,28 +13544,28 @@
         <v>73</v>
       </c>
       <c r="C249">
-        <v>-9.818321109702786</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D249" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E249">
-        <v>-11.35282402488517</v>
+        <v>-10.83464661792213</v>
       </c>
       <c r="F249">
         <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.09411832110970278</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H249">
-        <v>0.09295282402488517</v>
+        <v>0.09183464661792212</v>
       </c>
       <c r="I249">
-        <v>1.534502915182379</v>
+        <v>1.710679251321416</v>
       </c>
       <c r="J249">
-        <v>1.230019434549178</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K249">
         <v>42.25</v>
@@ -13565,16 +13574,166 @@
         <v>42.15</v>
       </c>
       <c r="M249">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N249">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O249">
         <v>1</v>
       </c>
       <c r="P249" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16">
+      <c r="A250" s="1">
+        <v>0</v>
+      </c>
+      <c r="B250" t="s">
+        <v>73</v>
+      </c>
+      <c r="C250">
+        <v>-9.62255528559681</v>
+      </c>
+      <c r="D250" t="s">
+        <v>134</v>
+      </c>
+      <c r="E250">
+        <v>-11.15636317418473</v>
+      </c>
+      <c r="F250">
+        <v>-1</v>
+      </c>
+      <c r="G250">
+        <v>0.09392255528559681</v>
+      </c>
+      <c r="H250">
+        <v>0.09275636317418472</v>
+      </c>
+      <c r="I250">
+        <v>1.533807888587916</v>
+      </c>
+      <c r="J250">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K250">
+        <v>42.25</v>
+      </c>
+      <c r="L250">
+        <v>42.15</v>
+      </c>
+      <c r="M250">
+        <v>42.4</v>
+      </c>
+      <c r="N250">
+        <v>40.8</v>
+      </c>
+      <c r="O250">
+        <v>1</v>
+      </c>
+      <c r="P250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16">
+      <c r="A251" s="1">
+        <v>0</v>
+      </c>
+      <c r="B251" t="s">
+        <v>73</v>
+      </c>
+      <c r="C251">
+        <v>-9.818321109702786</v>
+      </c>
+      <c r="D251" t="s">
+        <v>134</v>
+      </c>
+      <c r="E251">
+        <v>-11.35282402488517</v>
+      </c>
+      <c r="F251">
+        <v>-1</v>
+      </c>
+      <c r="G251">
+        <v>0.09411832110970278</v>
+      </c>
+      <c r="H251">
+        <v>0.09295282402488517</v>
+      </c>
+      <c r="I251">
+        <v>1.534502915182379</v>
+      </c>
+      <c r="J251">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K251">
+        <v>42.25</v>
+      </c>
+      <c r="L251">
+        <v>42.15</v>
+      </c>
+      <c r="M251">
+        <v>42.4</v>
+      </c>
+      <c r="N251">
+        <v>40.8</v>
+      </c>
+      <c r="O251">
+        <v>1</v>
+      </c>
+      <c r="P251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16">
+      <c r="A252" s="1">
+        <v>0</v>
+      </c>
+      <c r="B252" t="s">
+        <v>73</v>
+      </c>
+      <c r="C252">
+        <v>-10.0736945186401</v>
+      </c>
+      <c r="D252" t="s">
+        <v>134</v>
+      </c>
+      <c r="E252">
+        <v>-11.60910408497847</v>
+      </c>
+      <c r="F252">
+        <v>-1</v>
+      </c>
+      <c r="G252">
+        <v>0.0943736945186401</v>
+      </c>
+      <c r="H252">
+        <v>0.09320910408497847</v>
+      </c>
+      <c r="I252">
+        <v>1.535409566338366</v>
+      </c>
+      <c r="J252">
+        <v>1.236063775589115</v>
+      </c>
+      <c r="K252">
+        <v>42.25</v>
+      </c>
+      <c r="L252">
+        <v>42.15</v>
+      </c>
+      <c r="M252">
+        <v>42.4</v>
+      </c>
+      <c r="N252">
+        <v>40.8</v>
+      </c>
+      <c r="O252">
+        <v>1</v>
+      </c>
+      <c r="P252" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="257">
   <si>
     <t>trade_time</t>
   </si>
@@ -730,6 +730,9 @@
     <t>2021-02-05</t>
   </si>
   <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2021-07-06</t>
   </si>
   <si>
@@ -779,6 +782,9 @@
   </si>
   <si>
     <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2021-08-19</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P252"/>
+  <dimension ref="A1:P255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -12744,28 +12750,28 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>2.217490520459279</v>
+        <v>3.121039347441581</v>
       </c>
       <c r="D233" t="s">
         <v>133</v>
       </c>
       <c r="E233">
-        <v>-0.06723898206826107</v>
+        <v>0.8398439341981927</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07622250947954072</v>
+        <v>0.07531896065255841</v>
       </c>
       <c r="H233">
-        <v>0.07422723898206826</v>
+        <v>0.07332015606580179</v>
       </c>
       <c r="I233">
-        <v>2.28472950252754</v>
+        <v>2.281195413243388</v>
       </c>
       <c r="J233">
-        <v>0.9648633501835912</v>
+        <v>0.941302754955891</v>
       </c>
       <c r="K233">
         <v>38.35</v>
@@ -12783,7 +12789,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12794,28 +12800,28 @@
         <v>72</v>
       </c>
       <c r="C234">
-        <v>1.750223976867943</v>
+        <v>2.63673401734458</v>
       </c>
       <c r="D234" t="s">
         <v>133</v>
       </c>
       <c r="E234">
-        <v>-0.5363331653346535</v>
+        <v>0.3536443198896109</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07668977602313205</v>
+        <v>0.07580326598265542</v>
       </c>
       <c r="H234">
-        <v>0.07469633316533465</v>
+        <v>0.07380635568011039</v>
       </c>
       <c r="I234">
-        <v>2.286557142202597</v>
+        <v>2.283089697454969</v>
       </c>
       <c r="J234">
-        <v>0.977047614684017</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K234">
         <v>38.35</v>
@@ -12833,7 +12839,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>129</v>
+        <v>238</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12844,28 +12850,28 @@
         <v>72</v>
       </c>
       <c r="C235">
-        <v>1.316205734022681</v>
+        <v>2.217490520459279</v>
       </c>
       <c r="D235" t="s">
         <v>133</v>
       </c>
       <c r="E235">
-        <v>-0.9720490023501114</v>
+        <v>-0.06723898206826107</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.07712379426597732</v>
+        <v>0.07622250947954072</v>
       </c>
       <c r="H235">
-        <v>0.0751320490023501</v>
+        <v>0.07422723898206826</v>
       </c>
       <c r="I235">
-        <v>2.288254736372792</v>
+        <v>2.28472950252754</v>
       </c>
       <c r="J235">
-        <v>0.988364909151951</v>
+        <v>0.9648633501835912</v>
       </c>
       <c r="K235">
         <v>38.35</v>
@@ -12883,7 +12889,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>238</v>
+        <v>71</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12891,49 +12897,49 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C236">
-        <v>-4.529040004034378</v>
+        <v>1.750223976867943</v>
       </c>
       <c r="D236" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E236">
-        <v>-6.044764406415567</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.08882904000403437</v>
+        <v>0.07668977602313205</v>
       </c>
       <c r="H236">
-        <v>0.08764476440641557</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I236">
-        <v>1.515724402381188</v>
+        <v>2.286557142202597</v>
       </c>
       <c r="J236">
-        <v>1.104829349207914</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K236">
-        <v>42.25</v>
+        <v>38.35</v>
       </c>
       <c r="L236">
-        <v>42.15</v>
+        <v>39.22</v>
       </c>
       <c r="M236">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N236">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O236">
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12941,49 +12947,49 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C237">
-        <v>-4.936139829727118</v>
+        <v>1.230859770361903</v>
       </c>
       <c r="D237" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E237">
-        <v>-6.453309556933249</v>
+        <v>-0.9720490023501114</v>
       </c>
       <c r="F237">
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.08923613982972711</v>
+        <v>0.07782914022963811</v>
       </c>
       <c r="H237">
-        <v>0.08805330955693325</v>
+        <v>0.0751320490023501</v>
       </c>
       <c r="I237">
-        <v>1.517169727206131</v>
+        <v>2.202908772712014</v>
       </c>
       <c r="J237">
-        <v>1.114464848040879</v>
+        <v>0.988364909151951</v>
       </c>
       <c r="K237">
-        <v>42.25</v>
+        <v>38.75</v>
       </c>
       <c r="L237">
-        <v>42.15</v>
+        <v>39.53</v>
       </c>
       <c r="M237">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N237">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O237">
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12994,28 +13000,28 @@
         <v>73</v>
       </c>
       <c r="C238">
-        <v>-5.398172562506375</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D238" t="s">
         <v>134</v>
       </c>
       <c r="E238">
-        <v>-6.916982642609952</v>
+        <v>-6.044764406415567</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.08969817256250637</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H238">
-        <v>0.08851698264260995</v>
+        <v>0.08764476440641557</v>
       </c>
       <c r="I238">
-        <v>1.518810080103577</v>
+        <v>1.515724402381188</v>
       </c>
       <c r="J238">
-        <v>1.12540053402382</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K238">
         <v>42.25</v>
@@ -13044,28 +13050,28 @@
         <v>73</v>
       </c>
       <c r="C239">
-        <v>-5.865740724353984</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D239" t="s">
         <v>134</v>
       </c>
       <c r="E239">
-        <v>-7.386210809765892</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.09016574072435399</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H239">
-        <v>0.08898621080976588</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I239">
-        <v>1.520470085411908</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J239">
-        <v>1.136467236079384</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K239">
         <v>42.25</v>
@@ -13083,7 +13089,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13094,28 +13100,28 @@
         <v>73</v>
       </c>
       <c r="C240">
-        <v>-6.356723940668068</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D240" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E240">
-        <v>-8.064128347698443</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.09065672394066807</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H240">
-        <v>0.08906412834769845</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I240">
-        <v>1.707404407030374</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J240">
-        <v>1.148088140607528</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K240">
         <v>42.25</v>
@@ -13124,16 +13130,16 @@
         <v>42.15</v>
       </c>
       <c r="M240">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N240">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13144,28 +13150,28 @@
         <v>73</v>
       </c>
       <c r="C241">
-        <v>-6.77136034625692</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D241" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E241">
-        <v>-8.479255447258403</v>
+        <v>-7.386210809765892</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.09107136034625692</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H241">
-        <v>0.0894792554472584</v>
+        <v>0.08898621080976588</v>
       </c>
       <c r="I241">
-        <v>1.707895101001483</v>
+        <v>1.520470085411908</v>
       </c>
       <c r="J241">
-        <v>1.15790202002975</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K241">
         <v>42.25</v>
@@ -13174,16 +13180,16 @@
         <v>42.15</v>
       </c>
       <c r="M241">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N241">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13194,28 +13200,28 @@
         <v>73</v>
       </c>
       <c r="C242">
-        <v>-7.112794598132552</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D242" t="s">
         <v>135</v>
       </c>
       <c r="E242">
-        <v>-8.821093763337437</v>
+        <v>-8.064128347698443</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.09141279459813255</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H242">
-        <v>0.08982109376333744</v>
+        <v>0.08906412834769845</v>
       </c>
       <c r="I242">
-        <v>1.708299165204885</v>
+        <v>1.707404407030374</v>
       </c>
       <c r="J242">
-        <v>1.165983304097812</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13233,7 +13239,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13244,28 +13250,28 @@
         <v>73</v>
       </c>
       <c r="C243">
-        <v>-7.379527992135429</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D243" t="s">
         <v>135</v>
       </c>
       <c r="E243">
-        <v>-9.088142818161622</v>
+        <v>-8.479255447258403</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.09167952799213544</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H243">
-        <v>0.09008814281816163</v>
+        <v>0.0894792554472584</v>
       </c>
       <c r="I243">
-        <v>1.708614826026192</v>
+        <v>1.707895101001483</v>
       </c>
       <c r="J243">
-        <v>1.172296520523916</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K243">
         <v>42.25</v>
@@ -13283,7 +13289,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13294,28 +13300,28 @@
         <v>73</v>
       </c>
       <c r="C244">
-        <v>-7.702700683679339</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D244" t="s">
         <v>135</v>
       </c>
       <c r="E244">
-        <v>-9.411697962594936</v>
+        <v>-8.821093763337437</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.09200270068367934</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H244">
-        <v>0.09041169796259493</v>
+        <v>0.08982109376333744</v>
       </c>
       <c r="I244">
-        <v>1.708997278915596</v>
+        <v>1.708299165204885</v>
       </c>
       <c r="J244">
-        <v>1.179945578311937</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K244">
         <v>42.25</v>
@@ -13333,7 +13339,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13344,28 +13350,28 @@
         <v>73</v>
       </c>
       <c r="C245">
-        <v>-8.001107320444035</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D245" t="s">
         <v>135</v>
       </c>
       <c r="E245">
-        <v>-9.71045774330846</v>
+        <v>-9.088142818161622</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.09230110732044404</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H245">
-        <v>0.09071045774330846</v>
+        <v>0.09008814281816163</v>
       </c>
       <c r="I245">
-        <v>1.709350422864425</v>
+        <v>1.708614826026192</v>
       </c>
       <c r="J245">
-        <v>1.187008457288616</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K245">
         <v>42.25</v>
@@ -13383,7 +13389,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13394,28 +13400,28 @@
         <v>73</v>
       </c>
       <c r="C246">
-        <v>-8.280300561754309</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D246" t="s">
         <v>135</v>
       </c>
       <c r="E246">
-        <v>-9.98998139082147</v>
+        <v>-9.411697962594936</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.09258030056175431</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H246">
-        <v>0.09098998139082147</v>
+        <v>0.09041169796259493</v>
       </c>
       <c r="I246">
-        <v>1.70968082906716</v>
+        <v>1.708997278915596</v>
       </c>
       <c r="J246">
-        <v>1.193616581343297</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13433,7 +13439,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13444,28 +13450,28 @@
         <v>73</v>
       </c>
       <c r="C247">
-        <v>-8.625026882373376</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D247" t="s">
         <v>135</v>
       </c>
       <c r="E247">
-        <v>-10.33511567158328</v>
+        <v>-9.71045774330846</v>
       </c>
       <c r="F247">
         <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.09292502688237338</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H247">
-        <v>0.09133511567158328</v>
+        <v>0.09071045774330846</v>
       </c>
       <c r="I247">
-        <v>1.710088789209905</v>
+        <v>1.709350422864425</v>
       </c>
       <c r="J247">
-        <v>1.201775784198186</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K247">
         <v>42.25</v>
@@ -13483,7 +13489,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13494,28 +13500,28 @@
         <v>73</v>
       </c>
       <c r="C248">
-        <v>-8.846388689296894</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D248" t="s">
         <v>135</v>
       </c>
       <c r="E248">
-        <v>-10.55673944514221</v>
+        <v>-9.98998139082147</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09314638868929688</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H248">
-        <v>0.09155673944514221</v>
+        <v>0.09098998139082147</v>
       </c>
       <c r="I248">
-        <v>1.710350755845319</v>
+        <v>1.70968082906716</v>
       </c>
       <c r="J248">
-        <v>1.207015116906435</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13533,7 +13539,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13544,28 +13550,28 @@
         <v>73</v>
       </c>
       <c r="C249">
-        <v>-9.123967366600709</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D249" t="s">
         <v>135</v>
       </c>
       <c r="E249">
-        <v>-10.83464661792213</v>
+        <v>-10.33511567158328</v>
       </c>
       <c r="F249">
         <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.0934239673666007</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H249">
-        <v>0.09183464661792212</v>
+        <v>0.09133511567158328</v>
       </c>
       <c r="I249">
-        <v>1.710679251321416</v>
+        <v>1.710088789209905</v>
       </c>
       <c r="J249">
-        <v>1.213585026428419</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K249">
         <v>42.25</v>
@@ -13583,7 +13589,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13594,28 +13600,28 @@
         <v>73</v>
       </c>
       <c r="C250">
-        <v>-9.62255528559681</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D250" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E250">
-        <v>-11.15636317418473</v>
+        <v>-10.55673944514221</v>
       </c>
       <c r="F250">
         <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09392255528559681</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H250">
-        <v>0.09275636317418472</v>
+        <v>0.09155673944514221</v>
       </c>
       <c r="I250">
-        <v>1.533807888587916</v>
+        <v>1.710350755845319</v>
       </c>
       <c r="J250">
-        <v>1.225385923919451</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K250">
         <v>42.25</v>
@@ -13624,16 +13630,16 @@
         <v>42.15</v>
       </c>
       <c r="M250">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N250">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O250">
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13644,28 +13650,28 @@
         <v>73</v>
       </c>
       <c r="C251">
-        <v>-9.818321109702786</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D251" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E251">
-        <v>-11.35282402488517</v>
+        <v>-10.83464661792213</v>
       </c>
       <c r="F251">
         <v>-1</v>
       </c>
       <c r="G251">
-        <v>0.09411832110970278</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H251">
-        <v>0.09295282402488517</v>
+        <v>0.09183464661792212</v>
       </c>
       <c r="I251">
-        <v>1.534502915182379</v>
+        <v>1.710679251321416</v>
       </c>
       <c r="J251">
-        <v>1.230019434549178</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K251">
         <v>42.25</v>
@@ -13674,16 +13680,16 @@
         <v>42.15</v>
       </c>
       <c r="M251">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N251">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O251">
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13694,28 +13700,28 @@
         <v>73</v>
       </c>
       <c r="C252">
-        <v>-10.0736945186401</v>
+        <v>-9.62255528559681</v>
       </c>
       <c r="D252" t="s">
         <v>134</v>
       </c>
       <c r="E252">
-        <v>-11.60910408497847</v>
+        <v>-11.15636317418473</v>
       </c>
       <c r="F252">
         <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.0943736945186401</v>
+        <v>0.09392255528559681</v>
       </c>
       <c r="H252">
-        <v>0.09320910408497847</v>
+        <v>0.09275636317418472</v>
       </c>
       <c r="I252">
-        <v>1.535409566338366</v>
+        <v>1.533807888587916</v>
       </c>
       <c r="J252">
-        <v>1.236063775589115</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K252">
         <v>42.25</v>
@@ -13733,7 +13739,157 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16">
+      <c r="A253" s="1">
+        <v>0</v>
+      </c>
+      <c r="B253" t="s">
+        <v>73</v>
+      </c>
+      <c r="C253">
+        <v>-9.818321109702786</v>
+      </c>
+      <c r="D253" t="s">
+        <v>134</v>
+      </c>
+      <c r="E253">
+        <v>-11.35282402488517</v>
+      </c>
+      <c r="F253">
+        <v>-1</v>
+      </c>
+      <c r="G253">
+        <v>0.09411832110970278</v>
+      </c>
+      <c r="H253">
+        <v>0.09295282402488517</v>
+      </c>
+      <c r="I253">
+        <v>1.534502915182379</v>
+      </c>
+      <c r="J253">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K253">
+        <v>42.25</v>
+      </c>
+      <c r="L253">
+        <v>42.15</v>
+      </c>
+      <c r="M253">
+        <v>42.4</v>
+      </c>
+      <c r="N253">
+        <v>40.8</v>
+      </c>
+      <c r="O253">
+        <v>1</v>
+      </c>
+      <c r="P253" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16">
+      <c r="A254" s="1">
+        <v>0</v>
+      </c>
+      <c r="B254" t="s">
+        <v>73</v>
+      </c>
+      <c r="C254">
+        <v>-10.0736945186401</v>
+      </c>
+      <c r="D254" t="s">
+        <v>134</v>
+      </c>
+      <c r="E254">
+        <v>-11.60910408497847</v>
+      </c>
+      <c r="F254">
+        <v>-1</v>
+      </c>
+      <c r="G254">
+        <v>0.0943736945186401</v>
+      </c>
+      <c r="H254">
+        <v>0.09320910408497847</v>
+      </c>
+      <c r="I254">
+        <v>1.535409566338366</v>
+      </c>
+      <c r="J254">
+        <v>1.236063775589115</v>
+      </c>
+      <c r="K254">
+        <v>42.25</v>
+      </c>
+      <c r="L254">
+        <v>42.15</v>
+      </c>
+      <c r="M254">
+        <v>42.4</v>
+      </c>
+      <c r="N254">
+        <v>40.8</v>
+      </c>
+      <c r="O254">
+        <v>1</v>
+      </c>
+      <c r="P254" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16">
+      <c r="A255" s="1">
+        <v>0</v>
+      </c>
+      <c r="B255" t="s">
+        <v>73</v>
+      </c>
+      <c r="C255">
+        <v>-10.27048417828931</v>
+      </c>
+      <c r="D255" t="s">
+        <v>134</v>
+      </c>
+      <c r="E255">
+        <v>-11.80659240614123</v>
+      </c>
+      <c r="F255">
+        <v>-1</v>
+      </c>
+      <c r="G255">
+        <v>0.09457048417828931</v>
+      </c>
+      <c r="H255">
+        <v>0.09340659240614121</v>
+      </c>
+      <c r="I255">
+        <v>1.536108227851919</v>
+      </c>
+      <c r="J255">
+        <v>1.240721519012765</v>
+      </c>
+      <c r="K255">
+        <v>42.25</v>
+      </c>
+      <c r="L255">
+        <v>42.15</v>
+      </c>
+      <c r="M255">
+        <v>42.4</v>
+      </c>
+      <c r="N255">
+        <v>40.8</v>
+      </c>
+      <c r="O255">
+        <v>1</v>
+      </c>
+      <c r="P255" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="258">
   <si>
     <t>trade_time</t>
   </si>
@@ -235,9 +235,15 @@
     <t>2021-07-09</t>
   </si>
   <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -406,9 +412,6 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
@@ -421,6 +424,9 @@
     <t>2021-08-24</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2021-08-25</t>
   </si>
   <si>
@@ -736,15 +742,15 @@
     <t>2021-07-06</t>
   </si>
   <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
     <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
     <t>2021-07-29</t>
   </si>
   <si>
@@ -752,9 +758,6 @@
   </si>
   <si>
     <t>2021-08-02</t>
-  </si>
-  <si>
-    <t>2021-08-03</t>
   </si>
   <si>
     <t>2021-08-04</t>
@@ -1142,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P255"/>
+  <dimension ref="A1:P257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1239,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1289,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1303,7 +1306,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1339,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1353,7 +1356,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1389,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1403,7 +1406,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1439,7 +1442,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1453,7 +1456,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1489,7 +1492,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1539,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1589,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1603,7 +1606,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1639,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1653,7 +1656,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1689,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1703,7 +1706,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1739,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1753,7 +1756,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1789,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1803,7 +1806,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1839,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1853,7 +1856,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1889,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1903,7 +1906,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1939,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1953,7 +1956,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1989,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2003,7 +2006,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2039,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2053,7 +2056,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2089,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2103,7 +2106,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2139,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2153,7 +2156,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2189,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2203,7 +2206,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2239,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2253,7 +2256,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2289,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2303,7 +2306,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2339,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2353,7 +2356,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2389,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2403,7 +2406,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2439,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2453,7 +2456,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2489,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2539,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2589,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2603,7 +2606,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2639,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2653,7 +2656,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2689,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2703,7 +2706,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2739,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2753,7 +2756,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2789,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2803,7 +2806,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2839,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2853,7 +2856,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2889,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2939,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2953,7 +2956,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2989,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3003,7 +3006,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3039,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3053,7 +3056,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3089,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3103,7 +3106,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3139,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3153,7 +3156,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3189,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3203,7 +3206,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3239,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3289,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3303,7 +3306,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3339,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3353,7 +3356,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3389,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3403,7 +3406,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3439,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3453,7 +3456,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3489,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3503,7 +3506,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3539,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3553,7 +3556,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3589,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3603,7 +3606,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3639,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3653,7 +3656,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3689,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3703,7 +3706,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3753,7 +3756,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3789,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3803,7 +3806,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3839,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3853,7 +3856,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3889,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3903,7 +3906,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3939,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3953,7 +3956,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3989,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4003,7 +4006,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4039,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4053,7 +4056,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4089,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4103,7 +4106,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4139,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4153,7 +4156,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4189,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4203,7 +4206,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4239,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4253,7 +4256,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4289,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4303,7 +4306,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4339,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4353,7 +4356,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4389,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4403,7 +4406,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4439,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4453,7 +4456,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4489,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4503,7 +4506,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4539,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4553,7 +4556,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4603,7 +4606,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4653,7 +4656,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4689,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4703,7 +4706,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4739,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4753,7 +4756,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4789,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4803,7 +4806,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4839,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4853,7 +4856,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4889,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4903,7 +4906,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4939,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4953,7 +4956,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4989,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5003,7 +5006,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5053,7 +5056,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5103,7 +5106,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5139,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5153,7 +5156,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5189,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5203,7 +5206,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5239,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5253,7 +5256,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5289,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5303,7 +5306,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5339,7 +5342,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5353,7 +5356,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5389,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5403,7 +5406,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5439,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5453,7 +5456,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5489,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5503,7 +5506,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5553,7 +5556,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5589,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5603,7 +5606,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5639,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5653,7 +5656,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5689,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5703,7 +5706,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5739,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5753,7 +5756,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5789,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5803,7 +5806,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5839,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5853,7 +5856,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5889,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5903,7 +5906,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5939,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5953,7 +5956,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5989,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6003,7 +6006,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6039,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6053,7 +6056,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6089,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6103,7 +6106,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6139,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6153,7 +6156,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6189,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6203,7 +6206,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6239,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6253,7 +6256,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6289,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6303,7 +6306,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6339,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6353,7 +6356,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6389,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6403,7 +6406,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6439,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6453,7 +6456,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6489,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6503,7 +6506,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6539,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6553,7 +6556,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6603,7 +6606,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6653,7 +6656,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6703,7 +6706,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6753,7 +6756,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6803,7 +6806,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6839,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6853,7 +6856,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6889,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6903,7 +6906,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6939,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6953,7 +6956,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6989,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7003,7 +7006,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7039,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7053,7 +7056,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7103,7 +7106,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7153,7 +7156,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7203,7 +7206,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7253,7 +7256,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7289,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7303,7 +7306,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7339,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7353,7 +7356,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7389,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7403,7 +7406,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7439,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7453,7 +7456,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7489,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7503,7 +7506,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7539,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7553,7 +7556,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7589,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7603,7 +7606,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7639,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7653,7 +7656,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7689,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7703,7 +7706,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7739,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7753,7 +7756,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7789,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7803,7 +7806,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7839,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7853,7 +7856,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7889,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7903,7 +7906,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7939,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7953,7 +7956,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7989,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8003,7 +8006,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8039,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8053,7 +8056,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8089,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8103,7 +8106,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8139,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8153,7 +8156,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8189,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8203,7 +8206,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8239,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8253,7 +8256,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8289,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8303,7 +8306,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8339,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8353,7 +8356,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8389,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8403,7 +8406,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8439,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8453,7 +8456,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8489,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8503,7 +8506,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8539,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8553,7 +8556,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8589,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8603,7 +8606,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8639,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8653,7 +8656,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8689,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8703,7 +8706,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8739,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8753,7 +8756,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8789,7 +8792,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8803,7 +8806,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8839,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8853,7 +8856,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8889,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8903,7 +8906,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8939,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8953,7 +8956,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8989,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9003,7 +9006,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9039,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9053,7 +9056,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9089,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9103,7 +9106,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9139,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9153,7 +9156,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9189,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9203,7 +9206,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9239,7 +9242,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9253,7 +9256,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9289,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9303,7 +9306,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9339,7 +9342,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9353,7 +9356,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9389,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9403,7 +9406,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9439,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9453,7 +9456,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9489,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9503,7 +9506,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9539,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9553,7 +9556,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9589,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9603,7 +9606,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9639,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9653,7 +9656,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9689,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9703,7 +9706,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9739,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9753,7 +9756,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9789,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9803,7 +9806,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9839,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9853,7 +9856,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9889,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9939,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9953,7 +9956,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9989,7 +9992,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10003,7 +10006,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10039,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10053,7 +10056,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10089,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10103,7 +10106,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10139,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10153,7 +10156,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10189,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10203,7 +10206,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10239,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10253,7 +10256,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10289,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10303,7 +10306,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10339,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10353,7 +10356,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10389,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10403,7 +10406,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10439,7 +10442,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10453,7 +10456,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10489,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10503,7 +10506,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10539,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10553,7 +10556,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10589,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10603,7 +10606,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10639,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10653,7 +10656,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10689,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10703,7 +10706,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10739,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10753,7 +10756,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10789,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10803,7 +10806,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10839,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10853,7 +10856,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10889,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10903,7 +10906,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10939,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10953,7 +10956,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10989,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11003,7 +11006,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11039,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11053,7 +11056,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11089,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11103,7 +11106,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11139,7 +11142,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11153,7 +11156,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11189,7 +11192,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11203,7 +11206,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11239,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11253,7 +11256,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11289,7 +11292,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11303,7 +11306,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11339,7 +11342,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11353,7 +11356,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11389,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11403,7 +11406,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11439,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11453,7 +11456,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11489,7 +11492,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11503,7 +11506,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11539,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11553,7 +11556,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11589,7 +11592,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11603,7 +11606,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11639,7 +11642,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11653,7 +11656,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11689,7 +11692,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11703,7 +11706,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11739,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11753,7 +11756,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11789,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11803,7 +11806,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11839,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11853,7 +11856,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11889,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11903,7 +11906,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11953,7 +11956,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11989,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12039,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12053,7 +12056,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12089,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12103,7 +12106,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12139,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12153,7 +12156,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12189,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12203,7 +12206,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12239,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12289,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12339,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12389,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12439,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12489,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12539,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12553,7 +12556,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12589,7 +12592,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12603,7 +12606,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12639,7 +12642,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12653,7 +12656,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12689,7 +12692,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12703,7 +12706,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12739,7 +12742,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12753,7 +12756,7 @@
         <v>3.121039347441581</v>
       </c>
       <c r="D233" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E233">
         <v>0.8398439341981927</v>
@@ -12803,7 +12806,7 @@
         <v>2.63673401734458</v>
       </c>
       <c r="D234" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E234">
         <v>0.3536443198896109</v>
@@ -12839,7 +12842,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12853,7 +12856,7 @@
         <v>2.217490520459279</v>
       </c>
       <c r="D235" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E235">
         <v>-0.06723898206826107</v>
@@ -12897,13 +12900,13 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C236">
-        <v>1.750223976867943</v>
+        <v>1.66940493099434</v>
       </c>
       <c r="D236" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E236">
         <v>-0.5363331653346535</v>
@@ -12912,22 +12915,22 @@
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07668977602313205</v>
+        <v>0.07739059506900565</v>
       </c>
       <c r="H236">
         <v>0.07469633316533465</v>
       </c>
       <c r="I236">
-        <v>2.286557142202597</v>
+        <v>2.205738096328993</v>
       </c>
       <c r="J236">
         <v>0.977047614684017</v>
       </c>
       <c r="K236">
-        <v>38.35</v>
+        <v>38.75</v>
       </c>
       <c r="L236">
-        <v>39.22</v>
+        <v>39.53</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12939,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12947,13 +12950,13 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C237">
-        <v>1.230859770361903</v>
+        <v>1.212494861209947</v>
       </c>
       <c r="D237" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E237">
         <v>-0.9720490023501114</v>
@@ -12962,22 +12965,22 @@
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.07782914022963811</v>
+        <v>0.07978750513879006</v>
       </c>
       <c r="H237">
         <v>0.0751320490023501</v>
       </c>
       <c r="I237">
-        <v>2.202908772712014</v>
+        <v>2.184543863560059</v>
       </c>
       <c r="J237">
         <v>0.988364909151951</v>
       </c>
       <c r="K237">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="L237">
-        <v>39.53</v>
+        <v>40.5</v>
       </c>
       <c r="M237">
         <v>38.5</v>
@@ -12989,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -12997,31 +13000,31 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C238">
-        <v>-4.529040004034378</v>
+        <v>-4.191976702465361</v>
       </c>
       <c r="D238" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E238">
-        <v>-6.044764406415567</v>
+        <v>-5.706504430403108</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.08882904000403437</v>
+        <v>0.08849197670246536</v>
       </c>
       <c r="H238">
-        <v>0.08764476440641557</v>
+        <v>0.0873065044304031</v>
       </c>
       <c r="I238">
-        <v>1.515724402381188</v>
+        <v>1.514527727937747</v>
       </c>
       <c r="J238">
-        <v>1.104829349207914</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K238">
         <v>42.25</v>
@@ -13039,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13047,31 +13050,31 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C239">
-        <v>-4.936139829727118</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D239" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E239">
-        <v>-6.453309556933249</v>
+        <v>-6.044764406415567</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.08923613982972711</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H239">
-        <v>0.08805330955693325</v>
+        <v>0.08764476440641557</v>
       </c>
       <c r="I239">
-        <v>1.517169727206131</v>
+        <v>1.515724402381188</v>
       </c>
       <c r="J239">
-        <v>1.114464848040879</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K239">
         <v>42.25</v>
@@ -13089,7 +13092,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>133</v>
+        <v>243</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13097,31 +13100,31 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C240">
-        <v>-5.398172562506375</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D240" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E240">
-        <v>-6.916982642609952</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.08969817256250637</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H240">
-        <v>0.08851698264260995</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I240">
-        <v>1.518810080103577</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J240">
-        <v>1.12540053402382</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K240">
         <v>42.25</v>
@@ -13139,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>241</v>
+        <v>134</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13147,81 +13150,81 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C241">
-        <v>-5.865740724353984</v>
+        <v>-5.523389518570603</v>
       </c>
       <c r="D241" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E241">
-        <v>-7.386210809765892</v>
+        <v>-7.749202268793276</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.09016574072435399</v>
+        <v>0.07674338951857061</v>
       </c>
       <c r="H241">
-        <v>0.08898621080976588</v>
+        <v>0.08610920226879328</v>
       </c>
       <c r="I241">
-        <v>1.520470085411908</v>
+        <v>2.225812750222673</v>
       </c>
       <c r="J241">
-        <v>1.136467236079384</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K241">
-        <v>42.25</v>
+        <v>36.55</v>
       </c>
       <c r="L241">
-        <v>42.15</v>
+        <v>35.61</v>
       </c>
       <c r="M241">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="N241">
-        <v>40.8</v>
+        <v>39.18</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B242" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C242">
-        <v>-6.356723940668068</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D242" t="s">
         <v>135</v>
       </c>
       <c r="E242">
-        <v>-8.064128347698443</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.09065672394066807</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H242">
-        <v>0.08906412834769845</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I242">
-        <v>1.707404407030374</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J242">
-        <v>1.148088140607528</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13230,16 +13233,16 @@
         <v>42.15</v>
       </c>
       <c r="M242">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N242">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13247,31 +13250,31 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C243">
-        <v>-6.77136034625692</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D243" t="s">
         <v>135</v>
       </c>
       <c r="E243">
-        <v>-8.479255447258403</v>
+        <v>-7.386210809765892</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.09107136034625692</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H243">
-        <v>0.0894792554472584</v>
+        <v>0.08898621080976588</v>
       </c>
       <c r="I243">
-        <v>1.707895101001483</v>
+        <v>1.520470085411908</v>
       </c>
       <c r="J243">
-        <v>1.15790202002975</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K243">
         <v>42.25</v>
@@ -13280,16 +13283,16 @@
         <v>42.15</v>
       </c>
       <c r="M243">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N243">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>244</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13297,31 +13300,31 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C244">
-        <v>-7.112794598132552</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D244" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E244">
-        <v>-8.821093763337437</v>
+        <v>-8.064128347698443</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.09141279459813255</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H244">
-        <v>0.08982109376333744</v>
+        <v>0.08906412834769845</v>
       </c>
       <c r="I244">
-        <v>1.708299165204885</v>
+        <v>1.707404407030374</v>
       </c>
       <c r="J244">
-        <v>1.165983304097812</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K244">
         <v>42.25</v>
@@ -13347,31 +13350,31 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C245">
-        <v>-7.379527992135429</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D245" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E245">
-        <v>-9.088142818161622</v>
+        <v>-8.479255447258403</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.09167952799213544</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H245">
-        <v>0.09008814281816163</v>
+        <v>0.0894792554472584</v>
       </c>
       <c r="I245">
-        <v>1.708614826026192</v>
+        <v>1.707895101001483</v>
       </c>
       <c r="J245">
-        <v>1.172296520523916</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K245">
         <v>42.25</v>
@@ -13397,31 +13400,31 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C246">
-        <v>-7.702700683679339</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D246" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E246">
-        <v>-9.411697962594936</v>
+        <v>-8.821093763337437</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.09200270068367934</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H246">
-        <v>0.09041169796259493</v>
+        <v>0.08982109376333744</v>
       </c>
       <c r="I246">
-        <v>1.708997278915596</v>
+        <v>1.708299165204885</v>
       </c>
       <c r="J246">
-        <v>1.179945578311937</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13447,31 +13450,31 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C247">
-        <v>-8.001107320444035</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D247" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E247">
-        <v>-9.71045774330846</v>
+        <v>-9.088142818161622</v>
       </c>
       <c r="F247">
         <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.09230110732044404</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H247">
-        <v>0.09071045774330846</v>
+        <v>0.09008814281816163</v>
       </c>
       <c r="I247">
-        <v>1.709350422864425</v>
+        <v>1.708614826026192</v>
       </c>
       <c r="J247">
-        <v>1.187008457288616</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K247">
         <v>42.25</v>
@@ -13489,7 +13492,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>248</v>
+        <v>136</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13497,31 +13500,31 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C248">
-        <v>-8.280300561754309</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D248" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E248">
-        <v>-9.98998139082147</v>
+        <v>-9.411697962594936</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09258030056175431</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H248">
-        <v>0.09098998139082147</v>
+        <v>0.09041169796259493</v>
       </c>
       <c r="I248">
-        <v>1.70968082906716</v>
+        <v>1.708997278915596</v>
       </c>
       <c r="J248">
-        <v>1.193616581343297</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13539,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13547,31 +13550,31 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C249">
-        <v>-8.625026882373376</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D249" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E249">
-        <v>-10.33511567158328</v>
+        <v>-9.71045774330846</v>
       </c>
       <c r="F249">
         <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.09292502688237338</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H249">
-        <v>0.09133511567158328</v>
+        <v>0.09071045774330846</v>
       </c>
       <c r="I249">
-        <v>1.710088789209905</v>
+        <v>1.709350422864425</v>
       </c>
       <c r="J249">
-        <v>1.201775784198186</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K249">
         <v>42.25</v>
@@ -13589,7 +13592,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13597,31 +13600,31 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C250">
-        <v>-8.846388689296894</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D250" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E250">
-        <v>-10.55673944514221</v>
+        <v>-9.98998139082147</v>
       </c>
       <c r="F250">
         <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09314638868929688</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H250">
-        <v>0.09155673944514221</v>
+        <v>0.09098998139082147</v>
       </c>
       <c r="I250">
-        <v>1.710350755845319</v>
+        <v>1.70968082906716</v>
       </c>
       <c r="J250">
-        <v>1.207015116906435</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K250">
         <v>42.25</v>
@@ -13639,7 +13642,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13647,31 +13650,31 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C251">
-        <v>-9.123967366600709</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D251" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E251">
-        <v>-10.83464661792213</v>
+        <v>-10.33511567158328</v>
       </c>
       <c r="F251">
         <v>-1</v>
       </c>
       <c r="G251">
-        <v>0.0934239673666007</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H251">
-        <v>0.09183464661792212</v>
+        <v>0.09133511567158328</v>
       </c>
       <c r="I251">
-        <v>1.710679251321416</v>
+        <v>1.710088789209905</v>
       </c>
       <c r="J251">
-        <v>1.213585026428419</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K251">
         <v>42.25</v>
@@ -13689,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13697,31 +13700,31 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C252">
-        <v>-9.62255528559681</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D252" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E252">
-        <v>-11.15636317418473</v>
+        <v>-10.55673944514221</v>
       </c>
       <c r="F252">
         <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.09392255528559681</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H252">
-        <v>0.09275636317418472</v>
+        <v>0.09155673944514221</v>
       </c>
       <c r="I252">
-        <v>1.533807888587916</v>
+        <v>1.710350755845319</v>
       </c>
       <c r="J252">
-        <v>1.225385923919451</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K252">
         <v>42.25</v>
@@ -13730,16 +13733,16 @@
         <v>42.15</v>
       </c>
       <c r="M252">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N252">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O252">
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13747,31 +13750,31 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C253">
-        <v>-9.818321109702786</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D253" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E253">
-        <v>-11.35282402488517</v>
+        <v>-10.83464661792213</v>
       </c>
       <c r="F253">
         <v>-1</v>
       </c>
       <c r="G253">
-        <v>0.09411832110970278</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H253">
-        <v>0.09295282402488517</v>
+        <v>0.09183464661792212</v>
       </c>
       <c r="I253">
-        <v>1.534502915182379</v>
+        <v>1.710679251321416</v>
       </c>
       <c r="J253">
-        <v>1.230019434549178</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K253">
         <v>42.25</v>
@@ -13780,16 +13783,16 @@
         <v>42.15</v>
       </c>
       <c r="M253">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N253">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13797,31 +13800,31 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C254">
-        <v>-10.0736945186401</v>
+        <v>-9.62255528559681</v>
       </c>
       <c r="D254" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E254">
-        <v>-11.60910408497847</v>
+        <v>-11.15636317418473</v>
       </c>
       <c r="F254">
         <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.0943736945186401</v>
+        <v>0.09392255528559681</v>
       </c>
       <c r="H254">
-        <v>0.09320910408497847</v>
+        <v>0.09275636317418472</v>
       </c>
       <c r="I254">
-        <v>1.535409566338366</v>
+        <v>1.533807888587916</v>
       </c>
       <c r="J254">
-        <v>1.236063775589115</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K254">
         <v>42.25</v>
@@ -13839,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13847,31 +13850,31 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C255">
-        <v>-10.27048417828931</v>
+        <v>-9.818321109702786</v>
       </c>
       <c r="D255" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E255">
-        <v>-11.80659240614123</v>
+        <v>-11.35282402488517</v>
       </c>
       <c r="F255">
         <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.09457048417828931</v>
+        <v>0.09411832110970278</v>
       </c>
       <c r="H255">
-        <v>0.09340659240614121</v>
+        <v>0.09295282402488517</v>
       </c>
       <c r="I255">
-        <v>1.536108227851919</v>
+        <v>1.534502915182379</v>
       </c>
       <c r="J255">
-        <v>1.240721519012765</v>
+        <v>1.230019434549178</v>
       </c>
       <c r="K255">
         <v>42.25</v>
@@ -13889,7 +13892,107 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16">
+      <c r="A256" s="1">
+        <v>0</v>
+      </c>
+      <c r="B256" t="s">
+        <v>74</v>
+      </c>
+      <c r="C256">
+        <v>-10.0736945186401</v>
+      </c>
+      <c r="D256" t="s">
+        <v>135</v>
+      </c>
+      <c r="E256">
+        <v>-11.60910408497847</v>
+      </c>
+      <c r="F256">
+        <v>-1</v>
+      </c>
+      <c r="G256">
+        <v>0.0943736945186401</v>
+      </c>
+      <c r="H256">
+        <v>0.09320910408497847</v>
+      </c>
+      <c r="I256">
+        <v>1.535409566338366</v>
+      </c>
+      <c r="J256">
+        <v>1.236063775589115</v>
+      </c>
+      <c r="K256">
+        <v>42.25</v>
+      </c>
+      <c r="L256">
+        <v>42.15</v>
+      </c>
+      <c r="M256">
+        <v>42.4</v>
+      </c>
+      <c r="N256">
+        <v>40.8</v>
+      </c>
+      <c r="O256">
+        <v>1</v>
+      </c>
+      <c r="P256" t="s">
         <v>256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16">
+      <c r="A257" s="1">
+        <v>0</v>
+      </c>
+      <c r="B257" t="s">
+        <v>74</v>
+      </c>
+      <c r="C257">
+        <v>-10.27048417828931</v>
+      </c>
+      <c r="D257" t="s">
+        <v>135</v>
+      </c>
+      <c r="E257">
+        <v>-11.80659240614123</v>
+      </c>
+      <c r="F257">
+        <v>-1</v>
+      </c>
+      <c r="G257">
+        <v>0.09457048417828931</v>
+      </c>
+      <c r="H257">
+        <v>0.09340659240614121</v>
+      </c>
+      <c r="I257">
+        <v>1.536108227851919</v>
+      </c>
+      <c r="J257">
+        <v>1.240721519012765</v>
+      </c>
+      <c r="K257">
+        <v>42.25</v>
+      </c>
+      <c r="L257">
+        <v>42.15</v>
+      </c>
+      <c r="M257">
+        <v>42.4</v>
+      </c>
+      <c r="N257">
+        <v>40.8</v>
+      </c>
+      <c r="O257">
+        <v>1</v>
+      </c>
+      <c r="P257" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="259">
   <si>
     <t>trade_time</t>
   </si>
@@ -428,6 +428,9 @@
   </si>
   <si>
     <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2016-12-22</t>
@@ -1242,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1292,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1342,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1392,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1442,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1492,7 +1495,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1542,7 +1545,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1592,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1642,7 +1645,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1692,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1742,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1792,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1842,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1892,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1942,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1992,7 +1995,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2042,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2092,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2142,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2192,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2242,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2292,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2342,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2392,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2442,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2492,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2542,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2592,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2642,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2692,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2742,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2792,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2842,7 +2845,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2892,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2942,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2992,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3042,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3092,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3142,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3192,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3242,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3292,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3342,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3392,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3442,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3492,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3542,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3592,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3642,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3692,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3792,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3842,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3892,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3942,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3992,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4042,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4092,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4142,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4192,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4242,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4292,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4342,7 +4345,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4392,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4442,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4492,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4542,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4692,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4742,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4792,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4842,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4892,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4942,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4992,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5142,7 +5145,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5192,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5242,7 +5245,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5292,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5342,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5392,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5442,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5492,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5592,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5642,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5692,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5742,7 +5745,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5792,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5842,7 +5845,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5892,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5942,7 +5945,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5992,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6042,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6092,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6142,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6192,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6242,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6292,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6342,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6392,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6442,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6492,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6542,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6842,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6892,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6942,7 +6945,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6992,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7042,7 +7045,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7292,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7342,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7392,7 +7395,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7442,7 +7445,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7492,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7542,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7592,7 +7595,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7642,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7842,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7892,7 +7895,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7942,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7992,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8042,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8092,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8142,7 +8145,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8192,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8242,7 +8245,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8292,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8342,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8392,7 +8395,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8442,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8492,7 +8495,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8542,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8592,7 +8595,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8642,7 +8645,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8692,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8742,7 +8745,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8792,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8842,7 +8845,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8892,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8942,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8992,7 +8995,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9042,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9092,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9142,7 +9145,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9192,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9242,7 +9245,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9292,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9342,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9392,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9442,7 +9445,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9492,7 +9495,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9542,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9592,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9642,7 +9645,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9692,7 +9695,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9742,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9792,7 +9795,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9842,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9892,7 +9895,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9942,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9992,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10042,7 +10045,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10092,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10642,7 +10645,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10692,7 +10695,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10742,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10792,7 +10795,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10842,7 +10845,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10892,7 +10895,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10942,7 +10945,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10992,7 +10995,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11042,7 +11045,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11092,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11142,7 +11145,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11192,7 +11195,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11242,7 +11245,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11292,7 +11295,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11342,7 +11345,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11392,7 +11395,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11442,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11492,7 +11495,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11542,7 +11545,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11592,7 +11595,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11642,7 +11645,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11692,7 +11695,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11742,7 +11745,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11792,7 +11795,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11842,7 +11845,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11892,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11992,7 +11995,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12042,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12092,7 +12095,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12142,7 +12145,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12192,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12242,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12292,7 +12295,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12492,7 +12495,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12542,7 +12545,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12692,7 +12695,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12742,7 +12745,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12842,7 +12845,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12850,10 +12853,10 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C235">
-        <v>2.217490520459279</v>
+        <v>2.146681830202255</v>
       </c>
       <c r="D235" t="s">
         <v>134</v>
@@ -12865,22 +12868,22 @@
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.07622250947954072</v>
+        <v>0.07885331816979775</v>
       </c>
       <c r="H235">
         <v>0.07422723898206826</v>
       </c>
       <c r="I235">
-        <v>2.28472950252754</v>
+        <v>2.213920812270516</v>
       </c>
       <c r="J235">
         <v>0.9648633501835912</v>
       </c>
       <c r="K235">
-        <v>38.35</v>
+        <v>39.75</v>
       </c>
       <c r="L235">
-        <v>39.22</v>
+        <v>40.5</v>
       </c>
       <c r="M235">
         <v>38.5</v>
@@ -12900,10 +12903,10 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C236">
-        <v>1.66940493099434</v>
+        <v>1.66235731631032</v>
       </c>
       <c r="D236" t="s">
         <v>134</v>
@@ -12915,22 +12918,22 @@
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07739059506900565</v>
+        <v>0.07933764268368969</v>
       </c>
       <c r="H236">
         <v>0.07469633316533465</v>
       </c>
       <c r="I236">
-        <v>2.205738096328993</v>
+        <v>2.198690481644974</v>
       </c>
       <c r="J236">
         <v>0.977047614684017</v>
       </c>
       <c r="K236">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="L236">
-        <v>39.53</v>
+        <v>40.5</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12992,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13042,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13092,7 +13095,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13192,7 +13195,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13242,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13256,10 +13259,10 @@
         <v>-5.865740724353984</v>
       </c>
       <c r="D243" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E243">
-        <v>-7.386210809765892</v>
+        <v>-7.572564086157946</v>
       </c>
       <c r="F243">
         <v>-1</v>
@@ -13268,10 +13271,10 @@
         <v>0.09016574072435399</v>
       </c>
       <c r="H243">
-        <v>0.08898621080976588</v>
+        <v>0.08857256408615793</v>
       </c>
       <c r="I243">
-        <v>1.520470085411908</v>
+        <v>1.706823361803963</v>
       </c>
       <c r="J243">
         <v>1.136467236079384</v>
@@ -13283,10 +13286,10 @@
         <v>42.15</v>
       </c>
       <c r="M243">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N243">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O243">
         <v>1</v>
@@ -13342,7 +13345,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13392,7 +13395,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13442,7 +13445,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13456,10 +13459,10 @@
         <v>-7.379527992135429</v>
       </c>
       <c r="D247" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E247">
-        <v>-9.088142818161622</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F247">
         <v>-1</v>
@@ -13468,10 +13471,10 @@
         <v>0.09167952799213544</v>
       </c>
       <c r="H247">
-        <v>0.09008814281816163</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I247">
-        <v>1.708614826026192</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J247">
         <v>1.172296520523916</v>
@@ -13483,10 +13486,10 @@
         <v>42.15</v>
       </c>
       <c r="M247">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N247">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O247">
         <v>1</v>
@@ -13542,7 +13545,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13592,7 +13595,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13642,7 +13645,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13692,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13742,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13792,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13842,7 +13845,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13892,7 +13895,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13942,7 +13945,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13992,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="260">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,10 +232,16 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-07-07</t>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
   </si>
   <si>
     <t>2021-08-20</t>
@@ -412,27 +418,21 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
     <t>2021-07-14</t>
   </si>
   <si>
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2021-08-24</t>
   </si>
   <si>
-    <t>2021-08-03</t>
-  </si>
-  <si>
     <t>2021-08-25</t>
   </si>
   <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -743,6 +743,9 @@
   </si>
   <si>
     <t>2021-07-06</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
   </si>
   <si>
     <t>2021-07-22</t>
@@ -1148,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P257"/>
+  <dimension ref="A1:P261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1309,7 +1312,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1359,7 +1362,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1409,7 +1412,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1459,7 +1462,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1609,7 +1612,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1659,7 +1662,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1709,7 +1712,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1759,7 +1762,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1809,7 +1812,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1859,7 +1862,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1909,7 +1912,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1959,7 +1962,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -2009,7 +2012,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2059,7 +2062,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2109,7 +2112,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2159,7 +2162,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2209,7 +2212,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2259,7 +2262,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2309,7 +2312,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2359,7 +2362,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2409,7 +2412,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2459,7 +2462,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2609,7 +2612,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2659,7 +2662,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2709,7 +2712,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2759,7 +2762,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2809,7 +2812,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2859,7 +2862,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2959,7 +2962,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -3009,7 +3012,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3059,7 +3062,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3109,7 +3112,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3159,7 +3162,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3209,7 +3212,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3309,7 +3312,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3359,7 +3362,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3409,7 +3412,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3459,7 +3462,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3509,7 +3512,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3559,7 +3562,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3609,7 +3612,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3659,7 +3662,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3709,7 +3712,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3759,7 +3762,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3809,7 +3812,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3859,7 +3862,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3909,7 +3912,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3959,7 +3962,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -4009,7 +4012,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4059,7 +4062,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4109,7 +4112,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4159,7 +4162,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4209,7 +4212,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4259,7 +4262,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4309,7 +4312,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4359,7 +4362,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4409,7 +4412,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4459,7 +4462,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4509,7 +4512,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4559,7 +4562,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4609,7 +4612,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4659,7 +4662,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4709,7 +4712,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4759,7 +4762,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4809,7 +4812,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4859,7 +4862,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4909,7 +4912,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4959,7 +4962,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -5009,7 +5012,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5059,7 +5062,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5109,7 +5112,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5159,7 +5162,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5209,7 +5212,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5259,7 +5262,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5309,7 +5312,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5359,7 +5362,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5409,7 +5412,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5459,7 +5462,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5509,7 +5512,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5559,7 +5562,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5609,7 +5612,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5659,7 +5662,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5709,7 +5712,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5759,7 +5762,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5809,7 +5812,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5859,7 +5862,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5909,7 +5912,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5959,7 +5962,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -6009,7 +6012,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6059,7 +6062,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6109,7 +6112,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6159,7 +6162,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6209,7 +6212,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6259,7 +6262,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6309,7 +6312,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6359,7 +6362,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6409,7 +6412,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6459,7 +6462,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6509,7 +6512,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6559,7 +6562,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6609,7 +6612,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6659,7 +6662,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6709,7 +6712,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6759,7 +6762,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6809,7 +6812,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6859,7 +6862,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6909,7 +6912,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6959,7 +6962,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -7009,7 +7012,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7059,7 +7062,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7109,7 +7112,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7159,7 +7162,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7209,7 +7212,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7259,7 +7262,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7309,7 +7312,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7359,7 +7362,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7409,7 +7412,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7459,7 +7462,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7509,7 +7512,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7559,7 +7562,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7609,7 +7612,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7659,7 +7662,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7695,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7709,7 +7712,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7745,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7759,7 +7762,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7795,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7809,7 +7812,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7859,7 +7862,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7909,7 +7912,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7959,7 +7962,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -8009,7 +8012,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8059,7 +8062,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8109,7 +8112,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8159,7 +8162,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8209,7 +8212,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8259,7 +8262,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8309,7 +8312,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8359,7 +8362,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8409,7 +8412,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8459,7 +8462,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8509,7 +8512,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8559,7 +8562,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8609,7 +8612,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8659,7 +8662,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8709,7 +8712,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8759,7 +8762,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8809,7 +8812,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8859,7 +8862,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8909,7 +8912,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8959,7 +8962,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -9009,7 +9012,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9059,7 +9062,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9109,7 +9112,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9159,7 +9162,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9209,7 +9212,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9259,7 +9262,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9309,7 +9312,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9359,7 +9362,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9409,7 +9412,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9459,7 +9462,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9509,7 +9512,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9559,7 +9562,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9609,7 +9612,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9659,7 +9662,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9709,7 +9712,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9759,7 +9762,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9809,7 +9812,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9859,7 +9862,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9959,7 +9962,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -10009,7 +10012,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10059,7 +10062,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10109,7 +10112,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10145,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10159,7 +10162,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10195,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10209,7 +10212,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10245,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10259,7 +10262,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10295,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10309,7 +10312,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10345,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10359,7 +10362,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10395,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10409,7 +10412,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10445,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10459,7 +10462,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10495,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10509,7 +10512,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10545,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10559,7 +10562,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10595,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10609,7 +10612,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10659,7 +10662,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10709,7 +10712,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10759,7 +10762,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10809,7 +10812,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10859,7 +10862,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10909,7 +10912,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10959,7 +10962,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -11009,7 +11012,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11059,7 +11062,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11109,7 +11112,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11159,7 +11162,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11209,7 +11212,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11259,7 +11262,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11309,7 +11312,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11359,7 +11362,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11409,7 +11412,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11459,7 +11462,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11509,7 +11512,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11559,7 +11562,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11609,7 +11612,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11659,7 +11662,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11709,7 +11712,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11759,7 +11762,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11809,7 +11812,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11859,7 +11862,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11909,7 +11912,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11959,7 +11962,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -12059,7 +12062,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12109,7 +12112,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12159,7 +12162,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12209,7 +12212,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12309,7 +12312,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12345,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12359,7 +12362,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12395,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12409,7 +12412,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12445,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12559,7 +12562,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12595,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12609,7 +12612,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12645,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12659,7 +12662,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12709,7 +12712,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12756,10 +12759,10 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>3.121039347441581</v>
+        <v>3.083215490503335</v>
       </c>
       <c r="D233" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E233">
         <v>0.8398439341981927</v>
@@ -12768,22 +12771,22 @@
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07531896065255841</v>
+        <v>0.07791678450949667</v>
       </c>
       <c r="H233">
         <v>0.07332015606580179</v>
       </c>
       <c r="I233">
-        <v>2.281195413243388</v>
+        <v>2.243371556305142</v>
       </c>
       <c r="J233">
         <v>0.941302754955891</v>
       </c>
       <c r="K233">
-        <v>38.35</v>
+        <v>39.75</v>
       </c>
       <c r="L233">
-        <v>39.22</v>
+        <v>40.5</v>
       </c>
       <c r="M233">
         <v>38.5</v>
@@ -12800,34 +12803,34 @@
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B234" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C234">
-        <v>2.63673401734458</v>
+        <v>3.121039347441581</v>
       </c>
       <c r="D234" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E234">
-        <v>0.3536443198896109</v>
+        <v>0.8398439341981927</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07580326598265542</v>
+        <v>0.07531896065255841</v>
       </c>
       <c r="H234">
-        <v>0.07380635568011039</v>
+        <v>0.07332015606580179</v>
       </c>
       <c r="I234">
-        <v>2.283089697454969</v>
+        <v>2.281195413243388</v>
       </c>
       <c r="J234">
-        <v>0.9539313163665036</v>
+        <v>0.941302754955891</v>
       </c>
       <c r="K234">
         <v>38.35</v>
@@ -12845,7 +12848,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>241</v>
+        <v>67</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12853,31 +12856,31 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C235">
-        <v>2.146681830202255</v>
+        <v>2.581230174431482</v>
       </c>
       <c r="D235" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E235">
-        <v>-0.06723898206826107</v>
+        <v>0.3536443198896109</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.07885331816979775</v>
+        <v>0.07841876982556852</v>
       </c>
       <c r="H235">
-        <v>0.07422723898206826</v>
+        <v>0.07380635568011039</v>
       </c>
       <c r="I235">
-        <v>2.213920812270516</v>
+        <v>2.227585854541871</v>
       </c>
       <c r="J235">
-        <v>0.9648633501835912</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K235">
         <v>39.75</v>
@@ -12895,7 +12898,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12903,31 +12906,31 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C236">
-        <v>1.66235731631032</v>
+        <v>2.146681830202255</v>
       </c>
       <c r="D236" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E236">
-        <v>-0.5363331653346535</v>
+        <v>-0.06723898206826107</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07933764268368969</v>
+        <v>0.07885331816979775</v>
       </c>
       <c r="H236">
-        <v>0.07469633316533465</v>
+        <v>0.07422723898206826</v>
       </c>
       <c r="I236">
-        <v>2.198690481644974</v>
+        <v>2.213920812270516</v>
       </c>
       <c r="J236">
-        <v>0.977047614684017</v>
+        <v>0.9648633501835912</v>
       </c>
       <c r="K236">
         <v>39.75</v>
@@ -12945,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12953,31 +12956,31 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C237">
-        <v>1.212494861209947</v>
+        <v>1.66235731631032</v>
       </c>
       <c r="D237" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E237">
-        <v>-0.9720490023501114</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F237">
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.07978750513879006</v>
+        <v>0.07933764268368969</v>
       </c>
       <c r="H237">
-        <v>0.0751320490023501</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I237">
-        <v>2.184543863560059</v>
+        <v>2.198690481644974</v>
       </c>
       <c r="J237">
-        <v>0.988364909151951</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K237">
         <v>39.75</v>
@@ -12995,7 +12998,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>242</v>
+        <v>133</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13003,49 +13006,49 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C238">
-        <v>-4.191976702465361</v>
+        <v>1.212494861209947</v>
       </c>
       <c r="D238" t="s">
         <v>135</v>
       </c>
       <c r="E238">
-        <v>-5.706504430403108</v>
+        <v>-0.9720490023501114</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.08849197670246536</v>
+        <v>0.07978750513879006</v>
       </c>
       <c r="H238">
-        <v>0.0873065044304031</v>
+        <v>0.0751320490023501</v>
       </c>
       <c r="I238">
-        <v>1.514527727937747</v>
+        <v>2.184543863560059</v>
       </c>
       <c r="J238">
-        <v>1.096851519584979</v>
+        <v>0.988364909151951</v>
       </c>
       <c r="K238">
-        <v>42.25</v>
+        <v>39.75</v>
       </c>
       <c r="L238">
-        <v>42.15</v>
+        <v>40.5</v>
       </c>
       <c r="M238">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N238">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O238">
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13056,46 +13059,46 @@
         <v>74</v>
       </c>
       <c r="C239">
-        <v>-4.529040004034378</v>
+        <v>-0.1382969714751567</v>
       </c>
       <c r="D239" t="s">
         <v>135</v>
       </c>
       <c r="E239">
-        <v>-6.044764406415567</v>
+        <v>-1.664486787769654</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.08882904000403437</v>
+        <v>0.07855829697147516</v>
       </c>
       <c r="H239">
-        <v>0.08764476440641557</v>
+        <v>0.07582448678776965</v>
       </c>
       <c r="I239">
-        <v>1.515724402381188</v>
+        <v>1.526189816294497</v>
       </c>
       <c r="J239">
-        <v>1.104829349207914</v>
+        <v>1.006350306175835</v>
       </c>
       <c r="K239">
-        <v>42.25</v>
+        <v>39.1</v>
       </c>
       <c r="L239">
-        <v>42.15</v>
+        <v>39.21</v>
       </c>
       <c r="M239">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N239">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13103,49 +13106,49 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C240">
-        <v>-4.936139829727118</v>
+        <v>-3.293901612234158</v>
       </c>
       <c r="D240" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E240">
-        <v>-6.453309556933249</v>
+        <v>-5.750840545762586</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.08923613982972711</v>
+        <v>0.08053390161223416</v>
       </c>
       <c r="H240">
-        <v>0.08805330955693325</v>
+        <v>0.08411084054576258</v>
       </c>
       <c r="I240">
-        <v>1.517169727206131</v>
+        <v>2.456938933528427</v>
       </c>
       <c r="J240">
-        <v>1.114464848040879</v>
+        <v>1.077478190545865</v>
       </c>
       <c r="K240">
-        <v>42.25</v>
+        <v>38.9</v>
       </c>
       <c r="L240">
-        <v>42.15</v>
+        <v>38.62</v>
       </c>
       <c r="M240">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="N240">
-        <v>40.8</v>
+        <v>39.18</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>134</v>
+        <v>243</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13153,81 +13156,81 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C241">
-        <v>-5.523389518570603</v>
+        <v>-4.191976702465361</v>
       </c>
       <c r="D241" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E241">
-        <v>-7.749202268793276</v>
+        <v>-5.706504430403108</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.07674338951857061</v>
+        <v>0.08849197670246536</v>
       </c>
       <c r="H241">
-        <v>0.08610920226879328</v>
+        <v>0.0873065044304031</v>
       </c>
       <c r="I241">
-        <v>2.225812750222673</v>
+        <v>1.514527727937747</v>
       </c>
       <c r="J241">
-        <v>1.12540053402382</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K241">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L241">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M241">
-        <v>41.7</v>
+        <v>42.4</v>
       </c>
       <c r="N241">
-        <v>39.18</v>
+        <v>40.8</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:16">
       <c r="A242" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C242">
-        <v>-5.398172562506375</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D242" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E242">
-        <v>-6.916982642609952</v>
+        <v>-6.044764406415567</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.08969817256250637</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H242">
-        <v>0.08851698264260995</v>
+        <v>0.08764476440641557</v>
       </c>
       <c r="I242">
-        <v>1.518810080103577</v>
+        <v>1.515724402381188</v>
       </c>
       <c r="J242">
-        <v>1.12540053402382</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13253,81 +13256,81 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C243">
-        <v>-5.865740724353984</v>
+        <v>-5.123690195894106</v>
       </c>
       <c r="D243" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E243">
-        <v>-7.572564086157946</v>
+        <v>-7.293184163304637</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.09016574072435399</v>
+        <v>0.07634369019589411</v>
       </c>
       <c r="H243">
-        <v>0.08857256408615793</v>
+        <v>0.08565318416330464</v>
       </c>
       <c r="I243">
-        <v>1.706823361803963</v>
+        <v>2.169493967410531</v>
       </c>
       <c r="J243">
-        <v>1.136467236079384</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K243">
-        <v>42.25</v>
+        <v>36.55</v>
       </c>
       <c r="L243">
-        <v>42.15</v>
+        <v>35.61</v>
       </c>
       <c r="M243">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="N243">
-        <v>40.5</v>
+        <v>39.18</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B244" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C244">
-        <v>-6.356723940668068</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D244" t="s">
         <v>137</v>
       </c>
       <c r="E244">
-        <v>-8.064128347698443</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.09065672394066807</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H244">
-        <v>0.08906412834769845</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I244">
-        <v>1.707404407030374</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J244">
-        <v>1.148088140607528</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K244">
         <v>42.25</v>
@@ -13336,16 +13339,16 @@
         <v>42.15</v>
       </c>
       <c r="M244">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N244">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13353,81 +13356,81 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C245">
-        <v>-6.77136034625692</v>
+        <v>-5.523389518570603</v>
       </c>
       <c r="D245" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E245">
-        <v>-8.479255447258403</v>
+        <v>-7.749202268793276</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.09107136034625692</v>
+        <v>0.07674338951857061</v>
       </c>
       <c r="H245">
-        <v>0.0894792554472584</v>
+        <v>0.08610920226879328</v>
       </c>
       <c r="I245">
-        <v>1.707895101001483</v>
+        <v>2.225812750222673</v>
       </c>
       <c r="J245">
-        <v>1.15790202002975</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K245">
-        <v>42.25</v>
+        <v>36.55</v>
       </c>
       <c r="L245">
-        <v>42.15</v>
+        <v>35.61</v>
       </c>
       <c r="M245">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="N245">
-        <v>40.5</v>
+        <v>39.18</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="246" spans="1:16">
       <c r="A246" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B246" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C246">
-        <v>-7.112794598132552</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D246" t="s">
         <v>137</v>
       </c>
       <c r="E246">
-        <v>-8.821093763337437</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.09141279459813255</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H246">
-        <v>0.08982109376333744</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I246">
-        <v>1.708299165204885</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J246">
-        <v>1.165983304097812</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13436,16 +13439,16 @@
         <v>42.15</v>
       </c>
       <c r="M246">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="N246">
-        <v>40.5</v>
+        <v>40.8</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13453,31 +13456,31 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C247">
-        <v>-7.379527992135429</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D247" t="s">
         <v>138</v>
       </c>
       <c r="E247">
-        <v>-9.501860820956622</v>
+        <v>-7.572564086157946</v>
       </c>
       <c r="F247">
         <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.09167952799213544</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H247">
-        <v>0.08428186082095662</v>
+        <v>0.08857256408615793</v>
       </c>
       <c r="I247">
-        <v>2.122332828821193</v>
+        <v>1.706823361803963</v>
       </c>
       <c r="J247">
-        <v>1.172296520523916</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K247">
         <v>42.25</v>
@@ -13486,16 +13489,16 @@
         <v>42.15</v>
       </c>
       <c r="M247">
-        <v>40</v>
+        <v>42.3</v>
       </c>
       <c r="N247">
-        <v>37.39</v>
+        <v>40.5</v>
       </c>
       <c r="O247">
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13503,31 +13506,31 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C248">
-        <v>-7.702700683679339</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D248" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E248">
-        <v>-9.411697962594936</v>
+        <v>-8.064128347698443</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09200270068367934</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H248">
-        <v>0.09041169796259493</v>
+        <v>0.08906412834769845</v>
       </c>
       <c r="I248">
-        <v>1.708997278915596</v>
+        <v>1.707404407030374</v>
       </c>
       <c r="J248">
-        <v>1.179945578311937</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13545,7 +13548,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13553,31 +13556,31 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C249">
-        <v>-8.001107320444035</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D249" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E249">
-        <v>-9.71045774330846</v>
+        <v>-8.479255447258403</v>
       </c>
       <c r="F249">
         <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.09230110732044404</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H249">
-        <v>0.09071045774330846</v>
+        <v>0.0894792554472584</v>
       </c>
       <c r="I249">
-        <v>1.709350422864425</v>
+        <v>1.707895101001483</v>
       </c>
       <c r="J249">
-        <v>1.187008457288616</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K249">
         <v>42.25</v>
@@ -13595,7 +13598,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13603,31 +13606,31 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C250">
-        <v>-8.280300561754309</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D250" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E250">
-        <v>-9.98998139082147</v>
+        <v>-8.821093763337437</v>
       </c>
       <c r="F250">
         <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09258030056175431</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H250">
-        <v>0.09098998139082147</v>
+        <v>0.08982109376333744</v>
       </c>
       <c r="I250">
-        <v>1.70968082906716</v>
+        <v>1.708299165204885</v>
       </c>
       <c r="J250">
-        <v>1.193616581343297</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K250">
         <v>42.25</v>
@@ -13645,7 +13648,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13653,31 +13656,31 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C251">
-        <v>-8.625026882373376</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D251" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E251">
-        <v>-10.33511567158328</v>
+        <v>-9.088142818161622</v>
       </c>
       <c r="F251">
         <v>-1</v>
       </c>
       <c r="G251">
-        <v>0.09292502688237338</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H251">
-        <v>0.09133511567158328</v>
+        <v>0.09008814281816163</v>
       </c>
       <c r="I251">
-        <v>1.710088789209905</v>
+        <v>1.708614826026192</v>
       </c>
       <c r="J251">
-        <v>1.201775784198186</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K251">
         <v>42.25</v>
@@ -13695,7 +13698,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>252</v>
+        <v>136</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13703,31 +13706,31 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C252">
-        <v>-8.846388689296894</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D252" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E252">
-        <v>-10.55673944514221</v>
+        <v>-9.411697962594936</v>
       </c>
       <c r="F252">
         <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.09314638868929688</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H252">
-        <v>0.09155673944514221</v>
+        <v>0.09041169796259493</v>
       </c>
       <c r="I252">
-        <v>1.710350755845319</v>
+        <v>1.708997278915596</v>
       </c>
       <c r="J252">
-        <v>1.207015116906435</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K252">
         <v>42.25</v>
@@ -13745,7 +13748,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13753,31 +13756,31 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C253">
-        <v>-9.123967366600709</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D253" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E253">
-        <v>-10.83464661792213</v>
+        <v>-9.71045774330846</v>
       </c>
       <c r="F253">
         <v>-1</v>
       </c>
       <c r="G253">
-        <v>0.0934239673666007</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H253">
-        <v>0.09183464661792212</v>
+        <v>0.09071045774330846</v>
       </c>
       <c r="I253">
-        <v>1.710679251321416</v>
+        <v>1.709350422864425</v>
       </c>
       <c r="J253">
-        <v>1.213585026428419</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K253">
         <v>42.25</v>
@@ -13795,7 +13798,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13803,31 +13806,31 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C254">
-        <v>-9.62255528559681</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D254" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E254">
-        <v>-11.15636317418473</v>
+        <v>-9.98998139082147</v>
       </c>
       <c r="F254">
         <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.09392255528559681</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H254">
-        <v>0.09275636317418472</v>
+        <v>0.09098998139082147</v>
       </c>
       <c r="I254">
-        <v>1.533807888587916</v>
+        <v>1.70968082906716</v>
       </c>
       <c r="J254">
-        <v>1.225385923919451</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K254">
         <v>42.25</v>
@@ -13836,16 +13839,16 @@
         <v>42.15</v>
       </c>
       <c r="M254">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N254">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O254">
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13853,31 +13856,31 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C255">
-        <v>-9.818321109702786</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D255" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E255">
-        <v>-11.35282402488517</v>
+        <v>-10.33511567158328</v>
       </c>
       <c r="F255">
         <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.09411832110970278</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H255">
-        <v>0.09295282402488517</v>
+        <v>0.09133511567158328</v>
       </c>
       <c r="I255">
-        <v>1.534502915182379</v>
+        <v>1.710088789209905</v>
       </c>
       <c r="J255">
-        <v>1.230019434549178</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K255">
         <v>42.25</v>
@@ -13886,16 +13889,16 @@
         <v>42.15</v>
       </c>
       <c r="M255">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N255">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O255">
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13903,31 +13906,31 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C256">
-        <v>-10.0736945186401</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D256" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E256">
-        <v>-11.60910408497847</v>
+        <v>-10.55673944514221</v>
       </c>
       <c r="F256">
         <v>-1</v>
       </c>
       <c r="G256">
-        <v>0.0943736945186401</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H256">
-        <v>0.09320910408497847</v>
+        <v>0.09155673944514221</v>
       </c>
       <c r="I256">
-        <v>1.535409566338366</v>
+        <v>1.710350755845319</v>
       </c>
       <c r="J256">
-        <v>1.236063775589115</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K256">
         <v>42.25</v>
@@ -13936,16 +13939,16 @@
         <v>42.15</v>
       </c>
       <c r="M256">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N256">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O256">
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13953,31 +13956,31 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C257">
-        <v>-10.27048417828931</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D257" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E257">
-        <v>-11.80659240614123</v>
+        <v>-10.83464661792213</v>
       </c>
       <c r="F257">
         <v>-1</v>
       </c>
       <c r="G257">
-        <v>0.09457048417828931</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H257">
-        <v>0.09340659240614121</v>
+        <v>0.09183464661792212</v>
       </c>
       <c r="I257">
-        <v>1.536108227851919</v>
+        <v>1.710679251321416</v>
       </c>
       <c r="J257">
-        <v>1.240721519012765</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K257">
         <v>42.25</v>
@@ -13986,16 +13989,216 @@
         <v>42.15</v>
       </c>
       <c r="M257">
+        <v>42.3</v>
+      </c>
+      <c r="N257">
+        <v>40.5</v>
+      </c>
+      <c r="O257">
+        <v>1</v>
+      </c>
+      <c r="P257" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16">
+      <c r="A258" s="1">
+        <v>0</v>
+      </c>
+      <c r="B258" t="s">
+        <v>76</v>
+      </c>
+      <c r="C258">
+        <v>-9.62255528559681</v>
+      </c>
+      <c r="D258" t="s">
+        <v>137</v>
+      </c>
+      <c r="E258">
+        <v>-11.15636317418473</v>
+      </c>
+      <c r="F258">
+        <v>-1</v>
+      </c>
+      <c r="G258">
+        <v>0.09392255528559681</v>
+      </c>
+      <c r="H258">
+        <v>0.09275636317418472</v>
+      </c>
+      <c r="I258">
+        <v>1.533807888587916</v>
+      </c>
+      <c r="J258">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K258">
+        <v>42.25</v>
+      </c>
+      <c r="L258">
+        <v>42.15</v>
+      </c>
+      <c r="M258">
         <v>42.4</v>
       </c>
-      <c r="N257">
+      <c r="N258">
         <v>40.8</v>
       </c>
-      <c r="O257">
-        <v>1</v>
-      </c>
-      <c r="P257" t="s">
+      <c r="O258">
+        <v>1</v>
+      </c>
+      <c r="P258" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16">
+      <c r="A259" s="1">
+        <v>0</v>
+      </c>
+      <c r="B259" t="s">
+        <v>76</v>
+      </c>
+      <c r="C259">
+        <v>-9.818321109702786</v>
+      </c>
+      <c r="D259" t="s">
+        <v>137</v>
+      </c>
+      <c r="E259">
+        <v>-11.35282402488517</v>
+      </c>
+      <c r="F259">
+        <v>-1</v>
+      </c>
+      <c r="G259">
+        <v>0.09411832110970278</v>
+      </c>
+      <c r="H259">
+        <v>0.09295282402488517</v>
+      </c>
+      <c r="I259">
+        <v>1.534502915182379</v>
+      </c>
+      <c r="J259">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K259">
+        <v>42.25</v>
+      </c>
+      <c r="L259">
+        <v>42.15</v>
+      </c>
+      <c r="M259">
+        <v>42.4</v>
+      </c>
+      <c r="N259">
+        <v>40.8</v>
+      </c>
+      <c r="O259">
+        <v>1</v>
+      </c>
+      <c r="P259" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16">
+      <c r="A260" s="1">
+        <v>0</v>
+      </c>
+      <c r="B260" t="s">
+        <v>76</v>
+      </c>
+      <c r="C260">
+        <v>-10.0736945186401</v>
+      </c>
+      <c r="D260" t="s">
+        <v>137</v>
+      </c>
+      <c r="E260">
+        <v>-11.60910408497847</v>
+      </c>
+      <c r="F260">
+        <v>-1</v>
+      </c>
+      <c r="G260">
+        <v>0.0943736945186401</v>
+      </c>
+      <c r="H260">
+        <v>0.09320910408497847</v>
+      </c>
+      <c r="I260">
+        <v>1.535409566338366</v>
+      </c>
+      <c r="J260">
+        <v>1.236063775589115</v>
+      </c>
+      <c r="K260">
+        <v>42.25</v>
+      </c>
+      <c r="L260">
+        <v>42.15</v>
+      </c>
+      <c r="M260">
+        <v>42.4</v>
+      </c>
+      <c r="N260">
+        <v>40.8</v>
+      </c>
+      <c r="O260">
+        <v>1</v>
+      </c>
+      <c r="P260" t="s">
         <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16">
+      <c r="A261" s="1">
+        <v>0</v>
+      </c>
+      <c r="B261" t="s">
+        <v>76</v>
+      </c>
+      <c r="C261">
+        <v>-10.27048417828931</v>
+      </c>
+      <c r="D261" t="s">
+        <v>137</v>
+      </c>
+      <c r="E261">
+        <v>-11.80659240614123</v>
+      </c>
+      <c r="F261">
+        <v>-1</v>
+      </c>
+      <c r="G261">
+        <v>0.09457048417828931</v>
+      </c>
+      <c r="H261">
+        <v>0.09340659240614121</v>
+      </c>
+      <c r="I261">
+        <v>1.536108227851919</v>
+      </c>
+      <c r="J261">
+        <v>1.240721519012765</v>
+      </c>
+      <c r="K261">
+        <v>42.25</v>
+      </c>
+      <c r="L261">
+        <v>42.15</v>
+      </c>
+      <c r="M261">
+        <v>42.4</v>
+      </c>
+      <c r="N261">
+        <v>40.8</v>
+      </c>
+      <c r="O261">
+        <v>1</v>
+      </c>
+      <c r="P261" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="262">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,10 +232,13 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2021-07-07</t>
   </si>
   <si>
-    <t>2021-07-09</t>
+    <t>2021-07-06</t>
   </si>
   <si>
     <t>2021-07-13</t>
@@ -433,6 +436,9 @@
     <t>2021-08-25</t>
   </si>
   <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -739,10 +745,10 @@
     <t>2021-02-05</t>
   </si>
   <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
     <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
   </si>
   <si>
     <t>2021-07-20</t>
@@ -1151,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P261"/>
+  <dimension ref="A1:P260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1248,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1298,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1312,7 +1318,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1348,7 +1354,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1362,7 +1368,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1398,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1412,7 +1418,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1448,7 +1454,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1462,7 +1468,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1498,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1548,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1598,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1612,7 +1618,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1648,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1662,7 +1668,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1698,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1712,7 +1718,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1748,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1762,7 +1768,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1798,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1812,7 +1818,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1848,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1862,7 +1868,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1898,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1912,7 +1918,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1948,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1962,7 +1968,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1998,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2012,7 +2018,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2048,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2062,7 +2068,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2098,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2112,7 +2118,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2148,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2162,7 +2168,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2198,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2212,7 +2218,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2248,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2262,7 +2268,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2298,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2312,7 +2318,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2348,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2362,7 +2368,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2398,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2412,7 +2418,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2448,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2462,7 +2468,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2498,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2548,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2598,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2612,7 +2618,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2648,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2662,7 +2668,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2698,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2712,7 +2718,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2748,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2762,7 +2768,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2798,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2812,7 +2818,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2848,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2862,7 +2868,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2898,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2948,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2962,7 +2968,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2998,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3012,7 +3018,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3048,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3062,7 +3068,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3098,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3112,7 +3118,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3148,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3162,7 +3168,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3198,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3212,7 +3218,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3248,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3298,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3312,7 +3318,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3348,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3362,7 +3368,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3398,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3412,7 +3418,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3448,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3462,7 +3468,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3498,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3512,7 +3518,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3548,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3562,7 +3568,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3598,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3612,7 +3618,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3648,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3662,7 +3668,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3698,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3712,7 +3718,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3762,7 +3768,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3798,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3812,7 +3818,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3848,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3862,7 +3868,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3898,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3912,7 +3918,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3948,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3962,7 +3968,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3998,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4012,7 +4018,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4048,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4062,7 +4068,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4098,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4112,7 +4118,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4148,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4162,7 +4168,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4198,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4212,7 +4218,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4248,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4262,7 +4268,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4298,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4312,7 +4318,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4348,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4362,7 +4368,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4398,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4412,7 +4418,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4448,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4462,7 +4468,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4498,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4512,7 +4518,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4548,7 +4554,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4562,7 +4568,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4612,7 +4618,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4662,7 +4668,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4698,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4712,7 +4718,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4748,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4762,7 +4768,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4798,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4812,7 +4818,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4848,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4862,7 +4868,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4898,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4912,7 +4918,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4948,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4962,7 +4968,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4998,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5012,7 +5018,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5062,7 +5068,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5112,7 +5118,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5148,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5162,7 +5168,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5198,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5212,7 +5218,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5248,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5262,7 +5268,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5298,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5312,7 +5318,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5348,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5362,7 +5368,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5398,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5412,7 +5418,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5448,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5462,7 +5468,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5498,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5512,7 +5518,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5562,7 +5568,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5598,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5612,7 +5618,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5648,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5662,7 +5668,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5698,7 +5704,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5712,7 +5718,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5748,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5762,7 +5768,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5798,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5812,7 +5818,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5848,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5862,7 +5868,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5898,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5912,7 +5918,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5948,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5962,7 +5968,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5998,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6012,7 +6018,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6048,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6062,7 +6068,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6098,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6112,7 +6118,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6148,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6162,7 +6168,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6198,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6212,7 +6218,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6248,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6262,7 +6268,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6298,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6312,7 +6318,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6348,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6362,7 +6368,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6398,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6412,7 +6418,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6448,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6462,7 +6468,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6498,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6512,7 +6518,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6548,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6562,7 +6568,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6612,7 +6618,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6662,7 +6668,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6712,7 +6718,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6762,7 +6768,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6812,7 +6818,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6848,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6862,7 +6868,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6898,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6912,7 +6918,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6948,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6962,7 +6968,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6998,7 +7004,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7012,7 +7018,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7048,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7062,7 +7068,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7112,7 +7118,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7162,7 +7168,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7212,7 +7218,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7262,7 +7268,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7298,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7312,7 +7318,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7348,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7362,7 +7368,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7398,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7412,7 +7418,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7448,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7462,7 +7468,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7498,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7512,7 +7518,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7548,7 +7554,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7562,7 +7568,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7598,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7612,7 +7618,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7648,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7662,7 +7668,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7698,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7712,7 +7718,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7748,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7762,7 +7768,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7798,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7812,7 +7818,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7848,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7862,7 +7868,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7898,7 +7904,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7912,7 +7918,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7948,7 +7954,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7962,7 +7968,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7998,7 +8004,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8012,7 +8018,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8048,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8062,7 +8068,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8098,7 +8104,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8112,7 +8118,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8148,7 +8154,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8162,7 +8168,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8198,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8212,7 +8218,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8248,7 +8254,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8262,7 +8268,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8298,7 +8304,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8312,7 +8318,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8348,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8362,7 +8368,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8398,7 +8404,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8412,7 +8418,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8448,7 +8454,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8462,7 +8468,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8498,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8512,7 +8518,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8548,7 +8554,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8562,7 +8568,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8598,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8612,7 +8618,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8648,7 +8654,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8662,7 +8668,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8698,7 +8704,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8712,7 +8718,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8748,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8762,7 +8768,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8798,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8812,7 +8818,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8848,7 +8854,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8862,7 +8868,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8898,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8912,7 +8918,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8948,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8962,7 +8968,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8998,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9012,7 +9018,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9048,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9062,7 +9068,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9098,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9112,7 +9118,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9148,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9162,7 +9168,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9198,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9212,7 +9218,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9248,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9262,7 +9268,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9298,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9312,7 +9318,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9348,7 +9354,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9362,7 +9368,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9398,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9412,7 +9418,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9448,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9462,7 +9468,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9498,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9512,7 +9518,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9548,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9562,7 +9568,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9598,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9612,7 +9618,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9648,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9662,7 +9668,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9698,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9712,7 +9718,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9748,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9762,7 +9768,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9798,7 +9804,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9812,7 +9818,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9848,7 +9854,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9862,7 +9868,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9898,7 +9904,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9948,7 +9954,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9962,7 +9968,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9998,7 +10004,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10012,7 +10018,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10048,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10062,7 +10068,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10098,7 +10104,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10112,7 +10118,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10148,7 +10154,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10162,7 +10168,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10198,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10212,7 +10218,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10248,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10262,7 +10268,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10298,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10312,7 +10318,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10348,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10362,7 +10368,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10398,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10412,7 +10418,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10448,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10462,7 +10468,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10498,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10512,7 +10518,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10548,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10562,7 +10568,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10598,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10612,7 +10618,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10648,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10662,7 +10668,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10698,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10712,7 +10718,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10748,7 +10754,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10762,7 +10768,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10798,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10812,7 +10818,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10848,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10862,7 +10868,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10898,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10912,7 +10918,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10948,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10962,7 +10968,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10998,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11012,7 +11018,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11048,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11062,7 +11068,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11098,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11112,7 +11118,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11148,7 +11154,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11162,7 +11168,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11198,7 +11204,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11212,7 +11218,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11248,7 +11254,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11262,7 +11268,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11298,7 +11304,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11312,7 +11318,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11348,7 +11354,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11362,7 +11368,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11398,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11412,7 +11418,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11448,7 +11454,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11462,7 +11468,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11498,7 +11504,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11512,7 +11518,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11548,7 +11554,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11562,7 +11568,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11598,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11612,7 +11618,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11648,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11662,7 +11668,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11698,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11712,7 +11718,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11748,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11762,7 +11768,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11798,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11812,7 +11818,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11848,7 +11854,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11862,7 +11868,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11898,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11912,7 +11918,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11962,7 +11968,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11998,7 +12004,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12048,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12062,7 +12068,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12098,7 +12104,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12112,7 +12118,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12148,7 +12154,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12162,7 +12168,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12198,7 +12204,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12212,7 +12218,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12248,7 +12254,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12298,7 +12304,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12312,7 +12318,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12348,7 +12354,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12362,7 +12368,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12398,7 +12404,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12412,7 +12418,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12448,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12498,7 +12504,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12548,7 +12554,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12562,7 +12568,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12598,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12612,7 +12618,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12648,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12662,7 +12668,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12698,7 +12704,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12712,7 +12718,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12748,7 +12754,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12759,34 +12765,34 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>3.083215490503335</v>
+        <v>3.53364299489855</v>
       </c>
       <c r="D233" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E233">
-        <v>0.8398439341981927</v>
+        <v>1.25406141599985</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07791678450949667</v>
+        <v>0.07490635700510145</v>
       </c>
       <c r="H233">
-        <v>0.07332015606580179</v>
+        <v>0.07290593858400016</v>
       </c>
       <c r="I233">
-        <v>2.243371556305142</v>
+        <v>2.2795815788987</v>
       </c>
       <c r="J233">
-        <v>0.941302754955891</v>
+        <v>0.9305438593246792</v>
       </c>
       <c r="K233">
-        <v>39.75</v>
+        <v>38.35</v>
       </c>
       <c r="L233">
-        <v>40.5</v>
+        <v>39.22</v>
       </c>
       <c r="M233">
         <v>38.5</v>
@@ -12798,21 +12804,21 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B234" t="s">
         <v>73</v>
       </c>
       <c r="C234">
-        <v>3.121039347441581</v>
+        <v>3.083215490503335</v>
       </c>
       <c r="D234" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E234">
         <v>0.8398439341981927</v>
@@ -12821,22 +12827,22 @@
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07531896065255841</v>
+        <v>0.07791678450949667</v>
       </c>
       <c r="H234">
         <v>0.07332015606580179</v>
       </c>
       <c r="I234">
-        <v>2.281195413243388</v>
+        <v>2.243371556305142</v>
       </c>
       <c r="J234">
         <v>0.941302754955891</v>
       </c>
       <c r="K234">
-        <v>38.35</v>
+        <v>39.75</v>
       </c>
       <c r="L234">
-        <v>39.22</v>
+        <v>40.5</v>
       </c>
       <c r="M234">
         <v>38.5</v>
@@ -12856,13 +12862,13 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C235">
         <v>2.581230174431482</v>
       </c>
       <c r="D235" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E235">
         <v>0.3536443198896109</v>
@@ -12898,7 +12904,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12906,13 +12912,13 @@
         <v>0</v>
       </c>
       <c r="B236" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C236">
-        <v>2.146681830202255</v>
+        <v>2.093709160165531</v>
       </c>
       <c r="D236" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E236">
         <v>-0.06723898206826107</v>
@@ -12921,22 +12927,22 @@
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07885331816979775</v>
+        <v>0.07918629083983447</v>
       </c>
       <c r="H236">
         <v>0.07422723898206826</v>
       </c>
       <c r="I236">
-        <v>2.213920812270516</v>
+        <v>2.160948142233792</v>
       </c>
       <c r="J236">
         <v>0.9648633501835912</v>
       </c>
       <c r="K236">
-        <v>39.75</v>
+        <v>39.95</v>
       </c>
       <c r="L236">
-        <v>40.5</v>
+        <v>40.64</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12956,13 +12962,13 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C237">
-        <v>1.66235731631032</v>
+        <v>1.606947793373521</v>
       </c>
       <c r="D237" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E237">
         <v>-0.5363331653346535</v>
@@ -12971,22 +12977,22 @@
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.07933764268368969</v>
+        <v>0.07967305220662649</v>
       </c>
       <c r="H237">
         <v>0.07469633316533465</v>
       </c>
       <c r="I237">
-        <v>2.198690481644974</v>
+        <v>2.143280958708175</v>
       </c>
       <c r="J237">
         <v>0.977047614684017</v>
       </c>
       <c r="K237">
-        <v>39.75</v>
+        <v>39.95</v>
       </c>
       <c r="L237">
-        <v>40.5</v>
+        <v>40.64</v>
       </c>
       <c r="M237">
         <v>38.5</v>
@@ -12998,7 +13004,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13006,37 +13012,37 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C238">
-        <v>1.212494861209947</v>
+        <v>-0.1382969714751567</v>
       </c>
       <c r="D238" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E238">
-        <v>-0.9720490023501114</v>
+        <v>-1.664486787769654</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.07978750513879006</v>
+        <v>0.07855829697147516</v>
       </c>
       <c r="H238">
-        <v>0.0751320490023501</v>
+        <v>0.07582448678776965</v>
       </c>
       <c r="I238">
-        <v>2.184543863560059</v>
+        <v>1.526189816294497</v>
       </c>
       <c r="J238">
-        <v>0.988364909151951</v>
+        <v>1.006350306175835</v>
       </c>
       <c r="K238">
-        <v>39.75</v>
+        <v>39.1</v>
       </c>
       <c r="L238">
-        <v>40.5</v>
+        <v>39.21</v>
       </c>
       <c r="M238">
         <v>38.5</v>
@@ -13048,7 +13054,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>242</v>
+        <v>70</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13056,49 +13062,49 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C239">
-        <v>-0.1382969714751567</v>
+        <v>-3.293901612234158</v>
       </c>
       <c r="D239" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E239">
-        <v>-1.664486787769654</v>
+        <v>-5.750840545762586</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.07855829697147516</v>
+        <v>0.08053390161223416</v>
       </c>
       <c r="H239">
-        <v>0.07582448678776965</v>
+        <v>0.08411084054576258</v>
       </c>
       <c r="I239">
-        <v>1.526189816294497</v>
+        <v>2.456938933528427</v>
       </c>
       <c r="J239">
-        <v>1.006350306175835</v>
+        <v>1.077478190545865</v>
       </c>
       <c r="K239">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="L239">
-        <v>39.21</v>
+        <v>38.62</v>
       </c>
       <c r="M239">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="N239">
-        <v>37.08</v>
+        <v>39.18</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>70</v>
+        <v>245</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13106,49 +13112,49 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C240">
-        <v>-3.293901612234158</v>
+        <v>-4.191976702465361</v>
       </c>
       <c r="D240" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E240">
-        <v>-5.750840545762586</v>
+        <v>-5.706504430403108</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.08053390161223416</v>
+        <v>0.08849197670246536</v>
       </c>
       <c r="H240">
-        <v>0.08411084054576258</v>
+        <v>0.0873065044304031</v>
       </c>
       <c r="I240">
-        <v>2.456938933528427</v>
+        <v>1.514527727937747</v>
       </c>
       <c r="J240">
-        <v>1.077478190545865</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K240">
-        <v>38.9</v>
+        <v>42.25</v>
       </c>
       <c r="L240">
-        <v>38.62</v>
+        <v>42.15</v>
       </c>
       <c r="M240">
-        <v>41.7</v>
+        <v>42.4</v>
       </c>
       <c r="N240">
-        <v>39.18</v>
+        <v>40.8</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13156,31 +13162,31 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C241">
-        <v>-4.191976702465361</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D241" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E241">
-        <v>-5.706504430403108</v>
+        <v>-6.044764406415567</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.08849197670246536</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H241">
-        <v>0.0873065044304031</v>
+        <v>0.08764476440641557</v>
       </c>
       <c r="I241">
-        <v>1.514527727937747</v>
+        <v>1.515724402381188</v>
       </c>
       <c r="J241">
-        <v>1.096851519584979</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K241">
         <v>42.25</v>
@@ -13198,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13206,231 +13212,231 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C242">
-        <v>-4.529040004034378</v>
+        <v>-5.123690195894106</v>
       </c>
       <c r="D242" t="s">
         <v>137</v>
       </c>
       <c r="E242">
-        <v>-6.044764406415567</v>
+        <v>-7.293184163304637</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.08882904000403437</v>
+        <v>0.07634369019589411</v>
       </c>
       <c r="H242">
-        <v>0.08764476440641557</v>
+        <v>0.08565318416330464</v>
       </c>
       <c r="I242">
-        <v>1.515724402381188</v>
+        <v>2.169493967410531</v>
       </c>
       <c r="J242">
-        <v>1.104829349207914</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K242">
-        <v>42.25</v>
+        <v>36.55</v>
       </c>
       <c r="L242">
-        <v>42.15</v>
+        <v>35.61</v>
       </c>
       <c r="M242">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="N242">
-        <v>40.8</v>
+        <v>39.18</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>245</v>
+        <v>136</v>
       </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B243" t="s">
         <v>77</v>
       </c>
       <c r="C243">
-        <v>-5.123690195894106</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D243" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E243">
-        <v>-7.293184163304637</v>
+        <v>-6.453309556933249</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.07634369019589411</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H243">
-        <v>0.08565318416330464</v>
+        <v>0.08805330955693325</v>
       </c>
       <c r="I243">
-        <v>2.169493967410531</v>
+        <v>1.517169727206131</v>
       </c>
       <c r="J243">
         <v>1.114464848040879</v>
       </c>
       <c r="K243">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L243">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M243">
-        <v>41.7</v>
+        <v>42.4</v>
       </c>
       <c r="N243">
-        <v>39.18</v>
+        <v>40.8</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="244" spans="1:16">
       <c r="A244" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C244">
-        <v>-4.936139829727118</v>
+        <v>-5.523389518570603</v>
       </c>
       <c r="D244" t="s">
         <v>137</v>
       </c>
       <c r="E244">
-        <v>-6.453309556933249</v>
+        <v>-7.749202268793276</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.08923613982972711</v>
+        <v>0.07674338951857061</v>
       </c>
       <c r="H244">
-        <v>0.08805330955693325</v>
+        <v>0.08610920226879328</v>
       </c>
       <c r="I244">
-        <v>1.517169727206131</v>
+        <v>2.225812750222673</v>
       </c>
       <c r="J244">
-        <v>1.114464848040879</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K244">
-        <v>42.25</v>
+        <v>36.55</v>
       </c>
       <c r="L244">
-        <v>42.15</v>
+        <v>35.61</v>
       </c>
       <c r="M244">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="N244">
-        <v>40.8</v>
+        <v>39.18</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B245" t="s">
         <v>77</v>
       </c>
       <c r="C245">
-        <v>-5.523389518570603</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D245" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E245">
-        <v>-7.749202268793276</v>
+        <v>-6.916982642609952</v>
       </c>
       <c r="F245">
         <v>-1</v>
       </c>
       <c r="G245">
-        <v>0.07674338951857061</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H245">
-        <v>0.08610920226879328</v>
+        <v>0.08851698264260995</v>
       </c>
       <c r="I245">
-        <v>2.225812750222673</v>
+        <v>1.518810080103577</v>
       </c>
       <c r="J245">
         <v>1.12540053402382</v>
       </c>
       <c r="K245">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L245">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M245">
-        <v>41.7</v>
+        <v>42.4</v>
       </c>
       <c r="N245">
-        <v>39.18</v>
+        <v>40.8</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="246" spans="1:16">
       <c r="A246" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C246">
-        <v>-5.398172562506375</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D246" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E246">
-        <v>-6.916982642609952</v>
+        <v>-7.572564086157946</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.08969817256250637</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H246">
-        <v>0.08851698264260995</v>
+        <v>0.08857256408615793</v>
       </c>
       <c r="I246">
-        <v>1.518810080103577</v>
+        <v>1.706823361803963</v>
       </c>
       <c r="J246">
-        <v>1.12540053402382</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13439,16 +13445,16 @@
         <v>42.15</v>
       </c>
       <c r="M246">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N246">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>246</v>
+        <v>78</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13456,31 +13462,31 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C247">
-        <v>-5.865740724353984</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D247" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E247">
-        <v>-7.572564086157946</v>
+        <v>-8.064128347698443</v>
       </c>
       <c r="F247">
         <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.09016574072435399</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H247">
-        <v>0.08857256408615793</v>
+        <v>0.08906412834769845</v>
       </c>
       <c r="I247">
-        <v>1.706823361803963</v>
+        <v>1.707404407030374</v>
       </c>
       <c r="J247">
-        <v>1.136467236079384</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K247">
         <v>42.25</v>
@@ -13498,7 +13504,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>77</v>
+        <v>249</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13506,31 +13512,31 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C248">
-        <v>-6.356723940668068</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D248" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E248">
-        <v>-8.064128347698443</v>
+        <v>-8.479255447258403</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09065672394066807</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H248">
-        <v>0.08906412834769845</v>
+        <v>0.0894792554472584</v>
       </c>
       <c r="I248">
-        <v>1.707404407030374</v>
+        <v>1.707895101001483</v>
       </c>
       <c r="J248">
-        <v>1.148088140607528</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13548,7 +13554,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13556,31 +13562,31 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C249">
-        <v>-6.77136034625692</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D249" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E249">
-        <v>-8.479255447258403</v>
+        <v>-8.821093763337437</v>
       </c>
       <c r="F249">
         <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.09107136034625692</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H249">
-        <v>0.0894792554472584</v>
+        <v>0.08982109376333744</v>
       </c>
       <c r="I249">
-        <v>1.707895101001483</v>
+        <v>1.708299165204885</v>
       </c>
       <c r="J249">
-        <v>1.15790202002975</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K249">
         <v>42.25</v>
@@ -13598,7 +13604,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13606,31 +13612,31 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C250">
-        <v>-7.112794598132552</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D250" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E250">
-        <v>-8.821093763337437</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F250">
         <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09141279459813255</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H250">
-        <v>0.08982109376333744</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I250">
-        <v>1.708299165204885</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J250">
-        <v>1.165983304097812</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K250">
         <v>42.25</v>
@@ -13639,16 +13645,16 @@
         <v>42.15</v>
       </c>
       <c r="M250">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N250">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O250">
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13656,31 +13662,31 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C251">
-        <v>-7.379527992135429</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D251" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E251">
-        <v>-9.088142818161622</v>
+        <v>-9.411697962594936</v>
       </c>
       <c r="F251">
         <v>-1</v>
       </c>
       <c r="G251">
-        <v>0.09167952799213544</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H251">
-        <v>0.09008814281816163</v>
+        <v>0.09041169796259493</v>
       </c>
       <c r="I251">
-        <v>1.708614826026192</v>
+        <v>1.708997278915596</v>
       </c>
       <c r="J251">
-        <v>1.172296520523916</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K251">
         <v>42.25</v>
@@ -13698,7 +13704,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13706,31 +13712,31 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C252">
-        <v>-7.702700683679339</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D252" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E252">
-        <v>-9.411697962594936</v>
+        <v>-9.71045774330846</v>
       </c>
       <c r="F252">
         <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.09200270068367934</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H252">
-        <v>0.09041169796259493</v>
+        <v>0.09071045774330846</v>
       </c>
       <c r="I252">
-        <v>1.708997278915596</v>
+        <v>1.709350422864425</v>
       </c>
       <c r="J252">
-        <v>1.179945578311937</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K252">
         <v>42.25</v>
@@ -13748,7 +13754,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13756,31 +13762,31 @@
         <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C253">
-        <v>-8.001107320444035</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D253" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E253">
-        <v>-9.71045774330846</v>
+        <v>-9.98998139082147</v>
       </c>
       <c r="F253">
         <v>-1</v>
       </c>
       <c r="G253">
-        <v>0.09230110732044404</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H253">
-        <v>0.09071045774330846</v>
+        <v>0.09098998139082147</v>
       </c>
       <c r="I253">
-        <v>1.709350422864425</v>
+        <v>1.70968082906716</v>
       </c>
       <c r="J253">
-        <v>1.187008457288616</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K253">
         <v>42.25</v>
@@ -13798,7 +13804,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13806,31 +13812,31 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C254">
-        <v>-8.280300561754309</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D254" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E254">
-        <v>-9.98998139082147</v>
+        <v>-10.33511567158328</v>
       </c>
       <c r="F254">
         <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.09258030056175431</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H254">
-        <v>0.09098998139082147</v>
+        <v>0.09133511567158328</v>
       </c>
       <c r="I254">
-        <v>1.70968082906716</v>
+        <v>1.710088789209905</v>
       </c>
       <c r="J254">
-        <v>1.193616581343297</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K254">
         <v>42.25</v>
@@ -13848,7 +13854,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13856,31 +13862,31 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C255">
-        <v>-8.625026882373376</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D255" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E255">
-        <v>-10.33511567158328</v>
+        <v>-10.55673944514221</v>
       </c>
       <c r="F255">
         <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.09292502688237338</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H255">
-        <v>0.09133511567158328</v>
+        <v>0.09155673944514221</v>
       </c>
       <c r="I255">
-        <v>1.710088789209905</v>
+        <v>1.710350755845319</v>
       </c>
       <c r="J255">
-        <v>1.201775784198186</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K255">
         <v>42.25</v>
@@ -13898,7 +13904,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13906,31 +13912,31 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C256">
-        <v>-8.846388689296894</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D256" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E256">
-        <v>-10.55673944514221</v>
+        <v>-10.83464661792213</v>
       </c>
       <c r="F256">
         <v>-1</v>
       </c>
       <c r="G256">
-        <v>0.09314638868929688</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H256">
-        <v>0.09155673944514221</v>
+        <v>0.09183464661792212</v>
       </c>
       <c r="I256">
-        <v>1.710350755845319</v>
+        <v>1.710679251321416</v>
       </c>
       <c r="J256">
-        <v>1.207015116906435</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K256">
         <v>42.25</v>
@@ -13948,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13956,31 +13962,31 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C257">
-        <v>-9.123967366600709</v>
+        <v>-9.62255528559681</v>
       </c>
       <c r="D257" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E257">
-        <v>-10.83464661792213</v>
+        <v>-11.33382458179278</v>
       </c>
       <c r="F257">
         <v>-1</v>
       </c>
       <c r="G257">
-        <v>0.0934239673666007</v>
+        <v>0.09392255528559681</v>
       </c>
       <c r="H257">
-        <v>0.09183464661792212</v>
+        <v>0.09233382458179279</v>
       </c>
       <c r="I257">
-        <v>1.710679251321416</v>
+        <v>1.711269296195965</v>
       </c>
       <c r="J257">
-        <v>1.213585026428419</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K257">
         <v>42.25</v>
@@ -13998,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14006,31 +14012,31 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C258">
-        <v>-9.62255528559681</v>
+        <v>-9.818321109702786</v>
       </c>
       <c r="D258" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E258">
-        <v>-11.15636317418473</v>
+        <v>-11.52982208143024</v>
       </c>
       <c r="F258">
         <v>-1</v>
       </c>
       <c r="G258">
-        <v>0.09392255528559681</v>
+        <v>0.09411832110970278</v>
       </c>
       <c r="H258">
-        <v>0.09275636317418472</v>
+        <v>0.09252982208143024</v>
       </c>
       <c r="I258">
-        <v>1.533807888587916</v>
+        <v>1.711500971727453</v>
       </c>
       <c r="J258">
-        <v>1.225385923919451</v>
+        <v>1.230019434549178</v>
       </c>
       <c r="K258">
         <v>42.25</v>
@@ -14039,16 +14045,16 @@
         <v>42.15</v>
       </c>
       <c r="M258">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N258">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O258">
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14056,31 +14062,31 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C259">
-        <v>-9.818321109702786</v>
+        <v>-10.0736945186401</v>
       </c>
       <c r="D259" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E259">
-        <v>-11.35282402488517</v>
+        <v>-11.60910408497847</v>
       </c>
       <c r="F259">
         <v>-1</v>
       </c>
       <c r="G259">
-        <v>0.09411832110970278</v>
+        <v>0.0943736945186401</v>
       </c>
       <c r="H259">
-        <v>0.09295282402488517</v>
+        <v>0.09320910408497847</v>
       </c>
       <c r="I259">
-        <v>1.534502915182379</v>
+        <v>1.535409566338366</v>
       </c>
       <c r="J259">
-        <v>1.230019434549178</v>
+        <v>1.236063775589115</v>
       </c>
       <c r="K259">
         <v>42.25</v>
@@ -14098,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14106,31 +14112,31 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C260">
-        <v>-10.0736945186401</v>
+        <v>-10.27048417828931</v>
       </c>
       <c r="D260" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E260">
-        <v>-11.60910408497847</v>
+        <v>-11.80659240614123</v>
       </c>
       <c r="F260">
         <v>-1</v>
       </c>
       <c r="G260">
-        <v>0.0943736945186401</v>
+        <v>0.09457048417828931</v>
       </c>
       <c r="H260">
-        <v>0.09320910408497847</v>
+        <v>0.09340659240614121</v>
       </c>
       <c r="I260">
-        <v>1.535409566338366</v>
+        <v>1.536108227851919</v>
       </c>
       <c r="J260">
-        <v>1.236063775589115</v>
+        <v>1.240721519012765</v>
       </c>
       <c r="K260">
         <v>42.25</v>
@@ -14148,57 +14154,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16">
-      <c r="A261" s="1">
-        <v>0</v>
-      </c>
-      <c r="B261" t="s">
-        <v>76</v>
-      </c>
-      <c r="C261">
-        <v>-10.27048417828931</v>
-      </c>
-      <c r="D261" t="s">
-        <v>137</v>
-      </c>
-      <c r="E261">
-        <v>-11.80659240614123</v>
-      </c>
-      <c r="F261">
-        <v>-1</v>
-      </c>
-      <c r="G261">
-        <v>0.09457048417828931</v>
-      </c>
-      <c r="H261">
-        <v>0.09340659240614121</v>
-      </c>
-      <c r="I261">
-        <v>1.536108227851919</v>
-      </c>
-      <c r="J261">
-        <v>1.240721519012765</v>
-      </c>
-      <c r="K261">
-        <v>42.25</v>
-      </c>
-      <c r="L261">
-        <v>42.15</v>
-      </c>
-      <c r="M261">
-        <v>42.4</v>
-      </c>
-      <c r="N261">
-        <v>40.8</v>
-      </c>
-      <c r="O261">
-        <v>1</v>
-      </c>
-      <c r="P261" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="260">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,546 +232,546 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-07-07</t>
-  </si>
-  <si>
     <t>2021-07-06</t>
   </si>
   <si>
     <t>2021-07-13</t>
   </si>
   <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-14</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-28</t>
   </si>
   <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-14</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-08-02</t>
   </si>
   <si>
     <t>2021-08-03</t>
   </si>
   <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-08-02</t>
-  </si>
-  <si>
     <t>2021-08-04</t>
   </si>
   <si>
@@ -794,12 +794,6 @@
   </si>
   <si>
     <t>2021-08-16</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P260"/>
+  <dimension ref="A1:P259"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1318,7 +1312,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1368,7 +1362,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1418,7 +1412,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1468,7 +1462,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1618,7 +1612,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1668,7 +1662,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1718,7 +1712,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1768,7 +1762,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1818,7 +1812,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1868,7 +1862,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1918,7 +1912,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1968,7 +1962,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -2018,7 +2012,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2068,7 +2062,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2118,7 +2112,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2168,7 +2162,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2218,7 +2212,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2268,7 +2262,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2318,7 +2312,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2368,7 +2362,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2418,7 +2412,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2468,7 +2462,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2618,7 +2612,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2668,7 +2662,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2718,7 +2712,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2768,7 +2762,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2818,7 +2812,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2868,7 +2862,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2968,7 +2962,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -3018,7 +3012,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3068,7 +3062,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3118,7 +3112,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3168,7 +3162,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3218,7 +3212,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3318,7 +3312,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3368,7 +3362,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3418,7 +3412,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3468,7 +3462,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3518,7 +3512,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3568,7 +3562,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3618,7 +3612,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3668,7 +3662,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3718,7 +3712,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3768,7 +3762,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3818,7 +3812,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3868,7 +3862,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3918,7 +3912,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3968,7 +3962,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -4018,7 +4012,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4068,7 +4062,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4118,7 +4112,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4168,7 +4162,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4218,7 +4212,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4268,7 +4262,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4318,7 +4312,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4368,7 +4362,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4418,7 +4412,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4468,7 +4462,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4518,7 +4512,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4568,7 +4562,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4618,7 +4612,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4668,7 +4662,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4718,7 +4712,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4768,7 +4762,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4818,7 +4812,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4868,7 +4862,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4918,7 +4912,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4968,7 +4962,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -5018,7 +5012,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5068,7 +5062,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5118,7 +5112,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5168,7 +5162,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5218,7 +5212,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5268,7 +5262,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5318,7 +5312,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5368,7 +5362,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5418,7 +5412,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5468,7 +5462,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5518,7 +5512,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5568,7 +5562,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5618,7 +5612,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5668,7 +5662,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5718,7 +5712,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5768,7 +5762,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5818,7 +5812,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5868,7 +5862,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5918,7 +5912,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5968,7 +5962,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -6018,7 +6012,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6068,7 +6062,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6118,7 +6112,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6168,7 +6162,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6218,7 +6212,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6268,7 +6262,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6318,7 +6312,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6368,7 +6362,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6418,7 +6412,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6468,7 +6462,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6518,7 +6512,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6568,7 +6562,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6618,7 +6612,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6668,7 +6662,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6718,7 +6712,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6768,7 +6762,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6818,7 +6812,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6868,7 +6862,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6918,7 +6912,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6968,7 +6962,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -7018,7 +7012,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7068,7 +7062,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7118,7 +7112,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7168,7 +7162,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7218,7 +7212,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7268,7 +7262,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7318,7 +7312,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7368,7 +7362,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7418,7 +7412,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7468,7 +7462,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7518,7 +7512,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7568,7 +7562,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7618,7 +7612,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7668,7 +7662,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7704,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7718,7 +7712,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7754,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7768,7 +7762,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7804,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7818,7 +7812,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7868,7 +7862,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7918,7 +7912,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7968,7 +7962,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -8018,7 +8012,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8068,7 +8062,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8118,7 +8112,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8168,7 +8162,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8218,7 +8212,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8268,7 +8262,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8318,7 +8312,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8368,7 +8362,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8418,7 +8412,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8468,7 +8462,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8518,7 +8512,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8568,7 +8562,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8618,7 +8612,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8668,7 +8662,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8718,7 +8712,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8768,7 +8762,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8818,7 +8812,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8868,7 +8862,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8918,7 +8912,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8968,7 +8962,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -9018,7 +9012,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9068,7 +9062,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9118,7 +9112,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9168,7 +9162,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9218,7 +9212,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9268,7 +9262,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9318,7 +9312,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9368,7 +9362,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9418,7 +9412,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9468,7 +9462,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9518,7 +9512,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9568,7 +9562,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9618,7 +9612,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9668,7 +9662,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9718,7 +9712,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9768,7 +9762,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9818,7 +9812,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9868,7 +9862,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9968,7 +9962,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -10018,7 +10012,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10068,7 +10062,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10118,7 +10112,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10154,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10168,7 +10162,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10204,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10218,7 +10212,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10254,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10268,7 +10262,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10304,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10318,7 +10312,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10354,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10368,7 +10362,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10404,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10418,7 +10412,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10454,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10468,7 +10462,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10504,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10518,7 +10512,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10554,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10568,7 +10562,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10604,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10618,7 +10612,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10668,7 +10662,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10718,7 +10712,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10768,7 +10762,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10818,7 +10812,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10868,7 +10862,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10918,7 +10912,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10968,7 +10962,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -11018,7 +11012,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11068,7 +11062,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11118,7 +11112,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11168,7 +11162,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11218,7 +11212,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11268,7 +11262,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11318,7 +11312,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11368,7 +11362,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11418,7 +11412,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11468,7 +11462,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11518,7 +11512,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11568,7 +11562,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11618,7 +11612,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11668,7 +11662,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11718,7 +11712,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11768,7 +11762,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11818,7 +11812,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11868,7 +11862,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11918,7 +11912,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11968,7 +11962,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -12068,7 +12062,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12118,7 +12112,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12168,7 +12162,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12218,7 +12212,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12318,7 +12312,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12354,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12368,7 +12362,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12404,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12418,7 +12412,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12454,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12604,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12654,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12668,7 +12662,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12718,7 +12712,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12765,34 +12759,34 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>3.53364299489855</v>
+        <v>4.049021235741485</v>
       </c>
       <c r="D233" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E233">
-        <v>1.25406141599985</v>
+        <v>1.775278429586088</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07490635700510145</v>
+        <v>0.07695097876425851</v>
       </c>
       <c r="H233">
-        <v>0.07290593858400016</v>
+        <v>0.07238472157041392</v>
       </c>
       <c r="I233">
-        <v>2.2795815788987</v>
+        <v>2.273742806155397</v>
       </c>
       <c r="J233">
-        <v>0.9305438593246792</v>
+        <v>0.9170057550756859</v>
       </c>
       <c r="K233">
-        <v>38.35</v>
+        <v>39.75</v>
       </c>
       <c r="L233">
-        <v>39.22</v>
+        <v>40.5</v>
       </c>
       <c r="M233">
         <v>38.5</v>
@@ -12804,45 +12798,45 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>243</v>
+        <v>69</v>
       </c>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B234" t="s">
         <v>73</v>
       </c>
       <c r="C234">
-        <v>3.083215490503335</v>
+        <v>4.052829292847441</v>
       </c>
       <c r="D234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E234">
-        <v>0.8398439341981927</v>
+        <v>1.775278429586088</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07791678450949667</v>
+        <v>0.07438717070715256</v>
       </c>
       <c r="H234">
-        <v>0.07332015606580179</v>
+        <v>0.07238472157041392</v>
       </c>
       <c r="I234">
-        <v>2.243371556305142</v>
+        <v>2.277550863261354</v>
       </c>
       <c r="J234">
-        <v>0.941302754955891</v>
+        <v>0.9170057550756859</v>
       </c>
       <c r="K234">
-        <v>39.75</v>
+        <v>38.35</v>
       </c>
       <c r="L234">
-        <v>40.5</v>
+        <v>39.22</v>
       </c>
       <c r="M234">
         <v>38.5</v>
@@ -12854,7 +12848,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -12862,31 +12856,31 @@
         <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C235">
-        <v>2.581230174431482</v>
+        <v>3.510881591844004</v>
       </c>
       <c r="D235" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E235">
-        <v>0.3536443198896109</v>
+        <v>1.25406141599985</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.07841876982556852</v>
+        <v>0.077489118408156</v>
       </c>
       <c r="H235">
-        <v>0.07380635568011039</v>
+        <v>0.07290593858400016</v>
       </c>
       <c r="I235">
-        <v>2.227585854541871</v>
+        <v>2.256820175844155</v>
       </c>
       <c r="J235">
-        <v>0.9539313163665036</v>
+        <v>0.9305438593246792</v>
       </c>
       <c r="K235">
         <v>39.75</v>
@@ -12904,45 +12898,45 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B236" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C236">
-        <v>2.093709160165531</v>
+        <v>3.53364299489855</v>
       </c>
       <c r="D236" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E236">
-        <v>-0.06723898206826107</v>
+        <v>1.25406141599985</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07918629083983447</v>
+        <v>0.07490635700510145</v>
       </c>
       <c r="H236">
-        <v>0.07422723898206826</v>
+        <v>0.07290593858400016</v>
       </c>
       <c r="I236">
-        <v>2.160948142233792</v>
+        <v>2.2795815788987</v>
       </c>
       <c r="J236">
-        <v>0.9648633501835912</v>
+        <v>0.9305438593246792</v>
       </c>
       <c r="K236">
-        <v>39.95</v>
+        <v>38.35</v>
       </c>
       <c r="L236">
-        <v>40.64</v>
+        <v>39.22</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12954,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>71</v>
+        <v>243</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12965,28 +12959,28 @@
         <v>74</v>
       </c>
       <c r="C237">
-        <v>1.606947793373521</v>
+        <v>3.034954939512154</v>
       </c>
       <c r="D237" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E237">
-        <v>-0.5363331653346535</v>
+        <v>0.8398439341981927</v>
       </c>
       <c r="F237">
         <v>-1</v>
       </c>
       <c r="G237">
-        <v>0.07967305220662649</v>
+        <v>0.07824504506048785</v>
       </c>
       <c r="H237">
-        <v>0.07469633316533465</v>
+        <v>0.07332015606580179</v>
       </c>
       <c r="I237">
-        <v>2.143280958708175</v>
+        <v>2.195111005313962</v>
       </c>
       <c r="J237">
-        <v>0.977047614684017</v>
+        <v>0.941302754955891</v>
       </c>
       <c r="K237">
         <v>39.95</v>
@@ -13004,7 +12998,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13012,37 +13006,37 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C238">
-        <v>-0.1382969714751567</v>
+        <v>2.53044391115818</v>
       </c>
       <c r="D238" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E238">
-        <v>-1.664486787769654</v>
+        <v>0.3536443198896109</v>
       </c>
       <c r="F238">
         <v>-1</v>
       </c>
       <c r="G238">
-        <v>0.07855829697147516</v>
+        <v>0.07874955608884182</v>
       </c>
       <c r="H238">
-        <v>0.07582448678776965</v>
+        <v>0.07380635568011039</v>
       </c>
       <c r="I238">
-        <v>1.526189816294497</v>
+        <v>2.176799591268569</v>
       </c>
       <c r="J238">
-        <v>1.006350306175835</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K238">
-        <v>39.1</v>
+        <v>39.95</v>
       </c>
       <c r="L238">
-        <v>39.21</v>
+        <v>40.64</v>
       </c>
       <c r="M238">
         <v>38.5</v>
@@ -13054,7 +13048,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13062,49 +13056,49 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C239">
-        <v>-3.293901612234158</v>
+        <v>2.093709160165531</v>
       </c>
       <c r="D239" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E239">
-        <v>-5.750840545762586</v>
+        <v>-0.06723898206826107</v>
       </c>
       <c r="F239">
         <v>-1</v>
       </c>
       <c r="G239">
-        <v>0.08053390161223416</v>
+        <v>0.07918629083983447</v>
       </c>
       <c r="H239">
-        <v>0.08411084054576258</v>
+        <v>0.07422723898206826</v>
       </c>
       <c r="I239">
-        <v>2.456938933528427</v>
+        <v>2.160948142233792</v>
       </c>
       <c r="J239">
-        <v>1.077478190545865</v>
+        <v>0.9648633501835912</v>
       </c>
       <c r="K239">
-        <v>38.9</v>
+        <v>39.95</v>
       </c>
       <c r="L239">
-        <v>38.62</v>
+        <v>40.64</v>
       </c>
       <c r="M239">
-        <v>41.7</v>
+        <v>38.5</v>
       </c>
       <c r="N239">
-        <v>39.18</v>
+        <v>37.08</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>245</v>
+        <v>71</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13112,49 +13106,49 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C240">
-        <v>-4.191976702465361</v>
+        <v>1.606947793373521</v>
       </c>
       <c r="D240" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E240">
-        <v>-5.706504430403108</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F240">
         <v>-1</v>
       </c>
       <c r="G240">
-        <v>0.08849197670246536</v>
+        <v>0.07967305220662649</v>
       </c>
       <c r="H240">
-        <v>0.0873065044304031</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I240">
-        <v>1.514527727937747</v>
+        <v>2.143280958708175</v>
       </c>
       <c r="J240">
-        <v>1.096851519584979</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K240">
-        <v>42.25</v>
+        <v>39.95</v>
       </c>
       <c r="L240">
-        <v>42.15</v>
+        <v>40.64</v>
       </c>
       <c r="M240">
-        <v>42.4</v>
+        <v>38.5</v>
       </c>
       <c r="N240">
-        <v>40.8</v>
+        <v>37.08</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>246</v>
+        <v>133</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13162,49 +13156,49 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C241">
-        <v>-4.529040004034378</v>
+        <v>-0.1382969714751567</v>
       </c>
       <c r="D241" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E241">
-        <v>-6.044764406415567</v>
+        <v>-1.985913874432278</v>
       </c>
       <c r="F241">
         <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.08882904000403437</v>
+        <v>0.07855829697147516</v>
       </c>
       <c r="H241">
-        <v>0.08764476440641557</v>
+        <v>0.07278591387443228</v>
       </c>
       <c r="I241">
-        <v>1.515724402381188</v>
+        <v>1.847616902957121</v>
       </c>
       <c r="J241">
-        <v>1.104829349207914</v>
+        <v>1.006350306175835</v>
       </c>
       <c r="K241">
-        <v>42.25</v>
+        <v>39.1</v>
       </c>
       <c r="L241">
-        <v>42.15</v>
+        <v>39.21</v>
       </c>
       <c r="M241">
-        <v>42.4</v>
+        <v>37.15</v>
       </c>
       <c r="N241">
-        <v>40.8</v>
+        <v>35.4</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>247</v>
+        <v>70</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13212,81 +13206,81 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C242">
-        <v>-5.123690195894106</v>
+        <v>-4.191976702465361</v>
       </c>
       <c r="D242" t="s">
         <v>137</v>
       </c>
       <c r="E242">
-        <v>-7.293184163304637</v>
+        <v>-5.896819278444603</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.07634369019589411</v>
+        <v>0.08849197670246536</v>
       </c>
       <c r="H242">
-        <v>0.08565318416330464</v>
+        <v>0.08689681927844461</v>
       </c>
       <c r="I242">
-        <v>2.169493967410531</v>
+        <v>1.704842575979242</v>
       </c>
       <c r="J242">
-        <v>1.114464848040879</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K242">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L242">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M242">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="N242">
-        <v>39.18</v>
+        <v>40.5</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>136</v>
+        <v>245</v>
       </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C243">
-        <v>-4.936139829727118</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D243" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E243">
-        <v>-6.453309556933249</v>
+        <v>-6.234281471494768</v>
       </c>
       <c r="F243">
         <v>-1</v>
       </c>
       <c r="G243">
-        <v>0.08923613982972711</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H243">
-        <v>0.08805330955693325</v>
+        <v>0.08723428147149477</v>
       </c>
       <c r="I243">
-        <v>1.517169727206131</v>
+        <v>1.70524146746039</v>
       </c>
       <c r="J243">
-        <v>1.114464848040879</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K243">
         <v>42.25</v>
@@ -13295,16 +13289,16 @@
         <v>42.15</v>
       </c>
       <c r="M243">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N243">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13312,66 +13306,66 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C244">
-        <v>-5.523389518570603</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D244" t="s">
         <v>137</v>
       </c>
       <c r="E244">
-        <v>-7.749202268793276</v>
+        <v>-6.641863072129162</v>
       </c>
       <c r="F244">
         <v>-1</v>
       </c>
       <c r="G244">
-        <v>0.07674338951857061</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H244">
-        <v>0.08610920226879328</v>
+        <v>0.08764186307212915</v>
       </c>
       <c r="I244">
-        <v>2.225812750222673</v>
+        <v>1.705723242402044</v>
       </c>
       <c r="J244">
-        <v>1.12540053402382</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K244">
-        <v>36.55</v>
+        <v>42.25</v>
       </c>
       <c r="L244">
-        <v>35.61</v>
+        <v>42.15</v>
       </c>
       <c r="M244">
-        <v>41.7</v>
+        <v>42.3</v>
       </c>
       <c r="N244">
-        <v>39.18</v>
+        <v>40.5</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>248</v>
+        <v>135</v>
       </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C245">
         <v>-5.398172562506375</v>
       </c>
       <c r="D245" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E245">
-        <v>-6.916982642609952</v>
+        <v>-7.104442589207565</v>
       </c>
       <c r="F245">
         <v>-1</v>
@@ -13380,10 +13374,10 @@
         <v>0.08969817256250637</v>
       </c>
       <c r="H245">
-        <v>0.08851698264260995</v>
+        <v>0.08810444258920756</v>
       </c>
       <c r="I245">
-        <v>1.518810080103577</v>
+        <v>1.706270026701191</v>
       </c>
       <c r="J245">
         <v>1.12540053402382</v>
@@ -13395,16 +13389,16 @@
         <v>42.15</v>
       </c>
       <c r="M245">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="N245">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13412,13 +13406,13 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C246">
         <v>-5.865740724353984</v>
       </c>
       <c r="D246" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E246">
         <v>-7.572564086157946</v>
@@ -13454,7 +13448,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13462,16 +13456,16 @@
         <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C247">
         <v>-6.356723940668068</v>
       </c>
       <c r="D247" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E247">
-        <v>-8.064128347698443</v>
+        <v>-8.080849021151664</v>
       </c>
       <c r="F247">
         <v>-1</v>
@@ -13480,10 +13474,10 @@
         <v>0.09065672394066807</v>
       </c>
       <c r="H247">
-        <v>0.08906412834769845</v>
+        <v>0.08698084902115168</v>
       </c>
       <c r="I247">
-        <v>1.707404407030374</v>
+        <v>1.724125080483596</v>
       </c>
       <c r="J247">
         <v>1.148088140607528</v>
@@ -13495,10 +13489,10 @@
         <v>42.15</v>
       </c>
       <c r="M247">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="N247">
-        <v>40.5</v>
+        <v>39.45</v>
       </c>
       <c r="O247">
         <v>1</v>
@@ -13512,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C248">
         <v>-6.77136034625692</v>
@@ -13521,7 +13515,7 @@
         <v>139</v>
       </c>
       <c r="E248">
-        <v>-8.479255447258403</v>
+        <v>-8.926080801189983</v>
       </c>
       <c r="F248">
         <v>-1</v>
@@ -13530,10 +13524,10 @@
         <v>0.09107136034625692</v>
       </c>
       <c r="H248">
-        <v>0.0894792554472584</v>
+        <v>0.08370608080118999</v>
       </c>
       <c r="I248">
-        <v>1.707895101001483</v>
+        <v>2.154720454933063</v>
       </c>
       <c r="J248">
         <v>1.15790202002975</v>
@@ -13545,16 +13539,16 @@
         <v>42.15</v>
       </c>
       <c r="M248">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N248">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O248">
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>250</v>
+        <v>136</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13562,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C249">
         <v>-7.112794598132552</v>
@@ -13571,7 +13565,7 @@
         <v>139</v>
       </c>
       <c r="E249">
-        <v>-8.821093763337437</v>
+        <v>-9.24933216391247</v>
       </c>
       <c r="F249">
         <v>-1</v>
@@ -13580,10 +13574,10 @@
         <v>0.09141279459813255</v>
       </c>
       <c r="H249">
-        <v>0.08982109376333744</v>
+        <v>0.08402933216391248</v>
       </c>
       <c r="I249">
-        <v>1.708299165204885</v>
+        <v>2.136537565779918</v>
       </c>
       <c r="J249">
         <v>1.165983304097812</v>
@@ -13595,16 +13589,16 @@
         <v>42.15</v>
       </c>
       <c r="M249">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N249">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O249">
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13612,13 +13606,13 @@
         <v>0</v>
       </c>
       <c r="B250" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C250">
         <v>-7.379527992135429</v>
       </c>
       <c r="D250" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E250">
         <v>-9.501860820956622</v>
@@ -13654,7 +13648,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>137</v>
+        <v>251</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -13662,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C251">
         <v>-7.702700683679339</v>
@@ -13671,7 +13665,7 @@
         <v>139</v>
       </c>
       <c r="E251">
-        <v>-9.411697962594936</v>
+        <v>-9.80782313247748</v>
       </c>
       <c r="F251">
         <v>-1</v>
@@ -13680,10 +13674,10 @@
         <v>0.09200270068367934</v>
       </c>
       <c r="H251">
-        <v>0.09041169796259493</v>
+        <v>0.08458782313247748</v>
       </c>
       <c r="I251">
-        <v>1.708997278915596</v>
+        <v>2.105122448798141</v>
       </c>
       <c r="J251">
         <v>1.179945578311937</v>
@@ -13695,10 +13689,10 @@
         <v>42.15</v>
       </c>
       <c r="M251">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N251">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O251">
         <v>1</v>
@@ -13712,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C252">
         <v>-8.001107320444035</v>
@@ -13721,7 +13715,7 @@
         <v>139</v>
       </c>
       <c r="E252">
-        <v>-9.71045774330846</v>
+        <v>-10.09033829154465</v>
       </c>
       <c r="F252">
         <v>-1</v>
@@ -13730,10 +13724,10 @@
         <v>0.09230110732044404</v>
       </c>
       <c r="H252">
-        <v>0.09071045774330846</v>
+        <v>0.08487033829154464</v>
       </c>
       <c r="I252">
-        <v>1.709350422864425</v>
+        <v>2.089230971100612</v>
       </c>
       <c r="J252">
         <v>1.187008457288616</v>
@@ -13745,10 +13739,10 @@
         <v>42.15</v>
       </c>
       <c r="M252">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N252">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O252">
         <v>1</v>
@@ -13759,52 +13753,52 @@
     </row>
     <row r="253" spans="1:16">
       <c r="A253" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B253" t="s">
         <v>77</v>
       </c>
       <c r="C253">
-        <v>-8.280300561754309</v>
+        <v>-11.26849157246293</v>
       </c>
       <c r="D253" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E253">
-        <v>-9.98998139082147</v>
+        <v>-11.81055975563346</v>
       </c>
       <c r="F253">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G253">
-        <v>0.09258030056175431</v>
+        <v>0.09864849157246292</v>
       </c>
       <c r="H253">
-        <v>0.09098998139082147</v>
+        <v>0.1032105597556335</v>
       </c>
       <c r="I253">
-        <v>1.70968082906716</v>
+        <v>-0.5420681831705281</v>
       </c>
       <c r="J253">
-        <v>1.193616581343297</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K253">
-        <v>42.25</v>
+        <v>46.3</v>
       </c>
       <c r="L253">
-        <v>42.15</v>
+        <v>43.69</v>
       </c>
       <c r="M253">
-        <v>42.3</v>
+        <v>48.45</v>
       </c>
       <c r="N253">
-        <v>40.5</v>
+        <v>45.7</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13812,31 +13806,31 @@
         <v>0</v>
       </c>
       <c r="B254" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C254">
-        <v>-8.625026882373376</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D254" t="s">
         <v>139</v>
       </c>
       <c r="E254">
-        <v>-10.33511567158328</v>
+        <v>-10.35466325373189</v>
       </c>
       <c r="F254">
         <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.09292502688237338</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H254">
-        <v>0.09133511567158328</v>
+        <v>0.0851346632537319</v>
       </c>
       <c r="I254">
-        <v>1.710088789209905</v>
+        <v>2.074362691977583</v>
       </c>
       <c r="J254">
-        <v>1.201775784198186</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K254">
         <v>42.25</v>
@@ -13845,16 +13839,16 @@
         <v>42.15</v>
       </c>
       <c r="M254">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N254">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O254">
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -13862,31 +13856,31 @@
         <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C255">
-        <v>-8.846388689296894</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D255" t="s">
         <v>139</v>
       </c>
       <c r="E255">
-        <v>-10.55673944514221</v>
+        <v>-10.68103136792746</v>
       </c>
       <c r="F255">
         <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.09314638868929688</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H255">
-        <v>0.09155673944514221</v>
+        <v>0.08546103136792746</v>
       </c>
       <c r="I255">
-        <v>1.710350755845319</v>
+        <v>2.056004485554084</v>
       </c>
       <c r="J255">
-        <v>1.207015116906435</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K255">
         <v>42.25</v>
@@ -13895,16 +13889,16 @@
         <v>42.15</v>
       </c>
       <c r="M255">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N255">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O255">
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13912,31 +13906,31 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C256">
-        <v>-9.123967366600709</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D256" t="s">
         <v>139</v>
       </c>
       <c r="E256">
-        <v>-10.83464661792213</v>
+        <v>-10.89060467625741</v>
       </c>
       <c r="F256">
         <v>-1</v>
       </c>
       <c r="G256">
-        <v>0.0934239673666007</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H256">
-        <v>0.09183464661792212</v>
+        <v>0.08567060467625741</v>
       </c>
       <c r="I256">
-        <v>1.710679251321416</v>
+        <v>2.044215986960516</v>
       </c>
       <c r="J256">
-        <v>1.213585026428419</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K256">
         <v>42.25</v>
@@ -13945,16 +13939,16 @@
         <v>42.15</v>
       </c>
       <c r="M256">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N256">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O256">
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13962,31 +13956,31 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C257">
-        <v>-9.62255528559681</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D257" t="s">
         <v>139</v>
       </c>
       <c r="E257">
-        <v>-11.33382458179278</v>
+        <v>-11.15340105713676</v>
       </c>
       <c r="F257">
         <v>-1</v>
       </c>
       <c r="G257">
-        <v>0.09392255528559681</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H257">
-        <v>0.09233382458179279</v>
+        <v>0.08593340105713676</v>
       </c>
       <c r="I257">
-        <v>1.711269296195965</v>
+        <v>2.029433690536052</v>
       </c>
       <c r="J257">
-        <v>1.225385923919451</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K257">
         <v>42.25</v>
@@ -13995,16 +13989,16 @@
         <v>42.15</v>
       </c>
       <c r="M257">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N257">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O257">
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14012,31 +14006,31 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C258">
-        <v>-9.818321109702786</v>
+        <v>-9.62255528559681</v>
       </c>
       <c r="D258" t="s">
         <v>139</v>
       </c>
       <c r="E258">
-        <v>-11.52982208143024</v>
+        <v>-11.62543695677805</v>
       </c>
       <c r="F258">
         <v>-1</v>
       </c>
       <c r="G258">
-        <v>0.09411832110970278</v>
+        <v>0.09392255528559681</v>
       </c>
       <c r="H258">
-        <v>0.09252982208143024</v>
+        <v>0.08640543695677805</v>
       </c>
       <c r="I258">
-        <v>1.711500971727453</v>
+        <v>2.002881671181235</v>
       </c>
       <c r="J258">
-        <v>1.230019434549178</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K258">
         <v>42.25</v>
@@ -14045,16 +14039,16 @@
         <v>42.15</v>
       </c>
       <c r="M258">
-        <v>42.3</v>
+        <v>40</v>
       </c>
       <c r="N258">
-        <v>40.5</v>
+        <v>37.39</v>
       </c>
       <c r="O258">
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14062,31 +14056,31 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C259">
-        <v>-10.0736945186401</v>
+        <v>-9.818321109702786</v>
       </c>
       <c r="D259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E259">
-        <v>-11.60910408497847</v>
+        <v>-11.81077738196714</v>
       </c>
       <c r="F259">
         <v>-1</v>
       </c>
       <c r="G259">
-        <v>0.0943736945186401</v>
+        <v>0.09411832110970278</v>
       </c>
       <c r="H259">
-        <v>0.09320910408497847</v>
+        <v>0.08659077738196715</v>
       </c>
       <c r="I259">
-        <v>1.535409566338366</v>
+        <v>1.992456272264349</v>
       </c>
       <c r="J259">
-        <v>1.236063775589115</v>
+        <v>1.230019434549178</v>
       </c>
       <c r="K259">
         <v>42.25</v>
@@ -14095,66 +14089,16 @@
         <v>42.15</v>
       </c>
       <c r="M259">
-        <v>42.4</v>
+        <v>40</v>
       </c>
       <c r="N259">
-        <v>40.8</v>
+        <v>37.39</v>
       </c>
       <c r="O259">
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16">
-      <c r="A260" s="1">
-        <v>0</v>
-      </c>
-      <c r="B260" t="s">
-        <v>77</v>
-      </c>
-      <c r="C260">
-        <v>-10.27048417828931</v>
-      </c>
-      <c r="D260" t="s">
-        <v>138</v>
-      </c>
-      <c r="E260">
-        <v>-11.80659240614123</v>
-      </c>
-      <c r="F260">
-        <v>-1</v>
-      </c>
-      <c r="G260">
-        <v>0.09457048417828931</v>
-      </c>
-      <c r="H260">
-        <v>0.09340659240614121</v>
-      </c>
-      <c r="I260">
-        <v>1.536108227851919</v>
-      </c>
-      <c r="J260">
-        <v>1.240721519012765</v>
-      </c>
-      <c r="K260">
-        <v>42.25</v>
-      </c>
-      <c r="L260">
-        <v>42.15</v>
-      </c>
-      <c r="M260">
-        <v>42.4</v>
-      </c>
-      <c r="N260">
-        <v>40.8</v>
-      </c>
-      <c r="O260">
-        <v>1</v>
-      </c>
-      <c r="P260" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="260">
   <si>
     <t>trade_time</t>
   </si>
@@ -241,529 +241,529 @@
     <t>2021-07-06</t>
   </si>
   <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
     <t>2021-07-13</t>
   </si>
   <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
     <t>2021-07-14</t>
   </si>
   <si>
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-07-30</t>
-  </si>
-  <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-08-02</t>
@@ -1151,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P259"/>
+  <dimension ref="A1:P271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1248,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1298,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1312,7 +1312,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1348,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1362,7 +1362,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1412,7 +1412,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1462,7 +1462,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1498,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1548,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1612,7 +1612,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1648,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1662,7 +1662,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1712,7 +1712,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1762,7 +1762,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1812,7 +1812,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1848,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1862,7 +1862,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1898,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1912,7 +1912,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1962,7 +1962,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2012,7 +2012,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2048,7 +2048,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2062,7 +2062,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2112,7 +2112,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2148,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2162,7 +2162,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2212,7 +2212,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2262,7 +2262,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2312,7 +2312,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2348,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2362,7 +2362,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2412,7 +2412,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2448,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2462,7 +2462,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2548,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2612,7 +2612,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2648,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2662,7 +2662,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2712,7 +2712,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2748,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2762,7 +2762,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2812,7 +2812,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2862,7 +2862,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2898,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2948,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2962,7 +2962,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2998,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3012,7 +3012,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3048,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3062,7 +3062,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3098,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3112,7 +3112,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3148,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3162,7 +3162,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3198,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3212,7 +3212,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3248,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3298,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3312,7 +3312,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3348,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3362,7 +3362,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3412,7 +3412,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3448,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3462,7 +3462,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3512,7 +3512,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3548,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3562,7 +3562,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3598,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3612,7 +3612,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3648,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3662,7 +3662,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3698,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3712,7 +3712,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3762,7 +3762,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3812,7 +3812,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3848,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3862,7 +3862,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3898,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3912,7 +3912,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3948,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3962,7 +3962,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3998,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4012,7 +4012,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4048,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4062,7 +4062,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4098,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4112,7 +4112,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4148,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4162,7 +4162,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4212,7 +4212,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4248,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4262,7 +4262,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4298,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4312,7 +4312,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4348,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4362,7 +4362,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4398,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4412,7 +4412,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4448,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4462,7 +4462,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4498,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4512,7 +4512,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4548,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4562,7 +4562,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4612,7 +4612,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4662,7 +4662,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4712,7 +4712,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4748,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4762,7 +4762,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4798,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4812,7 +4812,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4848,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4862,7 +4862,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4898,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4912,7 +4912,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4948,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4962,7 +4962,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4998,7 +4998,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5012,7 +5012,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5062,7 +5062,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5112,7 +5112,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5148,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5162,7 +5162,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5198,7 +5198,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5212,7 +5212,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5248,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5262,7 +5262,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5298,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5312,7 +5312,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5348,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5362,7 +5362,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5398,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5412,7 +5412,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5448,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5462,7 +5462,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5512,7 +5512,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5562,7 +5562,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5598,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5612,7 +5612,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5662,7 +5662,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5698,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5712,7 +5712,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5748,7 +5748,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5762,7 +5762,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5798,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5812,7 +5812,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5848,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5862,7 +5862,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5898,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5912,7 +5912,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5948,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5962,7 +5962,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5998,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6012,7 +6012,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6048,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6062,7 +6062,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6098,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6112,7 +6112,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6148,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6162,7 +6162,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6198,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6212,7 +6212,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6262,7 +6262,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6298,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6312,7 +6312,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6348,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6362,7 +6362,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6398,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6412,7 +6412,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6448,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6462,7 +6462,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6498,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6512,7 +6512,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6548,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6562,7 +6562,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6612,7 +6612,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6662,7 +6662,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6712,7 +6712,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6762,7 +6762,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6812,7 +6812,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6848,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6862,7 +6862,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6898,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6912,7 +6912,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6948,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6962,7 +6962,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6998,7 +6998,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7012,7 +7012,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7048,7 +7048,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7062,7 +7062,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7112,7 +7112,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7162,7 +7162,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7212,7 +7212,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7262,7 +7262,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7298,7 +7298,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7312,7 +7312,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7362,7 +7362,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7398,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7412,7 +7412,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7448,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7462,7 +7462,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7498,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7512,7 +7512,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7548,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7562,7 +7562,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7598,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7612,7 +7612,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7648,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7662,7 +7662,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7698,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7712,7 +7712,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7748,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7762,7 +7762,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7798,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7812,7 +7812,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7848,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7862,7 +7862,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7898,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7912,7 +7912,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7948,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7962,7 +7962,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7998,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8012,7 +8012,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8048,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8062,7 +8062,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8098,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8112,7 +8112,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8148,7 +8148,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8162,7 +8162,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8198,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8212,7 +8212,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8248,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8262,7 +8262,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8298,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8312,7 +8312,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8348,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8362,7 +8362,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8398,7 +8398,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8412,7 +8412,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8448,7 +8448,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8462,7 +8462,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8498,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8512,7 +8512,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8548,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8562,7 +8562,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8598,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8612,7 +8612,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8648,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8662,7 +8662,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8712,7 +8712,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8748,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8762,7 +8762,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8798,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8812,7 +8812,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8848,7 +8848,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8862,7 +8862,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8898,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8912,7 +8912,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8948,7 +8948,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8962,7 +8962,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8998,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9012,7 +9012,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9048,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9062,7 +9062,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9098,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9112,7 +9112,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9148,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9162,7 +9162,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9198,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9212,7 +9212,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9248,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9262,7 +9262,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9298,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9312,7 +9312,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9348,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9362,7 +9362,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9412,7 +9412,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9448,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9462,7 +9462,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9498,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9512,7 +9512,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9548,7 +9548,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9562,7 +9562,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9598,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9612,7 +9612,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9648,7 +9648,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9662,7 +9662,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9712,7 +9712,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9748,7 +9748,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9762,7 +9762,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9798,7 +9798,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9812,7 +9812,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9848,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9862,7 +9862,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9898,7 +9898,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9948,7 +9948,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9962,7 +9962,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9998,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10012,7 +10012,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10048,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10062,7 +10062,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10098,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10112,7 +10112,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10148,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10162,7 +10162,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10198,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10212,7 +10212,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10248,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10262,7 +10262,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10298,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10312,7 +10312,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10348,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10362,7 +10362,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10398,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10412,7 +10412,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10448,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10462,7 +10462,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10498,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10512,7 +10512,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10548,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10562,7 +10562,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10598,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10612,7 +10612,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10648,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10662,7 +10662,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10698,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10712,7 +10712,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10748,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10762,7 +10762,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10798,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10812,7 +10812,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10848,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10862,7 +10862,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10898,7 +10898,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10912,7 +10912,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10948,7 +10948,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10962,7 +10962,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10998,7 +10998,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11012,7 +11012,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11048,7 +11048,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11062,7 +11062,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11098,7 +11098,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11112,7 +11112,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11148,7 +11148,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11162,7 +11162,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11198,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11212,7 +11212,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11248,7 +11248,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11262,7 +11262,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11298,7 +11298,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11312,7 +11312,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11348,7 +11348,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11362,7 +11362,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11398,7 +11398,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11412,7 +11412,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11448,7 +11448,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11462,7 +11462,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11498,7 +11498,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11512,7 +11512,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11548,7 +11548,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11562,7 +11562,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11598,7 +11598,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11612,7 +11612,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11648,7 +11648,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11662,7 +11662,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11698,7 +11698,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11712,7 +11712,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11748,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11762,7 +11762,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11812,7 +11812,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11848,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11862,7 +11862,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11898,7 +11898,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11912,7 +11912,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11962,7 +11962,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11998,7 +11998,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12048,7 +12048,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12062,7 +12062,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12098,7 +12098,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12112,7 +12112,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12148,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12198,7 +12198,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12248,7 +12248,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12298,7 +12298,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12348,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12398,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12448,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12498,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12548,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12562,7 +12562,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12598,7 +12598,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12612,7 +12612,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12648,7 +12648,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12698,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12748,7 +12748,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12898,7 +12898,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12948,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13048,7 +13048,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13148,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13159,46 +13159,46 @@
         <v>75</v>
       </c>
       <c r="C241">
-        <v>-0.1382969714751567</v>
+        <v>-7.442456123892228</v>
       </c>
       <c r="D241" t="s">
         <v>136</v>
       </c>
       <c r="E241">
-        <v>-1.985913874432278</v>
+        <v>-7.653085819975225</v>
       </c>
       <c r="F241">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G241">
-        <v>0.07855829697147516</v>
+        <v>0.09884245612389224</v>
       </c>
       <c r="H241">
-        <v>0.07278591387443228</v>
+        <v>0.09819308581997524</v>
       </c>
       <c r="I241">
-        <v>1.847616902957121</v>
+        <v>-0.2106296960829965</v>
       </c>
       <c r="J241">
-        <v>1.006350306175835</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K241">
-        <v>39.1</v>
+        <v>48.45</v>
       </c>
       <c r="L241">
-        <v>39.21</v>
+        <v>45.7</v>
       </c>
       <c r="M241">
-        <v>37.15</v>
+        <v>48.25</v>
       </c>
       <c r="N241">
-        <v>35.4</v>
+        <v>45.27</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13209,28 +13209,28 @@
         <v>76</v>
       </c>
       <c r="C242">
-        <v>-4.191976702465361</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D242" t="s">
         <v>137</v>
       </c>
       <c r="E242">
-        <v>-5.896819278444603</v>
+        <v>-6.234281471494768</v>
       </c>
       <c r="F242">
         <v>-1</v>
       </c>
       <c r="G242">
-        <v>0.08849197670246536</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H242">
-        <v>0.08689681927844461</v>
+        <v>0.08723428147149477</v>
       </c>
       <c r="I242">
-        <v>1.704842575979242</v>
+        <v>1.70524146746039</v>
       </c>
       <c r="J242">
-        <v>1.096851519584979</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K242">
         <v>42.25</v>
@@ -13253,52 +13253,52 @@
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B243" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C243">
-        <v>-4.529040004034378</v>
+        <v>-7.82898196912344</v>
       </c>
       <c r="D243" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E243">
-        <v>-6.234281471494768</v>
+        <v>-8.038016099281855</v>
       </c>
       <c r="F243">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G243">
-        <v>0.08882904000403437</v>
+        <v>0.09922898196912346</v>
       </c>
       <c r="H243">
-        <v>0.08723428147149477</v>
+        <v>0.09857801609928185</v>
       </c>
       <c r="I243">
-        <v>1.70524146746039</v>
+        <v>-0.2090341301584147</v>
       </c>
       <c r="J243">
         <v>1.104829349207914</v>
       </c>
       <c r="K243">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L243">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M243">
-        <v>42.3</v>
+        <v>48.25</v>
       </c>
       <c r="N243">
-        <v>40.5</v>
+        <v>45.27</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13353,52 +13353,52 @@
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B245" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C245">
-        <v>-5.398172562506375</v>
+        <v>-8.295821887580566</v>
       </c>
       <c r="D245" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E245">
-        <v>-7.104442589207565</v>
+        <v>-8.502928917972383</v>
       </c>
       <c r="F245">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G245">
-        <v>0.08969817256250637</v>
+        <v>0.09969582188758057</v>
       </c>
       <c r="H245">
-        <v>0.08810444258920756</v>
+        <v>0.09904292891797239</v>
       </c>
       <c r="I245">
-        <v>1.706270026701191</v>
+        <v>-0.2071070303918177</v>
       </c>
       <c r="J245">
-        <v>1.12540053402382</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K245">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L245">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M245">
-        <v>42.3</v>
+        <v>48.25</v>
       </c>
       <c r="N245">
-        <v>40.5</v>
+        <v>45.27</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>247</v>
+        <v>135</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13409,28 +13409,28 @@
         <v>76</v>
       </c>
       <c r="C246">
-        <v>-5.865740724353984</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D246" t="s">
         <v>137</v>
       </c>
       <c r="E246">
-        <v>-7.572564086157946</v>
+        <v>-7.104442589207565</v>
       </c>
       <c r="F246">
         <v>-1</v>
       </c>
       <c r="G246">
-        <v>0.09016574072435399</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H246">
-        <v>0.08857256408615793</v>
+        <v>0.08810444258920756</v>
       </c>
       <c r="I246">
-        <v>1.706823361803963</v>
+        <v>1.706270026701191</v>
       </c>
       <c r="J246">
-        <v>1.136467236079384</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K246">
         <v>42.25</v>
@@ -13448,57 +13448,57 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:16">
       <c r="A247" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B247" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C247">
-        <v>-6.356723940668068</v>
+        <v>-8.82565587345406</v>
       </c>
       <c r="D247" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E247">
-        <v>-8.080849021151664</v>
+        <v>-9.030575766649292</v>
       </c>
       <c r="F247">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G247">
-        <v>0.09065672394066807</v>
+        <v>0.1002256558734541</v>
       </c>
       <c r="H247">
-        <v>0.08698084902115168</v>
+        <v>0.09957057576664929</v>
       </c>
       <c r="I247">
-        <v>1.724125080483596</v>
+        <v>-0.2049198931952319</v>
       </c>
       <c r="J247">
-        <v>1.148088140607528</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K247">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L247">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M247">
-        <v>41.4</v>
+        <v>48.25</v>
       </c>
       <c r="N247">
-        <v>39.45</v>
+        <v>45.27</v>
       </c>
       <c r="O247">
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13509,28 +13509,28 @@
         <v>76</v>
       </c>
       <c r="C248">
-        <v>-6.77136034625692</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D248" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E248">
-        <v>-8.926080801189983</v>
+        <v>-7.599743573686503</v>
       </c>
       <c r="F248">
         <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09107136034625692</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H248">
-        <v>0.08370608080118999</v>
+        <v>0.08649974357368652</v>
       </c>
       <c r="I248">
-        <v>2.154720454933063</v>
+        <v>1.734002849332519</v>
       </c>
       <c r="J248">
-        <v>1.15790202002975</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K248">
         <v>42.25</v>
@@ -13539,66 +13539,66 @@
         <v>42.15</v>
       </c>
       <c r="M248">
-        <v>40</v>
+        <v>41.4</v>
       </c>
       <c r="N248">
-        <v>37.39</v>
+        <v>39.45</v>
       </c>
       <c r="O248">
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>136</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B249" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C249">
-        <v>-7.112794598132552</v>
+        <v>-9.361837588046164</v>
       </c>
       <c r="D249" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E249">
-        <v>-9.24933216391247</v>
+        <v>-9.564544140830286</v>
       </c>
       <c r="F249">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G249">
-        <v>0.09141279459813255</v>
+        <v>0.1007618375880462</v>
       </c>
       <c r="H249">
-        <v>0.08402933216391248</v>
+        <v>0.1001045441408303</v>
       </c>
       <c r="I249">
-        <v>2.136537565779918</v>
+        <v>-0.2027065527841216</v>
       </c>
       <c r="J249">
-        <v>1.165983304097812</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K249">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L249">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M249">
-        <v>40</v>
+        <v>48.25</v>
       </c>
       <c r="N249">
-        <v>37.39</v>
+        <v>45.27</v>
       </c>
       <c r="O249">
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -13609,28 +13609,28 @@
         <v>76</v>
       </c>
       <c r="C250">
-        <v>-7.379527992135429</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D250" t="s">
         <v>139</v>
       </c>
       <c r="E250">
-        <v>-9.501860820956622</v>
+        <v>-8.533525624301134</v>
       </c>
       <c r="F250">
         <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09167952799213544</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H250">
-        <v>0.08428186082095662</v>
+        <v>0.08331352562430114</v>
       </c>
       <c r="I250">
-        <v>2.122332828821193</v>
+        <v>2.176801683633066</v>
       </c>
       <c r="J250">
-        <v>1.172296520523916</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K250">
         <v>42.25</v>
@@ -13648,57 +13648,57 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251" spans="1:16">
       <c r="A251" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B251" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C251">
-        <v>-7.702700683679339</v>
+        <v>-9.924870412434743</v>
       </c>
       <c r="D251" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E251">
-        <v>-9.80782313247748</v>
+        <v>-10.12525278431324</v>
       </c>
       <c r="F251">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G251">
-        <v>0.09200270068367934</v>
+        <v>0.1013248704124348</v>
       </c>
       <c r="H251">
-        <v>0.08458782313247748</v>
+        <v>0.1006652527843132</v>
       </c>
       <c r="I251">
-        <v>2.105122448798141</v>
+        <v>-0.2003823718784972</v>
       </c>
       <c r="J251">
-        <v>1.179945578311937</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K251">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L251">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M251">
-        <v>40</v>
+        <v>48.25</v>
       </c>
       <c r="N251">
-        <v>37.39</v>
+        <v>45.27</v>
       </c>
       <c r="O251">
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -13709,28 +13709,28 @@
         <v>76</v>
       </c>
       <c r="C252">
-        <v>-8.001107320444035</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D252" t="s">
         <v>139</v>
       </c>
       <c r="E252">
-        <v>-10.09033829154465</v>
+        <v>-8.926080801189983</v>
       </c>
       <c r="F252">
         <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.09230110732044404</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H252">
-        <v>0.08487033829154464</v>
+        <v>0.08370608080118999</v>
       </c>
       <c r="I252">
-        <v>2.089230971100612</v>
+        <v>2.154720454933063</v>
       </c>
       <c r="J252">
-        <v>1.187008457288616</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K252">
         <v>42.25</v>
@@ -13748,7 +13748,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -13756,49 +13756,49 @@
         <v>1</v>
       </c>
       <c r="B253" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C253">
-        <v>-11.26849157246293</v>
+        <v>-10.40035287044137</v>
       </c>
       <c r="D253" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E253">
-        <v>-11.81055975563346</v>
+        <v>-10.59877246643541</v>
       </c>
       <c r="F253">
         <v>1</v>
       </c>
       <c r="G253">
-        <v>0.09864849157246292</v>
+        <v>0.1018003528704414</v>
       </c>
       <c r="H253">
-        <v>0.1032105597556335</v>
+        <v>0.1011387724664354</v>
       </c>
       <c r="I253">
-        <v>-0.5420681831705281</v>
+        <v>-0.1984195959940465</v>
       </c>
       <c r="J253">
-        <v>1.187008457288616</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K253">
-        <v>46.3</v>
+        <v>48.45</v>
       </c>
       <c r="L253">
-        <v>43.69</v>
+        <v>45.7</v>
       </c>
       <c r="M253">
-        <v>48.45</v>
+        <v>48.25</v>
       </c>
       <c r="N253">
-        <v>45.7</v>
+        <v>45.27</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -13809,28 +13809,28 @@
         <v>76</v>
       </c>
       <c r="C254">
-        <v>-8.280300561754309</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D254" t="s">
         <v>139</v>
       </c>
       <c r="E254">
-        <v>-10.35466325373189</v>
+        <v>-9.24933216391247</v>
       </c>
       <c r="F254">
         <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.09258030056175431</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H254">
-        <v>0.0851346632537319</v>
+        <v>0.08402933216391248</v>
       </c>
       <c r="I254">
-        <v>2.074362691977583</v>
+        <v>2.136537565779918</v>
       </c>
       <c r="J254">
-        <v>1.193616581343297</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K254">
         <v>42.25</v>
@@ -13848,57 +13848,57 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="255" spans="1:16">
       <c r="A255" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B255" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C255">
-        <v>-8.625026882373376</v>
+        <v>-10.79189108353899</v>
       </c>
       <c r="D255" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E255">
-        <v>-10.68103136792746</v>
+        <v>-10.98869442271942</v>
       </c>
       <c r="F255">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G255">
-        <v>0.09292502688237338</v>
+        <v>0.102191891083539</v>
       </c>
       <c r="H255">
-        <v>0.08546103136792746</v>
+        <v>0.1015286944227194</v>
       </c>
       <c r="I255">
-        <v>2.056004485554084</v>
+        <v>-0.196803339180434</v>
       </c>
       <c r="J255">
-        <v>1.201775784198186</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K255">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L255">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M255">
-        <v>40</v>
+        <v>48.25</v>
       </c>
       <c r="N255">
-        <v>37.39</v>
+        <v>45.27</v>
       </c>
       <c r="O255">
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -13909,28 +13909,28 @@
         <v>76</v>
       </c>
       <c r="C256">
-        <v>-8.846388689296894</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D256" t="s">
         <v>139</v>
       </c>
       <c r="E256">
-        <v>-10.89060467625741</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F256">
         <v>-1</v>
       </c>
       <c r="G256">
-        <v>0.09314638868929688</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H256">
-        <v>0.08567060467625741</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I256">
-        <v>2.044215986960516</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J256">
-        <v>1.207015116906435</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K256">
         <v>42.25</v>
@@ -13948,57 +13948,57 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:16">
       <c r="A257" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B257" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C257">
-        <v>-9.123967366600709</v>
+        <v>-11.09776641938371</v>
       </c>
       <c r="D257" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E257">
-        <v>-11.15340105713676</v>
+        <v>-11.29330711527892</v>
       </c>
       <c r="F257">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G257">
-        <v>0.0934239673666007</v>
+        <v>0.1024977664193837</v>
       </c>
       <c r="H257">
-        <v>0.08593340105713676</v>
+        <v>0.1018333071152789</v>
       </c>
       <c r="I257">
-        <v>2.029433690536052</v>
+        <v>-0.1955406958952111</v>
       </c>
       <c r="J257">
-        <v>1.213585026428419</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K257">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L257">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M257">
-        <v>40</v>
+        <v>48.25</v>
       </c>
       <c r="N257">
-        <v>37.39</v>
+        <v>45.27</v>
       </c>
       <c r="O257">
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14009,28 +14009,28 @@
         <v>76</v>
       </c>
       <c r="C258">
-        <v>-9.62255528559681</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D258" t="s">
         <v>139</v>
       </c>
       <c r="E258">
-        <v>-11.62543695677805</v>
+        <v>-9.80782313247748</v>
       </c>
       <c r="F258">
         <v>-1</v>
       </c>
       <c r="G258">
-        <v>0.09392255528559681</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H258">
-        <v>0.08640543695677805</v>
+        <v>0.08458782313247748</v>
       </c>
       <c r="I258">
-        <v>2.002881671181235</v>
+        <v>2.105122448798141</v>
       </c>
       <c r="J258">
-        <v>1.225385923919451</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K258">
         <v>42.25</v>
@@ -14048,56 +14048,656 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="259" spans="1:16">
       <c r="A259" s="1">
+        <v>1</v>
+      </c>
+      <c r="B259" t="s">
+        <v>75</v>
+      </c>
+      <c r="C259">
+        <v>-11.46836326921335</v>
+      </c>
+      <c r="D259" t="s">
+        <v>136</v>
+      </c>
+      <c r="E259">
+        <v>-11.66237415355096</v>
+      </c>
+      <c r="F259">
+        <v>1</v>
+      </c>
+      <c r="G259">
+        <v>0.1028683632692134</v>
+      </c>
+      <c r="H259">
+        <v>0.102202374153551</v>
+      </c>
+      <c r="I259">
+        <v>-0.194010884337608</v>
+      </c>
+      <c r="J259">
+        <v>1.179945578311937</v>
+      </c>
+      <c r="K259">
+        <v>48.45</v>
+      </c>
+      <c r="L259">
+        <v>45.7</v>
+      </c>
+      <c r="M259">
+        <v>48.25</v>
+      </c>
+      <c r="N259">
+        <v>45.27</v>
+      </c>
+      <c r="O259">
+        <v>1</v>
+      </c>
+      <c r="P259" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16">
+      <c r="A260" s="1">
         <v>0</v>
       </c>
-      <c r="B259" t="s">
+      <c r="B260" t="s">
         <v>76</v>
       </c>
-      <c r="C259">
-        <v>-9.818321109702786</v>
-      </c>
-      <c r="D259" t="s">
+      <c r="C260">
+        <v>-8.001107320444035</v>
+      </c>
+      <c r="D260" t="s">
         <v>139</v>
       </c>
-      <c r="E259">
-        <v>-11.81077738196714</v>
-      </c>
-      <c r="F259">
-        <v>-1</v>
-      </c>
-      <c r="G259">
-        <v>0.09411832110970278</v>
-      </c>
-      <c r="H259">
-        <v>0.08659077738196715</v>
-      </c>
-      <c r="I259">
-        <v>1.992456272264349</v>
-      </c>
-      <c r="J259">
+      <c r="E260">
+        <v>-10.09033829154465</v>
+      </c>
+      <c r="F260">
+        <v>-1</v>
+      </c>
+      <c r="G260">
+        <v>0.09230110732044404</v>
+      </c>
+      <c r="H260">
+        <v>0.08487033829154464</v>
+      </c>
+      <c r="I260">
+        <v>2.089230971100612</v>
+      </c>
+      <c r="J260">
+        <v>1.187008457288616</v>
+      </c>
+      <c r="K260">
+        <v>42.25</v>
+      </c>
+      <c r="L260">
+        <v>42.15</v>
+      </c>
+      <c r="M260">
+        <v>40</v>
+      </c>
+      <c r="N260">
+        <v>37.39</v>
+      </c>
+      <c r="O260">
+        <v>1</v>
+      </c>
+      <c r="P260" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16">
+      <c r="A261" s="1">
+        <v>1</v>
+      </c>
+      <c r="B261" t="s">
+        <v>75</v>
+      </c>
+      <c r="C261">
+        <v>-11.81055975563346</v>
+      </c>
+      <c r="D261" t="s">
+        <v>136</v>
+      </c>
+      <c r="E261">
+        <v>-12.00315806417573</v>
+      </c>
+      <c r="F261">
+        <v>1</v>
+      </c>
+      <c r="G261">
+        <v>0.1032105597556335</v>
+      </c>
+      <c r="H261">
+        <v>0.1025431580641757</v>
+      </c>
+      <c r="I261">
+        <v>-0.1925983085422729</v>
+      </c>
+      <c r="J261">
+        <v>1.187008457288616</v>
+      </c>
+      <c r="K261">
+        <v>48.45</v>
+      </c>
+      <c r="L261">
+        <v>45.7</v>
+      </c>
+      <c r="M261">
+        <v>48.25</v>
+      </c>
+      <c r="N261">
+        <v>45.27</v>
+      </c>
+      <c r="O261">
+        <v>1</v>
+      </c>
+      <c r="P261" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16">
+      <c r="A262" s="1">
+        <v>0</v>
+      </c>
+      <c r="B262" t="s">
+        <v>76</v>
+      </c>
+      <c r="C262">
+        <v>-8.280300561754309</v>
+      </c>
+      <c r="D262" t="s">
+        <v>139</v>
+      </c>
+      <c r="E262">
+        <v>-10.35466325373189</v>
+      </c>
+      <c r="F262">
+        <v>-1</v>
+      </c>
+      <c r="G262">
+        <v>0.09258030056175431</v>
+      </c>
+      <c r="H262">
+        <v>0.0851346632537319</v>
+      </c>
+      <c r="I262">
+        <v>2.074362691977583</v>
+      </c>
+      <c r="J262">
+        <v>1.193616581343297</v>
+      </c>
+      <c r="K262">
+        <v>42.25</v>
+      </c>
+      <c r="L262">
+        <v>42.15</v>
+      </c>
+      <c r="M262">
+        <v>40</v>
+      </c>
+      <c r="N262">
+        <v>37.39</v>
+      </c>
+      <c r="O262">
+        <v>1</v>
+      </c>
+      <c r="P262" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16">
+      <c r="A263" s="1">
+        <v>1</v>
+      </c>
+      <c r="B263" t="s">
+        <v>75</v>
+      </c>
+      <c r="C263">
+        <v>-12.13072336608275</v>
+      </c>
+      <c r="D263" t="s">
+        <v>136</v>
+      </c>
+      <c r="E263">
+        <v>-12.32200004981409</v>
+      </c>
+      <c r="F263">
+        <v>1</v>
+      </c>
+      <c r="G263">
+        <v>0.1035307233660828</v>
+      </c>
+      <c r="H263">
+        <v>0.1028620000498141</v>
+      </c>
+      <c r="I263">
+        <v>-0.1912766837313384</v>
+      </c>
+      <c r="J263">
+        <v>1.193616581343297</v>
+      </c>
+      <c r="K263">
+        <v>48.45</v>
+      </c>
+      <c r="L263">
+        <v>45.7</v>
+      </c>
+      <c r="M263">
+        <v>48.25</v>
+      </c>
+      <c r="N263">
+        <v>45.27</v>
+      </c>
+      <c r="O263">
+        <v>1</v>
+      </c>
+      <c r="P263" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16">
+      <c r="A264" s="1">
+        <v>0</v>
+      </c>
+      <c r="B264" t="s">
+        <v>76</v>
+      </c>
+      <c r="C264">
+        <v>-8.625026882373376</v>
+      </c>
+      <c r="D264" t="s">
+        <v>139</v>
+      </c>
+      <c r="E264">
+        <v>-10.68103136792746</v>
+      </c>
+      <c r="F264">
+        <v>-1</v>
+      </c>
+      <c r="G264">
+        <v>0.09292502688237338</v>
+      </c>
+      <c r="H264">
+        <v>0.08546103136792746</v>
+      </c>
+      <c r="I264">
+        <v>2.056004485554084</v>
+      </c>
+      <c r="J264">
+        <v>1.201775784198186</v>
+      </c>
+      <c r="K264">
+        <v>42.25</v>
+      </c>
+      <c r="L264">
+        <v>42.15</v>
+      </c>
+      <c r="M264">
+        <v>40</v>
+      </c>
+      <c r="N264">
+        <v>37.39</v>
+      </c>
+      <c r="O264">
+        <v>1</v>
+      </c>
+      <c r="P264" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16">
+      <c r="A265" s="1">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
+        <v>75</v>
+      </c>
+      <c r="C265">
+        <v>-12.52603674440213</v>
+      </c>
+      <c r="D265" t="s">
+        <v>136</v>
+      </c>
+      <c r="E265">
+        <v>-12.71568158756249</v>
+      </c>
+      <c r="F265">
+        <v>1</v>
+      </c>
+      <c r="G265">
+        <v>0.1039260367444021</v>
+      </c>
+      <c r="H265">
+        <v>0.1032556815875625</v>
+      </c>
+      <c r="I265">
+        <v>-0.1896448431603588</v>
+      </c>
+      <c r="J265">
+        <v>1.201775784198186</v>
+      </c>
+      <c r="K265">
+        <v>48.45</v>
+      </c>
+      <c r="L265">
+        <v>45.7</v>
+      </c>
+      <c r="M265">
+        <v>48.25</v>
+      </c>
+      <c r="N265">
+        <v>45.27</v>
+      </c>
+      <c r="O265">
+        <v>1</v>
+      </c>
+      <c r="P265" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16">
+      <c r="A266" s="1">
+        <v>0</v>
+      </c>
+      <c r="B266" t="s">
+        <v>76</v>
+      </c>
+      <c r="C266">
+        <v>-8.846388689296894</v>
+      </c>
+      <c r="D266" t="s">
+        <v>139</v>
+      </c>
+      <c r="E266">
+        <v>-10.89060467625741</v>
+      </c>
+      <c r="F266">
+        <v>-1</v>
+      </c>
+      <c r="G266">
+        <v>0.09314638868929688</v>
+      </c>
+      <c r="H266">
+        <v>0.08567060467625741</v>
+      </c>
+      <c r="I266">
+        <v>2.044215986960516</v>
+      </c>
+      <c r="J266">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K266">
+        <v>42.25</v>
+      </c>
+      <c r="L266">
+        <v>42.15</v>
+      </c>
+      <c r="M266">
+        <v>40</v>
+      </c>
+      <c r="N266">
+        <v>37.39</v>
+      </c>
+      <c r="O266">
+        <v>1</v>
+      </c>
+      <c r="P266" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16">
+      <c r="A267" s="1">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
+        <v>75</v>
+      </c>
+      <c r="C267">
+        <v>-12.77988241411679</v>
+      </c>
+      <c r="D267" t="s">
+        <v>136</v>
+      </c>
+      <c r="E267">
+        <v>-12.9684793907355</v>
+      </c>
+      <c r="F267">
+        <v>1</v>
+      </c>
+      <c r="G267">
+        <v>0.1041798824141168</v>
+      </c>
+      <c r="H267">
+        <v>0.1035084793907355</v>
+      </c>
+      <c r="I267">
+        <v>-0.1885969766187117</v>
+      </c>
+      <c r="J267">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K267">
+        <v>48.45</v>
+      </c>
+      <c r="L267">
+        <v>45.7</v>
+      </c>
+      <c r="M267">
+        <v>48.25</v>
+      </c>
+      <c r="N267">
+        <v>45.27</v>
+      </c>
+      <c r="O267">
+        <v>1</v>
+      </c>
+      <c r="P267" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16">
+      <c r="A268" s="1">
+        <v>0</v>
+      </c>
+      <c r="B268" t="s">
+        <v>76</v>
+      </c>
+      <c r="C268">
+        <v>-9.123967366600709</v>
+      </c>
+      <c r="D268" t="s">
+        <v>139</v>
+      </c>
+      <c r="E268">
+        <v>-11.15340105713676</v>
+      </c>
+      <c r="F268">
+        <v>-1</v>
+      </c>
+      <c r="G268">
+        <v>0.0934239673666007</v>
+      </c>
+      <c r="H268">
+        <v>0.08593340105713676</v>
+      </c>
+      <c r="I268">
+        <v>2.029433690536052</v>
+      </c>
+      <c r="J268">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K268">
+        <v>42.25</v>
+      </c>
+      <c r="L268">
+        <v>42.15</v>
+      </c>
+      <c r="M268">
+        <v>40</v>
+      </c>
+      <c r="N268">
+        <v>37.39</v>
+      </c>
+      <c r="O268">
+        <v>1</v>
+      </c>
+      <c r="P268" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16">
+      <c r="A269" s="1">
+        <v>1</v>
+      </c>
+      <c r="B269" t="s">
+        <v>75</v>
+      </c>
+      <c r="C269">
+        <v>-13.09819453045691</v>
+      </c>
+      <c r="D269" t="s">
+        <v>136</v>
+      </c>
+      <c r="E269">
+        <v>-13.28547752517122</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+      <c r="G269">
+        <v>0.1044981945304569</v>
+      </c>
+      <c r="H269">
+        <v>0.1038254775251712</v>
+      </c>
+      <c r="I269">
+        <v>-0.187282994714316</v>
+      </c>
+      <c r="J269">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K269">
+        <v>48.45</v>
+      </c>
+      <c r="L269">
+        <v>45.7</v>
+      </c>
+      <c r="M269">
+        <v>48.25</v>
+      </c>
+      <c r="N269">
+        <v>45.27</v>
+      </c>
+      <c r="O269">
+        <v>1</v>
+      </c>
+      <c r="P269" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16">
+      <c r="A270" s="1">
+        <v>0</v>
+      </c>
+      <c r="B270" t="s">
+        <v>75</v>
+      </c>
+      <c r="C270">
+        <v>-13.6699480138974</v>
+      </c>
+      <c r="D270" t="s">
+        <v>136</v>
+      </c>
+      <c r="E270">
+        <v>-13.85487082911352</v>
+      </c>
+      <c r="F270">
+        <v>1</v>
+      </c>
+      <c r="G270">
+        <v>0.1050699480138974</v>
+      </c>
+      <c r="H270">
+        <v>0.1043948708291135</v>
+      </c>
+      <c r="I270">
+        <v>-0.1849228152161118</v>
+      </c>
+      <c r="J270">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K270">
+        <v>48.45</v>
+      </c>
+      <c r="L270">
+        <v>45.7</v>
+      </c>
+      <c r="M270">
+        <v>48.25</v>
+      </c>
+      <c r="N270">
+        <v>45.27</v>
+      </c>
+      <c r="O270">
+        <v>1</v>
+      </c>
+      <c r="P270" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16">
+      <c r="A271" s="1">
+        <v>0</v>
+      </c>
+      <c r="B271" t="s">
+        <v>75</v>
+      </c>
+      <c r="C271">
+        <v>-13.89444160390769</v>
+      </c>
+      <c r="D271" t="s">
+        <v>136</v>
+      </c>
+      <c r="E271">
+        <v>-14.07843771699785</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+      <c r="G271">
+        <v>0.1052944416039077</v>
+      </c>
+      <c r="H271">
+        <v>0.1046184377169979</v>
+      </c>
+      <c r="I271">
+        <v>-0.18399611309016</v>
+      </c>
+      <c r="J271">
         <v>1.230019434549178</v>
       </c>
-      <c r="K259">
-        <v>42.25</v>
-      </c>
-      <c r="L259">
-        <v>42.15</v>
-      </c>
-      <c r="M259">
-        <v>40</v>
-      </c>
-      <c r="N259">
-        <v>37.39</v>
-      </c>
-      <c r="O259">
-        <v>1</v>
-      </c>
-      <c r="P259" t="s">
+      <c r="K271">
+        <v>48.45</v>
+      </c>
+      <c r="L271">
+        <v>45.7</v>
+      </c>
+      <c r="M271">
+        <v>48.25</v>
+      </c>
+      <c r="N271">
+        <v>45.27</v>
+      </c>
+      <c r="O271">
+        <v>1</v>
+      </c>
+      <c r="P271" t="s">
         <v>259</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="267">
   <si>
     <t>trade_time</t>
   </si>
@@ -241,6 +241,12 @@
     <t>2021-07-06</t>
   </si>
   <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
@@ -415,16 +421,16 @@
     <t>2021-07-05</t>
   </si>
   <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
     <t>2021-07-14</t>
   </si>
   <si>
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-09-07</t>
+    <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -748,6 +754,21 @@
     <t>2021-06-30</t>
   </si>
   <si>
+    <t>2021-07-15</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
     <t>2021-07-22</t>
   </si>
   <si>
@@ -763,9 +784,6 @@
     <t>2021-07-29</t>
   </si>
   <si>
-    <t>2021-07-30</t>
-  </si>
-  <si>
     <t>2021-08-02</t>
   </si>
   <si>
@@ -794,6 +812,9 @@
   </si>
   <si>
     <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P271"/>
+  <dimension ref="A1:P279"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1248,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1298,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1312,7 +1333,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1348,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1362,7 +1383,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1398,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1412,7 +1433,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1448,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1462,7 +1483,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1498,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1548,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1598,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1612,7 +1633,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1648,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1662,7 +1683,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1698,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1712,7 +1733,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1748,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1762,7 +1783,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1798,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1812,7 +1833,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1848,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1862,7 +1883,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1898,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1912,7 +1933,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1948,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1962,7 +1983,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -1998,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2012,7 +2033,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2048,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2062,7 +2083,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2098,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2112,7 +2133,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2148,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2162,7 +2183,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2198,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2212,7 +2233,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2248,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2262,7 +2283,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2298,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2312,7 +2333,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2348,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2362,7 +2383,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2398,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2412,7 +2433,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2448,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2462,7 +2483,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2498,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2548,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2598,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2612,7 +2633,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2648,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2662,7 +2683,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2698,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2712,7 +2733,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2748,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2762,7 +2783,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2798,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2812,7 +2833,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2848,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2862,7 +2883,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2898,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2948,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2962,7 +2983,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -2998,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3012,7 +3033,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3048,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3062,7 +3083,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3098,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3112,7 +3133,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3148,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3162,7 +3183,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3198,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3212,7 +3233,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3248,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3298,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3312,7 +3333,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3348,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3362,7 +3383,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3398,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3412,7 +3433,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3448,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3462,7 +3483,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3498,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3512,7 +3533,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3548,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3562,7 +3583,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3598,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3612,7 +3633,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3648,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3662,7 +3683,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3698,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3712,7 +3733,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3762,7 +3783,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3798,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3812,7 +3833,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3848,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3862,7 +3883,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3898,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3912,7 +3933,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3948,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3962,7 +3983,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -3998,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4012,7 +4033,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4048,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4062,7 +4083,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4098,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4112,7 +4133,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4148,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4162,7 +4183,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4198,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4212,7 +4233,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4248,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4262,7 +4283,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4298,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4312,7 +4333,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4348,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4362,7 +4383,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4398,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4412,7 +4433,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4448,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4462,7 +4483,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4498,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4512,7 +4533,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4548,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4562,7 +4583,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4612,7 +4633,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4662,7 +4683,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4698,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4712,7 +4733,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4748,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4762,7 +4783,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4798,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4812,7 +4833,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4848,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4862,7 +4883,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4898,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4912,7 +4933,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4948,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4962,7 +4983,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -4998,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5012,7 +5033,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5062,7 +5083,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5112,7 +5133,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5148,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5162,7 +5183,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5198,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5212,7 +5233,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5248,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5262,7 +5283,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5298,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5312,7 +5333,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5348,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5362,7 +5383,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5398,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5412,7 +5433,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5448,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5462,7 +5483,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5498,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5512,7 +5533,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5562,7 +5583,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5598,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5612,7 +5633,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5648,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5662,7 +5683,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5698,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5712,7 +5733,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5748,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5762,7 +5783,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5798,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5812,7 +5833,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5848,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5862,7 +5883,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5898,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5912,7 +5933,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5948,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5962,7 +5983,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -5998,7 +6019,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6012,7 +6033,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6048,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6062,7 +6083,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6098,7 +6119,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6112,7 +6133,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6148,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6162,7 +6183,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6198,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6212,7 +6233,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6248,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6262,7 +6283,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6298,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6312,7 +6333,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6348,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6362,7 +6383,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6398,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6412,7 +6433,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6448,7 +6469,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6462,7 +6483,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6498,7 +6519,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6512,7 +6533,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6548,7 +6569,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6562,7 +6583,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6612,7 +6633,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6662,7 +6683,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6712,7 +6733,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6762,7 +6783,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6812,7 +6833,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6848,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6862,7 +6883,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6898,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6912,7 +6933,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6948,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6962,7 +6983,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -6998,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7012,7 +7033,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7048,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7062,7 +7083,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7112,7 +7133,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7162,7 +7183,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7212,7 +7233,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7262,7 +7283,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7298,7 +7319,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7312,7 +7333,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7348,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7362,7 +7383,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7398,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7412,7 +7433,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7448,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7462,7 +7483,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7498,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7512,7 +7533,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7548,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7562,7 +7583,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7598,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7612,7 +7633,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7648,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7662,7 +7683,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7698,7 +7719,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7712,7 +7733,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7748,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7762,7 +7783,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7798,7 +7819,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7812,7 +7833,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7848,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7862,7 +7883,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7898,7 +7919,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7912,7 +7933,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7948,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7962,7 +7983,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -7998,7 +8019,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8012,7 +8033,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8048,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8062,7 +8083,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8098,7 +8119,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8112,7 +8133,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8148,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8162,7 +8183,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8198,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8212,7 +8233,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8248,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8262,7 +8283,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8298,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8312,7 +8333,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8348,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8362,7 +8383,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8398,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8412,7 +8433,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8448,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8462,7 +8483,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8498,7 +8519,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8512,7 +8533,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8548,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8562,7 +8583,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8598,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8612,7 +8633,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8648,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8662,7 +8683,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8698,7 +8719,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8712,7 +8733,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8748,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8762,7 +8783,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8798,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8812,7 +8833,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8848,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8862,7 +8883,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8898,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8912,7 +8933,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8948,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8962,7 +8983,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -8998,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9012,7 +9033,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9048,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9062,7 +9083,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9098,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9112,7 +9133,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9148,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9162,7 +9183,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9198,7 +9219,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9212,7 +9233,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9248,7 +9269,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9262,7 +9283,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9298,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9312,7 +9333,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9348,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9362,7 +9383,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9398,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9412,7 +9433,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9448,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9462,7 +9483,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9498,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9512,7 +9533,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9548,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9562,7 +9583,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9598,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9612,7 +9633,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9648,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9662,7 +9683,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9698,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9712,7 +9733,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9748,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9762,7 +9783,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9798,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9812,7 +9833,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9848,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9862,7 +9883,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9898,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9948,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9962,7 +9983,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -9998,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10012,7 +10033,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10048,7 +10069,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10062,7 +10083,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10098,7 +10119,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10112,7 +10133,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10148,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10162,7 +10183,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10198,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10212,7 +10233,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10248,7 +10269,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10262,7 +10283,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10298,7 +10319,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10312,7 +10333,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10348,7 +10369,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10362,7 +10383,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10398,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10412,7 +10433,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10448,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10462,7 +10483,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10498,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10512,7 +10533,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10548,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10562,7 +10583,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10598,7 +10619,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10612,7 +10633,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10648,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10662,7 +10683,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10698,7 +10719,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10712,7 +10733,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10748,7 +10769,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10762,7 +10783,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10798,7 +10819,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10812,7 +10833,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10848,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10862,7 +10883,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10898,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10912,7 +10933,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10948,7 +10969,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10962,7 +10983,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -10998,7 +11019,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11012,7 +11033,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11048,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11062,7 +11083,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11098,7 +11119,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11112,7 +11133,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11148,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11162,7 +11183,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11198,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11212,7 +11233,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11248,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11262,7 +11283,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11298,7 +11319,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11312,7 +11333,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11348,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11362,7 +11383,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11398,7 +11419,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11412,7 +11433,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11448,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11462,7 +11483,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11498,7 +11519,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11512,7 +11533,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11548,7 +11569,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11562,7 +11583,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11598,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11612,7 +11633,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11648,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11662,7 +11683,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11698,7 +11719,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11712,7 +11733,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11748,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11762,7 +11783,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11798,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11812,7 +11833,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11848,7 +11869,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11862,7 +11883,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11898,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11912,7 +11933,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11962,7 +11983,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -11998,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12048,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12062,7 +12083,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12098,7 +12119,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12112,7 +12133,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12148,7 +12169,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12198,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12248,7 +12269,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12298,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12348,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12398,7 +12419,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12448,7 +12469,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12498,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12548,7 +12569,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12562,7 +12583,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12598,7 +12619,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12612,7 +12633,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12648,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12662,7 +12683,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12698,7 +12719,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12712,7 +12733,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12748,7 +12769,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12762,7 +12783,7 @@
         <v>4.049021235741485</v>
       </c>
       <c r="D233" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E233">
         <v>1.775278429586088</v>
@@ -12812,7 +12833,7 @@
         <v>4.052829292847441</v>
       </c>
       <c r="D234" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E234">
         <v>1.775278429586088</v>
@@ -12862,7 +12883,7 @@
         <v>3.510881591844004</v>
       </c>
       <c r="D235" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E235">
         <v>1.25406141599985</v>
@@ -12898,7 +12919,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12912,7 +12933,7 @@
         <v>3.53364299489855</v>
       </c>
       <c r="D236" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E236">
         <v>1.25406141599985</v>
@@ -12948,7 +12969,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12962,7 +12983,7 @@
         <v>3.034954939512154</v>
       </c>
       <c r="D237" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E237">
         <v>0.8398439341981927</v>
@@ -13012,7 +13033,7 @@
         <v>2.53044391115818</v>
       </c>
       <c r="D238" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E238">
         <v>0.3536443198896109</v>
@@ -13048,7 +13069,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13062,7 +13083,7 @@
         <v>2.093709160165531</v>
       </c>
       <c r="D239" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E239">
         <v>-0.06723898206826107</v>
@@ -13112,7 +13133,7 @@
         <v>1.606947793373521</v>
       </c>
       <c r="D240" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E240">
         <v>-0.5363331653346535</v>
@@ -13148,7 +13169,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13159,46 +13180,46 @@
         <v>75</v>
       </c>
       <c r="C241">
-        <v>-7.442456123892228</v>
+        <v>-0.1382969714751567</v>
       </c>
       <c r="D241" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E241">
-        <v>-7.653085819975225</v>
+        <v>-1.985913874432278</v>
       </c>
       <c r="F241">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G241">
-        <v>0.09884245612389224</v>
+        <v>0.07855829697147516</v>
       </c>
       <c r="H241">
-        <v>0.09819308581997524</v>
+        <v>0.07278591387443228</v>
       </c>
       <c r="I241">
-        <v>-0.2106296960829965</v>
+        <v>1.847616902957121</v>
       </c>
       <c r="J241">
-        <v>1.096851519584979</v>
+        <v>1.006350306175835</v>
       </c>
       <c r="K241">
-        <v>48.45</v>
+        <v>39.1</v>
       </c>
       <c r="L241">
-        <v>45.7</v>
+        <v>39.21</v>
       </c>
       <c r="M241">
-        <v>48.25</v>
+        <v>37.15</v>
       </c>
       <c r="N241">
-        <v>45.27</v>
+        <v>35.4</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13209,96 +13230,96 @@
         <v>76</v>
       </c>
       <c r="C242">
-        <v>-4.529040004034378</v>
+        <v>-4.102905583088159</v>
       </c>
       <c r="D242" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E242">
-        <v>-6.234281471494768</v>
+        <v>-3.319160233959089</v>
       </c>
       <c r="F242">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G242">
-        <v>0.08882904000403437</v>
+        <v>0.09464290558308816</v>
       </c>
       <c r="H242">
-        <v>0.08723428147149477</v>
+        <v>0.0924591602339591</v>
       </c>
       <c r="I242">
-        <v>1.70524146746039</v>
+        <v>0.7837453491290702</v>
       </c>
       <c r="J242">
-        <v>1.104829349207914</v>
+        <v>1.023272654571775</v>
       </c>
       <c r="K242">
-        <v>42.25</v>
+        <v>48.25</v>
       </c>
       <c r="L242">
-        <v>42.15</v>
+        <v>45.27</v>
       </c>
       <c r="M242">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="N242">
-        <v>40.5</v>
+        <v>44.57</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
     </row>
     <row r="243" spans="1:16">
       <c r="A243" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C243">
-        <v>-7.82898196912344</v>
+        <v>-4.731848097981405</v>
       </c>
       <c r="D243" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E243">
-        <v>-8.038016099281855</v>
+        <v>-3.929201885710462</v>
       </c>
       <c r="F243">
         <v>1</v>
       </c>
       <c r="G243">
-        <v>0.09922898196912346</v>
+        <v>0.09527184809798141</v>
       </c>
       <c r="H243">
-        <v>0.09857801609928185</v>
+        <v>0.09306920188571047</v>
       </c>
       <c r="I243">
-        <v>-0.2090341301584147</v>
+        <v>0.8026462122709432</v>
       </c>
       <c r="J243">
-        <v>1.104829349207914</v>
+        <v>1.036307732600651</v>
       </c>
       <c r="K243">
-        <v>48.45</v>
+        <v>48.25</v>
       </c>
       <c r="L243">
-        <v>45.7</v>
+        <v>45.27</v>
       </c>
       <c r="M243">
-        <v>48.25</v>
+        <v>46.8</v>
       </c>
       <c r="N243">
-        <v>45.27</v>
+        <v>44.57</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13309,96 +13330,96 @@
         <v>76</v>
       </c>
       <c r="C244">
-        <v>-4.936139829727118</v>
+        <v>-5.390256815248073</v>
       </c>
       <c r="D244" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E244">
-        <v>-6.641863072129162</v>
+        <v>-4.567824227017816</v>
       </c>
       <c r="F244">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G244">
-        <v>0.08923613982972711</v>
+        <v>0.09593025681524807</v>
       </c>
       <c r="H244">
-        <v>0.08764186307212915</v>
+        <v>0.09370782422701783</v>
       </c>
       <c r="I244">
-        <v>1.705723242402044</v>
+        <v>0.8224325882302566</v>
       </c>
       <c r="J244">
-        <v>1.114464848040879</v>
+        <v>1.049953509124312</v>
       </c>
       <c r="K244">
-        <v>42.25</v>
+        <v>48.25</v>
       </c>
       <c r="L244">
-        <v>42.15</v>
+        <v>45.27</v>
       </c>
       <c r="M244">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="N244">
-        <v>40.5</v>
+        <v>44.57</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>135</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245" spans="1:16">
       <c r="A245" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C245">
-        <v>-8.295821887580566</v>
+        <v>-6.102994871026347</v>
       </c>
       <c r="D245" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E245">
-        <v>-8.502928917972383</v>
+        <v>-5.259143211689803</v>
       </c>
       <c r="F245">
         <v>1</v>
       </c>
       <c r="G245">
-        <v>0.09969582188758057</v>
+        <v>0.09664299487102636</v>
       </c>
       <c r="H245">
-        <v>0.09904292891797239</v>
+        <v>0.09439914321168981</v>
       </c>
       <c r="I245">
-        <v>-0.2071070303918177</v>
+        <v>0.8438516593365435</v>
       </c>
       <c r="J245">
-        <v>1.114464848040879</v>
+        <v>1.064725282301064</v>
       </c>
       <c r="K245">
-        <v>48.45</v>
+        <v>48.25</v>
       </c>
       <c r="L245">
-        <v>45.7</v>
+        <v>45.27</v>
       </c>
       <c r="M245">
-        <v>48.25</v>
+        <v>46.8</v>
       </c>
       <c r="N245">
-        <v>45.27</v>
+        <v>44.57</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13409,96 +13430,96 @@
         <v>76</v>
       </c>
       <c r="C246">
-        <v>-5.398172562506375</v>
+        <v>-6.718322693837997</v>
       </c>
       <c r="D246" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E246">
-        <v>-7.104442589207565</v>
+        <v>-5.855979317546492</v>
       </c>
       <c r="F246">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G246">
-        <v>0.08969817256250637</v>
+        <v>0.09725832269383801</v>
       </c>
       <c r="H246">
-        <v>0.08810444258920756</v>
+        <v>0.0949959793175465</v>
       </c>
       <c r="I246">
-        <v>1.706270026701191</v>
+        <v>0.8623433762915056</v>
       </c>
       <c r="J246">
-        <v>1.12540053402382</v>
+        <v>1.077478190545865</v>
       </c>
       <c r="K246">
-        <v>42.25</v>
+        <v>48.25</v>
       </c>
       <c r="L246">
-        <v>42.15</v>
+        <v>45.27</v>
       </c>
       <c r="M246">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="N246">
-        <v>40.5</v>
+        <v>44.57</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:16">
       <c r="A247" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B247" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C247">
-        <v>-8.82565587345406</v>
+        <v>-7.201115064711686</v>
       </c>
       <c r="D247" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E247">
-        <v>-9.030575766649292</v>
+        <v>-6.324262902145222</v>
       </c>
       <c r="F247">
         <v>1</v>
       </c>
       <c r="G247">
-        <v>0.1002256558734541</v>
+        <v>0.0977411150647117</v>
       </c>
       <c r="H247">
-        <v>0.09957057576664929</v>
+        <v>0.09546426290214523</v>
       </c>
       <c r="I247">
-        <v>-0.2049198931952319</v>
+        <v>0.8768521625664647</v>
       </c>
       <c r="J247">
-        <v>1.12540053402382</v>
+        <v>1.087484250045838</v>
       </c>
       <c r="K247">
-        <v>48.45</v>
+        <v>48.25</v>
       </c>
       <c r="L247">
-        <v>45.7</v>
+        <v>45.27</v>
       </c>
       <c r="M247">
-        <v>48.25</v>
+        <v>46.8</v>
       </c>
       <c r="N247">
-        <v>45.27</v>
+        <v>44.57</v>
       </c>
       <c r="O247">
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13506,1131 +13527,1131 @@
         <v>0</v>
       </c>
       <c r="B248" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C248">
-        <v>-5.865740724353984</v>
+        <v>-7.442456123892228</v>
       </c>
       <c r="D248" t="s">
         <v>138</v>
       </c>
       <c r="E248">
-        <v>-7.599743573686503</v>
+        <v>-6.762651116577004</v>
       </c>
       <c r="F248">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G248">
-        <v>0.09016574072435399</v>
+        <v>0.09884245612389224</v>
       </c>
       <c r="H248">
-        <v>0.08649974357368652</v>
+        <v>0.095902651116577</v>
       </c>
       <c r="I248">
-        <v>1.734002849332519</v>
+        <v>0.679805007315224</v>
       </c>
       <c r="J248">
-        <v>1.136467236079384</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K248">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L248">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M248">
-        <v>41.4</v>
+        <v>46.8</v>
       </c>
       <c r="N248">
-        <v>39.45</v>
+        <v>44.57</v>
       </c>
       <c r="O248">
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C249">
-        <v>-9.361837588046164</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D249" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E249">
-        <v>-9.564544140830286</v>
+        <v>-6.234281471494768</v>
       </c>
       <c r="F249">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.1007618375880462</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H249">
-        <v>0.1001045441408303</v>
+        <v>0.08723428147149477</v>
       </c>
       <c r="I249">
-        <v>-0.2027065527841216</v>
+        <v>1.70524146746039</v>
       </c>
       <c r="J249">
-        <v>1.136467236079384</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K249">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L249">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M249">
-        <v>48.25</v>
+        <v>42.3</v>
       </c>
       <c r="N249">
-        <v>45.27</v>
+        <v>40.5</v>
       </c>
       <c r="O249">
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="250" spans="1:16">
       <c r="A250" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B250" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C250">
-        <v>-6.356723940668068</v>
+        <v>-7.82898196912344</v>
       </c>
       <c r="D250" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E250">
-        <v>-8.533525624301134</v>
+        <v>-7.136013542930378</v>
       </c>
       <c r="F250">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G250">
-        <v>0.09065672394066807</v>
+        <v>0.09922898196912346</v>
       </c>
       <c r="H250">
-        <v>0.08331352562430114</v>
+        <v>0.09627601354293037</v>
       </c>
       <c r="I250">
-        <v>2.176801683633066</v>
+        <v>0.6929684261930618</v>
       </c>
       <c r="J250">
-        <v>1.148088140607528</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K250">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L250">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M250">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N250">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O250">
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="251" spans="1:16">
       <c r="A251" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C251">
-        <v>-9.924870412434743</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D251" t="s">
+        <v>139</v>
+      </c>
+      <c r="E251">
+        <v>-6.641863072129162</v>
+      </c>
+      <c r="F251">
+        <v>-1</v>
+      </c>
+      <c r="G251">
+        <v>0.08923613982972711</v>
+      </c>
+      <c r="H251">
+        <v>0.08764186307212915</v>
+      </c>
+      <c r="I251">
+        <v>1.705723242402044</v>
+      </c>
+      <c r="J251">
+        <v>1.114464848040879</v>
+      </c>
+      <c r="K251">
+        <v>42.25</v>
+      </c>
+      <c r="L251">
+        <v>42.15</v>
+      </c>
+      <c r="M251">
+        <v>42.3</v>
+      </c>
+      <c r="N251">
+        <v>40.5</v>
+      </c>
+      <c r="O251">
+        <v>1</v>
+      </c>
+      <c r="P251" t="s">
         <v>136</v>
-      </c>
-      <c r="E251">
-        <v>-10.12525278431324</v>
-      </c>
-      <c r="F251">
-        <v>1</v>
-      </c>
-      <c r="G251">
-        <v>0.1013248704124348</v>
-      </c>
-      <c r="H251">
-        <v>0.1006652527843132</v>
-      </c>
-      <c r="I251">
-        <v>-0.2003823718784972</v>
-      </c>
-      <c r="J251">
-        <v>1.148088140607528</v>
-      </c>
-      <c r="K251">
-        <v>48.45</v>
-      </c>
-      <c r="L251">
-        <v>45.7</v>
-      </c>
-      <c r="M251">
-        <v>48.25</v>
-      </c>
-      <c r="N251">
-        <v>45.27</v>
-      </c>
-      <c r="O251">
-        <v>1</v>
-      </c>
-      <c r="P251" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="252" spans="1:16">
       <c r="A252" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C252">
-        <v>-6.77136034625692</v>
+        <v>-8.295821887580566</v>
       </c>
       <c r="D252" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E252">
-        <v>-8.926080801189983</v>
+        <v>-7.586954888313109</v>
       </c>
       <c r="F252">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G252">
-        <v>0.09107136034625692</v>
+        <v>0.09969582188758057</v>
       </c>
       <c r="H252">
-        <v>0.08370608080118999</v>
+        <v>0.09672695488831312</v>
       </c>
       <c r="I252">
-        <v>2.154720454933063</v>
+        <v>0.7088669992674568</v>
       </c>
       <c r="J252">
-        <v>1.15790202002975</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K252">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L252">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M252">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N252">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O252">
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>249</v>
+        <v>136</v>
       </c>
     </row>
     <row r="253" spans="1:16">
       <c r="A253" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C253">
-        <v>-10.40035287044137</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D253" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E253">
-        <v>-10.59877246643541</v>
+        <v>-7.141582108586128</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G253">
-        <v>0.1018003528704414</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H253">
-        <v>0.1011387724664354</v>
+        <v>0.08604158210858615</v>
       </c>
       <c r="I253">
-        <v>-0.1984195959940465</v>
+        <v>1.743409546079754</v>
       </c>
       <c r="J253">
-        <v>1.15790202002975</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K253">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L253">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M253">
-        <v>48.25</v>
+        <v>41.4</v>
       </c>
       <c r="N253">
-        <v>45.27</v>
+        <v>39.45</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="254" spans="1:16">
       <c r="A254" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B254" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C254">
-        <v>-7.112794598132552</v>
+        <v>-8.82565587345406</v>
       </c>
       <c r="D254" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E254">
-        <v>-9.24933216391247</v>
+        <v>-8.098744992314749</v>
       </c>
       <c r="F254">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G254">
-        <v>0.09141279459813255</v>
+        <v>0.1002256558734541</v>
       </c>
       <c r="H254">
-        <v>0.08402933216391248</v>
+        <v>0.09723874499231475</v>
       </c>
       <c r="I254">
-        <v>2.136537565779918</v>
+        <v>0.726910881139311</v>
       </c>
       <c r="J254">
-        <v>1.165983304097812</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K254">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L254">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M254">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N254">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O254">
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="255" spans="1:16">
       <c r="A255" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C255">
-        <v>-10.79189108353899</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D255" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E255">
-        <v>-10.98869442271942</v>
+        <v>-8.068689443175366</v>
       </c>
       <c r="F255">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.102191891083539</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H255">
-        <v>0.1015286944227194</v>
+        <v>0.08284868944317537</v>
       </c>
       <c r="I255">
-        <v>-0.196803339180434</v>
+        <v>2.202948718821382</v>
       </c>
       <c r="J255">
-        <v>1.165983304097812</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K255">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L255">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M255">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N255">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O255">
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:16">
       <c r="A256" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B256" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C256">
-        <v>-7.379527992135429</v>
+        <v>-9.361837588046164</v>
       </c>
       <c r="D256" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E256">
-        <v>-9.501860820956622</v>
+        <v>-8.616666648515178</v>
       </c>
       <c r="F256">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G256">
-        <v>0.09167952799213544</v>
+        <v>0.1007618375880462</v>
       </c>
       <c r="H256">
-        <v>0.08428186082095662</v>
+        <v>0.09775666664851518</v>
       </c>
       <c r="I256">
-        <v>2.122332828821193</v>
+        <v>0.7451709395309862</v>
       </c>
       <c r="J256">
-        <v>1.172296520523916</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K256">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L256">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M256">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N256">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O256">
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:16">
       <c r="A257" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C257">
-        <v>-11.09776641938371</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D257" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E257">
-        <v>-11.29330711527892</v>
+        <v>-8.533525624301134</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G257">
-        <v>0.1024977664193837</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H257">
-        <v>0.1018333071152789</v>
+        <v>0.08331352562430114</v>
       </c>
       <c r="I257">
-        <v>-0.1955406958952111</v>
+        <v>2.176801683633066</v>
       </c>
       <c r="J257">
-        <v>1.172296520523916</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K257">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L257">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M257">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N257">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O257">
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258" spans="1:16">
       <c r="A258" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B258" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C258">
-        <v>-7.702700683679339</v>
+        <v>-9.924870412434743</v>
       </c>
       <c r="D258" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E258">
-        <v>-9.80782313247748</v>
+        <v>-9.160524980432321</v>
       </c>
       <c r="F258">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G258">
-        <v>0.09200270068367934</v>
+        <v>0.1013248704124348</v>
       </c>
       <c r="H258">
-        <v>0.08458782313247748</v>
+        <v>0.09830052498043233</v>
       </c>
       <c r="I258">
-        <v>2.105122448798141</v>
+        <v>0.7643454320024219</v>
       </c>
       <c r="J258">
-        <v>1.179945578311937</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K258">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L258">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M258">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N258">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O258">
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="259" spans="1:16">
       <c r="A259" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C259">
-        <v>-11.46836326921335</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D259" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E259">
-        <v>-11.66237415355096</v>
+        <v>-8.926080801189983</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G259">
-        <v>0.1028683632692134</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H259">
-        <v>0.102202374153551</v>
+        <v>0.08370608080118999</v>
       </c>
       <c r="I259">
-        <v>-0.194010884337608</v>
+        <v>2.154720454933063</v>
       </c>
       <c r="J259">
-        <v>1.179945578311937</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K259">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L259">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M259">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N259">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O259">
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>252</v>
+        <v>137</v>
       </c>
     </row>
     <row r="260" spans="1:16">
       <c r="A260" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B260" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C260">
-        <v>-8.001107320444035</v>
+        <v>-10.40035287044137</v>
       </c>
       <c r="D260" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E260">
-        <v>-10.09033829154465</v>
+        <v>-9.61981453739228</v>
       </c>
       <c r="F260">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G260">
-        <v>0.09230110732044404</v>
+        <v>0.1018003528704414</v>
       </c>
       <c r="H260">
-        <v>0.08487033829154464</v>
+        <v>0.09875981453739228</v>
       </c>
       <c r="I260">
-        <v>2.089230971100612</v>
+        <v>0.7805383330490869</v>
       </c>
       <c r="J260">
-        <v>1.187008457288616</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K260">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L260">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M260">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N260">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O260">
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
     </row>
     <row r="261" spans="1:16">
       <c r="A261" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C261">
-        <v>-11.81055975563346</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D261" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E261">
-        <v>-12.00315806417573</v>
+        <v>-9.24933216391247</v>
       </c>
       <c r="F261">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G261">
-        <v>0.1032105597556335</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H261">
-        <v>0.1025431580641757</v>
+        <v>0.08402933216391248</v>
       </c>
       <c r="I261">
-        <v>-0.1925983085422729</v>
+        <v>2.136537565779918</v>
       </c>
       <c r="J261">
-        <v>1.187008457288616</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K261">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L261">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M261">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N261">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O261">
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="262" spans="1:16">
       <c r="A262" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B262" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C262">
-        <v>-8.280300561754309</v>
+        <v>-10.79189108353899</v>
       </c>
       <c r="D262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E262">
-        <v>-10.35466325373189</v>
+        <v>-9.99801863177759</v>
       </c>
       <c r="F262">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G262">
-        <v>0.09258030056175431</v>
+        <v>0.102191891083539</v>
       </c>
       <c r="H262">
-        <v>0.0851346632537319</v>
+        <v>0.09913801863177758</v>
       </c>
       <c r="I262">
-        <v>2.074362691977583</v>
+        <v>0.7938724517613949</v>
       </c>
       <c r="J262">
-        <v>1.193616581343297</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K262">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L262">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M262">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N262">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O262">
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="263" spans="1:16">
       <c r="A263" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C263">
-        <v>-12.13072336608275</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D263" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E263">
-        <v>-12.32200004981409</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F263">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G263">
-        <v>0.1035307233660828</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H263">
-        <v>0.1028620000498141</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I263">
-        <v>-0.1912766837313384</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J263">
-        <v>1.193616581343297</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K263">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L263">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M263">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N263">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O263">
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="264" spans="1:16">
       <c r="A264" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B264" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C264">
-        <v>-8.625026882373376</v>
+        <v>-11.09776641938371</v>
       </c>
       <c r="D264" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E264">
-        <v>-10.68103136792746</v>
+        <v>-10.29347716051925</v>
       </c>
       <c r="F264">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G264">
-        <v>0.09292502688237338</v>
+        <v>0.1024977664193837</v>
       </c>
       <c r="H264">
-        <v>0.08546103136792746</v>
+        <v>0.09943347716051924</v>
       </c>
       <c r="I264">
-        <v>2.056004485554084</v>
+        <v>0.8042892588644648</v>
       </c>
       <c r="J264">
-        <v>1.201775784198186</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K264">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L264">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M264">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N264">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O264">
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="265" spans="1:16">
       <c r="A265" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B265" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C265">
-        <v>-12.52603674440213</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D265" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E265">
-        <v>-12.71568158756249</v>
+        <v>-9.80782313247748</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G265">
-        <v>0.1039260367444021</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H265">
-        <v>0.1032556815875625</v>
+        <v>0.08458782313247748</v>
       </c>
       <c r="I265">
-        <v>-0.1896448431603588</v>
+        <v>2.105122448798141</v>
       </c>
       <c r="J265">
-        <v>1.201775784198186</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K265">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L265">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M265">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N265">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O265">
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="266" spans="1:16">
       <c r="A266" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B266" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C266">
-        <v>-8.846388689296894</v>
+        <v>-11.46836326921335</v>
       </c>
       <c r="D266" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E266">
-        <v>-10.89060467625741</v>
+        <v>-10.65145306499865</v>
       </c>
       <c r="F266">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G266">
-        <v>0.09314638868929688</v>
+        <v>0.1028683632692134</v>
       </c>
       <c r="H266">
-        <v>0.08567060467625741</v>
+        <v>0.09979145306499865</v>
       </c>
       <c r="I266">
-        <v>2.044215986960516</v>
+        <v>0.8169102042147003</v>
       </c>
       <c r="J266">
-        <v>1.207015116906435</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K266">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L266">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M266">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N266">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O266">
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="267" spans="1:16">
       <c r="A267" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B267" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C267">
-        <v>-12.77988241411679</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D267" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E267">
-        <v>-12.9684793907355</v>
+        <v>-10.09033829154465</v>
       </c>
       <c r="F267">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G267">
-        <v>0.1041798824141168</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H267">
-        <v>0.1035084793907355</v>
+        <v>0.08487033829154464</v>
       </c>
       <c r="I267">
-        <v>-0.1885969766187117</v>
+        <v>2.089230971100612</v>
       </c>
       <c r="J267">
-        <v>1.207015116906435</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K267">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L267">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M267">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N267">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O267">
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="268" spans="1:16">
       <c r="A268" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B268" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C268">
-        <v>-9.123967366600709</v>
+        <v>-11.81055975563346</v>
       </c>
       <c r="D268" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E268">
-        <v>-11.15340105713676</v>
+        <v>-10.98199580110723</v>
       </c>
       <c r="F268">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G268">
-        <v>0.0934239673666007</v>
+        <v>0.1032105597556335</v>
       </c>
       <c r="H268">
-        <v>0.08593340105713676</v>
+        <v>0.1001219958011072</v>
       </c>
       <c r="I268">
-        <v>2.029433690536052</v>
+        <v>0.8285639545262242</v>
       </c>
       <c r="J268">
-        <v>1.213585026428419</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K268">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L268">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M268">
-        <v>40</v>
+        <v>46.8</v>
       </c>
       <c r="N268">
-        <v>37.39</v>
+        <v>44.57</v>
       </c>
       <c r="O268">
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="269" spans="1:16">
       <c r="A269" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B269" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C269">
-        <v>-13.09819453045691</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D269" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E269">
-        <v>-13.28547752517122</v>
+        <v>-10.35466325373189</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G269">
-        <v>0.1044981945304569</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H269">
-        <v>0.1038254775251712</v>
+        <v>0.0851346632537319</v>
       </c>
       <c r="I269">
-        <v>-0.187282994714316</v>
+        <v>2.074362691977583</v>
       </c>
       <c r="J269">
-        <v>1.213585026428419</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K269">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L269">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M269">
-        <v>48.25</v>
+        <v>40</v>
       </c>
       <c r="N269">
-        <v>45.27</v>
+        <v>37.39</v>
       </c>
       <c r="O269">
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="270" spans="1:16">
       <c r="A270" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B270" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C270">
-        <v>-13.6699480138974</v>
+        <v>-12.13072336608275</v>
       </c>
       <c r="D270" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E270">
-        <v>-13.85487082911352</v>
+        <v>-11.29125600686631</v>
       </c>
       <c r="F270">
         <v>1</v>
       </c>
       <c r="G270">
-        <v>0.1050699480138974</v>
+        <v>0.1035307233660828</v>
       </c>
       <c r="H270">
-        <v>0.1043948708291135</v>
+        <v>0.1004312560068663</v>
       </c>
       <c r="I270">
-        <v>-0.1849228152161118</v>
+        <v>0.8394673592164423</v>
       </c>
       <c r="J270">
-        <v>1.225385923919451</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K270">
         <v>48.45</v>
@@ -14639,16 +14660,16 @@
         <v>45.7</v>
       </c>
       <c r="M270">
-        <v>48.25</v>
+        <v>46.8</v>
       </c>
       <c r="N270">
-        <v>45.27</v>
+        <v>44.57</v>
       </c>
       <c r="O270">
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -14656,49 +14677,449 @@
         <v>0</v>
       </c>
       <c r="B271" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C271">
-        <v>-13.89444160390769</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D271" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E271">
+        <v>-10.68103136792746</v>
+      </c>
+      <c r="F271">
+        <v>-1</v>
+      </c>
+      <c r="G271">
+        <v>0.09292502688237338</v>
+      </c>
+      <c r="H271">
+        <v>0.08546103136792746</v>
+      </c>
+      <c r="I271">
+        <v>2.056004485554084</v>
+      </c>
+      <c r="J271">
+        <v>1.201775784198186</v>
+      </c>
+      <c r="K271">
+        <v>42.25</v>
+      </c>
+      <c r="L271">
+        <v>42.15</v>
+      </c>
+      <c r="M271">
+        <v>40</v>
+      </c>
+      <c r="N271">
+        <v>37.39</v>
+      </c>
+      <c r="O271">
+        <v>1</v>
+      </c>
+      <c r="P271" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16">
+      <c r="A272" s="1">
+        <v>1</v>
+      </c>
+      <c r="B272" t="s">
+        <v>77</v>
+      </c>
+      <c r="C272">
+        <v>-12.52603674440213</v>
+      </c>
+      <c r="D272" t="s">
+        <v>138</v>
+      </c>
+      <c r="E272">
+        <v>-11.67310670047512</v>
+      </c>
+      <c r="F272">
+        <v>1</v>
+      </c>
+      <c r="G272">
+        <v>0.1039260367444021</v>
+      </c>
+      <c r="H272">
+        <v>0.1008131067004751</v>
+      </c>
+      <c r="I272">
+        <v>0.8529300439270102</v>
+      </c>
+      <c r="J272">
+        <v>1.201775784198186</v>
+      </c>
+      <c r="K272">
+        <v>48.45</v>
+      </c>
+      <c r="L272">
+        <v>45.7</v>
+      </c>
+      <c r="M272">
+        <v>46.8</v>
+      </c>
+      <c r="N272">
+        <v>44.57</v>
+      </c>
+      <c r="O272">
+        <v>1</v>
+      </c>
+      <c r="P272" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16">
+      <c r="A273" s="1">
+        <v>0</v>
+      </c>
+      <c r="B273" t="s">
+        <v>78</v>
+      </c>
+      <c r="C273">
+        <v>-8.846388689296894</v>
+      </c>
+      <c r="D273" t="s">
+        <v>141</v>
+      </c>
+      <c r="E273">
+        <v>-10.89060467625741</v>
+      </c>
+      <c r="F273">
+        <v>-1</v>
+      </c>
+      <c r="G273">
+        <v>0.09314638868929688</v>
+      </c>
+      <c r="H273">
+        <v>0.08567060467625741</v>
+      </c>
+      <c r="I273">
+        <v>2.044215986960516</v>
+      </c>
+      <c r="J273">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K273">
+        <v>42.25</v>
+      </c>
+      <c r="L273">
+        <v>42.15</v>
+      </c>
+      <c r="M273">
+        <v>40</v>
+      </c>
+      <c r="N273">
+        <v>37.39</v>
+      </c>
+      <c r="O273">
+        <v>1</v>
+      </c>
+      <c r="P273" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16">
+      <c r="A274" s="1">
+        <v>1</v>
+      </c>
+      <c r="B274" t="s">
+        <v>77</v>
+      </c>
+      <c r="C274">
+        <v>-12.77988241411679</v>
+      </c>
+      <c r="D274" t="s">
+        <v>138</v>
+      </c>
+      <c r="E274">
+        <v>-11.91830747122117</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+      <c r="G274">
+        <v>0.1041798824141168</v>
+      </c>
+      <c r="H274">
+        <v>0.1010583074712212</v>
+      </c>
+      <c r="I274">
+        <v>0.8615749428956221</v>
+      </c>
+      <c r="J274">
+        <v>1.207015116906435</v>
+      </c>
+      <c r="K274">
+        <v>48.45</v>
+      </c>
+      <c r="L274">
+        <v>45.7</v>
+      </c>
+      <c r="M274">
+        <v>46.8</v>
+      </c>
+      <c r="N274">
+        <v>44.57</v>
+      </c>
+      <c r="O274">
+        <v>1</v>
+      </c>
+      <c r="P274" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16">
+      <c r="A275" s="1">
+        <v>0</v>
+      </c>
+      <c r="B275" t="s">
+        <v>78</v>
+      </c>
+      <c r="C275">
+        <v>-9.123967366600709</v>
+      </c>
+      <c r="D275" t="s">
+        <v>141</v>
+      </c>
+      <c r="E275">
+        <v>-11.15340105713676</v>
+      </c>
+      <c r="F275">
+        <v>-1</v>
+      </c>
+      <c r="G275">
+        <v>0.0934239673666007</v>
+      </c>
+      <c r="H275">
+        <v>0.08593340105713676</v>
+      </c>
+      <c r="I275">
+        <v>2.029433690536052</v>
+      </c>
+      <c r="J275">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K275">
+        <v>42.25</v>
+      </c>
+      <c r="L275">
+        <v>42.15</v>
+      </c>
+      <c r="M275">
+        <v>40</v>
+      </c>
+      <c r="N275">
+        <v>37.39</v>
+      </c>
+      <c r="O275">
+        <v>1</v>
+      </c>
+      <c r="P275" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16">
+      <c r="A276" s="1">
+        <v>1</v>
+      </c>
+      <c r="B276" t="s">
+        <v>77</v>
+      </c>
+      <c r="C276">
+        <v>-13.09819453045691</v>
+      </c>
+      <c r="D276" t="s">
+        <v>138</v>
+      </c>
+      <c r="E276">
+        <v>-12.22577923685001</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276">
+        <v>0.1044981945304569</v>
+      </c>
+      <c r="H276">
+        <v>0.10136577923685</v>
+      </c>
+      <c r="I276">
+        <v>0.872415293606899</v>
+      </c>
+      <c r="J276">
+        <v>1.213585026428419</v>
+      </c>
+      <c r="K276">
+        <v>48.45</v>
+      </c>
+      <c r="L276">
+        <v>45.7</v>
+      </c>
+      <c r="M276">
+        <v>46.8</v>
+      </c>
+      <c r="N276">
+        <v>44.57</v>
+      </c>
+      <c r="O276">
+        <v>1</v>
+      </c>
+      <c r="P276" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16">
+      <c r="A277" s="1">
+        <v>0</v>
+      </c>
+      <c r="B277" t="s">
+        <v>77</v>
+      </c>
+      <c r="C277">
+        <v>-13.6699480138974</v>
+      </c>
+      <c r="D277" t="s">
+        <v>138</v>
+      </c>
+      <c r="E277">
+        <v>-12.77806123943031</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+      <c r="G277">
+        <v>0.1050699480138974</v>
+      </c>
+      <c r="H277">
+        <v>0.1019180612394303</v>
+      </c>
+      <c r="I277">
+        <v>0.8918867744670962</v>
+      </c>
+      <c r="J277">
+        <v>1.225385923919451</v>
+      </c>
+      <c r="K277">
+        <v>48.45</v>
+      </c>
+      <c r="L277">
+        <v>45.7</v>
+      </c>
+      <c r="M277">
+        <v>46.8</v>
+      </c>
+      <c r="N277">
+        <v>44.57</v>
+      </c>
+      <c r="O277">
+        <v>1</v>
+      </c>
+      <c r="P277" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16">
+      <c r="A278" s="1">
+        <v>0</v>
+      </c>
+      <c r="B278" t="s">
+        <v>76</v>
+      </c>
+      <c r="C278">
         <v>-14.07843771699785</v>
       </c>
-      <c r="F271">
-        <v>1</v>
-      </c>
-      <c r="G271">
-        <v>0.1052944416039077</v>
-      </c>
-      <c r="H271">
+      <c r="D278" t="s">
+        <v>138</v>
+      </c>
+      <c r="E278">
+        <v>-12.99490953690155</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+      <c r="G278">
         <v>0.1046184377169979</v>
       </c>
-      <c r="I271">
-        <v>-0.18399611309016</v>
-      </c>
-      <c r="J271">
+      <c r="H278">
+        <v>0.1021349095369015</v>
+      </c>
+      <c r="I278">
+        <v>1.083528180096309</v>
+      </c>
+      <c r="J278">
         <v>1.230019434549178</v>
       </c>
-      <c r="K271">
-        <v>48.45</v>
-      </c>
-      <c r="L271">
-        <v>45.7</v>
-      </c>
-      <c r="M271">
+      <c r="K278">
         <v>48.25</v>
       </c>
-      <c r="N271">
+      <c r="L278">
         <v>45.27</v>
       </c>
-      <c r="O271">
-        <v>1</v>
-      </c>
-      <c r="P271" t="s">
-        <v>259</v>
+      <c r="M278">
+        <v>46.8</v>
+      </c>
+      <c r="N278">
+        <v>44.57</v>
+      </c>
+      <c r="O278">
+        <v>1</v>
+      </c>
+      <c r="P278" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16">
+      <c r="A279" s="1">
+        <v>0</v>
+      </c>
+      <c r="B279" t="s">
+        <v>76</v>
+      </c>
+      <c r="C279">
+        <v>-14.37007717217479</v>
+      </c>
+      <c r="D279" t="s">
+        <v>138</v>
+      </c>
+      <c r="E279">
+        <v>-13.27778469757057</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>0.1049100771721748</v>
+      </c>
+      <c r="H279">
+        <v>0.1024177846975706</v>
+      </c>
+      <c r="I279">
+        <v>1.092292474604214</v>
+      </c>
+      <c r="J279">
+        <v>1.236063775589115</v>
+      </c>
+      <c r="K279">
+        <v>48.25</v>
+      </c>
+      <c r="L279">
+        <v>45.27</v>
+      </c>
+      <c r="M279">
+        <v>46.8</v>
+      </c>
+      <c r="N279">
+        <v>44.57</v>
+      </c>
+      <c r="O279">
+        <v>1</v>
+      </c>
+      <c r="P279" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="267">
   <si>
     <t>trade_time</t>
   </si>
@@ -235,24 +235,24 @@
     <t>2021-07-07</t>
   </si>
   <si>
+    <t>2021-07-06</t>
+  </si>
+  <si>
     <t>2021-07-09</t>
   </si>
   <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-09-07</t>
   </si>
   <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
     <t>2021-09-06</t>
   </si>
   <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
     <t>2017-06-06</t>
   </si>
   <si>
@@ -430,7 +430,7 @@
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-09-08</t>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2021-08-25</t>
@@ -442,6 +442,9 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
     <t>2016-12-22</t>
   </si>
   <si>
@@ -812,9 +815,6 @@
   </si>
   <si>
     <t>2021-08-16</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P279"/>
+  <dimension ref="A1:P281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1269,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1319,7 +1319,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1369,7 +1369,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1419,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1469,7 +1469,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1519,7 +1519,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1569,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1619,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1719,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1769,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1819,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1869,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1919,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1969,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2119,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2169,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2219,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2269,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2369,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2419,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2469,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2519,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2569,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2619,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2669,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2719,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2769,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2819,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2869,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3019,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3069,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3119,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3219,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3269,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3319,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3369,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3419,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3469,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3519,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3619,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3669,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3819,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3869,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3919,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3969,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4019,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4069,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4119,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4169,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4219,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4269,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4319,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4369,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4419,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4469,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4519,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4569,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4719,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4769,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4969,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5019,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5169,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5219,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5269,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5319,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5369,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5419,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5469,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5519,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5619,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5669,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5719,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5769,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5819,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5869,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5919,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5969,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6019,7 +6019,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6069,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6119,7 +6119,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6169,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6219,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6269,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6369,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6419,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6469,7 +6469,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6519,7 +6519,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6569,7 +6569,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6869,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6919,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6969,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7019,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7069,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7319,7 +7319,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7369,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7419,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7469,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7519,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7619,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7869,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7919,7 +7919,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7969,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8019,7 +8019,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8069,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8119,7 +8119,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8169,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8219,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8269,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8319,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8369,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8419,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8469,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8519,7 +8519,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8569,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8619,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8669,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8719,7 +8719,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8769,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8819,7 +8819,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8869,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8919,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8969,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9019,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9069,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9119,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9169,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9219,7 +9219,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9269,7 +9269,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9319,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9369,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9419,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9469,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9519,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9569,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9619,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9669,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9769,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9819,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9869,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9919,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10019,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10069,7 +10069,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10119,7 +10119,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10669,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10719,7 +10719,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10769,7 +10769,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10819,7 +10819,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10869,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10919,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10969,7 +10969,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11019,7 +11019,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11069,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11119,7 +11119,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11169,7 +11169,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11219,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11269,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11319,7 +11319,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11369,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11419,7 +11419,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11469,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11519,7 +11519,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11569,7 +11569,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11619,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11669,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11719,7 +11719,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11769,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11819,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11869,7 +11869,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11919,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12019,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12069,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12119,7 +12119,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12169,7 +12169,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12219,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12269,7 +12269,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12319,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12333,7 +12333,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12383,7 +12383,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12433,7 +12433,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12519,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12569,7 +12569,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12719,7 +12719,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12769,7 +12769,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12780,28 +12780,28 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>4.049021235741485</v>
+        <v>4.567308451383006</v>
       </c>
       <c r="D233" t="s">
         <v>136</v>
       </c>
       <c r="E233">
-        <v>1.775278429586088</v>
+        <v>2.277267305113099</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07695097876425851</v>
+        <v>0.07643269154861698</v>
       </c>
       <c r="H233">
-        <v>0.07238472157041392</v>
+        <v>0.0718827326948869</v>
       </c>
       <c r="I233">
-        <v>2.273742806155397</v>
+        <v>2.290041146269907</v>
       </c>
       <c r="J233">
-        <v>0.9170057550756859</v>
+        <v>0.9039670829840752</v>
       </c>
       <c r="K233">
         <v>39.75</v>
@@ -12819,18 +12819,18 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="234" spans="1:16">
       <c r="A234" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B234" t="s">
         <v>73</v>
       </c>
       <c r="C234">
-        <v>4.052829292847441</v>
+        <v>4.005620084726345</v>
       </c>
       <c r="D234" t="s">
         <v>136</v>
@@ -12842,22 +12842,22 @@
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07438717070715256</v>
+        <v>0.07727437991527365</v>
       </c>
       <c r="H234">
         <v>0.07238472157041392</v>
       </c>
       <c r="I234">
-        <v>2.277550863261354</v>
+        <v>2.230341655140258</v>
       </c>
       <c r="J234">
         <v>0.9170057550756859</v>
       </c>
       <c r="K234">
-        <v>38.35</v>
+        <v>39.95</v>
       </c>
       <c r="L234">
-        <v>39.22</v>
+        <v>40.64</v>
       </c>
       <c r="M234">
         <v>38.5</v>
@@ -12874,40 +12874,40 @@
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B235" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C235">
-        <v>3.510881591844004</v>
+        <v>4.052829292847441</v>
       </c>
       <c r="D235" t="s">
         <v>136</v>
       </c>
       <c r="E235">
-        <v>1.25406141599985</v>
+        <v>1.775278429586088</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.077489118408156</v>
+        <v>0.07438717070715256</v>
       </c>
       <c r="H235">
-        <v>0.07290593858400016</v>
+        <v>0.07238472157041392</v>
       </c>
       <c r="I235">
-        <v>2.256820175844155</v>
+        <v>2.277550863261354</v>
       </c>
       <c r="J235">
-        <v>0.9305438593246792</v>
+        <v>0.9170057550756859</v>
       </c>
       <c r="K235">
-        <v>39.75</v>
+        <v>38.35</v>
       </c>
       <c r="L235">
-        <v>40.5</v>
+        <v>39.22</v>
       </c>
       <c r="M235">
         <v>38.5</v>
@@ -12919,18 +12919,18 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
     </row>
     <row r="236" spans="1:16">
       <c r="A236" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B236" t="s">
         <v>73</v>
       </c>
       <c r="C236">
-        <v>3.53364299489855</v>
+        <v>3.464772819979061</v>
       </c>
       <c r="D236" t="s">
         <v>136</v>
@@ -12942,22 +12942,22 @@
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07490635700510145</v>
+        <v>0.07781522718002094</v>
       </c>
       <c r="H236">
         <v>0.07290593858400016</v>
       </c>
       <c r="I236">
-        <v>2.2795815788987</v>
+        <v>2.210711403979211</v>
       </c>
       <c r="J236">
         <v>0.9305438593246792</v>
       </c>
       <c r="K236">
-        <v>38.35</v>
+        <v>39.95</v>
       </c>
       <c r="L236">
-        <v>39.22</v>
+        <v>40.64</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12969,7 +12969,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12977,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C237">
         <v>3.034954939512154</v>
@@ -13027,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C238">
         <v>2.53044391115818</v>
@@ -13069,7 +13069,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13077,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C239">
         <v>2.093709160165531</v>
@@ -13127,7 +13127,7 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C240">
         <v>1.606947793373521</v>
@@ -13236,7 +13236,7 @@
         <v>138</v>
       </c>
       <c r="E242">
-        <v>-3.319160233959089</v>
+        <v>-2.84010562307369</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -13245,10 +13245,10 @@
         <v>0.09464290558308816</v>
       </c>
       <c r="H242">
-        <v>0.0924591602339591</v>
+        <v>0.09478010562307369</v>
       </c>
       <c r="I242">
-        <v>0.7837453491290702</v>
+        <v>1.262799960014469</v>
       </c>
       <c r="J242">
         <v>1.023272654571775</v>
@@ -13260,10 +13260,10 @@
         <v>45.27</v>
       </c>
       <c r="M242">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N242">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O242">
         <v>1</v>
@@ -13286,7 +13286,7 @@
         <v>138</v>
       </c>
       <c r="E243">
-        <v>-3.929201885710462</v>
+        <v>-3.461878845051054</v>
       </c>
       <c r="F243">
         <v>1</v>
@@ -13295,10 +13295,10 @@
         <v>0.09527184809798141</v>
       </c>
       <c r="H243">
-        <v>0.09306920188571047</v>
+        <v>0.09540187884505105</v>
       </c>
       <c r="I243">
-        <v>0.8026462122709432</v>
+        <v>1.269969252930352</v>
       </c>
       <c r="J243">
         <v>1.036307732600651</v>
@@ -13310,16 +13310,16 @@
         <v>45.27</v>
       </c>
       <c r="M243">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N243">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13336,7 +13336,7 @@
         <v>138</v>
       </c>
       <c r="E244">
-        <v>-4.567824227017816</v>
+        <v>-4.112782385229707</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -13345,10 +13345,10 @@
         <v>0.09593025681524807</v>
       </c>
       <c r="H244">
-        <v>0.09370782422701783</v>
+        <v>0.09605278238522971</v>
       </c>
       <c r="I244">
-        <v>0.8224325882302566</v>
+        <v>1.277474430018366</v>
       </c>
       <c r="J244">
         <v>1.049953509124312</v>
@@ -13360,16 +13360,16 @@
         <v>45.27</v>
       </c>
       <c r="M244">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N244">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13386,7 +13386,7 @@
         <v>138</v>
       </c>
       <c r="E245">
-        <v>-5.259143211689803</v>
+        <v>-4.817395965760767</v>
       </c>
       <c r="F245">
         <v>1</v>
@@ -13395,10 +13395,10 @@
         <v>0.09664299487102636</v>
       </c>
       <c r="H245">
-        <v>0.09439914321168981</v>
+        <v>0.09675739596576077</v>
       </c>
       <c r="I245">
-        <v>0.8438516593365435</v>
+        <v>1.28559890526558</v>
       </c>
       <c r="J245">
         <v>1.064725282301064</v>
@@ -13410,16 +13410,16 @@
         <v>45.27</v>
       </c>
       <c r="M245">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N245">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13436,7 +13436,7 @@
         <v>138</v>
       </c>
       <c r="E246">
-        <v>-5.855979317546492</v>
+        <v>-5.425709689037774</v>
       </c>
       <c r="F246">
         <v>1</v>
@@ -13445,10 +13445,10 @@
         <v>0.09725832269383801</v>
       </c>
       <c r="H246">
-        <v>0.0949959793175465</v>
+        <v>0.09736570968903778</v>
       </c>
       <c r="I246">
-        <v>0.8623433762915056</v>
+        <v>1.292613004800224</v>
       </c>
       <c r="J246">
         <v>1.077478190545865</v>
@@ -13460,16 +13460,16 @@
         <v>45.27</v>
       </c>
       <c r="M246">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N246">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13486,7 +13486,7 @@
         <v>138</v>
       </c>
       <c r="E247">
-        <v>-6.324262902145222</v>
+        <v>-5.902998727186485</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -13495,10 +13495,10 @@
         <v>0.0977411150647117</v>
       </c>
       <c r="H247">
-        <v>0.09546426290214523</v>
+        <v>0.09784299872718649</v>
       </c>
       <c r="I247">
-        <v>0.8768521625664647</v>
+        <v>1.298116337525201</v>
       </c>
       <c r="J247">
         <v>1.087484250045838</v>
@@ -13510,16 +13510,16 @@
         <v>45.27</v>
       </c>
       <c r="M247">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N247">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O247">
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13530,90 +13530,90 @@
         <v>77</v>
       </c>
       <c r="C248">
-        <v>-7.442456123892228</v>
+        <v>-4.191976702465361</v>
       </c>
       <c r="D248" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E248">
-        <v>-6.762651116577004</v>
+        <v>-5.896819278444603</v>
       </c>
       <c r="F248">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G248">
-        <v>0.09884245612389224</v>
+        <v>0.08849197670246536</v>
       </c>
       <c r="H248">
-        <v>0.095902651116577</v>
+        <v>0.08689681927844461</v>
       </c>
       <c r="I248">
-        <v>0.679805007315224</v>
+        <v>1.704842575979242</v>
       </c>
       <c r="J248">
         <v>1.096851519584979</v>
       </c>
       <c r="K248">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L248">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M248">
-        <v>46.8</v>
+        <v>42.3</v>
       </c>
       <c r="N248">
-        <v>44.57</v>
+        <v>40.5</v>
       </c>
       <c r="O248">
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B249" t="s">
         <v>78</v>
       </c>
       <c r="C249">
-        <v>-4.529040004034378</v>
+        <v>-7.442456123892228</v>
       </c>
       <c r="D249" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E249">
-        <v>-6.234281471494768</v>
+        <v>-6.349817484203498</v>
       </c>
       <c r="F249">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G249">
-        <v>0.08882904000403437</v>
+        <v>0.09884245612389224</v>
       </c>
       <c r="H249">
-        <v>0.08723428147149477</v>
+        <v>0.0982898174842035</v>
       </c>
       <c r="I249">
-        <v>1.70524146746039</v>
+        <v>1.09263863968873</v>
       </c>
       <c r="J249">
-        <v>1.104829349207914</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K249">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L249">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M249">
-        <v>42.3</v>
+        <v>47.7</v>
       </c>
       <c r="N249">
-        <v>40.5</v>
+        <v>45.97</v>
       </c>
       <c r="O249">
         <v>1</v>
@@ -13624,146 +13624,146 @@
     </row>
     <row r="250" spans="1:16">
       <c r="A250" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B250" t="s">
         <v>77</v>
       </c>
       <c r="C250">
-        <v>-7.82898196912344</v>
+        <v>-4.529040004034378</v>
       </c>
       <c r="D250" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E250">
-        <v>-7.136013542930378</v>
+        <v>-6.234281471494768</v>
       </c>
       <c r="F250">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G250">
-        <v>0.09922898196912346</v>
+        <v>0.08882904000403437</v>
       </c>
       <c r="H250">
-        <v>0.09627601354293037</v>
+        <v>0.08723428147149477</v>
       </c>
       <c r="I250">
-        <v>0.6929684261930618</v>
+        <v>1.70524146746039</v>
       </c>
       <c r="J250">
         <v>1.104829349207914</v>
       </c>
       <c r="K250">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L250">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M250">
-        <v>46.8</v>
+        <v>42.3</v>
       </c>
       <c r="N250">
-        <v>44.57</v>
+        <v>40.5</v>
       </c>
       <c r="O250">
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="251" spans="1:16">
       <c r="A251" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B251" t="s">
         <v>78</v>
       </c>
       <c r="C251">
-        <v>-4.936139829727118</v>
+        <v>-7.82898196912344</v>
       </c>
       <c r="D251" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E251">
-        <v>-6.641863072129162</v>
+        <v>-6.730359957217509</v>
       </c>
       <c r="F251">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G251">
-        <v>0.08923613982972711</v>
+        <v>0.09922898196912346</v>
       </c>
       <c r="H251">
-        <v>0.08764186307212915</v>
+        <v>0.0986703599572175</v>
       </c>
       <c r="I251">
-        <v>1.705723242402044</v>
+        <v>1.098622011905931</v>
       </c>
       <c r="J251">
-        <v>1.114464848040879</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K251">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L251">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M251">
-        <v>42.3</v>
+        <v>47.7</v>
       </c>
       <c r="N251">
-        <v>40.5</v>
+        <v>45.97</v>
       </c>
       <c r="O251">
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
     </row>
     <row r="252" spans="1:16">
       <c r="A252" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B252" t="s">
         <v>77</v>
       </c>
       <c r="C252">
-        <v>-8.295821887580566</v>
+        <v>-4.936139829727118</v>
       </c>
       <c r="D252" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E252">
-        <v>-7.586954888313109</v>
+        <v>-6.688844708892368</v>
       </c>
       <c r="F252">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G252">
-        <v>0.09969582188758057</v>
+        <v>0.08923613982972711</v>
       </c>
       <c r="H252">
-        <v>0.09672695488831312</v>
+        <v>0.08558884470889237</v>
       </c>
       <c r="I252">
-        <v>0.7088669992674568</v>
+        <v>1.75270487916525</v>
       </c>
       <c r="J252">
         <v>1.114464848040879</v>
       </c>
       <c r="K252">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L252">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M252">
-        <v>46.8</v>
+        <v>41.4</v>
       </c>
       <c r="N252">
-        <v>44.57</v>
+        <v>39.45</v>
       </c>
       <c r="O252">
         <v>1</v>
@@ -13774,146 +13774,146 @@
     </row>
     <row r="253" spans="1:16">
       <c r="A253" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B253" t="s">
         <v>78</v>
       </c>
       <c r="C253">
-        <v>-5.398172562506375</v>
+        <v>-8.295821887580566</v>
       </c>
       <c r="D253" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E253">
-        <v>-7.141582108586128</v>
+        <v>-7.189973251549908</v>
       </c>
       <c r="F253">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G253">
-        <v>0.08969817256250637</v>
+        <v>0.09969582188758057</v>
       </c>
       <c r="H253">
-        <v>0.08604158210858615</v>
+        <v>0.0991299732515499</v>
       </c>
       <c r="I253">
-        <v>1.743409546079754</v>
+        <v>1.105848636030657</v>
       </c>
       <c r="J253">
-        <v>1.12540053402382</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K253">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L253">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M253">
-        <v>41.4</v>
+        <v>47.7</v>
       </c>
       <c r="N253">
-        <v>39.45</v>
+        <v>45.97</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>253</v>
+        <v>136</v>
       </c>
     </row>
     <row r="254" spans="1:16">
       <c r="A254" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B254" t="s">
         <v>77</v>
       </c>
       <c r="C254">
-        <v>-8.82565587345406</v>
+        <v>-5.398172562506375</v>
       </c>
       <c r="D254" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E254">
-        <v>-8.098744992314749</v>
+        <v>-7.141582108586128</v>
       </c>
       <c r="F254">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G254">
-        <v>0.1002256558734541</v>
+        <v>0.08969817256250637</v>
       </c>
       <c r="H254">
-        <v>0.09723874499231475</v>
+        <v>0.08604158210858615</v>
       </c>
       <c r="I254">
-        <v>0.726910881139311</v>
+        <v>1.743409546079754</v>
       </c>
       <c r="J254">
         <v>1.12540053402382</v>
       </c>
       <c r="K254">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L254">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M254">
-        <v>46.8</v>
+        <v>41.4</v>
       </c>
       <c r="N254">
-        <v>44.57</v>
+        <v>39.45</v>
       </c>
       <c r="O254">
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="255" spans="1:16">
       <c r="A255" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B255" t="s">
         <v>78</v>
       </c>
       <c r="C255">
-        <v>-5.865740724353984</v>
+        <v>-8.82565587345406</v>
       </c>
       <c r="D255" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E255">
-        <v>-8.068689443175366</v>
+        <v>-7.711605472936199</v>
       </c>
       <c r="F255">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G255">
-        <v>0.09016574072435399</v>
+        <v>0.1002256558734541</v>
       </c>
       <c r="H255">
-        <v>0.08284868944317537</v>
+        <v>0.09965160547293619</v>
       </c>
       <c r="I255">
-        <v>2.202948718821382</v>
+        <v>1.114050400517861</v>
       </c>
       <c r="J255">
-        <v>1.136467236079384</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K255">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L255">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M255">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N255">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O255">
         <v>1</v>
@@ -13924,96 +13924,96 @@
     </row>
     <row r="256" spans="1:16">
       <c r="A256" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B256" t="s">
         <v>77</v>
       </c>
       <c r="C256">
-        <v>-9.361837588046164</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D256" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E256">
-        <v>-8.616666648515178</v>
+        <v>-8.068689443175366</v>
       </c>
       <c r="F256">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G256">
-        <v>0.1007618375880462</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H256">
-        <v>0.09775666664851518</v>
+        <v>0.08284868944317537</v>
       </c>
       <c r="I256">
-        <v>0.7451709395309862</v>
+        <v>2.202948718821382</v>
       </c>
       <c r="J256">
         <v>1.136467236079384</v>
       </c>
       <c r="K256">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L256">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M256">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N256">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O256">
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="257" spans="1:16">
       <c r="A257" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B257" t="s">
         <v>78</v>
       </c>
       <c r="C257">
-        <v>-6.356723940668068</v>
+        <v>-9.361837588046164</v>
       </c>
       <c r="D257" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E257">
-        <v>-8.533525624301134</v>
+        <v>-8.239487160986627</v>
       </c>
       <c r="F257">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G257">
-        <v>0.09065672394066807</v>
+        <v>0.1007618375880462</v>
       </c>
       <c r="H257">
-        <v>0.08331352562430114</v>
+        <v>0.1001794871609866</v>
       </c>
       <c r="I257">
-        <v>2.176801683633066</v>
+        <v>1.122350427059537</v>
       </c>
       <c r="J257">
-        <v>1.148088140607528</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K257">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L257">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M257">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N257">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O257">
         <v>1</v>
@@ -14024,146 +14024,146 @@
     </row>
     <row r="258" spans="1:16">
       <c r="A258" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B258" t="s">
         <v>77</v>
       </c>
       <c r="C258">
-        <v>-9.924870412434743</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D258" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E258">
-        <v>-9.160524980432321</v>
+        <v>-8.533525624301134</v>
       </c>
       <c r="F258">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G258">
-        <v>0.1013248704124348</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H258">
-        <v>0.09830052498043233</v>
+        <v>0.08331352562430114</v>
       </c>
       <c r="I258">
-        <v>0.7643454320024219</v>
+        <v>2.176801683633066</v>
       </c>
       <c r="J258">
         <v>1.148088140607528</v>
       </c>
       <c r="K258">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L258">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M258">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N258">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O258">
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="1:16">
       <c r="A259" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B259" t="s">
         <v>78</v>
       </c>
       <c r="C259">
-        <v>-6.77136034625692</v>
+        <v>-9.924870412434743</v>
       </c>
       <c r="D259" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E259">
-        <v>-8.926080801189983</v>
+        <v>-8.793804306979105</v>
       </c>
       <c r="F259">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G259">
-        <v>0.09107136034625692</v>
+        <v>0.1013248704124348</v>
       </c>
       <c r="H259">
-        <v>0.08370608080118999</v>
+        <v>0.1007338043069791</v>
       </c>
       <c r="I259">
-        <v>2.154720454933063</v>
+        <v>1.131066105455638</v>
       </c>
       <c r="J259">
-        <v>1.15790202002975</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K259">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L259">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M259">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N259">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O259">
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>137</v>
+        <v>256</v>
       </c>
     </row>
     <row r="260" spans="1:16">
       <c r="A260" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B260" t="s">
         <v>77</v>
       </c>
       <c r="C260">
-        <v>-10.40035287044137</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D260" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E260">
-        <v>-9.61981453739228</v>
+        <v>-8.926080801189983</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G260">
-        <v>0.1018003528704414</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H260">
-        <v>0.09875981453739228</v>
+        <v>0.08370608080118999</v>
       </c>
       <c r="I260">
-        <v>0.7805383330490869</v>
+        <v>2.154720454933063</v>
       </c>
       <c r="J260">
         <v>1.15790202002975</v>
       </c>
       <c r="K260">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L260">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M260">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N260">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O260">
         <v>1</v>
@@ -14174,146 +14174,146 @@
     </row>
     <row r="261" spans="1:16">
       <c r="A261" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B261" t="s">
         <v>78</v>
       </c>
       <c r="C261">
-        <v>-7.112794598132552</v>
+        <v>-10.40035287044137</v>
       </c>
       <c r="D261" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E261">
-        <v>-9.24933216391247</v>
+        <v>-9.261926355419064</v>
       </c>
       <c r="F261">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G261">
-        <v>0.09141279459813255</v>
+        <v>0.1018003528704414</v>
       </c>
       <c r="H261">
-        <v>0.08402933216391248</v>
+        <v>0.1012019263554191</v>
       </c>
       <c r="I261">
-        <v>2.136537565779918</v>
+        <v>1.138426515022303</v>
       </c>
       <c r="J261">
-        <v>1.165983304097812</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K261">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L261">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M261">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N261">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O261">
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>256</v>
+        <v>137</v>
       </c>
     </row>
     <row r="262" spans="1:16">
       <c r="A262" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B262" t="s">
         <v>77</v>
       </c>
       <c r="C262">
-        <v>-10.79189108353899</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D262" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E262">
-        <v>-9.99801863177759</v>
+        <v>-9.24933216391247</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G262">
-        <v>0.102191891083539</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H262">
-        <v>0.09913801863177758</v>
+        <v>0.08402933216391248</v>
       </c>
       <c r="I262">
-        <v>0.7938724517613949</v>
+        <v>2.136537565779918</v>
       </c>
       <c r="J262">
         <v>1.165983304097812</v>
       </c>
       <c r="K262">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L262">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M262">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N262">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O262">
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="1:16">
       <c r="A263" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B263" t="s">
         <v>78</v>
       </c>
       <c r="C263">
-        <v>-7.379527992135429</v>
+        <v>-10.79189108353899</v>
       </c>
       <c r="D263" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E263">
-        <v>-9.501860820956622</v>
+        <v>-9.647403605465627</v>
       </c>
       <c r="F263">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G263">
-        <v>0.09167952799213544</v>
+        <v>0.102191891083539</v>
       </c>
       <c r="H263">
-        <v>0.08428186082095662</v>
+        <v>0.1015874036054656</v>
       </c>
       <c r="I263">
-        <v>2.122332828821193</v>
+        <v>1.144487478073358</v>
       </c>
       <c r="J263">
-        <v>1.172296520523916</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K263">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L263">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M263">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N263">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O263">
         <v>1</v>
@@ -14324,96 +14324,96 @@
     </row>
     <row r="264" spans="1:16">
       <c r="A264" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B264" t="s">
         <v>77</v>
       </c>
       <c r="C264">
-        <v>-11.09776641938371</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D264" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E264">
-        <v>-10.29347716051925</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G264">
-        <v>0.1024977664193837</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H264">
-        <v>0.09943347716051924</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I264">
-        <v>0.8042892588644648</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J264">
         <v>1.172296520523916</v>
       </c>
       <c r="K264">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L264">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M264">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N264">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O264">
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="265" spans="1:16">
       <c r="A265" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B265" t="s">
         <v>78</v>
       </c>
       <c r="C265">
-        <v>-7.702700683679339</v>
+        <v>-11.09776641938371</v>
       </c>
       <c r="D265" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E265">
-        <v>-9.80782313247748</v>
+        <v>-9.948544028990774</v>
       </c>
       <c r="F265">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G265">
-        <v>0.09200270068367934</v>
+        <v>0.1024977664193837</v>
       </c>
       <c r="H265">
-        <v>0.08458782313247748</v>
+        <v>0.1018885440289908</v>
       </c>
       <c r="I265">
-        <v>2.105122448798141</v>
+        <v>1.149222390392936</v>
       </c>
       <c r="J265">
-        <v>1.179945578311937</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K265">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L265">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M265">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N265">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O265">
         <v>1</v>
@@ -14424,96 +14424,96 @@
     </row>
     <row r="266" spans="1:16">
       <c r="A266" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B266" t="s">
         <v>77</v>
       </c>
       <c r="C266">
-        <v>-11.46836326921335</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D266" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E266">
-        <v>-10.65145306499865</v>
+        <v>-9.80782313247748</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G266">
-        <v>0.1028683632692134</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H266">
-        <v>0.09979145306499865</v>
+        <v>0.08458782313247748</v>
       </c>
       <c r="I266">
-        <v>0.8169102042147003</v>
+        <v>2.105122448798141</v>
       </c>
       <c r="J266">
         <v>1.179945578311937</v>
       </c>
       <c r="K266">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L266">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M266">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N266">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O266">
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="267" spans="1:16">
       <c r="A267" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B267" t="s">
         <v>78</v>
       </c>
       <c r="C267">
-        <v>-8.001107320444035</v>
+        <v>-11.46836326921335</v>
       </c>
       <c r="D267" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E267">
-        <v>-10.09033829154465</v>
+        <v>-10.3134040854794</v>
       </c>
       <c r="F267">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G267">
-        <v>0.09230110732044404</v>
+        <v>0.1028683632692134</v>
       </c>
       <c r="H267">
-        <v>0.08487033829154464</v>
+        <v>0.1022534040854794</v>
       </c>
       <c r="I267">
-        <v>2.089230971100612</v>
+        <v>1.154959183733951</v>
       </c>
       <c r="J267">
-        <v>1.187008457288616</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K267">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L267">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M267">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N267">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O267">
         <v>1</v>
@@ -14524,96 +14524,96 @@
     </row>
     <row r="268" spans="1:16">
       <c r="A268" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B268" t="s">
         <v>77</v>
       </c>
       <c r="C268">
-        <v>-11.81055975563346</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D268" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E268">
-        <v>-10.98199580110723</v>
+        <v>-10.09033829154465</v>
       </c>
       <c r="F268">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G268">
-        <v>0.1032105597556335</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H268">
-        <v>0.1001219958011072</v>
+        <v>0.08487033829154464</v>
       </c>
       <c r="I268">
-        <v>0.8285639545262242</v>
+        <v>2.089230971100612</v>
       </c>
       <c r="J268">
         <v>1.187008457288616</v>
       </c>
       <c r="K268">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L268">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M268">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N268">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O268">
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="269" spans="1:16">
       <c r="A269" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B269" t="s">
         <v>78</v>
       </c>
       <c r="C269">
-        <v>-8.280300561754309</v>
+        <v>-11.81055975563346</v>
       </c>
       <c r="D269" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E269">
-        <v>-10.35466325373189</v>
+        <v>-10.65030341266699</v>
       </c>
       <c r="F269">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G269">
-        <v>0.09258030056175431</v>
+        <v>0.1032105597556335</v>
       </c>
       <c r="H269">
-        <v>0.0851346632537319</v>
+        <v>0.102590303412667</v>
       </c>
       <c r="I269">
-        <v>2.074362691977583</v>
+        <v>1.160256342966463</v>
       </c>
       <c r="J269">
-        <v>1.193616581343297</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K269">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L269">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M269">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N269">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O269">
         <v>1</v>
@@ -14624,96 +14624,96 @@
     </row>
     <row r="270" spans="1:16">
       <c r="A270" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B270" t="s">
         <v>77</v>
       </c>
       <c r="C270">
-        <v>-12.13072336608275</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D270" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E270">
-        <v>-11.29125600686631</v>
+        <v>-10.35466325373189</v>
       </c>
       <c r="F270">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G270">
-        <v>0.1035307233660828</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H270">
-        <v>0.1004312560068663</v>
+        <v>0.0851346632537319</v>
       </c>
       <c r="I270">
-        <v>0.8394673592164423</v>
+        <v>2.074362691977583</v>
       </c>
       <c r="J270">
         <v>1.193616581343297</v>
       </c>
       <c r="K270">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L270">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M270">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N270">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O270">
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="271" spans="1:16">
       <c r="A271" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B271" t="s">
         <v>78</v>
       </c>
       <c r="C271">
-        <v>-8.625026882373376</v>
+        <v>-12.13072336608275</v>
       </c>
       <c r="D271" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E271">
-        <v>-10.68103136792746</v>
+        <v>-10.96551093007528</v>
       </c>
       <c r="F271">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G271">
-        <v>0.09292502688237338</v>
+        <v>0.1035307233660828</v>
       </c>
       <c r="H271">
-        <v>0.08546103136792746</v>
+        <v>0.1029055109300753</v>
       </c>
       <c r="I271">
-        <v>2.056004485554084</v>
+        <v>1.165212436007472</v>
       </c>
       <c r="J271">
-        <v>1.201775784198186</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K271">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L271">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M271">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N271">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O271">
         <v>1</v>
@@ -14724,96 +14724,96 @@
     </row>
     <row r="272" spans="1:16">
       <c r="A272" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B272" t="s">
         <v>77</v>
       </c>
       <c r="C272">
-        <v>-12.52603674440213</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D272" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E272">
-        <v>-11.67310670047512</v>
+        <v>-10.68103136792746</v>
       </c>
       <c r="F272">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G272">
-        <v>0.1039260367444021</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H272">
-        <v>0.1008131067004751</v>
+        <v>0.08546103136792746</v>
       </c>
       <c r="I272">
-        <v>0.8529300439270102</v>
+        <v>2.056004485554084</v>
       </c>
       <c r="J272">
         <v>1.201775784198186</v>
       </c>
       <c r="K272">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L272">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M272">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N272">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O272">
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:16">
       <c r="A273" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B273" t="s">
         <v>78</v>
       </c>
       <c r="C273">
-        <v>-8.846388689296894</v>
+        <v>-12.52603674440213</v>
       </c>
       <c r="D273" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E273">
-        <v>-10.89060467625741</v>
+        <v>-11.3547049062535</v>
       </c>
       <c r="F273">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G273">
-        <v>0.09314638868929688</v>
+        <v>0.1039260367444021</v>
       </c>
       <c r="H273">
-        <v>0.08567060467625741</v>
+        <v>0.1032947049062535</v>
       </c>
       <c r="I273">
-        <v>2.044215986960516</v>
+        <v>1.171331838148639</v>
       </c>
       <c r="J273">
-        <v>1.207015116906435</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K273">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L273">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M273">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N273">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O273">
         <v>1</v>
@@ -14824,96 +14824,96 @@
     </row>
     <row r="274" spans="1:16">
       <c r="A274" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B274" t="s">
         <v>77</v>
       </c>
       <c r="C274">
-        <v>-12.77988241411679</v>
+        <v>-8.846388689296894</v>
       </c>
       <c r="D274" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E274">
-        <v>-11.91830747122117</v>
+        <v>-10.89060467625741</v>
       </c>
       <c r="F274">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G274">
-        <v>0.1041798824141168</v>
+        <v>0.09314638868929688</v>
       </c>
       <c r="H274">
-        <v>0.1010583074712212</v>
+        <v>0.08567060467625741</v>
       </c>
       <c r="I274">
-        <v>0.8615749428956221</v>
+        <v>2.044215986960516</v>
       </c>
       <c r="J274">
         <v>1.207015116906435</v>
       </c>
       <c r="K274">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L274">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M274">
-        <v>46.8</v>
+        <v>40</v>
       </c>
       <c r="N274">
-        <v>44.57</v>
+        <v>37.39</v>
       </c>
       <c r="O274">
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="275" spans="1:16">
       <c r="A275" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B275" t="s">
         <v>78</v>
       </c>
       <c r="C275">
-        <v>-9.123967366600709</v>
+        <v>-12.77988241411679</v>
       </c>
       <c r="D275" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E275">
-        <v>-11.15340105713676</v>
+        <v>-11.60462107643697</v>
       </c>
       <c r="F275">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G275">
-        <v>0.0934239673666007</v>
+        <v>0.1041798824141168</v>
       </c>
       <c r="H275">
-        <v>0.08593340105713676</v>
+        <v>0.103544621076437</v>
       </c>
       <c r="I275">
-        <v>2.029433690536052</v>
+        <v>1.175261337679821</v>
       </c>
       <c r="J275">
-        <v>1.213585026428419</v>
+        <v>1.207015116906435</v>
       </c>
       <c r="K275">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L275">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M275">
-        <v>40</v>
+        <v>47.7</v>
       </c>
       <c r="N275">
-        <v>37.39</v>
+        <v>45.97</v>
       </c>
       <c r="O275">
         <v>1</v>
@@ -14924,84 +14924,84 @@
     </row>
     <row r="276" spans="1:16">
       <c r="A276" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B276" t="s">
         <v>77</v>
       </c>
       <c r="C276">
-        <v>-13.09819453045691</v>
+        <v>-9.123967366600709</v>
       </c>
       <c r="D276" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E276">
-        <v>-12.22577923685001</v>
+        <v>-12.4989867236358</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G276">
-        <v>0.1044981945304569</v>
+        <v>0.0934239673666007</v>
       </c>
       <c r="H276">
-        <v>0.10136577923685</v>
+        <v>0.09987898672363579</v>
       </c>
       <c r="I276">
-        <v>0.872415293606899</v>
+        <v>3.375019357035093</v>
       </c>
       <c r="J276">
         <v>1.213585026428419</v>
       </c>
       <c r="K276">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L276">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M276">
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
       <c r="N276">
-        <v>44.57</v>
+        <v>43.69</v>
       </c>
       <c r="O276">
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="277" spans="1:16">
       <c r="A277" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B277" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C277">
-        <v>-13.6699480138974</v>
+        <v>-13.09819453045691</v>
       </c>
       <c r="D277" t="s">
         <v>138</v>
       </c>
       <c r="E277">
-        <v>-12.77806123943031</v>
+        <v>-11.91800576063559</v>
       </c>
       <c r="F277">
         <v>1</v>
       </c>
       <c r="G277">
-        <v>0.1050699480138974</v>
+        <v>0.1044981945304569</v>
       </c>
       <c r="H277">
-        <v>0.1019180612394303</v>
+        <v>0.1038580057606356</v>
       </c>
       <c r="I277">
-        <v>0.8918867744670962</v>
+        <v>1.180188769821314</v>
       </c>
       <c r="J277">
-        <v>1.225385923919451</v>
+        <v>1.213585026428419</v>
       </c>
       <c r="K277">
         <v>48.45</v>
@@ -15010,10 +15010,10 @@
         <v>45.7</v>
       </c>
       <c r="M277">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N277">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O277">
         <v>1</v>
@@ -15027,43 +15027,43 @@
         <v>0</v>
       </c>
       <c r="B278" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C278">
-        <v>-14.07843771699785</v>
+        <v>-9.62255528559681</v>
       </c>
       <c r="D278" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E278">
-        <v>-12.99490953690155</v>
+        <v>-13.04536827747059</v>
       </c>
       <c r="F278">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G278">
-        <v>0.1046184377169979</v>
+        <v>0.09392255528559681</v>
       </c>
       <c r="H278">
-        <v>0.1021349095369015</v>
+        <v>0.1004253682774706</v>
       </c>
       <c r="I278">
-        <v>1.083528180096309</v>
+        <v>3.422812991873776</v>
       </c>
       <c r="J278">
-        <v>1.230019434549178</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K278">
-        <v>48.25</v>
+        <v>42.25</v>
       </c>
       <c r="L278">
-        <v>45.27</v>
+        <v>42.15</v>
       </c>
       <c r="M278">
-        <v>46.8</v>
+        <v>46.3</v>
       </c>
       <c r="N278">
-        <v>44.57</v>
+        <v>43.69</v>
       </c>
       <c r="O278">
         <v>1</v>
@@ -15074,34 +15074,34 @@
     </row>
     <row r="279" spans="1:16">
       <c r="A279" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B279" t="s">
         <v>76</v>
       </c>
       <c r="C279">
-        <v>-14.37007717217479</v>
+        <v>-13.85487082911352</v>
       </c>
       <c r="D279" t="s">
         <v>138</v>
       </c>
       <c r="E279">
-        <v>-13.27778469757057</v>
+        <v>-12.48090857095782</v>
       </c>
       <c r="F279">
         <v>1</v>
       </c>
       <c r="G279">
-        <v>0.1049100771721748</v>
+        <v>0.1043948708291135</v>
       </c>
       <c r="H279">
-        <v>0.1024177846975706</v>
+        <v>0.1044209085709578</v>
       </c>
       <c r="I279">
-        <v>1.092292474604214</v>
+        <v>1.373962258155693</v>
       </c>
       <c r="J279">
-        <v>1.236063775589115</v>
+        <v>1.225385923919451</v>
       </c>
       <c r="K279">
         <v>48.25</v>
@@ -15110,15 +15110,115 @@
         <v>45.27</v>
       </c>
       <c r="M279">
-        <v>46.8</v>
+        <v>47.7</v>
       </c>
       <c r="N279">
-        <v>44.57</v>
+        <v>45.97</v>
       </c>
       <c r="O279">
         <v>1</v>
       </c>
       <c r="P279" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16">
+      <c r="A280" s="1">
+        <v>0</v>
+      </c>
+      <c r="B280" t="s">
+        <v>77</v>
+      </c>
+      <c r="C280">
+        <v>-9.818321109702786</v>
+      </c>
+      <c r="D280" t="s">
+        <v>142</v>
+      </c>
+      <c r="E280">
+        <v>-13.25989981962696</v>
+      </c>
+      <c r="F280">
+        <v>-1</v>
+      </c>
+      <c r="G280">
+        <v>0.09411832110970278</v>
+      </c>
+      <c r="H280">
+        <v>0.100639899819627</v>
+      </c>
+      <c r="I280">
+        <v>3.441578709924173</v>
+      </c>
+      <c r="J280">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K280">
+        <v>42.25</v>
+      </c>
+      <c r="L280">
+        <v>42.15</v>
+      </c>
+      <c r="M280">
+        <v>46.3</v>
+      </c>
+      <c r="N280">
+        <v>43.69</v>
+      </c>
+      <c r="O280">
+        <v>1</v>
+      </c>
+      <c r="P280" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16">
+      <c r="A281" s="1">
+        <v>1</v>
+      </c>
+      <c r="B281" t="s">
+        <v>76</v>
+      </c>
+      <c r="C281">
+        <v>-14.07843771699785</v>
+      </c>
+      <c r="D281" t="s">
+        <v>138</v>
+      </c>
+      <c r="E281">
+        <v>-12.70192702799581</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+      <c r="G281">
+        <v>0.1046184377169979</v>
+      </c>
+      <c r="H281">
+        <v>0.1046419270279958</v>
+      </c>
+      <c r="I281">
+        <v>1.376510689002039</v>
+      </c>
+      <c r="J281">
+        <v>1.230019434549178</v>
+      </c>
+      <c r="K281">
+        <v>48.25</v>
+      </c>
+      <c r="L281">
+        <v>45.27</v>
+      </c>
+      <c r="M281">
+        <v>47.7</v>
+      </c>
+      <c r="N281">
+        <v>45.97</v>
+      </c>
+      <c r="O281">
+        <v>1</v>
+      </c>
+      <c r="P281" t="s">
         <v>266</v>
       </c>
     </row>

--- a/s60_signal/position-00914-600585.xlsx
+++ b/s60_signal/position-00914-600585.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="266">
   <si>
     <t>trade_time</t>
   </si>
@@ -232,561 +232,555 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-07-09</t>
+  </si>
+  <si>
     <t>2021-07-07</t>
   </si>
   <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-13</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-15</t>
+  </si>
+  <si>
+    <t>2017-06-16</t>
+  </si>
+  <si>
+    <t>2017-06-19</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-21</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-26</t>
+  </si>
+  <si>
+    <t>2017-06-27</t>
+  </si>
+  <si>
+    <t>2017-06-28</t>
+  </si>
+  <si>
+    <t>2017-06-30</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-07-12</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2018-03-26</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-08</t>
+  </si>
+  <si>
+    <t>2018-08-09</t>
+  </si>
+  <si>
+    <t>2018-08-10</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-08-05</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-20</t>
+  </si>
+  <si>
+    <t>2020-01-21</t>
+  </si>
+  <si>
+    <t>2020-01-02</t>
+  </si>
+  <si>
+    <t>2020-02-03</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-03-03</t>
+  </si>
+  <si>
+    <t>2020-04-01</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-03-18</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-03-05</t>
+  </si>
+  <si>
+    <t>2021-07-05</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
+  </si>
+  <si>
+    <t>2021-07-14</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-01-05</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-16</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2017-01-18</t>
+  </si>
+  <si>
+    <t>2017-01-19</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2017-01-23</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2017-02-09</t>
+  </si>
+  <si>
+    <t>2017-02-10</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2018-02-12</t>
+  </si>
+  <si>
+    <t>2018-02-13</t>
+  </si>
+  <si>
+    <t>2018-03-02</t>
+  </si>
+  <si>
+    <t>2018-03-05</t>
+  </si>
+  <si>
+    <t>2018-03-06</t>
+  </si>
+  <si>
+    <t>2018-03-08</t>
+  </si>
+  <si>
+    <t>2018-03-09</t>
+  </si>
+  <si>
+    <t>2018-03-12</t>
+  </si>
+  <si>
+    <t>2018-03-13</t>
+  </si>
+  <si>
+    <t>2018-03-14</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-03-16</t>
+  </si>
+  <si>
+    <t>2018-03-19</t>
+  </si>
+  <si>
+    <t>2019-03-28</t>
+  </si>
+  <si>
+    <t>2019-04-03</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-28</t>
+  </si>
+  <si>
+    <t>2019-07-02</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-11</t>
+  </si>
+  <si>
+    <t>2019-07-12</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-07-26</t>
+  </si>
+  <si>
+    <t>2019-07-30</t>
+  </si>
+  <si>
+    <t>2019-08-01</t>
+  </si>
+  <si>
+    <t>2019-08-02</t>
+  </si>
+  <si>
+    <t>2019-08-06</t>
+  </si>
+  <si>
+    <t>2019-08-07</t>
+  </si>
+  <si>
+    <t>2019-08-08</t>
+  </si>
+  <si>
+    <t>2019-08-09</t>
+  </si>
+  <si>
+    <t>2019-08-12</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-15</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2019-08-19</t>
+  </si>
+  <si>
+    <t>2019-08-20</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2019-08-22</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-27</t>
+  </si>
+  <si>
+    <t>2020-02-05</t>
+  </si>
+  <si>
+    <t>2020-02-06</t>
+  </si>
+  <si>
+    <t>2020-10-20</t>
+  </si>
+  <si>
+    <t>2020-10-21</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-16</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-29</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-06</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
     <t>2021-07-06</t>
   </si>
   <si>
-    <t>2021-07-09</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2021-09-06</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-13</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-15</t>
-  </si>
-  <si>
-    <t>2017-06-16</t>
-  </si>
-  <si>
-    <t>2017-06-19</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-21</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-26</t>
-  </si>
-  <si>
-    <t>2017-06-27</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2017-06-30</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-07-12</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2018-03-26</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-08</t>
-  </si>
-  <si>
-    <t>2018-08-09</t>
-  </si>
-  <si>
-    <t>2018-08-10</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-20</t>
-  </si>
-  <si>
-    <t>2020-01-21</t>
-  </si>
-  <si>
-    <t>2020-01-02</t>
-  </si>
-  <si>
-    <t>2020-02-03</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-03-03</t>
-  </si>
-  <si>
-    <t>2020-04-01</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-14</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
+    <t>2021-07-15</t>
+  </si>
+  <si>
+    <t>2021-07-16</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
   </si>
   <si>
     <t>2021-07-30</t>
   </si>
   <si>
-    <t>2021-09-09</t>
-  </si>
-  <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-08-26</t>
-  </si>
-  <si>
-    <t>2021-08-30</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-01-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-16</t>
-  </si>
-  <si>
-    <t>2017-01-17</t>
-  </si>
-  <si>
-    <t>2017-01-18</t>
-  </si>
-  <si>
-    <t>2017-01-19</t>
-  </si>
-  <si>
-    <t>2017-01-20</t>
-  </si>
-  <si>
-    <t>2017-01-23</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2017-02-09</t>
-  </si>
-  <si>
-    <t>2017-02-10</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2018-02-12</t>
-  </si>
-  <si>
-    <t>2018-02-13</t>
-  </si>
-  <si>
-    <t>2018-03-02</t>
-  </si>
-  <si>
-    <t>2018-03-05</t>
-  </si>
-  <si>
-    <t>2018-03-06</t>
-  </si>
-  <si>
-    <t>2018-03-08</t>
-  </si>
-  <si>
-    <t>2018-03-09</t>
-  </si>
-  <si>
-    <t>2018-03-12</t>
-  </si>
-  <si>
-    <t>2018-03-13</t>
-  </si>
-  <si>
-    <t>2018-03-14</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-03-16</t>
-  </si>
-  <si>
-    <t>2018-03-19</t>
-  </si>
-  <si>
-    <t>2019-03-28</t>
-  </si>
-  <si>
-    <t>2019-04-03</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2019-07-02</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-11</t>
-  </si>
-  <si>
-    <t>2019-07-12</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-07-26</t>
-  </si>
-  <si>
-    <t>2019-07-30</t>
-  </si>
-  <si>
-    <t>2019-08-01</t>
-  </si>
-  <si>
-    <t>2019-08-02</t>
-  </si>
-  <si>
-    <t>2019-08-06</t>
-  </si>
-  <si>
-    <t>2019-08-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-08-09</t>
-  </si>
-  <si>
-    <t>2019-08-12</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-15</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-08-20</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-27</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2020-02-06</t>
-  </si>
-  <si>
-    <t>2020-10-20</t>
-  </si>
-  <si>
-    <t>2020-10-21</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-16</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-29</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
-  </si>
-  <si>
-    <t>2021-07-22</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-28</t>
-  </si>
-  <si>
-    <t>2021-07-29</t>
-  </si>
-  <si>
     <t>2021-08-02</t>
   </si>
   <si>
@@ -815,6 +809,9 @@
   </si>
   <si>
     <t>2021-08-16</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P281"/>
+  <dimension ref="A1:P271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1269,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1319,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1333,7 +1330,7 @@
         <v>3.865859388393531</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4">
         <v>4.097842290047694</v>
@@ -1369,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1383,7 +1380,7 @@
         <v>3.867842290047694</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5">
         <v>4.097842290047694</v>
@@ -1419,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1433,7 +1430,7 @@
         <v>3.461721442525899</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>3.39419673099987</v>
@@ -1469,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1483,7 +1480,7 @@
         <v>3.459734423297274</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>3.39419673099987</v>
@@ -1519,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1569,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1619,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1633,7 +1630,7 @@
         <v>3.16694425131325</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>3.359129610475641</v>
@@ -1669,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1683,7 +1680,7 @@
         <v>3.394897239794993</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11">
         <v>3.359129610475641</v>
@@ -1719,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1733,7 +1730,7 @@
         <v>3.117640232442373</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>2.635536081278246</v>
@@ -1769,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1783,7 +1780,7 @@
         <v>3.321848534770627</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E13">
         <v>2.635536081278246</v>
@@ -1819,7 +1816,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1833,7 +1830,7 @@
         <v>3.344834697556873</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E14">
         <v>2.635536081278246</v>
@@ -1869,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1883,7 +1880,7 @@
         <v>2.993112189363568</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15">
         <v>2.673112189363568</v>
@@ -1919,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1933,7 +1930,7 @@
         <v>3.20019421576287</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16">
         <v>2.673112189363568</v>
@@ -1969,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1983,7 +1980,7 @@
         <v>3.218390838430704</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E17">
         <v>2.673112189363568</v>
@@ -2019,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2033,7 +2030,7 @@
         <v>3.103012988322206</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>2.62988710634049</v>
@@ -2069,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2083,7 +2080,7 @@
         <v>3.117383578413634</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E19">
         <v>2.62988710634049</v>
@@ -2119,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2133,7 +2130,7 @@
         <v>2.953610693719877</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E20">
         <v>2.537157276716563</v>
@@ -2169,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2183,7 +2180,7 @@
         <v>2.962099303708847</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21">
         <v>2.537157276716563</v>
@@ -2219,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2233,7 +2230,7 @@
         <v>2.872635186535728</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E22">
         <v>2.682635186535727</v>
@@ -2269,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2283,7 +2280,7 @@
         <v>2.877935784430836</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23">
         <v>2.682635186535727</v>
@@ -2319,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2333,7 +2330,7 @@
         <v>2.852267607428114</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E24">
         <v>2.629917990017542</v>
@@ -2369,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2383,7 +2380,7 @@
         <v>2.856766332130007</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E25">
         <v>2.629917990017542</v>
@@ -2419,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2433,7 +2430,7 @@
         <v>2.811761351230931</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E26">
         <v>2.640825752700035</v>
@@ -2469,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2483,7 +2480,7 @@
         <v>2.814665341436871</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E27">
         <v>2.640825752700035</v>
@@ -2519,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2569,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2619,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2633,7 +2630,7 @@
         <v>2.63826823762383</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E30">
         <v>2.63791236922124</v>
@@ -2669,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -2683,7 +2680,7 @@
         <v>2.634341790286186</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E31">
         <v>2.63791236922124</v>
@@ -2719,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -2733,7 +2730,7 @@
         <v>2.644964559990708</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E32">
         <v>2.63791236922124</v>
@@ -2769,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2783,7 +2780,7 @@
         <v>2.731915275790641</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E33">
         <v>2.352208534673963</v>
@@ -2819,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -2833,7 +2830,7 @@
         <v>2.610439248718354</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E34">
         <v>2.352208534673963</v>
@@ -2869,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2883,7 +2880,7 @@
         <v>2.746753374580404</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E35">
         <v>2.350225795209379</v>
@@ -2919,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2969,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -2983,7 +2980,7 @@
         <v>2.787117571133386</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37">
         <v>2.823906542063554</v>
@@ -3019,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3033,7 +3030,7 @@
         <v>2.883884958958227</v>
       </c>
       <c r="D38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>2.823906542063554</v>
@@ -3069,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3083,7 +3080,7 @@
         <v>2.85679612614372</v>
       </c>
       <c r="D39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E39">
         <v>2.509699758109345</v>
@@ -3119,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3133,7 +3130,7 @@
         <v>2.784156488881695</v>
       </c>
       <c r="D40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E40">
         <v>2.482559097029725</v>
@@ -3169,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3183,7 +3180,7 @@
         <v>2.712068545906188</v>
       </c>
       <c r="D41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E41">
         <v>2.389269688337961</v>
@@ -3219,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3233,7 +3230,7 @@
         <v>2.702691411029491</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E42">
         <v>2.366731283785484</v>
@@ -3269,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3319,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3333,7 +3330,7 @@
         <v>2.972898466540091</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E44">
         <v>2.959777273665928</v>
@@ -3369,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3383,7 +3380,7 @@
         <v>2.921933117969051</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45">
         <v>2.740731067560024</v>
@@ -3419,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3433,7 +3430,7 @@
         <v>2.98396235602636</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E46">
         <v>2.472809772939694</v>
@@ -3469,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3483,7 +3480,7 @@
         <v>0.9436087597884253</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47">
         <v>-1.99755555963268</v>
@@ -3519,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3533,7 +3530,7 @@
         <v>0.9931330872741064</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E48">
         <v>-1.945846335346161</v>
@@ -3569,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3583,7 +3580,7 @@
         <v>1.061208452840496</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E49">
         <v>-1.561324587868725</v>
@@ -3619,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3633,7 +3630,7 @@
         <v>1.119649719030264</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E50">
         <v>-1.498535232517298</v>
@@ -3669,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3683,7 +3680,7 @@
         <v>1.154541005165207</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E51">
         <v>-1.461047999494632</v>
@@ -3719,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3733,7 +3730,7 @@
         <v>1.131852687543812</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E52">
         <v>0.5478188871899121</v>
@@ -3783,7 +3780,7 @@
         <v>1.188936742513683</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E53">
         <v>1.063100941658099</v>
@@ -3819,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3833,7 +3830,7 @@
         <v>1.249982102732112</v>
       </c>
       <c r="D54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E54">
         <v>0.07301952552553104</v>
@@ -3869,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -3883,7 +3880,7 @@
         <v>1.342037179610671</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E55">
         <v>-0.05480301084717354</v>
@@ -3919,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -3933,7 +3930,7 @@
         <v>1.451972473813719</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>0.9119894589734443</v>
@@ -3969,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -3983,7 +3980,7 @@
         <v>1.510041973607841</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E57">
         <v>1.302812532847142</v>
@@ -4019,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4033,7 +4030,7 @@
         <v>1.540830568775363</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E58">
         <v>0.9301997197644951</v>
@@ -4069,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4083,7 +4080,7 @@
         <v>1.597939172685521</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E59">
         <v>0.792592453180788</v>
@@ -4119,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4133,7 +4130,7 @@
         <v>1.703402241378249</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>1.579882369457003</v>
@@ -4169,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4183,7 +4180,7 @@
         <v>7.082322116014304</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E61">
         <v>9.39892979714033</v>
@@ -4219,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4233,7 +4230,7 @@
         <v>6.03547807457366</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>8.392943592760137</v>
@@ -4269,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4283,7 +4280,7 @@
         <v>-3.725741650745938</v>
       </c>
       <c r="D63" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>-1.061483620645447</v>
@@ -4319,7 +4316,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4333,7 +4330,7 @@
         <v>-3.390064231685251</v>
       </c>
       <c r="D64" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>-1.061483620645447</v>
@@ -4369,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4383,7 +4380,7 @@
         <v>-4.367653322749888</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E65">
         <v>-1.625808861219163</v>
@@ -4419,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4433,7 +4430,7 @@
         <v>-4.031312771796635</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E66">
         <v>-1.625808861219163</v>
@@ -4469,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4483,7 +4480,7 @@
         <v>-4.607517906916144</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E67">
         <v>-1.836681548332265</v>
@@ -4519,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4533,7 +4530,7 @@
         <v>-4.270929561970988</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E68">
         <v>-1.836681548332265</v>
@@ -4569,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4583,7 +4580,7 @@
         <v>-4.387223400334264</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E69">
         <v>-2.098063558594617</v>
@@ -4633,7 +4630,7 @@
         <v>-4.567940612410105</v>
       </c>
       <c r="D70" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E70">
         <v>-2.098063558594617</v>
@@ -4683,7 +4680,7 @@
         <v>-4.572133036248417</v>
       </c>
       <c r="D71" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E71">
         <v>-2.256530930359915</v>
@@ -4719,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -4733,7 +4730,7 @@
         <v>-4.748008707001226</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E72">
         <v>-2.256530930359915</v>
@@ -4769,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -4783,7 +4780,7 @@
         <v>-4.6969899027008</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E73">
         <v>-2.363533139172588</v>
@@ -4819,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -4833,7 +4830,7 @@
         <v>-4.869596410787189</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E74">
         <v>-2.363533139172588</v>
@@ -4869,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -4883,7 +4880,7 @@
         <v>-4.851917740072338</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E75">
         <v>-2.496306139780017</v>
@@ -4919,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -4933,7 +4930,7 @@
         <v>-4.5541965709862</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E76">
         <v>-2.496306139780017</v>
@@ -4969,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -4983,7 +4980,7 @@
         <v>-4.568923494933983</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E77">
         <v>-2.496306139780017</v>
@@ -5019,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5033,7 +5030,7 @@
         <v>-4.843752817660352</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E78">
         <v>-2.753521553057368</v>
@@ -5083,7 +5080,7 @@
         <v>-4.803407083453244</v>
       </c>
       <c r="D79" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E79">
         <v>-2.753521553057368</v>
@@ -5133,7 +5130,7 @@
         <v>-5.12322060515109</v>
       </c>
       <c r="D80" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E80">
         <v>-3.001775297477636</v>
@@ -5169,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5183,7 +5180,7 @@
         <v>-5.086667231317023</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E81">
         <v>-3.001775297477636</v>
@@ -5219,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5233,7 +5230,7 @@
         <v>-5.498672524566146</v>
       </c>
       <c r="D82" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E82">
         <v>-3.335292607939238</v>
@@ -5269,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5283,7 +5280,7 @@
         <v>-5.467214009763808</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E83">
         <v>-3.335292607939238</v>
@@ -5319,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5333,7 +5330,7 @@
         <v>-5.942693680916477</v>
       </c>
       <c r="D84" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E84">
         <v>-3.729720587118912</v>
@@ -5369,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5383,7 +5380,7 @@
         <v>-5.917260505396555</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E85">
         <v>-3.729720587118912</v>
@@ -5419,7 +5416,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5433,7 +5430,7 @@
         <v>-6.304243385177699</v>
       </c>
       <c r="D86" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E86">
         <v>-4.050888435058688</v>
@@ -5469,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5483,7 +5480,7 @@
         <v>-6.283716416500575</v>
       </c>
       <c r="D87" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E87">
         <v>-4.050888435058688</v>
@@ -5519,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5533,7 +5530,7 @@
         <v>-6.70774440980211</v>
       </c>
       <c r="D88" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E88">
         <v>-4.422513380784331</v>
@@ -5583,7 +5580,7 @@
         <v>-7.026497484109498</v>
       </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E89">
         <v>-4.701873696165997</v>
@@ -5619,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5633,7 +5630,7 @@
         <v>-7.466555872236626</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E90">
         <v>-5.087547937459696</v>
@@ -5669,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5683,7 +5680,7 @@
         <v>-5.360456423998336</v>
       </c>
       <c r="D91" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E91">
         <v>-6.993426227125362</v>
@@ -5719,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5733,7 +5730,7 @@
         <v>-8.255385642797997</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E92">
         <v>-6.633019871061308</v>
@@ -5769,7 +5766,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5783,7 +5780,7 @@
         <v>-5.597771601185165</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E93">
         <v>-7.088994860354454</v>
@@ -5819,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -5833,7 +5830,7 @@
         <v>-5.553423604070751</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E94">
         <v>-7.191259698838785</v>
@@ -5869,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -5883,7 +5880,7 @@
         <v>-8.299892373677679</v>
       </c>
       <c r="D95" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E95">
         <v>-6.674413562841202</v>
@@ -5919,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -5933,7 +5930,7 @@
         <v>-5.645829142288029</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E96">
         <v>-7.139484463254028</v>
@@ -5969,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -5983,7 +5980,7 @@
         <v>-5.603572718318787</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E97">
         <v>-7.242673485221104</v>
@@ -6019,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6033,7 +6030,7 @@
         <v>-8.177862645389048</v>
       </c>
       <c r="D98" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E98">
         <v>-6.702607565134123</v>
@@ -6069,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6083,7 +6080,7 @@
         <v>-8.330206723969127</v>
       </c>
       <c r="D99" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E99">
         <v>-6.702607565134123</v>
@@ -6119,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6133,7 +6130,7 @@
         <v>-5.758656618823501</v>
       </c>
       <c r="D100" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E100">
         <v>-7.247843724527407</v>
@@ -6169,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6183,7 +6180,7 @@
         <v>-5.6785620145153</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E101">
         <v>-7.17387385735514</v>
@@ -6219,7 +6216,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6233,7 +6230,7 @@
         <v>-5.637730199357563</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E102">
         <v>-7.277692357634287</v>
@@ -6269,7 +6266,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6283,7 +6280,7 @@
         <v>-8.225632222005096</v>
       </c>
       <c r="D103" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E103">
         <v>-6.745854277581202</v>
@@ -6319,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6333,7 +6330,7 @@
         <v>-8.376705833121981</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E104">
         <v>-6.745854277581202</v>
@@ -6369,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6383,7 +6380,7 @@
         <v>-5.862563499790042</v>
       </c>
       <c r="D105" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E105">
         <v>-7.296273944224318</v>
@@ -6419,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6433,7 +6430,7 @@
         <v>-8.138199110881978</v>
       </c>
       <c r="D106" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E106">
         <v>-6.427417499781725</v>
@@ -6469,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6483,7 +6480,7 @@
         <v>-5.728770888660677</v>
       </c>
       <c r="D107" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E107">
         <v>-7.22662366642691</v>
@@ -6519,7 +6516,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6533,7 +6530,7 @@
         <v>-5.690124277539631</v>
       </c>
       <c r="D108" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E108">
         <v>-7.331407721978074</v>
@@ -6569,7 +6566,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6583,7 +6580,7 @@
         <v>-8.44310768470099</v>
       </c>
       <c r="D109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E109">
         <v>-6.807611628066162</v>
@@ -6633,7 +6630,7 @@
         <v>-5.928529929391487</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E110">
         <v>-7.365433468327915</v>
@@ -6683,7 +6680,7 @@
         <v>-8.210188877839769</v>
       </c>
       <c r="D111" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E111">
         <v>-6.495996461248566</v>
@@ -6733,7 +6730,7 @@
         <v>-5.80047037430009</v>
       </c>
       <c r="D112" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E112">
         <v>-7.301951668546046</v>
@@ -6783,7 +6780,7 @@
         <v>-5.764944287351611</v>
       </c>
       <c r="D113" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E113">
         <v>-7.408114560359508</v>
@@ -6833,7 +6830,7 @@
         <v>-8.501365905896868</v>
       </c>
       <c r="D114" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E114">
         <v>-6.861794957287685</v>
@@ -6869,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6883,7 +6880,7 @@
         <v>-5.986406129464761</v>
       </c>
       <c r="D115" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E115">
         <v>-7.426111156633567</v>
@@ -6919,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -6933,7 +6930,7 @@
         <v>-8.273349703442292</v>
       </c>
       <c r="D116" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E116">
         <v>-6.556164788057423</v>
@@ -6969,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6983,7 +6980,7 @@
         <v>-5.863376519154215</v>
       </c>
       <c r="D117" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E117">
         <v>-7.36804132275514</v>
@@ -7019,7 +7016,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7033,7 +7030,7 @@
         <v>-5.830588250251004</v>
       </c>
       <c r="D118" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E118">
         <v>-7.475413948123489</v>
@@ -7069,7 +7066,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7083,7 +7080,7 @@
         <v>-6.036191740627181</v>
       </c>
       <c r="D119" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E119">
         <v>-7.478306632362695</v>
@@ -7133,7 +7130,7 @@
         <v>-8.327681195491927</v>
       </c>
       <c r="D120" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E120">
         <v>-6.607922106592611</v>
@@ -7183,7 +7180,7 @@
         <v>-5.917488932606872</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E121">
         <v>-7.424892218669974</v>
@@ -7233,7 +7230,7 @@
         <v>-5.887055758621138</v>
       </c>
       <c r="D122" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E122">
         <v>-7.533305467373957</v>
@@ -7283,7 +7280,7 @@
         <v>-6.124286449526096</v>
       </c>
       <c r="D123" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E123">
         <v>-7.570665551593358</v>
@@ -7319,7 +7316,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7333,7 +7330,7 @@
         <v>-8.423819755698446</v>
       </c>
       <c r="D124" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E124">
         <v>-6.699505714853863</v>
@@ -7369,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7383,7 +7380,7 @@
         <v>-6.01323983732869</v>
       </c>
       <c r="D125" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E125">
         <v>-7.525488816950592</v>
@@ -7419,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7433,7 +7430,7 @@
         <v>-5.986973959803521</v>
       </c>
       <c r="D126" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E126">
         <v>-7.635743429206912</v>
@@ -7469,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7483,7 +7480,7 @@
         <v>-6.206127283819491</v>
       </c>
       <c r="D127" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E127">
         <v>-7.709858398136483</v>
@@ -7519,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7533,7 +7530,7 @@
         <v>-8.568708846748585</v>
       </c>
       <c r="D128" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E128">
         <v>-6.83753010098529</v>
@@ -7569,7 +7566,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7583,7 +7580,7 @@
         <v>-6.157544698172977</v>
       </c>
       <c r="D129" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E129">
         <v>-7.677096555367967</v>
@@ -7619,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -7633,7 +7630,7 @@
         <v>-6.137559295360667</v>
       </c>
       <c r="D130" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E130">
         <v>-7.790126261102067</v>
@@ -7669,7 +7666,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -7683,7 +7680,7 @@
         <v>-8.724455302555334</v>
       </c>
       <c r="D131" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E131">
         <v>-6.985897440438293</v>
@@ -7719,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7733,7 +7730,7 @@
         <v>-6.312663144077284</v>
       </c>
       <c r="D132" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E132">
         <v>-7.84006512505286</v>
@@ -7769,7 +7766,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -7783,7 +7780,7 @@
         <v>-6.299428847716271</v>
       </c>
       <c r="D133" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E133">
         <v>-7.956077877823574</v>
@@ -7819,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -7833,7 +7830,7 @@
         <v>-8.881996475438136</v>
       </c>
       <c r="D134" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E134">
         <v>-7.135974465009106</v>
@@ -7869,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -7883,7 +7880,7 @@
         <v>-6.469569070295236</v>
       </c>
       <c r="D135" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E135">
         <v>-8.004911634581433</v>
@@ -7919,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -7933,7 +7930,7 @@
         <v>-6.463163675581363</v>
       </c>
       <c r="D136" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E136">
         <v>-8.123941809010191</v>
@@ -7969,7 +7966,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -7983,7 +7980,7 @@
         <v>-6.555849051211844</v>
       </c>
       <c r="D137" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E137">
         <v>-8.070947070211147</v>
@@ -8019,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8033,7 +8030,7 @@
         <v>-8.944574494910249</v>
       </c>
       <c r="D138" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E138">
         <v>-7.195587598478006</v>
@@ -8069,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8083,7 +8080,7 @@
         <v>-6.531894759043666</v>
       </c>
       <c r="D139" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E139">
         <v>-8.070391457375841</v>
@@ -8119,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8133,7 +8130,7 @@
         <v>-6.52820191960933</v>
       </c>
       <c r="D140" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E140">
         <v>-8.190620202742068</v>
@@ -8169,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8183,7 +8180,7 @@
         <v>-9.097128692828768</v>
       </c>
       <c r="D141" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E141">
         <v>-7.340913926132238</v>
@@ -8219,7 +8216,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8233,7 +8230,7 @@
         <v>-6.683833819067353</v>
       </c>
       <c r="D142" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E142">
         <v>-8.230019741084938</v>
@@ -8269,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8283,7 +8280,7 @@
         <v>-6.686753712002471</v>
       </c>
       <c r="D143" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E143">
         <v>-8.35317039145162</v>
@@ -8319,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8333,7 +8330,7 @@
         <v>-9.226549811636133</v>
       </c>
       <c r="D144" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E144">
         <v>-7.464203197576758</v>
@@ -8369,7 +8366,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8383,7 +8380,7 @@
         <v>-6.812733078524694</v>
       </c>
       <c r="D145" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E145">
         <v>-8.365442242417643</v>
@@ -8419,7 +8416,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8433,7 +8430,7 @@
         <v>-9.195297631482575</v>
       </c>
       <c r="D146" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E146">
         <v>-7.43443171547483</v>
@@ -8469,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8483,7 +8480,7 @@
         <v>-6.78160691522659</v>
       </c>
       <c r="D147" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E147">
         <v>-8.33274086842632</v>
@@ -8519,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8533,7 +8530,7 @@
         <v>-9.178575533094566</v>
       </c>
       <c r="D148" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E148">
         <v>-7.418501893925765</v>
@@ -8569,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -8583,7 +8580,7 @@
         <v>-9.01172937356634</v>
       </c>
       <c r="D149" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E149">
         <v>-7.259560743971967</v>
@@ -8619,7 +8616,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -8633,7 +8630,7 @@
         <v>-6.598778851898729</v>
       </c>
       <c r="D150" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E150">
         <v>-8.14066037274381</v>
@@ -8669,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -8683,7 +8680,7 @@
         <v>-6.597996959825494</v>
       </c>
       <c r="D151" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E151">
         <v>-8.26217535066494</v>
@@ -8719,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -8733,7 +8730,7 @@
         <v>-6.580061112481111</v>
       </c>
       <c r="D152" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E152">
         <v>-8.095946089051466</v>
@@ -8769,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -8783,7 +8780,7 @@
         <v>-8.970596558592923</v>
       </c>
       <c r="D153" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E153">
         <v>-7.220376761966044</v>
@@ -8819,7 +8816,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -8833,7 +8830,7 @@
         <v>-6.557811895050207</v>
       </c>
       <c r="D154" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E154">
         <v>-8.09762018933413</v>
@@ -8869,7 +8866,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -8883,7 +8880,7 @@
         <v>-6.555247028134374</v>
       </c>
       <c r="D155" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E155">
         <v>-8.218347341162016</v>
@@ -8919,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -8933,7 +8930,7 @@
         <v>-6.577113402823095</v>
       </c>
       <c r="D156" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E156">
         <v>-8.092902570845517</v>
@@ -8969,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -8983,7 +8980,7 @@
         <v>-8.967428489274667</v>
       </c>
       <c r="D157" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E157">
         <v>-7.217358792706207</v>
@@ -9019,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9033,7 +9030,7 @@
         <v>-6.554656600205007</v>
       </c>
       <c r="D158" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E158">
         <v>-8.094305213575709</v>
@@ -9069,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9083,7 +9080,7 @@
         <v>-6.551954407703803</v>
       </c>
       <c r="D159" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E159">
         <v>-8.214971686656575</v>
@@ -9119,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9133,7 +9130,7 @@
         <v>-8.96588564418861</v>
       </c>
       <c r="D160" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E160">
         <v>-7.215889046127252</v>
@@ -9169,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9183,7 +9180,7 @@
         <v>-6.553119976268491</v>
       </c>
       <c r="D161" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E161">
         <v>-8.092690825269933</v>
@@ -9219,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9233,7 +9230,7 @@
         <v>-6.550350906409733</v>
       </c>
       <c r="D162" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E162">
         <v>-8.213327747890489</v>
@@ -9269,7 +9266,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9283,7 +9280,7 @@
         <v>-8.957282379415823</v>
       </c>
       <c r="D163" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E163">
         <v>-7.207693395713662</v>
@@ -9319,7 +9316,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9333,7 +9330,7 @@
         <v>-6.544551402079463</v>
       </c>
       <c r="D164" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E164">
         <v>-8.083688618783896</v>
@@ -9369,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9383,7 +9380,7 @@
         <v>-6.541409408445269</v>
       </c>
       <c r="D165" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E165">
         <v>-8.204160761131575</v>
@@ -9419,7 +9416,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9433,7 +9430,7 @@
         <v>-9.189704217204067</v>
       </c>
       <c r="D166" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E166">
         <v>-8.287425006865455</v>
@@ -9469,7 +9466,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9483,7 +9480,7 @@
         <v>-8.966990157030267</v>
       </c>
       <c r="D167" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E167">
         <v>-7.216941228219355</v>
@@ -9519,7 +9516,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9533,7 +9530,7 @@
         <v>-6.554220035429331</v>
       </c>
       <c r="D168" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E168">
         <v>-8.09384655544094</v>
@@ -9569,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9583,7 +9580,7 @@
         <v>-6.551498842639312</v>
       </c>
       <c r="D169" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E169">
         <v>-8.214504633045351</v>
@@ -9619,7 +9616,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9633,7 +9630,7 @@
         <v>-9.200987551467627</v>
       </c>
       <c r="D170" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E170">
         <v>-8.062628257853937</v>
@@ -9669,7 +9666,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9683,7 +9680,7 @@
         <v>-5.744424659624897</v>
       </c>
       <c r="D171" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E171">
         <v>-9.168004982467224</v>
@@ -9719,7 +9716,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9733,7 +9730,7 @@
         <v>-9.320459183580553</v>
       </c>
       <c r="D172" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E172">
         <v>-8.519444616447643</v>
@@ -9769,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9783,7 +9780,7 @@
         <v>-9.758278581073185</v>
       </c>
       <c r="D173" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E173">
         <v>-8.519444616447643</v>
@@ -9819,7 +9816,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9833,7 +9830,7 @@
         <v>1.93748613778034</v>
       </c>
       <c r="D174" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E174">
         <v>-3.785088938010851</v>
@@ -9869,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9883,7 +9880,7 @@
         <v>-9.449792997965268</v>
       </c>
       <c r="D175" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E175">
         <v>-3.02668852932127</v>
@@ -9919,7 +9916,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9969,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9983,7 +9980,7 @@
         <v>-7.49349826462975</v>
       </c>
       <c r="D177" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E177">
         <v>-2.563031396720049</v>
@@ -10019,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10033,7 +10030,7 @@
         <v>-7.400654460855741</v>
       </c>
       <c r="D178" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E178">
         <v>-2.563031396720049</v>
@@ -10069,7 +10066,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10083,7 +10080,7 @@
         <v>-7.310878524281797</v>
       </c>
       <c r="D179" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E179">
         <v>-2.470392808492726</v>
@@ -10119,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10133,7 +10130,7 @@
         <v>-1.137705700364087</v>
       </c>
       <c r="D180" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E180">
         <v>-5.327198547332877</v>
@@ -10169,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10183,7 +10180,7 @@
         <v>-7.43565059492704</v>
       </c>
       <c r="D181" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E181">
         <v>-4.511272425220589</v>
@@ -10219,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10233,7 +10230,7 @@
         <v>-7.728087200798136</v>
       </c>
       <c r="D182" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E182">
         <v>-4.511272425220589</v>
@@ -10269,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10283,7 +10280,7 @@
         <v>-7.776944970817269</v>
       </c>
       <c r="D183" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E183">
         <v>-4.636449928781524</v>
@@ -10319,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10333,7 +10330,7 @@
         <v>-2.366005602048894</v>
       </c>
       <c r="D184" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E184">
         <v>-5.159190826471352</v>
@@ -10369,7 +10366,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10383,7 +10380,7 @@
         <v>-3.086643025309506</v>
       </c>
       <c r="D185" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E185">
         <v>-5.921712484906784</v>
@@ -10419,7 +10416,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10433,7 +10430,7 @@
         <v>-8.081861396637805</v>
       </c>
       <c r="D186" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E186">
         <v>-5.158033193571107</v>
@@ -10469,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10483,7 +10480,7 @@
         <v>-8.385297335303981</v>
       </c>
       <c r="D187" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E187">
         <v>-5.158033193571107</v>
@@ -10519,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10533,7 +10530,7 @@
         <v>-8.415456239571483</v>
       </c>
       <c r="D188" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E188">
         <v>-5.252412565305825</v>
@@ -10569,7 +10566,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10583,7 +10580,7 @@
         <v>-2.950620140107226</v>
       </c>
       <c r="D189" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E189">
         <v>-5.733355998374364</v>
@@ -10619,7 +10616,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10633,7 +10630,7 @@
         <v>6.422751594100816</v>
       </c>
       <c r="D190" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E190">
         <v>2.901892440584781</v>
@@ -10669,7 +10666,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10683,7 +10680,7 @@
         <v>5.893713788467551</v>
       </c>
       <c r="D191" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E191">
         <v>2.901892440584781</v>
@@ -10719,7 +10716,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10733,7 +10730,7 @@
         <v>0.5179406222671616</v>
       </c>
       <c r="D192" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E192">
         <v>0.1467723461990573</v>
@@ -10769,7 +10766,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10783,7 +10780,7 @@
         <v>0.3677345405657775</v>
       </c>
       <c r="D193" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E193">
         <v>0.1467723461990573</v>
@@ -10819,7 +10816,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10833,7 +10830,7 @@
         <v>7.212705926337946</v>
       </c>
       <c r="D194" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E194">
         <v>3.676716599119786</v>
@@ -10869,7 +10866,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10883,7 +10880,7 @@
         <v>6.682075470841298</v>
       </c>
       <c r="D195" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E195">
         <v>3.676716599119786</v>
@@ -10919,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10933,7 +10930,7 @@
         <v>0.8352277483245487</v>
       </c>
       <c r="D196" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E196">
         <v>0.3846845807742838</v>
@@ -10969,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10983,7 +10980,7 @@
         <v>1.19909776925082</v>
       </c>
       <c r="D197" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E197">
         <v>0.3846845807742838</v>
@@ -11019,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11033,7 +11030,7 @@
         <v>15.85732541489383</v>
       </c>
       <c r="D198" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E198">
         <v>12.15576373860051</v>
@@ -11069,7 +11066,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11083,7 +11080,7 @@
         <v>9.154626138941545</v>
       </c>
       <c r="D199" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E199">
         <v>10.1457637386005</v>
@@ -11119,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11133,7 +11130,7 @@
         <v>20.52882535635497</v>
       </c>
       <c r="D200" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E200">
         <v>17.16608306198427</v>
@@ -11169,7 +11166,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11183,7 +11180,7 @@
         <v>20.01532326601529</v>
       </c>
       <c r="D201" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E201">
         <v>17.16182266903495</v>
@@ -11219,7 +11216,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11233,7 +11230,7 @@
         <v>20.52405408116763</v>
       </c>
       <c r="D202" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E202">
         <v>17.16182266903495</v>
@@ -11269,7 +11266,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11283,7 +11280,7 @@
         <v>19.97713105134113</v>
       </c>
       <c r="D203" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E203">
         <v>17.12745703463643</v>
@@ -11319,7 +11316,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11333,7 +11330,7 @@
         <v>19.78769619247149</v>
       </c>
       <c r="D204" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E204">
         <v>16.95700216162655</v>
@@ -11369,7 +11366,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11383,7 +11380,7 @@
         <v>19.72946947948954</v>
       </c>
       <c r="D205" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E205">
         <v>16.90460933896265</v>
@@ -11419,7 +11416,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11433,7 +11430,7 @@
         <v>19.66471905771537</v>
       </c>
       <c r="D206" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E206">
         <v>16.84634643536238</v>
@@ -11469,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11483,7 +11480,7 @@
         <v>19.5088598974271</v>
       </c>
       <c r="D207" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E207">
         <v>16.70610322176966</v>
@@ -11519,7 +11516,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11533,7 +11530,7 @@
         <v>19.28831605863447</v>
       </c>
       <c r="D208" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E208">
         <v>16.50765626085222</v>
@@ -11569,7 +11566,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -11583,7 +11580,7 @@
         <v>19.19520175231204</v>
       </c>
       <c r="D209" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E209">
         <v>16.42387132626151</v>
@@ -11619,7 +11616,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -11633,7 +11630,7 @@
         <v>19.05540054991548</v>
       </c>
       <c r="D210" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E210">
         <v>16.12799605103372</v>
@@ -11669,7 +11666,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -11683,7 +11680,7 @@
         <v>19.02007289952515</v>
       </c>
       <c r="D211" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E211">
         <v>16.09699076249269</v>
@@ -11719,7 +11716,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -11733,7 +11730,7 @@
         <v>18.63226776448187</v>
       </c>
       <c r="D212" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E212">
         <v>15.75663384724757</v>
@@ -11769,7 +11766,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -11783,7 +11780,7 @@
         <v>18.71498673226228</v>
       </c>
       <c r="D213" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E213">
         <v>15.39488806222844</v>
@@ -11819,7 +11816,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -11833,7 +11830,7 @@
         <v>18.26133487568657</v>
       </c>
       <c r="D214" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E214">
         <v>15.4310848475438</v>
@@ -11869,7 +11866,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -11883,7 +11880,7 @@
         <v>18.75654747588454</v>
       </c>
       <c r="D215" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E215">
         <v>15.4310848475438</v>
@@ -11919,7 +11916,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -11933,7 +11930,7 @@
         <v>18.16683845632306</v>
       </c>
       <c r="D216" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E216">
         <v>14.535139415301</v>
@@ -11983,7 +11980,7 @@
         <v>19.29117147225969</v>
       </c>
       <c r="D217" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E217">
         <v>15.75788232322333</v>
@@ -12019,7 +12016,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12069,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12083,7 +12080,7 @@
         <v>12.17255864879727</v>
       </c>
       <c r="D219" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E219">
         <v>11.43255864879727</v>
@@ -12119,7 +12116,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12133,7 +12130,7 @@
         <v>11.88655543238428</v>
       </c>
       <c r="D220" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E220">
         <v>11.43255864879727</v>
@@ -12169,7 +12166,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12183,7 +12180,7 @@
         <v>12.10927609080188</v>
       </c>
       <c r="D221" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E221">
         <v>12.08247455606389</v>
@@ -12219,7 +12216,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12233,7 +12230,7 @@
         <v>11.82138853023023</v>
       </c>
       <c r="D222" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E222">
         <v>12.08247455606389</v>
@@ -12269,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12319,7 +12316,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12333,7 +12330,7 @@
         <v>11.74270804654375</v>
       </c>
       <c r="D224" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E224">
         <v>11.73063502614344</v>
@@ -12369,7 +12366,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12383,7 +12380,7 @@
         <v>11.41854815733105</v>
       </c>
       <c r="D225" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E225">
         <v>11.73063502614344</v>
@@ -12419,7 +12416,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12433,7 +12430,7 @@
         <v>11.75391413984507</v>
       </c>
       <c r="D226" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E226">
         <v>11.73063502614344</v>
@@ -12469,7 +12466,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12519,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12569,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12583,7 +12580,7 @@
         <v>11.17350343307117</v>
       </c>
       <c r="D229" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E229">
         <v>10.95188140489946</v>
@@ -12619,7 +12616,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12633,7 +12630,7 @@
         <v>10.79733859878642</v>
       </c>
       <c r="D230" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="E230">
         <v>10.95188140489946</v>
@@ -12669,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12683,7 +12680,7 @@
         <v>10.77822897973078</v>
       </c>
       <c r="D231" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E231">
         <v>10.12779568583672</v>
@@ -12719,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12733,7 +12730,7 @@
         <v>10.66475181580885</v>
       </c>
       <c r="D232" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E232">
         <v>10.12779568583672</v>
@@ -12769,7 +12766,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12780,34 +12777,34 @@
         <v>72</v>
       </c>
       <c r="C233">
-        <v>4.567308451383006</v>
+        <v>2.63673401734458</v>
       </c>
       <c r="D233" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E233">
-        <v>2.277267305113099</v>
+        <v>0.3536443198896109</v>
       </c>
       <c r="F233">
         <v>-1</v>
       </c>
       <c r="G233">
-        <v>0.07643269154861698</v>
+        <v>0.07580326598265542</v>
       </c>
       <c r="H233">
-        <v>0.0718827326948869</v>
+        <v>0.07380635568011039</v>
       </c>
       <c r="I233">
-        <v>2.290041146269907</v>
+        <v>2.283089697454969</v>
       </c>
       <c r="J233">
-        <v>0.9039670829840752</v>
+        <v>0.9539313163665036</v>
       </c>
       <c r="K233">
-        <v>39.75</v>
+        <v>38.35</v>
       </c>
       <c r="L233">
-        <v>40.5</v>
+        <v>39.22</v>
       </c>
       <c r="M233">
         <v>38.5</v>
@@ -12819,7 +12816,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>66</v>
+        <v>242</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12827,37 +12824,37 @@
         <v>0</v>
       </c>
       <c r="B234" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C234">
-        <v>4.005620084726345</v>
+        <v>2.217490520459279</v>
       </c>
       <c r="D234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E234">
-        <v>1.775278429586088</v>
+        <v>-0.06723898206826107</v>
       </c>
       <c r="F234">
         <v>-1</v>
       </c>
       <c r="G234">
-        <v>0.07727437991527365</v>
+        <v>0.07622250947954072</v>
       </c>
       <c r="H234">
-        <v>0.07238472157041392</v>
+        <v>0.07422723898206826</v>
       </c>
       <c r="I234">
-        <v>2.230341655140258</v>
+        <v>2.28472950252754</v>
       </c>
       <c r="J234">
-        <v>0.9170057550756859</v>
+        <v>0.9648633501835912</v>
       </c>
       <c r="K234">
-        <v>39.95</v>
+        <v>38.35</v>
       </c>
       <c r="L234">
-        <v>40.64</v>
+        <v>39.22</v>
       </c>
       <c r="M234">
         <v>38.5</v>
@@ -12869,45 +12866,45 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="235" spans="1:16">
       <c r="A235" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B235" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C235">
-        <v>4.052829292847441</v>
+        <v>1.66235731631032</v>
       </c>
       <c r="D235" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E235">
-        <v>1.775278429586088</v>
+        <v>-0.5363331653346535</v>
       </c>
       <c r="F235">
         <v>-1</v>
       </c>
       <c r="G235">
-        <v>0.07438717070715256</v>
+        <v>0.07933764268368969</v>
       </c>
       <c r="H235">
-        <v>0.07238472157041392</v>
+        <v>0.07469633316533465</v>
       </c>
       <c r="I235">
-        <v>2.277550863261354</v>
+        <v>2.198690481644974</v>
       </c>
       <c r="J235">
-        <v>0.9170057550756859</v>
+        <v>0.977047614684017</v>
       </c>
       <c r="K235">
-        <v>38.35</v>
+        <v>39.75</v>
       </c>
       <c r="L235">
-        <v>39.22</v>
+        <v>40.5</v>
       </c>
       <c r="M235">
         <v>38.5</v>
@@ -12919,7 +12916,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -12930,34 +12927,34 @@
         <v>73</v>
       </c>
       <c r="C236">
-        <v>3.464772819979061</v>
+        <v>1.212494861209947</v>
       </c>
       <c r="D236" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E236">
-        <v>1.25406141599985</v>
+        <v>-0.9720490023501114</v>
       </c>
       <c r="F236">
         <v>-1</v>
       </c>
       <c r="G236">
-        <v>0.07781522718002094</v>
+        <v>0.07978750513879006</v>
       </c>
       <c r="H236">
-        <v>0.07290593858400016</v>
+        <v>0.0751320490023501</v>
       </c>
       <c r="I236">
-        <v>2.210711403979211</v>
+        <v>2.184543863560059</v>
       </c>
       <c r="J236">
-        <v>0.9305438593246792</v>
+        <v>0.988364909151951</v>
       </c>
       <c r="K236">
-        <v>39.95</v>
+        <v>39.75</v>
       </c>
       <c r="L236">
-        <v>40.64</v>
+        <v>40.5</v>
       </c>
       <c r="M236">
         <v>38.5</v>
@@ -12969,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -12977,49 +12974,49 @@
         <v>0</v>
       </c>
       <c r="B237" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C237">
-        <v>3.034954939512154</v>
+        <v>-4.102905583088159</v>
       </c>
       <c r="D237" t="s">
         <v>136</v>
       </c>
       <c r="E237">
-        <v>0.8398439341981927</v>
+        <v>-2.251051012188292</v>
       </c>
       <c r="F237">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G237">
-        <v>0.07824504506048785</v>
+        <v>0.09464290558308816</v>
       </c>
       <c r="H237">
-        <v>0.07332015606580179</v>
+        <v>0.09721105101218828</v>
       </c>
       <c r="I237">
-        <v>2.195111005313962</v>
+        <v>1.851854570899867</v>
       </c>
       <c r="J237">
-        <v>0.941302754955891</v>
+        <v>1.023272654571775</v>
       </c>
       <c r="K237">
-        <v>39.95</v>
+        <v>48.25</v>
       </c>
       <c r="L237">
-        <v>40.64</v>
+        <v>45.27</v>
       </c>
       <c r="M237">
-        <v>38.5</v>
+        <v>48.6</v>
       </c>
       <c r="N237">
-        <v>37.08</v>
+        <v>47.48</v>
       </c>
       <c r="O237">
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13027,49 +13024,49 @@
         <v>0</v>
       </c>
       <c r="B238" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C238">
-        <v>2.53044391115818</v>
+        <v>-4.731848097981405</v>
       </c>
       <c r="D238" t="s">
         <v>136</v>
       </c>
       <c r="E238">
-        <v>0.3536443198896109</v>
+        <v>-2.884555804391638</v>
       </c>
       <c r="F238">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G238">
-        <v>0.07874955608884182</v>
+        <v>0.09527184809798141</v>
       </c>
       <c r="H238">
-        <v>0.07380635568011039</v>
+        <v>0.09784455580439164</v>
       </c>
       <c r="I238">
-        <v>2.176799591268569</v>
+        <v>1.847292293589767</v>
       </c>
       <c r="J238">
-        <v>0.9539313163665036</v>
+        <v>1.036307732600651</v>
       </c>
       <c r="K238">
-        <v>39.95</v>
+        <v>48.25</v>
       </c>
       <c r="L238">
-        <v>40.64</v>
+        <v>45.27</v>
       </c>
       <c r="M238">
-        <v>38.5</v>
+        <v>48.6</v>
       </c>
       <c r="N238">
-        <v>37.08</v>
+        <v>47.48</v>
       </c>
       <c r="O238">
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13077,49 +13074,49 @@
         <v>0</v>
       </c>
       <c r="B239" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C239">
-        <v>2.093709160165531</v>
+        <v>-5.390256815248073</v>
       </c>
       <c r="D239" t="s">
         <v>136</v>
       </c>
       <c r="E239">
-        <v>-0.06723898206826107</v>
+        <v>-3.547740543441584</v>
       </c>
       <c r="F239">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G239">
-        <v>0.07918629083983447</v>
+        <v>0.09593025681524807</v>
       </c>
       <c r="H239">
-        <v>0.07422723898206826</v>
+        <v>0.09850774054344158</v>
       </c>
       <c r="I239">
-        <v>2.160948142233792</v>
+        <v>1.842516271806488</v>
       </c>
       <c r="J239">
-        <v>0.9648633501835912</v>
+        <v>1.049953509124312</v>
       </c>
       <c r="K239">
-        <v>39.95</v>
+        <v>48.25</v>
       </c>
       <c r="L239">
-        <v>40.64</v>
+        <v>45.27</v>
       </c>
       <c r="M239">
-        <v>38.5</v>
+        <v>48.6</v>
       </c>
       <c r="N239">
-        <v>37.08</v>
+        <v>47.48</v>
       </c>
       <c r="O239">
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>71</v>
+        <v>245</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13127,49 +13124,49 @@
         <v>0</v>
       </c>
       <c r="B240" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C240">
-        <v>1.606947793373521</v>
+        <v>-6.102994871026347</v>
       </c>
       <c r="D240" t="s">
         <v>136</v>
       </c>
       <c r="E240">
-        <v>-0.5363331653346535</v>
+        <v>-4.265648719831724</v>
       </c>
       <c r="F240">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G240">
-        <v>0.07967305220662649</v>
+        <v>0.09664299487102636</v>
       </c>
       <c r="H240">
-        <v>0.07469633316533465</v>
+        <v>0.09922564871983172</v>
       </c>
       <c r="I240">
-        <v>2.143280958708175</v>
+        <v>1.837346151194623</v>
       </c>
       <c r="J240">
-        <v>0.977047614684017</v>
+        <v>1.064725282301064</v>
       </c>
       <c r="K240">
-        <v>39.95</v>
+        <v>48.25</v>
       </c>
       <c r="L240">
-        <v>40.64</v>
+        <v>45.27</v>
       </c>
       <c r="M240">
-        <v>38.5</v>
+        <v>48.6</v>
       </c>
       <c r="N240">
-        <v>37.08</v>
+        <v>47.48</v>
       </c>
       <c r="O240">
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>134</v>
+        <v>246</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13177,49 +13174,49 @@
         <v>0</v>
       </c>
       <c r="B241" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C241">
-        <v>-0.1382969714751567</v>
+        <v>-6.718322693837997</v>
       </c>
       <c r="D241" t="s">
         <v>137</v>
       </c>
       <c r="E241">
-        <v>-1.985913874432278</v>
+        <v>-3.039313970056341</v>
       </c>
       <c r="F241">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G241">
-        <v>0.07855829697147516</v>
+        <v>0.09725832269383801</v>
       </c>
       <c r="H241">
-        <v>0.07278591387443228</v>
+        <v>0.1017993139700563</v>
       </c>
       <c r="I241">
-        <v>1.847616902957121</v>
+        <v>3.679008723781656</v>
       </c>
       <c r="J241">
-        <v>1.006350306175835</v>
+        <v>1.077478190545865</v>
       </c>
       <c r="K241">
-        <v>39.1</v>
+        <v>48.25</v>
       </c>
       <c r="L241">
-        <v>39.21</v>
+        <v>45.27</v>
       </c>
       <c r="M241">
-        <v>37.15</v>
+        <v>48.65</v>
       </c>
       <c r="N241">
-        <v>35.4</v>
+        <v>49.38</v>
       </c>
       <c r="O241">
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>70</v>
+        <v>247</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13227,31 +13224,31 @@
         <v>0</v>
       </c>
       <c r="B242" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C242">
-        <v>-4.102905583088159</v>
+        <v>-7.201115064711686</v>
       </c>
       <c r="D242" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E242">
-        <v>-2.84010562307369</v>
+        <v>-3.526108764730019</v>
       </c>
       <c r="F242">
         <v>1</v>
       </c>
       <c r="G242">
-        <v>0.09464290558308816</v>
+        <v>0.0977411150647117</v>
       </c>
       <c r="H242">
-        <v>0.09478010562307369</v>
+        <v>0.10228610876473</v>
       </c>
       <c r="I242">
-        <v>1.262799960014469</v>
+        <v>3.675006299981668</v>
       </c>
       <c r="J242">
-        <v>1.023272654571775</v>
+        <v>1.087484250045838</v>
       </c>
       <c r="K242">
         <v>48.25</v>
@@ -13260,16 +13257,16 @@
         <v>45.27</v>
       </c>
       <c r="M242">
-        <v>47.7</v>
+        <v>48.65</v>
       </c>
       <c r="N242">
-        <v>45.97</v>
+        <v>49.38</v>
       </c>
       <c r="O242">
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13277,31 +13274,31 @@
         <v>0</v>
       </c>
       <c r="B243" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C243">
-        <v>-4.731848097981405</v>
+        <v>-7.653085819975225</v>
       </c>
       <c r="D243" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E243">
-        <v>-3.461878845051054</v>
+        <v>-3.981826427809217</v>
       </c>
       <c r="F243">
         <v>1</v>
       </c>
       <c r="G243">
-        <v>0.09527184809798141</v>
+        <v>0.09819308581997524</v>
       </c>
       <c r="H243">
-        <v>0.09540187884505105</v>
+        <v>0.1027418264278092</v>
       </c>
       <c r="I243">
-        <v>1.269969252930352</v>
+        <v>3.671259392166007</v>
       </c>
       <c r="J243">
-        <v>1.036307732600651</v>
+        <v>1.096851519584979</v>
       </c>
       <c r="K243">
         <v>48.25</v>
@@ -13310,16 +13307,16 @@
         <v>45.27</v>
       </c>
       <c r="M243">
-        <v>47.7</v>
+        <v>48.65</v>
       </c>
       <c r="N243">
-        <v>45.97</v>
+        <v>49.38</v>
       </c>
       <c r="O243">
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13327,49 +13324,49 @@
         <v>0</v>
       </c>
       <c r="B244" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C244">
-        <v>-5.390256815248073</v>
+        <v>-7.82898196912344</v>
       </c>
       <c r="D244" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E244">
-        <v>-4.112782385229707</v>
+        <v>-4.369947838965025</v>
       </c>
       <c r="F244">
         <v>1</v>
       </c>
       <c r="G244">
-        <v>0.09593025681524807</v>
+        <v>0.09922898196912346</v>
       </c>
       <c r="H244">
-        <v>0.09605278238522971</v>
+        <v>0.103129947838965</v>
       </c>
       <c r="I244">
-        <v>1.277474430018366</v>
+        <v>3.459034130158415</v>
       </c>
       <c r="J244">
-        <v>1.049953509124312</v>
+        <v>1.104829349207914</v>
       </c>
       <c r="K244">
-        <v>48.25</v>
+        <v>48.45</v>
       </c>
       <c r="L244">
-        <v>45.27</v>
+        <v>45.7</v>
       </c>
       <c r="M244">
-        <v>47.7</v>
+        <v>48.65</v>
       </c>
       <c r="N244">
-        <v>45.97</v>
+        <v>49.38</v>
       </c>
       <c r="O244">
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13377,49 +13374,49 @@
         <v>0</v>
       </c>
       <c r="B245" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C245">
-        <v>-6.102994871026347</v>
+        <v>-8.295821887580566</v>
       </c>
       <c r="D245" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E245">
-        <v>-4.817395965760767</v>
+        <v>-4.838714857188734</v>
       </c>
       <c r="F245">
         <v>1</v>
       </c>
       <c r="G245">
-        <v>0.09664299487102636</v>
+        <v>0.09969582188758057</v>
       </c>
       <c r="H245">
-        <v>0.09675739596576077</v>
+        <v>0.1035987148571887</v>
       </c>
       <c r="I245">
-        <v>1.28559890526558</v>
+        <v>3.457107030391832</v>
       </c>
       <c r="J245">
-        <v>1.064725282301064</v>
+        <v>1.114464848040879</v>
       </c>
       <c r="K245">
-        <v>48.25</v>
+        <v>48.45</v>
       </c>
       <c r="L245">
-        <v>45.27</v>
+        <v>45.7</v>
       </c>
       <c r="M245">
-        <v>47.7</v>
+        <v>48.65</v>
       </c>
       <c r="N245">
-        <v>45.97</v>
+        <v>49.38</v>
       </c>
       <c r="O245">
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>249</v>
+        <v>135</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13427,49 +13424,49 @@
         <v>0</v>
       </c>
       <c r="B246" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C246">
-        <v>-6.718322693837997</v>
+        <v>-8.82565587345406</v>
       </c>
       <c r="D246" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E246">
-        <v>-5.425709689037774</v>
+        <v>-5.370735980258814</v>
       </c>
       <c r="F246">
         <v>1</v>
       </c>
       <c r="G246">
-        <v>0.09725832269383801</v>
+        <v>0.1002256558734541</v>
       </c>
       <c r="H246">
-        <v>0.09736570968903778</v>
+        <v>0.1041307359802588</v>
       </c>
       <c r="I246">
-        <v>1.292613004800224</v>
+        <v>3.454919893195246</v>
       </c>
       <c r="J246">
-        <v>1.077478190545865</v>
+        <v>1.12540053402382</v>
       </c>
       <c r="K246">
-        <v>48.25</v>
+        <v>48.45</v>
       </c>
       <c r="L246">
-        <v>45.27</v>
+        <v>45.7</v>
       </c>
       <c r="M246">
-        <v>47.7</v>
+        <v>48.65</v>
       </c>
       <c r="N246">
-        <v>45.97</v>
+        <v>49.38</v>
       </c>
       <c r="O246">
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13480,90 +13477,90 @@
         <v>76</v>
       </c>
       <c r="C247">
-        <v>-7.201115064711686</v>
+        <v>-5.865740724353984</v>
       </c>
       <c r="D247" t="s">
         <v>138</v>
       </c>
       <c r="E247">
-        <v>-5.902998727186485</v>
+        <v>-7.599743573686503</v>
       </c>
       <c r="F247">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G247">
-        <v>0.0977411150647117</v>
+        <v>0.09016574072435399</v>
       </c>
       <c r="H247">
-        <v>0.09784299872718649</v>
+        <v>0.08649974357368652</v>
       </c>
       <c r="I247">
-        <v>1.298116337525201</v>
+        <v>1.734002849332519</v>
       </c>
       <c r="J247">
-        <v>1.087484250045838</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K247">
-        <v>48.25</v>
+        <v>42.25</v>
       </c>
       <c r="L247">
-        <v>45.27</v>
+        <v>42.15</v>
       </c>
       <c r="M247">
-        <v>47.7</v>
+        <v>41.4</v>
       </c>
       <c r="N247">
-        <v>45.97</v>
+        <v>39.45</v>
       </c>
       <c r="O247">
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="248" spans="1:16">
       <c r="A248" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B248" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C248">
-        <v>-4.191976702465361</v>
+        <v>-9.361837588046164</v>
       </c>
       <c r="D248" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E248">
-        <v>-5.896819278444603</v>
+        <v>-5.909131035262035</v>
       </c>
       <c r="F248">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G248">
-        <v>0.08849197670246536</v>
+        <v>0.1007618375880462</v>
       </c>
       <c r="H248">
-        <v>0.08689681927844461</v>
+        <v>0.104669131035262</v>
       </c>
       <c r="I248">
-        <v>1.704842575979242</v>
+        <v>3.452706552784129</v>
       </c>
       <c r="J248">
-        <v>1.096851519584979</v>
+        <v>1.136467236079384</v>
       </c>
       <c r="K248">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L248">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M248">
-        <v>42.3</v>
+        <v>48.65</v>
       </c>
       <c r="N248">
-        <v>40.5</v>
+        <v>49.38</v>
       </c>
       <c r="O248">
         <v>1</v>
@@ -13574,96 +13571,96 @@
     </row>
     <row r="249" spans="1:16">
       <c r="A249" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B249" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C249">
-        <v>-7.442456123892228</v>
+        <v>-6.356723940668068</v>
       </c>
       <c r="D249" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E249">
-        <v>-6.349817484203498</v>
+        <v>-8.533525624301134</v>
       </c>
       <c r="F249">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G249">
-        <v>0.09884245612389224</v>
+        <v>0.09065672394066807</v>
       </c>
       <c r="H249">
-        <v>0.0982898174842035</v>
+        <v>0.08331352562430114</v>
       </c>
       <c r="I249">
-        <v>1.09263863968873</v>
+        <v>2.176801683633066</v>
       </c>
       <c r="J249">
-        <v>1.096851519584979</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K249">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L249">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M249">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N249">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O249">
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="250" spans="1:16">
       <c r="A250" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B250" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C250">
-        <v>-4.529040004034378</v>
+        <v>-9.924870412434743</v>
       </c>
       <c r="D250" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E250">
-        <v>-6.234281471494768</v>
+        <v>-6.474488040556245</v>
       </c>
       <c r="F250">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G250">
-        <v>0.08882904000403437</v>
+        <v>0.1013248704124348</v>
       </c>
       <c r="H250">
-        <v>0.08723428147149477</v>
+        <v>0.1052344880405562</v>
       </c>
       <c r="I250">
-        <v>1.70524146746039</v>
+        <v>3.450382371878497</v>
       </c>
       <c r="J250">
-        <v>1.104829349207914</v>
+        <v>1.148088140607528</v>
       </c>
       <c r="K250">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L250">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M250">
-        <v>42.3</v>
+        <v>48.65</v>
       </c>
       <c r="N250">
-        <v>40.5</v>
+        <v>49.38</v>
       </c>
       <c r="O250">
         <v>1</v>
@@ -13674,934 +13671,934 @@
     </row>
     <row r="251" spans="1:16">
       <c r="A251" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B251" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C251">
-        <v>-7.82898196912344</v>
+        <v>-6.77136034625692</v>
       </c>
       <c r="D251" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E251">
-        <v>-6.730359957217509</v>
+        <v>-8.926080801189983</v>
       </c>
       <c r="F251">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G251">
-        <v>0.09922898196912346</v>
+        <v>0.09107136034625692</v>
       </c>
       <c r="H251">
-        <v>0.0986703599572175</v>
+        <v>0.08370608080118999</v>
       </c>
       <c r="I251">
-        <v>1.098622011905931</v>
+        <v>2.154720454933063</v>
       </c>
       <c r="J251">
-        <v>1.104829349207914</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K251">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L251">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M251">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N251">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O251">
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="252" spans="1:16">
       <c r="A252" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C252">
-        <v>-4.936139829727118</v>
+        <v>-10.40035287044137</v>
       </c>
       <c r="D252" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E252">
-        <v>-6.688844708892368</v>
+        <v>-6.951933274447313</v>
       </c>
       <c r="F252">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G252">
-        <v>0.08923613982972711</v>
+        <v>0.1018003528704414</v>
       </c>
       <c r="H252">
-        <v>0.08558884470889237</v>
+        <v>0.1057119332744473</v>
       </c>
       <c r="I252">
-        <v>1.75270487916525</v>
+        <v>3.448419595994054</v>
       </c>
       <c r="J252">
-        <v>1.114464848040879</v>
+        <v>1.15790202002975</v>
       </c>
       <c r="K252">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L252">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M252">
-        <v>41.4</v>
+        <v>48.65</v>
       </c>
       <c r="N252">
-        <v>39.45</v>
+        <v>49.38</v>
       </c>
       <c r="O252">
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
     </row>
     <row r="253" spans="1:16">
       <c r="A253" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B253" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C253">
-        <v>-8.295821887580566</v>
+        <v>-7.112794598132552</v>
       </c>
       <c r="D253" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E253">
-        <v>-7.189973251549908</v>
+        <v>-9.24933216391247</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G253">
-        <v>0.09969582188758057</v>
+        <v>0.09141279459813255</v>
       </c>
       <c r="H253">
-        <v>0.0991299732515499</v>
+        <v>0.08402933216391248</v>
       </c>
       <c r="I253">
-        <v>1.105848636030657</v>
+        <v>2.136537565779918</v>
       </c>
       <c r="J253">
-        <v>1.114464848040879</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K253">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L253">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M253">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N253">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O253">
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>136</v>
+        <v>255</v>
       </c>
     </row>
     <row r="254" spans="1:16">
       <c r="A254" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B254" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C254">
-        <v>-5.398172562506375</v>
+        <v>-10.79189108353899</v>
       </c>
       <c r="D254" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E254">
-        <v>-7.141582108586128</v>
+        <v>-7.345087744358537</v>
       </c>
       <c r="F254">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G254">
-        <v>0.08969817256250637</v>
+        <v>0.102191891083539</v>
       </c>
       <c r="H254">
-        <v>0.08604158210858615</v>
+        <v>0.1061050877443585</v>
       </c>
       <c r="I254">
-        <v>1.743409546079754</v>
+        <v>3.446803339180448</v>
       </c>
       <c r="J254">
-        <v>1.12540053402382</v>
+        <v>1.165983304097812</v>
       </c>
       <c r="K254">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L254">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M254">
-        <v>41.4</v>
+        <v>48.65</v>
       </c>
       <c r="N254">
-        <v>39.45</v>
+        <v>49.38</v>
       </c>
       <c r="O254">
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="255" spans="1:16">
       <c r="A255" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B255" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C255">
-        <v>-8.82565587345406</v>
+        <v>-7.379527992135429</v>
       </c>
       <c r="D255" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E255">
-        <v>-7.711605472936199</v>
+        <v>-9.501860820956622</v>
       </c>
       <c r="F255">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G255">
-        <v>0.1002256558734541</v>
+        <v>0.09167952799213544</v>
       </c>
       <c r="H255">
-        <v>0.09965160547293619</v>
+        <v>0.08428186082095662</v>
       </c>
       <c r="I255">
-        <v>1.114050400517861</v>
+        <v>2.122332828821193</v>
       </c>
       <c r="J255">
-        <v>1.12540053402382</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K255">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L255">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M255">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N255">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O255">
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="256" spans="1:16">
       <c r="A256" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B256" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C256">
-        <v>-5.865740724353984</v>
+        <v>-11.09776641938371</v>
       </c>
       <c r="D256" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E256">
-        <v>-8.068689443175366</v>
+        <v>-7.652225723488485</v>
       </c>
       <c r="F256">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G256">
-        <v>0.09016574072435399</v>
+        <v>0.1024977664193837</v>
       </c>
       <c r="H256">
-        <v>0.08284868944317537</v>
+        <v>0.1064122257234885</v>
       </c>
       <c r="I256">
-        <v>2.202948718821382</v>
+        <v>3.445540695895225</v>
       </c>
       <c r="J256">
-        <v>1.136467236079384</v>
+        <v>1.172296520523916</v>
       </c>
       <c r="K256">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L256">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M256">
-        <v>40</v>
+        <v>48.65</v>
       </c>
       <c r="N256">
-        <v>37.39</v>
+        <v>49.38</v>
       </c>
       <c r="O256">
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="257" spans="1:16">
       <c r="A257" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C257">
-        <v>-9.361837588046164</v>
+        <v>-7.702700683679339</v>
       </c>
       <c r="D257" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E257">
-        <v>-8.239487160986627</v>
+        <v>-9.80782313247748</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G257">
-        <v>0.1007618375880462</v>
+        <v>0.09200270068367934</v>
       </c>
       <c r="H257">
-        <v>0.1001794871609866</v>
+        <v>0.08458782313247748</v>
       </c>
       <c r="I257">
-        <v>1.122350427059537</v>
+        <v>2.105122448798141</v>
       </c>
       <c r="J257">
-        <v>1.136467236079384</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K257">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L257">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M257">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N257">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O257">
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="258" spans="1:16">
       <c r="A258" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B258" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C258">
-        <v>-6.356723940668068</v>
+        <v>-11.46836326921335</v>
       </c>
       <c r="D258" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E258">
-        <v>-8.533525624301134</v>
+        <v>-8.024352384875733</v>
       </c>
       <c r="F258">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G258">
-        <v>0.09065672394066807</v>
+        <v>0.1028683632692134</v>
       </c>
       <c r="H258">
-        <v>0.08331352562430114</v>
+        <v>0.1067843523848757</v>
       </c>
       <c r="I258">
-        <v>2.176801683633066</v>
+        <v>3.444010884337615</v>
       </c>
       <c r="J258">
-        <v>1.148088140607528</v>
+        <v>1.179945578311937</v>
       </c>
       <c r="K258">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L258">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M258">
-        <v>40</v>
+        <v>48.65</v>
       </c>
       <c r="N258">
-        <v>37.39</v>
+        <v>49.38</v>
       </c>
       <c r="O258">
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259" spans="1:16">
       <c r="A259" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C259">
-        <v>-9.924870412434743</v>
+        <v>-8.001107320444035</v>
       </c>
       <c r="D259" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E259">
-        <v>-8.793804306979105</v>
+        <v>-10.09033829154465</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G259">
-        <v>0.1013248704124348</v>
+        <v>0.09230110732044404</v>
       </c>
       <c r="H259">
-        <v>0.1007338043069791</v>
+        <v>0.08487033829154464</v>
       </c>
       <c r="I259">
-        <v>1.131066105455638</v>
+        <v>2.089230971100612</v>
       </c>
       <c r="J259">
-        <v>1.148088140607528</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K259">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L259">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M259">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N259">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O259">
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="260" spans="1:16">
       <c r="A260" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B260" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C260">
-        <v>-6.77136034625692</v>
+        <v>-11.81055975563346</v>
       </c>
       <c r="D260" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E260">
-        <v>-8.926080801189983</v>
+        <v>-8.367961447091169</v>
       </c>
       <c r="F260">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G260">
-        <v>0.09107136034625692</v>
+        <v>0.1032105597556335</v>
       </c>
       <c r="H260">
-        <v>0.08370608080118999</v>
+        <v>0.1071279614470912</v>
       </c>
       <c r="I260">
-        <v>2.154720454933063</v>
+        <v>3.442598308542287</v>
       </c>
       <c r="J260">
-        <v>1.15790202002975</v>
+        <v>1.187008457288616</v>
       </c>
       <c r="K260">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L260">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M260">
-        <v>40</v>
+        <v>48.65</v>
       </c>
       <c r="N260">
-        <v>37.39</v>
+        <v>49.38</v>
       </c>
       <c r="O260">
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>137</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261" spans="1:16">
       <c r="A261" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C261">
-        <v>-10.40035287044137</v>
+        <v>-8.280300561754309</v>
       </c>
       <c r="D261" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E261">
-        <v>-9.261926355419064</v>
+        <v>-10.35466325373189</v>
       </c>
       <c r="F261">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G261">
-        <v>0.1018003528704414</v>
+        <v>0.09258030056175431</v>
       </c>
       <c r="H261">
-        <v>0.1012019263554191</v>
+        <v>0.0851346632537319</v>
       </c>
       <c r="I261">
-        <v>1.138426515022303</v>
+        <v>2.074362691977583</v>
       </c>
       <c r="J261">
-        <v>1.15790202002975</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K261">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L261">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M261">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N261">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O261">
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>137</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:16">
       <c r="A262" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B262" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C262">
-        <v>-7.112794598132552</v>
+        <v>-12.13072336608275</v>
       </c>
       <c r="D262" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E262">
-        <v>-9.24933216391247</v>
+        <v>-8.689446682351409</v>
       </c>
       <c r="F262">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G262">
-        <v>0.09141279459813255</v>
+        <v>0.1035307233660828</v>
       </c>
       <c r="H262">
-        <v>0.08402933216391248</v>
+        <v>0.1074494466823514</v>
       </c>
       <c r="I262">
-        <v>2.136537565779918</v>
+        <v>3.441276683731346</v>
       </c>
       <c r="J262">
-        <v>1.165983304097812</v>
+        <v>1.193616581343297</v>
       </c>
       <c r="K262">
-        <v>42.25</v>
+        <v>48.45</v>
       </c>
       <c r="L262">
-        <v>42.15</v>
+        <v>45.7</v>
       </c>
       <c r="M262">
-        <v>40</v>
+        <v>48.65</v>
       </c>
       <c r="N262">
-        <v>37.39</v>
+        <v>49.38</v>
       </c>
       <c r="O262">
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="263" spans="1:16">
       <c r="A263" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C263">
-        <v>-10.79189108353899</v>
+        <v>-8.625026882373376</v>
       </c>
       <c r="D263" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E263">
-        <v>-9.647403605465627</v>
+        <v>-10.68103136792746</v>
       </c>
       <c r="F263">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G263">
-        <v>0.102191891083539</v>
+        <v>0.09292502688237338</v>
       </c>
       <c r="H263">
-        <v>0.1015874036054656</v>
+        <v>0.08546103136792746</v>
       </c>
       <c r="I263">
-        <v>1.144487478073358</v>
+        <v>2.056004485554084</v>
       </c>
       <c r="J263">
-        <v>1.165983304097812</v>
+        <v>1.201775784198186</v>
       </c>
       <c r="K263">
-        <v>48.45</v>
+        <v>42.25</v>
       </c>
       <c r="L263">
-        <v>45.7</v>
+        <v>42.15</v>
       </c>
       <c r="M263">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="N263">
-        <v>45.97</v>
+        <v>37.39</v>
       </c>
       <c r="O263">
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="264" spans="1:16